--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>6070</v>
+        <v>5556</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
-        <v>6041</v>
+        <v>5560</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
-        <v>5998</v>
+        <v>5552</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
-        <v>5999</v>
+        <v>5515</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
-        <v>6073</v>
+        <v>5592</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
-        <v>5980</v>
+        <v>5565</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
-        <v>5943</v>
+        <v>5587</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
-        <v>5888</v>
+        <v>5595</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
-        <v>5894</v>
+        <v>5588</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
-        <v>5899</v>
+        <v>5540</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
-        <v>5950</v>
+        <v>5547</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
-        <v>5971</v>
+        <v>5574</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
-        <v>5941</v>
+        <v>5566</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
-        <v>5933</v>
+        <v>5611</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
-        <v>6005</v>
+        <v>5647</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
-        <v>6026</v>
+        <v>5686</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>6131</v>
+        <v>5796</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
-        <v>6158</v>
+        <v>5849</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
-        <v>6277</v>
+        <v>5922</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>6376</v>
+        <v>6161</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>6555</v>
+        <v>6163</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>6658</v>
+        <v>6237</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>6837</v>
+        <v>6346</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>6962</v>
+        <v>6505</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>7193</v>
+        <v>6779</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>7327</v>
+        <v>6901</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>7437</v>
+        <v>6982</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>7480</v>
+        <v>6984</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>7614</v>
+        <v>7050</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>7605</v>
+        <v>7006</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>7557</v>
+        <v>6952</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>7397</v>
+        <v>6837</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>7434</v>
+        <v>6635</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>7477</v>
+        <v>6604</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>7323</v>
+        <v>6520</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>7292</v>
+        <v>6363</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>7147</v>
+        <v>6166</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>7100</v>
+        <v>6057</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
-        <v>6977</v>
+        <v>5987</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
-        <v>6913</v>
+        <v>5889</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>6857</v>
+        <v>5792</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
-        <v>6810</v>
+        <v>5684</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>6775</v>
+        <v>5571</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>6749</v>
+        <v>5418</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>6676</v>
+        <v>5376</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>6704</v>
+        <v>5260</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>6613</v>
+        <v>5187</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>6683</v>
+        <v>5158</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>6696</v>
+        <v>5087</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>6797</v>
+        <v>5091</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>6801</v>
+        <v>5113</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>6803</v>
+        <v>4999</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>6947</v>
+        <v>4861</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
-        <v>6972</v>
+        <v>4762</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>6992</v>
+        <v>4832</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>6951</v>
+        <v>4829</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>6961</v>
+        <v>4953</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>6951</v>
+        <v>5028</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>6991</v>
+        <v>5142</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>7029</v>
+        <v>5311</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>7163</v>
+        <v>5488</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>7263</v>
+        <v>5672</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>7370</v>
+        <v>5862</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>7406</v>
+        <v>6132</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>7543</v>
+        <v>6338</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>7614</v>
+        <v>6529</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>7749</v>
+        <v>6747</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>7847</v>
+        <v>6942</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>7961</v>
+        <v>7020</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>8106</v>
+        <v>7173</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>8203</v>
+        <v>7414</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>7609</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>8220</v>
+        <v>7710</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>8200</v>
+        <v>7754</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>8215</v>
+        <v>7799</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>8143</v>
+        <v>7719</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>8120</v>
+        <v>7658</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>8077</v>
+        <v>7603</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>8005</v>
+        <v>7532</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>7911</v>
+        <v>7465</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>7788</v>
+        <v>7393</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
-        <v>7694</v>
+        <v>7299</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>7562</v>
+        <v>7161</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>7365</v>
+        <v>7024</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>7199</v>
+        <v>6746</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
-        <v>7015</v>
+        <v>6590</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
-        <v>6908</v>
+        <v>6440</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>6705</v>
+        <v>6314</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>6598</v>
+        <v>6194</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>6522</v>
+        <v>6104</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
-        <v>6430</v>
+        <v>6003</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>6262</v>
+        <v>5858</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B95">
-        <v>6217</v>
+        <v>5800</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B96">
-        <v>6168</v>
+        <v>5729</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B97">
-        <v>6113</v>
+        <v>5712</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B98">
-        <v>6125</v>
+        <v>5608</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B99">
-        <v>6048</v>
+        <v>5570</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B100">
-        <v>6031</v>
+        <v>5536</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>5540</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B102">
-        <v>5978</v>
+        <v>5579</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B103">
-        <v>5929</v>
+        <v>5585</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B104">
-        <v>5912</v>
+        <v>5574</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B105">
-        <v>5898</v>
+        <v>5547</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B106">
-        <v>5886</v>
+        <v>5566</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B107">
-        <v>5895</v>
+        <v>5540</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B108">
-        <v>5856</v>
+        <v>5528</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B109">
-        <v>5925</v>
+        <v>5534</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B110">
-        <v>5924</v>
+        <v>5613</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B111">
-        <v>5955</v>
+        <v>5614</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B112">
-        <v>5935</v>
+        <v>5636</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B113">
-        <v>5960</v>
+        <v>5662</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B114">
-        <v>6087</v>
+        <v>5745</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B115">
-        <v>6137</v>
+        <v>5827</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B116">
-        <v>6226</v>
+        <v>5934</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B117">
-        <v>6328</v>
+        <v>6070</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B118">
-        <v>6546</v>
+        <v>6101</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B119">
-        <v>6707</v>
+        <v>6251</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B120">
-        <v>6791</v>
+        <v>6296</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B121">
-        <v>6971</v>
+        <v>6420</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B122">
-        <v>7154</v>
+        <v>6647</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B123">
-        <v>7393</v>
+        <v>6689</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B124">
-        <v>7498</v>
+        <v>6671</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B125">
-        <v>7558</v>
+        <v>6630</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B126">
-        <v>7633</v>
+        <v>6574</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B127">
-        <v>7648</v>
+        <v>0</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B128">
-        <v>7607</v>
+        <v>0</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B129">
-        <v>7569</v>
+        <v>0</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B130">
-        <v>7562</v>
+        <v>0</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B131">
-        <v>7518</v>
+        <v>0</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B132">
-        <v>7459</v>
+        <v>0</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B133">
-        <v>7365</v>
+        <v>0</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B134">
-        <v>7149</v>
+        <v>0</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B135">
-        <v>7015</v>
+        <v>0</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B136">
-        <v>6910</v>
+        <v>0</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
-        <v>5556</v>
+        <v>5692</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
-        <v>5560</v>
+        <v>5640</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
-        <v>5552</v>
+        <v>5642</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
-        <v>5515</v>
+        <v>5599</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
-        <v>5592</v>
+        <v>5523</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
-        <v>5565</v>
+        <v>5541</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
-        <v>5587</v>
+        <v>5551</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
-        <v>5595</v>
+        <v>5521</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
-        <v>5588</v>
+        <v>5463</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
-        <v>5540</v>
+        <v>5469</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
-        <v>5547</v>
+        <v>5420</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
-        <v>5574</v>
+        <v>5412</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
-        <v>5566</v>
+        <v>5484</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
-        <v>5611</v>
+        <v>5541</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
-        <v>5647</v>
+        <v>5552</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
-        <v>5686</v>
+        <v>5601</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>5796</v>
+        <v>5623</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
-        <v>5849</v>
+        <v>5645</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
-        <v>5922</v>
+        <v>5745</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>6161</v>
+        <v>5847</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>6163</v>
+        <v>6054</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>6237</v>
+        <v>6108</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>6346</v>
+        <v>6222</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>6505</v>
+        <v>6352</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>6779</v>
+        <v>6462</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>6901</v>
+        <v>6554</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>6982</v>
+        <v>6576</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>6984</v>
+        <v>6511</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>7050</v>
+        <v>6429</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>7006</v>
+        <v>6414</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>6952</v>
+        <v>6309</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>6837</v>
+        <v>6240</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>6635</v>
+        <v>6085</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>6604</v>
+        <v>5971</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>6520</v>
+        <v>5824</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>6363</v>
+        <v>5754</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>6166</v>
+        <v>5604</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>6057</v>
+        <v>5487</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
-        <v>5987</v>
+        <v>5313</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
-        <v>5889</v>
+        <v>5217</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>5792</v>
+        <v>5191</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
-        <v>5684</v>
+        <v>5131</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>5571</v>
+        <v>5091</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>5418</v>
+        <v>4975</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>5376</v>
+        <v>4865</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
-        <v>5260</v>
+        <v>4868</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>5187</v>
+        <v>4918</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>5158</v>
+        <v>4958</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>5087</v>
+        <v>4957</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
-        <v>5091</v>
+        <v>5024</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>5113</v>
+        <v>5014</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
-        <v>4999</v>
+        <v>5218</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
-        <v>4861</v>
+        <v>5328</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
-        <v>4762</v>
+        <v>5269</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>4832</v>
+        <v>5319</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>4829</v>
+        <v>5314</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>4953</v>
+        <v>5404</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
-        <v>5028</v>
+        <v>5419</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>5142</v>
+        <v>5548</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>5311</v>
+        <v>5564</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>5488</v>
+        <v>0</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>5672</v>
+        <v>5774</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>5862</v>
+        <v>5924</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>6132</v>
+        <v>6037</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>6338</v>
+        <v>6186</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>6529</v>
+        <v>6367</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>6747</v>
+        <v>6516</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>6942</v>
+        <v>6637</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>7020</v>
+        <v>6760</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>7173</v>
+        <v>6865</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>7414</v>
+        <v>7006</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>7609</v>
+        <v>7194</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>7710</v>
+        <v>7340</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>7754</v>
+        <v>7404</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>7799</v>
+        <v>7409</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>7719</v>
+        <v>7407</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>7658</v>
+        <v>7361</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>7603</v>
+        <v>7327</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>7532</v>
+        <v>7274</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>7465</v>
+        <v>7203</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>7393</v>
+        <v>7107</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>7299</v>
+        <v>7028</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>7161</v>
+        <v>6951</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
-        <v>7024</v>
+        <v>6789</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>6746</v>
+        <v>6625</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>6590</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>6440</v>
+        <v>0</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>6314</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>6194</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>6104</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>6003</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>5858</v>
+        <v>0</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>5729</v>
+        <v>0</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>5712</v>
+        <v>0</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B98">
-        <v>5608</v>
+        <v>0</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>5570</v>
+        <v>0</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B100">
-        <v>5536</v>
+        <v>0</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>5540</v>
+        <v>0</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>5579</v>
+        <v>0</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>5585</v>
+        <v>0</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>5574</v>
+        <v>0</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>5547</v>
+        <v>0</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>5566</v>
+        <v>0</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B107">
-        <v>5540</v>
+        <v>0</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>5528</v>
+        <v>0</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>5534</v>
+        <v>0</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>5613</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B111">
-        <v>5614</v>
+        <v>0</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B112">
-        <v>5636</v>
+        <v>0</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>5662</v>
+        <v>0</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>5745</v>
+        <v>0</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>5827</v>
+        <v>0</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>5934</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>6070</v>
+        <v>0</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>6101</v>
+        <v>0</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>6251</v>
+        <v>0</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>6296</v>
+        <v>0</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>6420</v>
+        <v>0</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>6647</v>
+        <v>0</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>6689</v>
+        <v>0</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>6671</v>
+        <v>0</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>6630</v>
+        <v>0</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>6574</v>
+        <v>0</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
   <si>
     <t>Timestamp</t>
   </si>
@@ -602,6 +602,1146 @@
   </si>
   <si>
     <t>26.03.202696</t>
+  </si>
+  <si>
+    <t>27.03.20261</t>
+  </si>
+  <si>
+    <t>27.03.20262</t>
+  </si>
+  <si>
+    <t>27.03.20263</t>
+  </si>
+  <si>
+    <t>27.03.20264</t>
+  </si>
+  <si>
+    <t>27.03.20265</t>
+  </si>
+  <si>
+    <t>27.03.20266</t>
+  </si>
+  <si>
+    <t>27.03.20267</t>
+  </si>
+  <si>
+    <t>27.03.20268</t>
+  </si>
+  <si>
+    <t>27.03.20269</t>
+  </si>
+  <si>
+    <t>27.03.202610</t>
+  </si>
+  <si>
+    <t>27.03.202611</t>
+  </si>
+  <si>
+    <t>27.03.202612</t>
+  </si>
+  <si>
+    <t>27.03.202613</t>
+  </si>
+  <si>
+    <t>27.03.202614</t>
+  </si>
+  <si>
+    <t>27.03.202615</t>
+  </si>
+  <si>
+    <t>27.03.202616</t>
+  </si>
+  <si>
+    <t>27.03.202617</t>
+  </si>
+  <si>
+    <t>27.03.202618</t>
+  </si>
+  <si>
+    <t>27.03.202619</t>
+  </si>
+  <si>
+    <t>27.03.202620</t>
+  </si>
+  <si>
+    <t>27.03.202621</t>
+  </si>
+  <si>
+    <t>27.03.202622</t>
+  </si>
+  <si>
+    <t>27.03.202623</t>
+  </si>
+  <si>
+    <t>27.03.202624</t>
+  </si>
+  <si>
+    <t>27.03.202625</t>
+  </si>
+  <si>
+    <t>27.03.202626</t>
+  </si>
+  <si>
+    <t>27.03.202627</t>
+  </si>
+  <si>
+    <t>27.03.202628</t>
+  </si>
+  <si>
+    <t>27.03.202629</t>
+  </si>
+  <si>
+    <t>27.03.202630</t>
+  </si>
+  <si>
+    <t>27.03.202631</t>
+  </si>
+  <si>
+    <t>27.03.202632</t>
+  </si>
+  <si>
+    <t>27.03.202633</t>
+  </si>
+  <si>
+    <t>27.03.202634</t>
+  </si>
+  <si>
+    <t>27.03.202635</t>
+  </si>
+  <si>
+    <t>27.03.202636</t>
+  </si>
+  <si>
+    <t>27.03.202637</t>
+  </si>
+  <si>
+    <t>27.03.202638</t>
+  </si>
+  <si>
+    <t>27.03.202639</t>
+  </si>
+  <si>
+    <t>27.03.202640</t>
+  </si>
+  <si>
+    <t>27.03.202641</t>
+  </si>
+  <si>
+    <t>27.03.202642</t>
+  </si>
+  <si>
+    <t>27.03.202643</t>
+  </si>
+  <si>
+    <t>27.03.202644</t>
+  </si>
+  <si>
+    <t>27.03.202645</t>
+  </si>
+  <si>
+    <t>27.03.202646</t>
+  </si>
+  <si>
+    <t>27.03.202647</t>
+  </si>
+  <si>
+    <t>27.03.202648</t>
+  </si>
+  <si>
+    <t>27.03.202649</t>
+  </si>
+  <si>
+    <t>27.03.202650</t>
+  </si>
+  <si>
+    <t>27.03.202651</t>
+  </si>
+  <si>
+    <t>27.03.202652</t>
+  </si>
+  <si>
+    <t>27.03.202653</t>
+  </si>
+  <si>
+    <t>27.03.202654</t>
+  </si>
+  <si>
+    <t>27.03.202655</t>
+  </si>
+  <si>
+    <t>27.03.202656</t>
+  </si>
+  <si>
+    <t>27.03.202657</t>
+  </si>
+  <si>
+    <t>27.03.202658</t>
+  </si>
+  <si>
+    <t>27.03.202659</t>
+  </si>
+  <si>
+    <t>27.03.202660</t>
+  </si>
+  <si>
+    <t>27.03.202661</t>
+  </si>
+  <si>
+    <t>27.03.202662</t>
+  </si>
+  <si>
+    <t>27.03.202663</t>
+  </si>
+  <si>
+    <t>27.03.202664</t>
+  </si>
+  <si>
+    <t>27.03.202665</t>
+  </si>
+  <si>
+    <t>27.03.202666</t>
+  </si>
+  <si>
+    <t>27.03.202667</t>
+  </si>
+  <si>
+    <t>27.03.202668</t>
+  </si>
+  <si>
+    <t>27.03.202669</t>
+  </si>
+  <si>
+    <t>27.03.202670</t>
+  </si>
+  <si>
+    <t>27.03.202671</t>
+  </si>
+  <si>
+    <t>27.03.202672</t>
+  </si>
+  <si>
+    <t>27.03.202673</t>
+  </si>
+  <si>
+    <t>27.03.202674</t>
+  </si>
+  <si>
+    <t>27.03.202675</t>
+  </si>
+  <si>
+    <t>27.03.202676</t>
+  </si>
+  <si>
+    <t>27.03.202677</t>
+  </si>
+  <si>
+    <t>27.03.202678</t>
+  </si>
+  <si>
+    <t>27.03.202679</t>
+  </si>
+  <si>
+    <t>27.03.202680</t>
+  </si>
+  <si>
+    <t>27.03.202681</t>
+  </si>
+  <si>
+    <t>27.03.202682</t>
+  </si>
+  <si>
+    <t>27.03.202683</t>
+  </si>
+  <si>
+    <t>27.03.202684</t>
+  </si>
+  <si>
+    <t>27.03.202685</t>
+  </si>
+  <si>
+    <t>27.03.202686</t>
+  </si>
+  <si>
+    <t>27.03.202687</t>
+  </si>
+  <si>
+    <t>27.03.202688</t>
+  </si>
+  <si>
+    <t>27.03.202689</t>
+  </si>
+  <si>
+    <t>27.03.202690</t>
+  </si>
+  <si>
+    <t>27.03.202691</t>
+  </si>
+  <si>
+    <t>27.03.202692</t>
+  </si>
+  <si>
+    <t>27.03.202693</t>
+  </si>
+  <si>
+    <t>27.03.202694</t>
+  </si>
+  <si>
+    <t>27.03.202695</t>
+  </si>
+  <si>
+    <t>27.03.202696</t>
+  </si>
+  <si>
+    <t>28.03.20261</t>
+  </si>
+  <si>
+    <t>28.03.20262</t>
+  </si>
+  <si>
+    <t>28.03.20263</t>
+  </si>
+  <si>
+    <t>28.03.20264</t>
+  </si>
+  <si>
+    <t>28.03.20265</t>
+  </si>
+  <si>
+    <t>28.03.20266</t>
+  </si>
+  <si>
+    <t>28.03.20267</t>
+  </si>
+  <si>
+    <t>28.03.20268</t>
+  </si>
+  <si>
+    <t>28.03.20269</t>
+  </si>
+  <si>
+    <t>28.03.202610</t>
+  </si>
+  <si>
+    <t>28.03.202611</t>
+  </si>
+  <si>
+    <t>28.03.202612</t>
+  </si>
+  <si>
+    <t>28.03.202613</t>
+  </si>
+  <si>
+    <t>28.03.202614</t>
+  </si>
+  <si>
+    <t>28.03.202615</t>
+  </si>
+  <si>
+    <t>28.03.202616</t>
+  </si>
+  <si>
+    <t>28.03.202617</t>
+  </si>
+  <si>
+    <t>28.03.202618</t>
+  </si>
+  <si>
+    <t>28.03.202619</t>
+  </si>
+  <si>
+    <t>28.03.202620</t>
+  </si>
+  <si>
+    <t>28.03.202621</t>
+  </si>
+  <si>
+    <t>28.03.202622</t>
+  </si>
+  <si>
+    <t>28.03.202623</t>
+  </si>
+  <si>
+    <t>28.03.202624</t>
+  </si>
+  <si>
+    <t>28.03.202625</t>
+  </si>
+  <si>
+    <t>28.03.202626</t>
+  </si>
+  <si>
+    <t>28.03.202627</t>
+  </si>
+  <si>
+    <t>28.03.202628</t>
+  </si>
+  <si>
+    <t>28.03.202629</t>
+  </si>
+  <si>
+    <t>28.03.202630</t>
+  </si>
+  <si>
+    <t>28.03.202631</t>
+  </si>
+  <si>
+    <t>28.03.202632</t>
+  </si>
+  <si>
+    <t>28.03.202633</t>
+  </si>
+  <si>
+    <t>28.03.202634</t>
+  </si>
+  <si>
+    <t>28.03.202635</t>
+  </si>
+  <si>
+    <t>28.03.202636</t>
+  </si>
+  <si>
+    <t>28.03.202637</t>
+  </si>
+  <si>
+    <t>28.03.202638</t>
+  </si>
+  <si>
+    <t>28.03.202639</t>
+  </si>
+  <si>
+    <t>28.03.202640</t>
+  </si>
+  <si>
+    <t>28.03.202641</t>
+  </si>
+  <si>
+    <t>28.03.202642</t>
+  </si>
+  <si>
+    <t>28.03.202643</t>
+  </si>
+  <si>
+    <t>28.03.202644</t>
+  </si>
+  <si>
+    <t>28.03.202645</t>
+  </si>
+  <si>
+    <t>28.03.202646</t>
+  </si>
+  <si>
+    <t>28.03.202647</t>
+  </si>
+  <si>
+    <t>28.03.202648</t>
+  </si>
+  <si>
+    <t>28.03.202649</t>
+  </si>
+  <si>
+    <t>28.03.202650</t>
+  </si>
+  <si>
+    <t>28.03.202651</t>
+  </si>
+  <si>
+    <t>28.03.202652</t>
+  </si>
+  <si>
+    <t>28.03.202653</t>
+  </si>
+  <si>
+    <t>28.03.202654</t>
+  </si>
+  <si>
+    <t>28.03.202655</t>
+  </si>
+  <si>
+    <t>28.03.202656</t>
+  </si>
+  <si>
+    <t>28.03.202657</t>
+  </si>
+  <si>
+    <t>28.03.202658</t>
+  </si>
+  <si>
+    <t>28.03.202659</t>
+  </si>
+  <si>
+    <t>28.03.202660</t>
+  </si>
+  <si>
+    <t>28.03.202661</t>
+  </si>
+  <si>
+    <t>28.03.202662</t>
+  </si>
+  <si>
+    <t>28.03.202663</t>
+  </si>
+  <si>
+    <t>28.03.202664</t>
+  </si>
+  <si>
+    <t>28.03.202665</t>
+  </si>
+  <si>
+    <t>28.03.202666</t>
+  </si>
+  <si>
+    <t>28.03.202667</t>
+  </si>
+  <si>
+    <t>28.03.202668</t>
+  </si>
+  <si>
+    <t>28.03.202669</t>
+  </si>
+  <si>
+    <t>28.03.202670</t>
+  </si>
+  <si>
+    <t>28.03.202671</t>
+  </si>
+  <si>
+    <t>28.03.202672</t>
+  </si>
+  <si>
+    <t>28.03.202673</t>
+  </si>
+  <si>
+    <t>28.03.202674</t>
+  </si>
+  <si>
+    <t>28.03.202675</t>
+  </si>
+  <si>
+    <t>28.03.202676</t>
+  </si>
+  <si>
+    <t>28.03.202677</t>
+  </si>
+  <si>
+    <t>28.03.202678</t>
+  </si>
+  <si>
+    <t>28.03.202679</t>
+  </si>
+  <si>
+    <t>28.03.202680</t>
+  </si>
+  <si>
+    <t>28.03.202681</t>
+  </si>
+  <si>
+    <t>28.03.202682</t>
+  </si>
+  <si>
+    <t>28.03.202683</t>
+  </si>
+  <si>
+    <t>28.03.202684</t>
+  </si>
+  <si>
+    <t>28.03.202685</t>
+  </si>
+  <si>
+    <t>28.03.202686</t>
+  </si>
+  <si>
+    <t>28.03.202687</t>
+  </si>
+  <si>
+    <t>28.03.202688</t>
+  </si>
+  <si>
+    <t>28.03.202689</t>
+  </si>
+  <si>
+    <t>28.03.202690</t>
+  </si>
+  <si>
+    <t>28.03.202691</t>
+  </si>
+  <si>
+    <t>28.03.202692</t>
+  </si>
+  <si>
+    <t>28.03.202693</t>
+  </si>
+  <si>
+    <t>28.03.202694</t>
+  </si>
+  <si>
+    <t>28.03.202695</t>
+  </si>
+  <si>
+    <t>28.03.202696</t>
+  </si>
+  <si>
+    <t>29.03.20261</t>
+  </si>
+  <si>
+    <t>29.03.20262</t>
+  </si>
+  <si>
+    <t>29.03.20263</t>
+  </si>
+  <si>
+    <t>29.03.20264</t>
+  </si>
+  <si>
+    <t>29.03.20265</t>
+  </si>
+  <si>
+    <t>29.03.20266</t>
+  </si>
+  <si>
+    <t>29.03.20267</t>
+  </si>
+  <si>
+    <t>29.03.20268</t>
+  </si>
+  <si>
+    <t>29.03.20269</t>
+  </si>
+  <si>
+    <t>29.03.202610</t>
+  </si>
+  <si>
+    <t>29.03.202611</t>
+  </si>
+  <si>
+    <t>29.03.202612</t>
+  </si>
+  <si>
+    <t>29.03.202613</t>
+  </si>
+  <si>
+    <t>29.03.202614</t>
+  </si>
+  <si>
+    <t>29.03.202615</t>
+  </si>
+  <si>
+    <t>29.03.202616</t>
+  </si>
+  <si>
+    <t>29.03.202617</t>
+  </si>
+  <si>
+    <t>29.03.202618</t>
+  </si>
+  <si>
+    <t>29.03.202619</t>
+  </si>
+  <si>
+    <t>29.03.202620</t>
+  </si>
+  <si>
+    <t>29.03.202621</t>
+  </si>
+  <si>
+    <t>29.03.202622</t>
+  </si>
+  <si>
+    <t>29.03.202623</t>
+  </si>
+  <si>
+    <t>29.03.202624</t>
+  </si>
+  <si>
+    <t>29.03.202625</t>
+  </si>
+  <si>
+    <t>29.03.202626</t>
+  </si>
+  <si>
+    <t>29.03.202627</t>
+  </si>
+  <si>
+    <t>29.03.202628</t>
+  </si>
+  <si>
+    <t>29.03.202629</t>
+  </si>
+  <si>
+    <t>29.03.202630</t>
+  </si>
+  <si>
+    <t>29.03.202631</t>
+  </si>
+  <si>
+    <t>29.03.202632</t>
+  </si>
+  <si>
+    <t>29.03.202633</t>
+  </si>
+  <si>
+    <t>29.03.202634</t>
+  </si>
+  <si>
+    <t>29.03.202635</t>
+  </si>
+  <si>
+    <t>29.03.202636</t>
+  </si>
+  <si>
+    <t>29.03.202637</t>
+  </si>
+  <si>
+    <t>29.03.202638</t>
+  </si>
+  <si>
+    <t>29.03.202639</t>
+  </si>
+  <si>
+    <t>29.03.202640</t>
+  </si>
+  <si>
+    <t>29.03.202641</t>
+  </si>
+  <si>
+    <t>29.03.202642</t>
+  </si>
+  <si>
+    <t>29.03.202643</t>
+  </si>
+  <si>
+    <t>29.03.202644</t>
+  </si>
+  <si>
+    <t>29.03.202645</t>
+  </si>
+  <si>
+    <t>29.03.202646</t>
+  </si>
+  <si>
+    <t>29.03.202647</t>
+  </si>
+  <si>
+    <t>29.03.202648</t>
+  </si>
+  <si>
+    <t>29.03.202649</t>
+  </si>
+  <si>
+    <t>29.03.202650</t>
+  </si>
+  <si>
+    <t>29.03.202651</t>
+  </si>
+  <si>
+    <t>29.03.202652</t>
+  </si>
+  <si>
+    <t>29.03.202653</t>
+  </si>
+  <si>
+    <t>29.03.202654</t>
+  </si>
+  <si>
+    <t>29.03.202655</t>
+  </si>
+  <si>
+    <t>29.03.202656</t>
+  </si>
+  <si>
+    <t>29.03.202657</t>
+  </si>
+  <si>
+    <t>29.03.202658</t>
+  </si>
+  <si>
+    <t>29.03.202659</t>
+  </si>
+  <si>
+    <t>29.03.202660</t>
+  </si>
+  <si>
+    <t>29.03.202661</t>
+  </si>
+  <si>
+    <t>29.03.202662</t>
+  </si>
+  <si>
+    <t>29.03.202663</t>
+  </si>
+  <si>
+    <t>29.03.202664</t>
+  </si>
+  <si>
+    <t>29.03.202665</t>
+  </si>
+  <si>
+    <t>29.03.202666</t>
+  </si>
+  <si>
+    <t>29.03.202667</t>
+  </si>
+  <si>
+    <t>29.03.202668</t>
+  </si>
+  <si>
+    <t>29.03.202669</t>
+  </si>
+  <si>
+    <t>29.03.202670</t>
+  </si>
+  <si>
+    <t>29.03.202671</t>
+  </si>
+  <si>
+    <t>29.03.202672</t>
+  </si>
+  <si>
+    <t>29.03.202673</t>
+  </si>
+  <si>
+    <t>29.03.202674</t>
+  </si>
+  <si>
+    <t>29.03.202675</t>
+  </si>
+  <si>
+    <t>29.03.202676</t>
+  </si>
+  <si>
+    <t>29.03.202677</t>
+  </si>
+  <si>
+    <t>29.03.202678</t>
+  </si>
+  <si>
+    <t>29.03.202679</t>
+  </si>
+  <si>
+    <t>29.03.202680</t>
+  </si>
+  <si>
+    <t>29.03.202681</t>
+  </si>
+  <si>
+    <t>29.03.202682</t>
+  </si>
+  <si>
+    <t>29.03.202683</t>
+  </si>
+  <si>
+    <t>29.03.202684</t>
+  </si>
+  <si>
+    <t>29.03.202685</t>
+  </si>
+  <si>
+    <t>29.03.202686</t>
+  </si>
+  <si>
+    <t>29.03.202687</t>
+  </si>
+  <si>
+    <t>29.03.202688</t>
+  </si>
+  <si>
+    <t>29.03.202689</t>
+  </si>
+  <si>
+    <t>29.03.202690</t>
+  </si>
+  <si>
+    <t>29.03.202691</t>
+  </si>
+  <si>
+    <t>29.03.202692</t>
+  </si>
+  <si>
+    <t>30.03.202693</t>
+  </si>
+  <si>
+    <t>30.03.202694</t>
+  </si>
+  <si>
+    <t>30.03.202695</t>
+  </si>
+  <si>
+    <t>30.03.202696</t>
+  </si>
+  <si>
+    <t>30.03.20261</t>
+  </si>
+  <si>
+    <t>30.03.20262</t>
+  </si>
+  <si>
+    <t>30.03.20263</t>
+  </si>
+  <si>
+    <t>30.03.20264</t>
+  </si>
+  <si>
+    <t>30.03.20265</t>
+  </si>
+  <si>
+    <t>30.03.20266</t>
+  </si>
+  <si>
+    <t>30.03.20267</t>
+  </si>
+  <si>
+    <t>30.03.20268</t>
+  </si>
+  <si>
+    <t>30.03.20269</t>
+  </si>
+  <si>
+    <t>30.03.202610</t>
+  </si>
+  <si>
+    <t>30.03.202611</t>
+  </si>
+  <si>
+    <t>30.03.202612</t>
+  </si>
+  <si>
+    <t>30.03.202613</t>
+  </si>
+  <si>
+    <t>30.03.202614</t>
+  </si>
+  <si>
+    <t>30.03.202615</t>
+  </si>
+  <si>
+    <t>30.03.202616</t>
+  </si>
+  <si>
+    <t>30.03.202617</t>
+  </si>
+  <si>
+    <t>30.03.202618</t>
+  </si>
+  <si>
+    <t>30.03.202619</t>
+  </si>
+  <si>
+    <t>30.03.202620</t>
+  </si>
+  <si>
+    <t>30.03.202621</t>
+  </si>
+  <si>
+    <t>30.03.202622</t>
+  </si>
+  <si>
+    <t>30.03.202623</t>
+  </si>
+  <si>
+    <t>30.03.202624</t>
+  </si>
+  <si>
+    <t>30.03.202625</t>
+  </si>
+  <si>
+    <t>30.03.202626</t>
+  </si>
+  <si>
+    <t>30.03.202627</t>
+  </si>
+  <si>
+    <t>30.03.202628</t>
+  </si>
+  <si>
+    <t>30.03.202629</t>
+  </si>
+  <si>
+    <t>30.03.202630</t>
+  </si>
+  <si>
+    <t>30.03.202631</t>
+  </si>
+  <si>
+    <t>30.03.202632</t>
+  </si>
+  <si>
+    <t>30.03.202633</t>
+  </si>
+  <si>
+    <t>30.03.202634</t>
+  </si>
+  <si>
+    <t>30.03.202635</t>
+  </si>
+  <si>
+    <t>30.03.202636</t>
+  </si>
+  <si>
+    <t>30.03.202637</t>
+  </si>
+  <si>
+    <t>30.03.202638</t>
+  </si>
+  <si>
+    <t>30.03.202639</t>
+  </si>
+  <si>
+    <t>30.03.202640</t>
+  </si>
+  <si>
+    <t>30.03.202641</t>
+  </si>
+  <si>
+    <t>30.03.202642</t>
+  </si>
+  <si>
+    <t>30.03.202643</t>
+  </si>
+  <si>
+    <t>30.03.202644</t>
+  </si>
+  <si>
+    <t>30.03.202645</t>
+  </si>
+  <si>
+    <t>30.03.202646</t>
+  </si>
+  <si>
+    <t>30.03.202647</t>
+  </si>
+  <si>
+    <t>30.03.202648</t>
+  </si>
+  <si>
+    <t>30.03.202649</t>
+  </si>
+  <si>
+    <t>30.03.202650</t>
+  </si>
+  <si>
+    <t>30.03.202651</t>
+  </si>
+  <si>
+    <t>30.03.202652</t>
+  </si>
+  <si>
+    <t>30.03.202653</t>
+  </si>
+  <si>
+    <t>30.03.202654</t>
+  </si>
+  <si>
+    <t>30.03.202655</t>
+  </si>
+  <si>
+    <t>30.03.202656</t>
+  </si>
+  <si>
+    <t>30.03.202657</t>
+  </si>
+  <si>
+    <t>30.03.202658</t>
+  </si>
+  <si>
+    <t>30.03.202659</t>
+  </si>
+  <si>
+    <t>30.03.202660</t>
+  </si>
+  <si>
+    <t>30.03.202661</t>
+  </si>
+  <si>
+    <t>30.03.202662</t>
+  </si>
+  <si>
+    <t>30.03.202663</t>
+  </si>
+  <si>
+    <t>30.03.202664</t>
+  </si>
+  <si>
+    <t>30.03.202665</t>
+  </si>
+  <si>
+    <t>30.03.202666</t>
+  </si>
+  <si>
+    <t>30.03.202667</t>
+  </si>
+  <si>
+    <t>30.03.202668</t>
+  </si>
+  <si>
+    <t>30.03.202669</t>
+  </si>
+  <si>
+    <t>30.03.202670</t>
+  </si>
+  <si>
+    <t>30.03.202671</t>
+  </si>
+  <si>
+    <t>30.03.202672</t>
+  </si>
+  <si>
+    <t>30.03.202673</t>
+  </si>
+  <si>
+    <t>30.03.202674</t>
+  </si>
+  <si>
+    <t>30.03.202675</t>
+  </si>
+  <si>
+    <t>30.03.202676</t>
+  </si>
+  <si>
+    <t>30.03.202677</t>
+  </si>
+  <si>
+    <t>30.03.202678</t>
+  </si>
+  <si>
+    <t>30.03.202679</t>
+  </si>
+  <si>
+    <t>30.03.202680</t>
+  </si>
+  <si>
+    <t>30.03.202681</t>
+  </si>
+  <si>
+    <t>30.03.202682</t>
+  </si>
+  <si>
+    <t>30.03.202683</t>
+  </si>
+  <si>
+    <t>30.03.202684</t>
+  </si>
+  <si>
+    <t>30.03.202685</t>
+  </si>
+  <si>
+    <t>30.03.202686</t>
+  </si>
+  <si>
+    <t>30.03.202687</t>
+  </si>
+  <si>
+    <t>30.03.202688</t>
+  </si>
+  <si>
+    <t>30.03.202689</t>
+  </si>
+  <si>
+    <t>30.03.202690</t>
+  </si>
+  <si>
+    <t>30.03.202691</t>
+  </si>
+  <si>
+    <t>30.03.202692</t>
   </si>
 </sst>
 </file>
@@ -963,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2175,7 +3315,7 @@
         <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>6483</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2189,7 +3329,7 @@
         <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>6403</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2203,7 +3343,7 @@
         <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>6233</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2217,7 +3357,7 @@
         <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>6066</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2231,7 +3371,7 @@
         <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>5963</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2245,7 +3385,7 @@
         <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>5832</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2259,7 +3399,7 @@
         <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>5748</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2273,7 +3413,7 @@
         <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>5670</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2287,7 +3427,7 @@
         <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>5613</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2301,7 +3441,7 @@
         <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>5596</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2315,7 +3455,7 @@
         <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>5521</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2329,7 +3469,7 @@
         <v>46107</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>5446</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2343,7 +3483,7 @@
         <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>5396</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2357,7 +3497,7 @@
         <v>46107.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>5384</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2371,7 +3511,7 @@
         <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>5341</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2385,7 +3525,7 @@
         <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>5406</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2399,7 +3539,7 @@
         <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>5394</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2413,7 +3553,7 @@
         <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>5388</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2427,7 +3567,7 @@
         <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>5398</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2441,7 +3581,7 @@
         <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>5451</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2455,7 +3595,7 @@
         <v>46107.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>5432</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2469,7 +3609,7 @@
         <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>5416</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2483,7 +3623,7 @@
         <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2497,7 +3637,7 @@
         <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>5456</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2511,7 +3651,7 @@
         <v>46107.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>5452</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2525,7 +3665,7 @@
         <v>46107.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5548</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2539,7 +3679,7 @@
         <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>5539</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2553,7 +3693,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>5566</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2567,7 +3707,7 @@
         <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>5610</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2581,7 +3721,7 @@
         <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>5688</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2595,7 +3735,7 @@
         <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>5766</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2609,7 +3749,7 @@
         <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>5865</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2623,7 +3763,7 @@
         <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>5957</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2637,7 +3777,7 @@
         <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>6065</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2651,7 +3791,7 @@
         <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>6213</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2665,7 +3805,7 @@
         <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>6418</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2679,7 +3819,7 @@
         <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>6571</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2693,7 +3833,7 @@
         <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>6614</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2707,7 +3847,7 @@
         <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>6639</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2721,7 +3861,7 @@
         <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>6661</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2735,7 +3875,7 @@
         <v>46107.30208333334</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>6653</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2749,7 +3889,7 @@
         <v>46107.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>6598</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2763,7 +3903,7 @@
         <v>46107.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>6481</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2777,7 +3917,7 @@
         <v>46107.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>6325</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2791,7 +3931,7 @@
         <v>46107.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>6259</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2805,7 +3945,7 @@
         <v>46107.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>6129</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2819,7 +3959,7 @@
         <v>46107.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>6169</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2833,7 +3973,7 @@
         <v>46107.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>6042</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2847,7 +3987,7 @@
         <v>46107.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>5934</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2861,7 +4001,7 @@
         <v>46107.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>5772</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2875,7 +4015,7 @@
         <v>46107.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>5574</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2889,7 +4029,7 @@
         <v>46107.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>5221</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2903,7 +4043,7 @@
         <v>46107.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>5143</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2917,7 +4057,7 @@
         <v>46107.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>5048</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2931,7 +4071,7 @@
         <v>46107.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>5001</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2945,7 +4085,7 @@
         <v>46107.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>4828</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2959,7 +4099,7 @@
         <v>46107.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>4844</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2973,7 +4113,7 @@
         <v>46107.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>4869</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2987,7 +4127,7 @@
         <v>46107.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>4944</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3001,7 +4141,7 @@
         <v>46107.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>4938</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3015,7 +4155,7 @@
         <v>46107.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>5072</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3029,7 +4169,7 @@
         <v>46107.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>5095</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3043,7 +4183,7 @@
         <v>46107.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>5181</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3057,7 +4197,7 @@
         <v>46107.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>5253</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3071,7 +4211,7 @@
         <v>46107.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>5345</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3085,7 +4225,7 @@
         <v>46107.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>5340</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3099,7 +4239,7 @@
         <v>46107.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>5386</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3113,7 +4253,7 @@
         <v>46107.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>5687</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3127,7 +4267,7 @@
         <v>46107.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>5889</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3141,7 +4281,7 @@
         <v>46107.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>5918</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3155,7 +4295,7 @@
         <v>46107.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>6153</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3169,7 +4309,7 @@
         <v>46107.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>6210</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3183,7 +4323,7 @@
         <v>46107.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>6239</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3197,7 +4337,7 @@
         <v>46107.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>6227</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3211,7 +4351,7 @@
         <v>46107.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>6418</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3225,7 +4365,7 @@
         <v>46107.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>6534</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3239,7 +4379,7 @@
         <v>46107.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>6734</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3253,7 +4393,7 @@
         <v>46107.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>6794</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3267,7 +4407,7 @@
         <v>46107.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>6862</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3281,7 +4421,7 @@
         <v>46107.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>6973</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3295,7 +4435,7 @@
         <v>46107.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>7078</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3309,7 +4449,7 @@
         <v>46107.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>7274</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3323,7 +4463,7 @@
         <v>46107.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>7397</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3337,7 +4477,7 @@
         <v>46107.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>7501</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3351,7 +4491,7 @@
         <v>46107.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>7587</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3365,7 +4505,7 @@
         <v>46107.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>7591</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3379,7 +4519,7 @@
         <v>46107.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>7615</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3393,7 +4533,7 @@
         <v>46107.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>7558</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3407,7 +4547,7 @@
         <v>46107.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>7498</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3421,7 +4561,7 @@
         <v>46107.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>7474</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3435,7 +4575,7 @@
         <v>46107.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>7374</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3449,7 +4589,7 @@
         <v>46107.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>7330</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3463,7 +4603,7 @@
         <v>46107.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>7165</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3477,7 +4617,7 @@
         <v>46107.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>7090</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3491,7 +4631,7 @@
         <v>46107.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6909</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3505,7 +4645,7 @@
         <v>46107.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>6734</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3519,7 +4659,7 @@
         <v>46107.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>6506</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3533,7 +4673,7 @@
         <v>46107.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3547,7 +4687,7 @@
         <v>46107.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>6248</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3561,7 +4701,7 @@
         <v>46107.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>6085</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3575,7 +4715,7 @@
         <v>46107.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5997</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3589,7 +4729,7 @@
         <v>46107.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>5958</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3603,7 +4743,7 @@
         <v>46107.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>5866</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3617,7 +4757,7 @@
         <v>46107.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>5721</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3631,7 +4771,7 @@
         <v>46107.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>5628</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3645,7 +4785,7 @@
         <v>46107.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>5615</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3659,13 +4799,5333 @@
         <v>46107.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>5573</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B194">
+        <v>5571</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46108.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>5475</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46108.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>5444</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46108.03125</v>
+      </c>
+      <c r="B197">
+        <v>5441</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46108.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>5467</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46108.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>5446</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46108.0625</v>
+      </c>
+      <c r="B200">
+        <v>5484</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46108.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>5473</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46108.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46108.09375</v>
+      </c>
+      <c r="B203">
+        <v>5538</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46108.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>5494</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46108.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>5477</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46108.125</v>
+      </c>
+      <c r="B206">
+        <v>5538</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46108.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>5605</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46108.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>5588</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46108.15625</v>
+      </c>
+      <c r="B209">
+        <v>5674</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46108.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>5720</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46108.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>5764</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46108.1875</v>
+      </c>
+      <c r="B212">
+        <v>5883</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46108.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>5929</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46108.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>5886</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46108.21875</v>
+      </c>
+      <c r="B215">
+        <v>6004</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46108.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>6112</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46108.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>6270</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46108.25</v>
+      </c>
+      <c r="B218">
+        <v>6471</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46108.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>6654</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46108.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>6747</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46108.28125</v>
+      </c>
+      <c r="B221">
+        <v>6843</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46108.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>6887</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46108.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>6955</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46108.3125</v>
+      </c>
+      <c r="B224">
+        <v>6951</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46108.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>6772</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46108.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>6719</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46108.34375</v>
+      </c>
+      <c r="B227">
+        <v>6640</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46108.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>6589</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46108.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>6479</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46108.375</v>
+      </c>
+      <c r="B230">
+        <v>6387</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46108.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>6220</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46108.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>6137</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46108.40625</v>
+      </c>
+      <c r="B233">
+        <v>6053</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46108.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>6032</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46108.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>5916</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46108.4375</v>
+      </c>
+      <c r="B236">
+        <v>5873</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46108.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>5865</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46108.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>5830</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46108.46875</v>
+      </c>
+      <c r="B239">
+        <v>5924</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46108.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>5931</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46108.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>5914</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46108.5</v>
+      </c>
+      <c r="B242">
+        <v>5984</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46108.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>6023</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46108.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>6097</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46108.53125</v>
+      </c>
+      <c r="B245">
+        <v>6107</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46108.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>6246</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46108.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>6292</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46108.5625</v>
+      </c>
+      <c r="B248">
+        <v>6252</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46108.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>6325</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46108.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>6345</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46108.59375</v>
+      </c>
+      <c r="B251">
+        <v>6416</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46108.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>6455</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46108.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>6513</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46108.625</v>
+      </c>
+      <c r="B254">
+        <v>6551</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46108.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>6726</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46108.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>6814</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46108.65625</v>
+      </c>
+      <c r="B257">
+        <v>6831</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46108.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>6850</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46108.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>6940</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46108.6875</v>
+      </c>
+      <c r="B260">
+        <v>7067</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46108.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>7158</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46108.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>7201</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46108.71875</v>
+      </c>
+      <c r="B263">
+        <v>7276</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46108.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>7391</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46108.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>7549</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46108.75</v>
+      </c>
+      <c r="B266">
+        <v>7619</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46108.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>7718</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46108.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>7692</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46108.78125</v>
+      </c>
+      <c r="B269">
+        <v>7653</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46108.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>7611</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46108.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>7581</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46108.8125</v>
+      </c>
+      <c r="B272">
+        <v>7470</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46108.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>7425</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46108.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>7270</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46108.84375</v>
+      </c>
+      <c r="B275">
+        <v>7157</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46108.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>7052</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46108.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>6880</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46108.875</v>
+      </c>
+      <c r="B278">
+        <v>6763</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46108.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>6582</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46108.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>6467</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46108.90625</v>
+      </c>
+      <c r="B281">
+        <v>6322</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46108.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>6210</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46108.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>6087</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46108.9375</v>
+      </c>
+      <c r="B284">
+        <v>5918</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46108.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>5969</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46108.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>5884</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46108.96875</v>
+      </c>
+      <c r="B287">
+        <v>5810</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46108.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>5773</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46108.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>5702</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46109</v>
+      </c>
+      <c r="B290">
+        <v>5573</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46109.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>5486</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46109.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>5453</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46109.03125</v>
+      </c>
+      <c r="B293">
+        <v>5465</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46109.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>5420</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46109.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>5371</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46109.0625</v>
+      </c>
+      <c r="B296">
+        <v>5394</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46109.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>5345</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46109.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>5286</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46109.09375</v>
+      </c>
+      <c r="B299">
+        <v>5353</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46109.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>5332</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46109.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>5336</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46109.125</v>
+      </c>
+      <c r="B302">
+        <v>5438</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46109.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>5469</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46109.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>5455</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46109.15625</v>
+      </c>
+      <c r="B305">
+        <v>5442</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46109.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>5466</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46109.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>5469</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46109.1875</v>
+      </c>
+      <c r="B308">
+        <v>5480</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46109.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5530</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46109.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5424</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46109.21875</v>
+      </c>
+      <c r="B311">
+        <v>5480</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46109.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5539</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46109.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5605</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46109.25</v>
+      </c>
+      <c r="B314">
+        <v>5728</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46109.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>5791</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46109.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>5946</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46109.28125</v>
+      </c>
+      <c r="B317">
+        <v>5974</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46109.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6104</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46109.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>6187</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46109.3125</v>
+      </c>
+      <c r="B320">
+        <v>6212</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46109.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>6310</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46109.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>6321</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46109.34375</v>
+      </c>
+      <c r="B323">
+        <v>6404</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46109.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>6407</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46109.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>6399</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46109.375</v>
+      </c>
+      <c r="B326">
+        <v>6407</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46109.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>6390</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46109.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>6466</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46109.40625</v>
+      </c>
+      <c r="B329">
+        <v>6465</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46109.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>6415</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46109.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>6447</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46109.4375</v>
+      </c>
+      <c r="B332">
+        <v>6403</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46109.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>6367</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46109.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>6254</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46109.46875</v>
+      </c>
+      <c r="B335">
+        <v>6210</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46109.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>6268</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46109.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>6243</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46109.5</v>
+      </c>
+      <c r="B338">
+        <v>6205</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46109.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>6226</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46109.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>6236</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46109.53125</v>
+      </c>
+      <c r="B341">
+        <v>6208</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46109.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>6085</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46109.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>6062</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46109.5625</v>
+      </c>
+      <c r="B344">
+        <v>6043</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46109.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>6060</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46109.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>6113</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46109.59375</v>
+      </c>
+      <c r="B347">
+        <v>6109</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46109.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>6161</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46109.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>6220</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46109.625</v>
+      </c>
+      <c r="B350">
+        <v>6290</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46109.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>6382</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46109.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>6405</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46109.65625</v>
+      </c>
+      <c r="B353">
+        <v>6395</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46109.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>6445</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46109.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>6521</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46109.6875</v>
+      </c>
+      <c r="B356">
+        <v>6579</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46109.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>6631</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46109.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>6657</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46109.71875</v>
+      </c>
+      <c r="B359">
+        <v>6783</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46109.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>6886</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46109.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>7016</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46109.75</v>
+      </c>
+      <c r="B362">
+        <v>7102</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46109.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>7191</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46109.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>7260</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46109.78125</v>
+      </c>
+      <c r="B365">
+        <v>7266</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46109.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>7242</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46109.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>7175</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46109.8125</v>
+      </c>
+      <c r="B368">
+        <v>7121</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46109.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>7015</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46109.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6824</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46109.84375</v>
+      </c>
+      <c r="B371">
+        <v>6744</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46109.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6645</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46109.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6525</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46109.875</v>
+      </c>
+      <c r="B374">
+        <v>6331</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46109.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>6208</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46109.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>6086</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46109.90625</v>
+      </c>
+      <c r="B377">
+        <v>5939</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46109.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5791</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46109.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5726</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46109.9375</v>
+      </c>
+      <c r="B380">
+        <v>5618</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46109.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5565</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46109.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5444</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46109.96875</v>
+      </c>
+      <c r="B383">
+        <v>5361</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46109.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>5299</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46109.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>5254</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46110</v>
+      </c>
+      <c r="B386">
+        <v>5206</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46110.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>5148</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46110.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>5145</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46110.03125</v>
+      </c>
+      <c r="B389">
+        <v>5125</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46110.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>5101</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46110.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>5021</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46110.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46110.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46110.125</v>
+      </c>
+      <c r="B394">
+        <v>5068</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46110.13541666666</v>
+      </c>
+      <c r="B395">
+        <v>5027</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46110.14583333334</v>
+      </c>
+      <c r="B396">
+        <v>5018</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46110.15625</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46110.16666666666</v>
+      </c>
+      <c r="B398">
+        <v>5044</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46110.17708333334</v>
+      </c>
+      <c r="B399">
+        <v>5102</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46110.1875</v>
+      </c>
+      <c r="B400">
+        <v>5075</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46110.19791666666</v>
+      </c>
+      <c r="B401">
+        <v>5097</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46110.20833333334</v>
+      </c>
+      <c r="B402">
+        <v>5087</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46110.21875</v>
+      </c>
+      <c r="B403">
+        <v>5105</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46110.22916666666</v>
+      </c>
+      <c r="B404">
+        <v>5166</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46110.23958333334</v>
+      </c>
+      <c r="B405">
+        <v>5108</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46110.25</v>
+      </c>
+      <c r="B406">
+        <v>5174</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46110.26041666666</v>
+      </c>
+      <c r="B407">
+        <v>5237</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46110.27083333334</v>
+      </c>
+      <c r="B408">
+        <v>5279</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46110.28125</v>
+      </c>
+      <c r="B409">
+        <v>5319</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46110.29166666666</v>
+      </c>
+      <c r="B410">
+        <v>5293</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46110.30208333334</v>
+      </c>
+      <c r="B411">
+        <v>5385</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46110.3125</v>
+      </c>
+      <c r="B412">
+        <v>5392</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46110.32291666666</v>
+      </c>
+      <c r="B413">
+        <v>5460</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46110.33333333334</v>
+      </c>
+      <c r="B414">
+        <v>5527</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46110.34375</v>
+      </c>
+      <c r="B415">
+        <v>5492</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46110.35416666666</v>
+      </c>
+      <c r="B416">
+        <v>5539</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46110.36458333334</v>
+      </c>
+      <c r="B417">
+        <v>5525</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46110.375</v>
+      </c>
+      <c r="B418">
+        <v>5599</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46110.38541666666</v>
+      </c>
+      <c r="B419">
+        <v>5542</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46110.39583333334</v>
+      </c>
+      <c r="B420">
+        <v>5505</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46110.40625</v>
+      </c>
+      <c r="B421">
+        <v>5459</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46110.41666666666</v>
+      </c>
+      <c r="B422">
+        <v>5510</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46110.42708333334</v>
+      </c>
+      <c r="B423">
+        <v>5489</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46110.4375</v>
+      </c>
+      <c r="B424">
+        <v>5458</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46110.44791666666</v>
+      </c>
+      <c r="B425">
+        <v>5515</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" s="2">
+        <v>46110.45833333334</v>
+      </c>
+      <c r="B426">
+        <v>5489</v>
+      </c>
+      <c r="C426">
+        <v>41</v>
+      </c>
+      <c r="D426" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" s="2">
+        <v>46110.46875</v>
+      </c>
+      <c r="B427">
+        <v>5542</v>
+      </c>
+      <c r="C427">
+        <v>42</v>
+      </c>
+      <c r="D427" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" s="2">
+        <v>46110.47916666666</v>
+      </c>
+      <c r="B428">
+        <v>5510</v>
+      </c>
+      <c r="C428">
+        <v>43</v>
+      </c>
+      <c r="D428" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" s="2">
+        <v>46110.48958333334</v>
+      </c>
+      <c r="B429">
+        <v>5492</v>
+      </c>
+      <c r="C429">
+        <v>44</v>
+      </c>
+      <c r="D429" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="2">
+        <v>46110.5</v>
+      </c>
+      <c r="B430">
+        <v>5533</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" s="2">
+        <v>46110.51041666666</v>
+      </c>
+      <c r="B431">
+        <v>5496</v>
+      </c>
+      <c r="C431">
+        <v>46</v>
+      </c>
+      <c r="D431" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" s="2">
+        <v>46110.52083333334</v>
+      </c>
+      <c r="B432">
+        <v>5486</v>
+      </c>
+      <c r="C432">
+        <v>47</v>
+      </c>
+      <c r="D432" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" s="2">
+        <v>46110.53125</v>
+      </c>
+      <c r="B433">
+        <v>5451</v>
+      </c>
+      <c r="C433">
+        <v>48</v>
+      </c>
+      <c r="D433" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" s="2">
+        <v>46110.54166666666</v>
+      </c>
+      <c r="B434">
+        <v>5445</v>
+      </c>
+      <c r="C434">
+        <v>49</v>
+      </c>
+      <c r="D434" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" s="2">
+        <v>46110.55208333334</v>
+      </c>
+      <c r="B435">
+        <v>5455</v>
+      </c>
+      <c r="C435">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="2">
+        <v>46110.5625</v>
+      </c>
+      <c r="B436">
+        <v>5430</v>
+      </c>
+      <c r="C436">
+        <v>51</v>
+      </c>
+      <c r="D436" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" s="2">
+        <v>46110.57291666666</v>
+      </c>
+      <c r="B437">
+        <v>5412</v>
+      </c>
+      <c r="C437">
+        <v>52</v>
+      </c>
+      <c r="D437" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="2">
+        <v>46110.58333333334</v>
+      </c>
+      <c r="B438">
+        <v>5435</v>
+      </c>
+      <c r="C438">
+        <v>53</v>
+      </c>
+      <c r="D438" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" s="2">
+        <v>46110.59375</v>
+      </c>
+      <c r="B439">
+        <v>5479</v>
+      </c>
+      <c r="C439">
+        <v>54</v>
+      </c>
+      <c r="D439" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="2">
+        <v>46110.60416666666</v>
+      </c>
+      <c r="B440">
+        <v>5459</v>
+      </c>
+      <c r="C440">
+        <v>55</v>
+      </c>
+      <c r="D440" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" s="2">
+        <v>46110.61458333334</v>
+      </c>
+      <c r="B441">
+        <v>5517</v>
+      </c>
+      <c r="C441">
+        <v>56</v>
+      </c>
+      <c r="D441" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" s="2">
+        <v>46110.625</v>
+      </c>
+      <c r="B442">
+        <v>5497</v>
+      </c>
+      <c r="C442">
+        <v>57</v>
+      </c>
+      <c r="D442" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" s="2">
+        <v>46110.63541666666</v>
+      </c>
+      <c r="B443">
+        <v>5592</v>
+      </c>
+      <c r="C443">
+        <v>58</v>
+      </c>
+      <c r="D443" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" s="2">
+        <v>46110.64583333334</v>
+      </c>
+      <c r="B444">
+        <v>5554</v>
+      </c>
+      <c r="C444">
+        <v>59</v>
+      </c>
+      <c r="D444" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" s="2">
+        <v>46110.65625</v>
+      </c>
+      <c r="B445">
+        <v>5653</v>
+      </c>
+      <c r="C445">
+        <v>60</v>
+      </c>
+      <c r="D445" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" s="2">
+        <v>46110.66666666666</v>
+      </c>
+      <c r="B446">
+        <v>5726</v>
+      </c>
+      <c r="C446">
+        <v>61</v>
+      </c>
+      <c r="D446" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" s="2">
+        <v>46110.67708333334</v>
+      </c>
+      <c r="B447">
+        <v>5745</v>
+      </c>
+      <c r="C447">
+        <v>62</v>
+      </c>
+      <c r="D447" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="2">
+        <v>46110.6875</v>
+      </c>
+      <c r="B448">
+        <v>5841</v>
+      </c>
+      <c r="C448">
+        <v>63</v>
+      </c>
+      <c r="D448" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="2">
+        <v>46110.69791666666</v>
+      </c>
+      <c r="B449">
+        <v>5896</v>
+      </c>
+      <c r="C449">
+        <v>64</v>
+      </c>
+      <c r="D449" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" s="2">
+        <v>46110.70833333334</v>
+      </c>
+      <c r="B450">
+        <v>5966</v>
+      </c>
+      <c r="C450">
+        <v>65</v>
+      </c>
+      <c r="D450" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="2">
+        <v>46110.71875</v>
+      </c>
+      <c r="B451">
+        <v>6036</v>
+      </c>
+      <c r="C451">
+        <v>66</v>
+      </c>
+      <c r="D451" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="2">
+        <v>46110.72916666666</v>
+      </c>
+      <c r="B452">
+        <v>6130</v>
+      </c>
+      <c r="C452">
+        <v>67</v>
+      </c>
+      <c r="D452" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" s="2">
+        <v>46110.73958333334</v>
+      </c>
+      <c r="B453">
+        <v>6260</v>
+      </c>
+      <c r="C453">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="2">
+        <v>46110.75</v>
+      </c>
+      <c r="B454">
+        <v>6215</v>
+      </c>
+      <c r="C454">
+        <v>69</v>
+      </c>
+      <c r="D454" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" s="2">
+        <v>46110.76041666666</v>
+      </c>
+      <c r="B455">
+        <v>6310</v>
+      </c>
+      <c r="C455">
+        <v>70</v>
+      </c>
+      <c r="D455" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="2">
+        <v>46110.77083333334</v>
+      </c>
+      <c r="B456">
+        <v>6471</v>
+      </c>
+      <c r="C456">
+        <v>71</v>
+      </c>
+      <c r="D456" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="2">
+        <v>46110.78125</v>
+      </c>
+      <c r="B457">
+        <v>6570</v>
+      </c>
+      <c r="C457">
+        <v>72</v>
+      </c>
+      <c r="D457" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" s="2">
+        <v>46110.79166666666</v>
+      </c>
+      <c r="B458">
+        <v>6687</v>
+      </c>
+      <c r="C458">
+        <v>73</v>
+      </c>
+      <c r="D458" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" s="2">
+        <v>46110.80208333334</v>
+      </c>
+      <c r="B459">
+        <v>6662</v>
+      </c>
+      <c r="C459">
+        <v>74</v>
+      </c>
+      <c r="D459" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" s="2">
+        <v>46110.8125</v>
+      </c>
+      <c r="B460">
+        <v>6689</v>
+      </c>
+      <c r="C460">
+        <v>75</v>
+      </c>
+      <c r="D460" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" s="2">
+        <v>46110.82291666666</v>
+      </c>
+      <c r="B461">
+        <v>6667</v>
+      </c>
+      <c r="C461">
+        <v>76</v>
+      </c>
+      <c r="D461" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="2">
+        <v>46110.83333333334</v>
+      </c>
+      <c r="B462">
+        <v>6650</v>
+      </c>
+      <c r="C462">
+        <v>77</v>
+      </c>
+      <c r="D462" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" s="2">
+        <v>46110.84375</v>
+      </c>
+      <c r="B463">
+        <v>6549</v>
+      </c>
+      <c r="C463">
+        <v>78</v>
+      </c>
+      <c r="D463" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="2">
+        <v>46110.85416666666</v>
+      </c>
+      <c r="B464">
+        <v>6437</v>
+      </c>
+      <c r="C464">
+        <v>79</v>
+      </c>
+      <c r="D464" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" s="2">
+        <v>46110.86458333334</v>
+      </c>
+      <c r="B465">
+        <v>6361</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+      <c r="D465" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="2">
+        <v>46110.875</v>
+      </c>
+      <c r="B466">
+        <v>6137</v>
+      </c>
+      <c r="C466">
+        <v>81</v>
+      </c>
+      <c r="D466" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" s="2">
+        <v>46110.88541666666</v>
+      </c>
+      <c r="B467">
+        <v>6084</v>
+      </c>
+      <c r="C467">
+        <v>82</v>
+      </c>
+      <c r="D467" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" s="2">
+        <v>46110.89583333334</v>
+      </c>
+      <c r="B468">
+        <v>6024</v>
+      </c>
+      <c r="C468">
+        <v>83</v>
+      </c>
+      <c r="D468" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" s="2">
+        <v>46110.90625</v>
+      </c>
+      <c r="B469">
+        <v>5891</v>
+      </c>
+      <c r="C469">
+        <v>84</v>
+      </c>
+      <c r="D469" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="2">
+        <v>46110.91666666666</v>
+      </c>
+      <c r="B470">
+        <v>5757</v>
+      </c>
+      <c r="C470">
+        <v>85</v>
+      </c>
+      <c r="D470" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="2">
+        <v>46110.92708333334</v>
+      </c>
+      <c r="B471">
+        <v>5693</v>
+      </c>
+      <c r="C471">
+        <v>86</v>
+      </c>
+      <c r="D471" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" s="2">
+        <v>46110.9375</v>
+      </c>
+      <c r="B472">
+        <v>5555</v>
+      </c>
+      <c r="C472">
+        <v>87</v>
+      </c>
+      <c r="D472" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" s="2">
+        <v>46110.94791666666</v>
+      </c>
+      <c r="B473">
+        <v>5520</v>
+      </c>
+      <c r="C473">
+        <v>88</v>
+      </c>
+      <c r="D473" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" s="2">
+        <v>46110.95833333334</v>
+      </c>
+      <c r="B474">
+        <v>5342</v>
+      </c>
+      <c r="C474">
+        <v>89</v>
+      </c>
+      <c r="D474" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="2">
+        <v>46110.96875</v>
+      </c>
+      <c r="B475">
+        <v>5306</v>
+      </c>
+      <c r="C475">
+        <v>90</v>
+      </c>
+      <c r="D475" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" s="2">
+        <v>46110.97916666666</v>
+      </c>
+      <c r="B476">
+        <v>5241</v>
+      </c>
+      <c r="C476">
+        <v>91</v>
+      </c>
+      <c r="D476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" s="2">
+        <v>46110.98958333334</v>
+      </c>
+      <c r="B477">
+        <v>5217</v>
+      </c>
+      <c r="C477">
+        <v>92</v>
+      </c>
+      <c r="D477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B478">
+        <v>5172</v>
+      </c>
+      <c r="C478">
+        <v>93</v>
+      </c>
+      <c r="D478" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" s="2">
+        <v>46111.01041666666</v>
+      </c>
+      <c r="B479">
+        <v>5082</v>
+      </c>
+      <c r="C479">
+        <v>94</v>
+      </c>
+      <c r="D479" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="2">
+        <v>46111.02083333334</v>
+      </c>
+      <c r="B480">
+        <v>5072</v>
+      </c>
+      <c r="C480">
+        <v>95</v>
+      </c>
+      <c r="D480" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" s="2">
+        <v>46111.03125</v>
+      </c>
+      <c r="B481">
+        <v>5018</v>
+      </c>
+      <c r="C481">
+        <v>96</v>
+      </c>
+      <c r="D481" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482" s="2">
+        <v>46111.04166666666</v>
+      </c>
+      <c r="B482">
+        <v>5101</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483" s="2">
+        <v>46111.05208333334</v>
+      </c>
+      <c r="B483">
+        <v>5035</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484" s="2">
+        <v>46111.0625</v>
+      </c>
+      <c r="B484">
+        <v>5075</v>
+      </c>
+      <c r="C484">
+        <v>3</v>
+      </c>
+      <c r="D484" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485" s="2">
+        <v>46111.07291666666</v>
+      </c>
+      <c r="B485">
+        <v>5063</v>
+      </c>
+      <c r="C485">
+        <v>4</v>
+      </c>
+      <c r="D485" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486" s="2">
+        <v>46111.08333333334</v>
+      </c>
+      <c r="B486">
+        <v>5061</v>
+      </c>
+      <c r="C486">
+        <v>5</v>
+      </c>
+      <c r="D486" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487" s="2">
+        <v>46111.09375</v>
+      </c>
+      <c r="B487">
+        <v>5003</v>
+      </c>
+      <c r="C487">
+        <v>6</v>
+      </c>
+      <c r="D487" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488" s="2">
+        <v>46111.10416666666</v>
+      </c>
+      <c r="B488">
+        <v>4984</v>
+      </c>
+      <c r="C488">
+        <v>7</v>
+      </c>
+      <c r="D488" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489" s="2">
+        <v>46111.11458333334</v>
+      </c>
+      <c r="B489">
+        <v>5006</v>
+      </c>
+      <c r="C489">
+        <v>8</v>
+      </c>
+      <c r="D489" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490" s="2">
+        <v>46111.125</v>
+      </c>
+      <c r="B490">
+        <v>5024</v>
+      </c>
+      <c r="C490">
+        <v>9</v>
+      </c>
+      <c r="D490" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" s="2">
+        <v>46111.13541666666</v>
+      </c>
+      <c r="B491">
+        <v>5043</v>
+      </c>
+      <c r="C491">
+        <v>10</v>
+      </c>
+      <c r="D491" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" s="2">
+        <v>46111.14583333334</v>
+      </c>
+      <c r="B492">
+        <v>5012</v>
+      </c>
+      <c r="C492">
+        <v>11</v>
+      </c>
+      <c r="D492" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" s="2">
+        <v>46111.15625</v>
+      </c>
+      <c r="B493">
+        <v>5041</v>
+      </c>
+      <c r="C493">
+        <v>12</v>
+      </c>
+      <c r="D493" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494" s="2">
+        <v>46111.16666666666</v>
+      </c>
+      <c r="B494">
+        <v>5147</v>
+      </c>
+      <c r="C494">
+        <v>13</v>
+      </c>
+      <c r="D494" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495" s="2">
+        <v>46111.17708333334</v>
+      </c>
+      <c r="B495">
+        <v>5229</v>
+      </c>
+      <c r="C495">
+        <v>14</v>
+      </c>
+      <c r="D495" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" s="2">
+        <v>46111.1875</v>
+      </c>
+      <c r="B496">
+        <v>5348</v>
+      </c>
+      <c r="C496">
+        <v>15</v>
+      </c>
+      <c r="D496" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" s="2">
+        <v>46111.19791666666</v>
+      </c>
+      <c r="B497">
+        <v>5447</v>
+      </c>
+      <c r="C497">
+        <v>16</v>
+      </c>
+      <c r="D497" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" s="2">
+        <v>46111.20833333334</v>
+      </c>
+      <c r="B498">
+        <v>5600</v>
+      </c>
+      <c r="C498">
+        <v>17</v>
+      </c>
+      <c r="D498" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" s="2">
+        <v>46111.21875</v>
+      </c>
+      <c r="B499">
+        <v>5810</v>
+      </c>
+      <c r="C499">
+        <v>18</v>
+      </c>
+      <c r="D499" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" s="2">
+        <v>46111.22916666666</v>
+      </c>
+      <c r="B500">
+        <v>5954</v>
+      </c>
+      <c r="C500">
+        <v>19</v>
+      </c>
+      <c r="D500" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501" s="2">
+        <v>46111.23958333334</v>
+      </c>
+      <c r="B501">
+        <v>6162</v>
+      </c>
+      <c r="C501">
+        <v>20</v>
+      </c>
+      <c r="D501" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502" s="2">
+        <v>46111.25</v>
+      </c>
+      <c r="B502">
+        <v>6409</v>
+      </c>
+      <c r="C502">
+        <v>21</v>
+      </c>
+      <c r="D502" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" s="2">
+        <v>46111.26041666666</v>
+      </c>
+      <c r="B503">
+        <v>6592</v>
+      </c>
+      <c r="C503">
+        <v>22</v>
+      </c>
+      <c r="D503" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" s="2">
+        <v>46111.27083333334</v>
+      </c>
+      <c r="B504">
+        <v>6724</v>
+      </c>
+      <c r="C504">
+        <v>23</v>
+      </c>
+      <c r="D504" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" s="2">
+        <v>46111.28125</v>
+      </c>
+      <c r="B505">
+        <v>6881</v>
+      </c>
+      <c r="C505">
+        <v>24</v>
+      </c>
+      <c r="D505" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" s="2">
+        <v>46111.29166666666</v>
+      </c>
+      <c r="B506">
+        <v>7090</v>
+      </c>
+      <c r="C506">
+        <v>25</v>
+      </c>
+      <c r="D506" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" s="2">
+        <v>46111.30208333334</v>
+      </c>
+      <c r="B507">
+        <v>0</v>
+      </c>
+      <c r="C507">
+        <v>26</v>
+      </c>
+      <c r="D507" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" s="2">
+        <v>46111.3125</v>
+      </c>
+      <c r="B508">
+        <v>0</v>
+      </c>
+      <c r="C508">
+        <v>27</v>
+      </c>
+      <c r="D508" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" s="2">
+        <v>46111.32291666666</v>
+      </c>
+      <c r="B509">
+        <v>0</v>
+      </c>
+      <c r="C509">
+        <v>28</v>
+      </c>
+      <c r="D509" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="2">
+        <v>46111.33333333334</v>
+      </c>
+      <c r="B510">
+        <v>0</v>
+      </c>
+      <c r="C510">
+        <v>29</v>
+      </c>
+      <c r="D510" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" s="2">
+        <v>46111.34375</v>
+      </c>
+      <c r="B511">
+        <v>0</v>
+      </c>
+      <c r="C511">
+        <v>30</v>
+      </c>
+      <c r="D511" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" s="2">
+        <v>46111.35416666666</v>
+      </c>
+      <c r="B512">
+        <v>0</v>
+      </c>
+      <c r="C512">
+        <v>31</v>
+      </c>
+      <c r="D512" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" s="2">
+        <v>46111.36458333334</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
+      </c>
+      <c r="C513">
+        <v>32</v>
+      </c>
+      <c r="D513" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" s="2">
+        <v>46111.375</v>
+      </c>
+      <c r="B514">
+        <v>0</v>
+      </c>
+      <c r="C514">
+        <v>33</v>
+      </c>
+      <c r="D514" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" s="2">
+        <v>46111.38541666666</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+      <c r="C515">
+        <v>34</v>
+      </c>
+      <c r="D515" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" s="2">
+        <v>46111.39583333334</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+      <c r="C516">
+        <v>35</v>
+      </c>
+      <c r="D516" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" s="2">
+        <v>46111.40625</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+      <c r="C517">
+        <v>36</v>
+      </c>
+      <c r="D517" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" s="2">
+        <v>46111.41666666666</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+      <c r="C518">
+        <v>37</v>
+      </c>
+      <c r="D518" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" s="2">
+        <v>46111.42708333334</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+      <c r="C519">
+        <v>38</v>
+      </c>
+      <c r="D519" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" s="2">
+        <v>46111.4375</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+      <c r="C520">
+        <v>39</v>
+      </c>
+      <c r="D520" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" s="2">
+        <v>46111.44791666666</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+      <c r="C521">
+        <v>40</v>
+      </c>
+      <c r="D521" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" s="2">
+        <v>46111.45833333334</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+      <c r="C522">
+        <v>41</v>
+      </c>
+      <c r="D522" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" s="2">
+        <v>46111.46875</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+      <c r="C523">
+        <v>42</v>
+      </c>
+      <c r="D523" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" s="2">
+        <v>46111.47916666666</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+      <c r="C524">
+        <v>43</v>
+      </c>
+      <c r="D524" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" s="2">
+        <v>46111.48958333334</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+      <c r="C525">
+        <v>44</v>
+      </c>
+      <c r="D525" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" s="2">
+        <v>46111.5</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+      <c r="C526">
+        <v>45</v>
+      </c>
+      <c r="D526" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" s="2">
+        <v>46111.51041666666</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+      <c r="C527">
+        <v>46</v>
+      </c>
+      <c r="D527" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" s="2">
+        <v>46111.52083333334</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+      <c r="C528">
+        <v>47</v>
+      </c>
+      <c r="D528" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4">
+      <c r="A529" s="2">
+        <v>46111.53125</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+      <c r="C529">
+        <v>48</v>
+      </c>
+      <c r="D529" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
+      <c r="A530" s="2">
+        <v>46111.54166666666</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+      <c r="C530">
+        <v>49</v>
+      </c>
+      <c r="D530" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
+      <c r="A531" s="2">
+        <v>46111.55208333334</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+      <c r="C531">
+        <v>50</v>
+      </c>
+      <c r="D531" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
+      <c r="A532" s="2">
+        <v>46111.5625</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+      <c r="C532">
+        <v>51</v>
+      </c>
+      <c r="D532" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
+      <c r="A533" s="2">
+        <v>46111.57291666666</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+      <c r="C533">
+        <v>52</v>
+      </c>
+      <c r="D533" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
+      <c r="A534" s="2">
+        <v>46111.58333333334</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+      <c r="C534">
+        <v>53</v>
+      </c>
+      <c r="D534" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
+      <c r="A535" s="2">
+        <v>46111.59375</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+      <c r="C535">
+        <v>54</v>
+      </c>
+      <c r="D535" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
+      <c r="A536" s="2">
+        <v>46111.60416666666</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+      <c r="C536">
+        <v>55</v>
+      </c>
+      <c r="D536" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
+      <c r="A537" s="2">
+        <v>46111.61458333334</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+      <c r="C537">
+        <v>56</v>
+      </c>
+      <c r="D537" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
+      <c r="A538" s="2">
+        <v>46111.625</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+      <c r="C538">
+        <v>57</v>
+      </c>
+      <c r="D538" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
+      <c r="A539" s="2">
+        <v>46111.63541666666</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+      <c r="C539">
+        <v>58</v>
+      </c>
+      <c r="D539" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4">
+      <c r="A540" s="2">
+        <v>46111.64583333334</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+      <c r="C540">
+        <v>59</v>
+      </c>
+      <c r="D540" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
+      <c r="A541" s="2">
+        <v>46111.65625</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+      <c r="C541">
+        <v>60</v>
+      </c>
+      <c r="D541" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
+      <c r="A542" s="2">
+        <v>46111.66666666666</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+      <c r="C542">
+        <v>61</v>
+      </c>
+      <c r="D542" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
+      <c r="A543" s="2">
+        <v>46111.67708333334</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+      <c r="C543">
+        <v>62</v>
+      </c>
+      <c r="D543" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
+      <c r="A544" s="2">
+        <v>46111.6875</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+      <c r="C544">
+        <v>63</v>
+      </c>
+      <c r="D544" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4">
+      <c r="A545" s="2">
+        <v>46111.69791666666</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+      <c r="C545">
+        <v>64</v>
+      </c>
+      <c r="D545" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
+      <c r="A546" s="2">
+        <v>46111.70833333334</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+      <c r="C546">
+        <v>65</v>
+      </c>
+      <c r="D546" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4">
+      <c r="A547" s="2">
+        <v>46111.71875</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+      <c r="C547">
+        <v>66</v>
+      </c>
+      <c r="D547" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4">
+      <c r="A548" s="2">
+        <v>46111.72916666666</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+      <c r="C548">
+        <v>67</v>
+      </c>
+      <c r="D548" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
+      <c r="A549" s="2">
+        <v>46111.73958333334</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+      <c r="C549">
+        <v>68</v>
+      </c>
+      <c r="D549" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
+      <c r="A550" s="2">
+        <v>46111.75</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+      <c r="C550">
+        <v>69</v>
+      </c>
+      <c r="D550" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
+      <c r="A551" s="2">
+        <v>46111.76041666666</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+      <c r="C551">
+        <v>70</v>
+      </c>
+      <c r="D551" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
+      <c r="A552" s="2">
+        <v>46111.77083333334</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+      <c r="C552">
+        <v>71</v>
+      </c>
+      <c r="D552" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4">
+      <c r="A553" s="2">
+        <v>46111.78125</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+      <c r="C553">
+        <v>72</v>
+      </c>
+      <c r="D553" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4">
+      <c r="A554" s="2">
+        <v>46111.79166666666</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+      <c r="C554">
+        <v>73</v>
+      </c>
+      <c r="D554" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
+      <c r="A555" s="2">
+        <v>46111.80208333334</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+      <c r="C555">
+        <v>74</v>
+      </c>
+      <c r="D555" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4">
+      <c r="A556" s="2">
+        <v>46111.8125</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+      <c r="C556">
+        <v>75</v>
+      </c>
+      <c r="D556" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4">
+      <c r="A557" s="2">
+        <v>46111.82291666666</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+      <c r="C557">
+        <v>76</v>
+      </c>
+      <c r="D557" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
+      <c r="A558" s="2">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+      <c r="C558">
+        <v>77</v>
+      </c>
+      <c r="D558" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
+      <c r="A559" s="2">
+        <v>46111.84375</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+      <c r="C559">
+        <v>78</v>
+      </c>
+      <c r="D559" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4">
+      <c r="A560" s="2">
+        <v>46111.85416666666</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+      <c r="C560">
+        <v>79</v>
+      </c>
+      <c r="D560" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4">
+      <c r="A561" s="2">
+        <v>46111.86458333334</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+      <c r="C561">
+        <v>80</v>
+      </c>
+      <c r="D561" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4">
+      <c r="A562" s="2">
+        <v>46111.875</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+      <c r="C562">
+        <v>81</v>
+      </c>
+      <c r="D562" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
+      <c r="A563" s="2">
+        <v>46111.88541666666</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+      <c r="C563">
+        <v>82</v>
+      </c>
+      <c r="D563" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4">
+      <c r="A564" s="2">
+        <v>46111.89583333334</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+      <c r="C564">
+        <v>83</v>
+      </c>
+      <c r="D564" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4">
+      <c r="A565" s="2">
+        <v>46111.90625</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+      <c r="C565">
+        <v>84</v>
+      </c>
+      <c r="D565" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
+      <c r="A566" s="2">
+        <v>46111.91666666666</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+      <c r="C566">
+        <v>85</v>
+      </c>
+      <c r="D566" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
+      <c r="A567" s="2">
+        <v>46111.92708333334</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+      <c r="C567">
+        <v>86</v>
+      </c>
+      <c r="D567" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" s="2">
+        <v>46111.9375</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+      <c r="C568">
+        <v>87</v>
+      </c>
+      <c r="D568" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" s="2">
+        <v>46111.94791666666</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+      <c r="C569">
+        <v>88</v>
+      </c>
+      <c r="D569" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" s="2">
+        <v>46111.95833333334</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+      <c r="C570">
+        <v>89</v>
+      </c>
+      <c r="D570" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" s="2">
+        <v>46111.96875</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+      <c r="C571">
+        <v>90</v>
+      </c>
+      <c r="D571" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" s="2">
+        <v>46111.97916666666</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+      <c r="C572">
+        <v>91</v>
+      </c>
+      <c r="D572" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" s="2">
+        <v>46111.98958333334</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+      <c r="C573">
+        <v>92</v>
+      </c>
+      <c r="D573" t="s">
+        <v>575</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>09.04.202694</t>
-  </si>
-  <si>
-    <t>09.04.202695</t>
-  </si>
-  <si>
-    <t>09.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>16.04.202694</t>
+  </si>
+  <si>
+    <t>16.04.202695</t>
+  </si>
+  <si>
+    <t>16.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
-        <v>5454</v>
+        <v>5313</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
-        <v>5423</v>
+        <v>5241</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
-        <v>5395</v>
+        <v>5160</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
-        <v>5351</v>
+        <v>5179</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
-        <v>5390</v>
+        <v>5160</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
-        <v>5392</v>
+        <v>5166</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
-        <v>5362</v>
+        <v>5106</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
-        <v>5351</v>
+        <v>5126</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
-        <v>5312</v>
+        <v>5160</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
-        <v>5274</v>
+        <v>5167</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
-        <v>5243</v>
+        <v>5130</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
-        <v>5322</v>
+        <v>5089</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
-        <v>5300</v>
+        <v>5167</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
-        <v>5310</v>
+        <v>5176</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
-        <v>5356</v>
+        <v>5154</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
-        <v>5361</v>
+        <v>5235</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
-        <v>5433</v>
+        <v>5326</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
-        <v>5511</v>
+        <v>5378</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
-        <v>5604</v>
+        <v>5386</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
-        <v>5664</v>
+        <v>5489</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
-        <v>5749</v>
+        <v>5606</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>5797</v>
+        <v>5715</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
-        <v>5909</v>
+        <v>5779</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>6022</v>
+        <v>5891</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>6224</v>
+        <v>6128</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>6329</v>
+        <v>6273</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>6392</v>
+        <v>6297</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>6438</v>
+        <v>6285</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>6522</v>
+        <v>6324</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>6449</v>
+        <v>6296</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>6390</v>
+        <v>6208</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>6321</v>
+        <v>6064</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>6306</v>
+        <v>5977</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>6291</v>
+        <v>5859</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>6275</v>
+        <v>5753</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>6169</v>
+        <v>5539</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>6163</v>
+        <v>5307</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
-        <v>5938</v>
+        <v>5161</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>5840</v>
+        <v>4995</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>5717</v>
+        <v>4871</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>5570</v>
+        <v>4656</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>5585</v>
+        <v>4546</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
-        <v>5578</v>
+        <v>4443</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>5490</v>
+        <v>4340</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>5481</v>
+        <v>4040</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>5635</v>
+        <v>4069</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
-        <v>5604</v>
+        <v>4010</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>5729</v>
+        <v>4003</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>5604</v>
+        <v>4047</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>5628</v>
+        <v>4138</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>5647</v>
+        <v>4022</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>5695</v>
+        <v>4012</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>5677</v>
+        <v>4150</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>5705</v>
+        <v>4182</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>5687</v>
+        <v>4213</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
-        <v>5718</v>
+        <v>4198</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>5772</v>
+        <v>4214</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>5841</v>
+        <v>4316</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>5896</v>
+        <v>4319</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>5968</v>
+        <v>4350</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>5956</v>
+        <v>4595</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>6073</v>
+        <v>4613</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>6063</v>
+        <v>4763</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>6021</v>
+        <v>4883</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
-        <v>6022</v>
+        <v>5107</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>6182</v>
+        <v>5212</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>6165</v>
+        <v>5421</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>6241</v>
+        <v>5479</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>6245</v>
+        <v>5707</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>6391</v>
+        <v>5896</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>6585</v>
+        <v>6040</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>6692</v>
+        <v>6228</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>6736</v>
+        <v>6347</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>6790</v>
+        <v>6525</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>6878</v>
+        <v>6666</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>6999</v>
+        <v>6739</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>7124</v>
+        <v>6885</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>7291</v>
+        <v>7111</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>7319</v>
+        <v>7187</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>7297</v>
+        <v>7223</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>7268</v>
+        <v>7216</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>7165</v>
+        <v>7161</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>7088</v>
+        <v>7026</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>7010</v>
+        <v>6864</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>6864</v>
+        <v>6751</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>6710</v>
+        <v>6617</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>6562</v>
+        <v>6426</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
-        <v>6446</v>
+        <v>6257</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
-        <v>6251</v>
+        <v>6049</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
-        <v>6122</v>
+        <v>5949</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
-        <v>6012</v>
+        <v>5805</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
-        <v>5936</v>
+        <v>5700</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
-        <v>5774</v>
+        <v>5543</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
-        <v>5636</v>
+        <v>5454</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
-        <v>5584</v>
+        <v>5372</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
-        <v>5521</v>
+        <v>5332</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
-        <v>5413</v>
+        <v>5273</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B99">
-        <v>5390</v>
+        <v>5261</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B100">
-        <v>5285</v>
+        <v>5164</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B101">
-        <v>5239</v>
+        <v>5196</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B102">
-        <v>5173</v>
+        <v>5246</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B103">
-        <v>5159</v>
+        <v>5257</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B104">
-        <v>5108</v>
+        <v>5211</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B105">
-        <v>5080</v>
+        <v>5182</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B106">
-        <v>5031</v>
+        <v>5193</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B107">
-        <v>5016</v>
+        <v>5166</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B108">
-        <v>4964</v>
+        <v>5192</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B109">
-        <v>5067</v>
+        <v>5200</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B110">
-        <v>5096</v>
+        <v>5193</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B111">
-        <v>5122</v>
+        <v>5179</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B112">
-        <v>5112</v>
+        <v>5208</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B113">
-        <v>5079</v>
+        <v>5272</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B114">
-        <v>5131</v>
+        <v>5309</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B115">
-        <v>5217</v>
+        <v>5322</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B116">
-        <v>5179</v>
+        <v>5408</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B117">
-        <v>5197</v>
+        <v>5504</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B118">
-        <v>5186</v>
+        <v>5541</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B119">
-        <v>5222</v>
+        <v>5646</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B120">
-        <v>5190</v>
+        <v>5675</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B121">
-        <v>5111</v>
+        <v>5801</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B122">
-        <v>5216</v>
+        <v>6041</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B123">
-        <v>5293</v>
+        <v>6216</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B124">
-        <v>5292</v>
+        <v>6119</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B125">
-        <v>5331</v>
+        <v>6140</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B126">
-        <v>5354</v>
+        <v>5946</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B127">
-        <v>5329</v>
+        <v>6182</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B128">
-        <v>5261</v>
+        <v>6075</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B129">
-        <v>5184</v>
+        <v>6042</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B130">
-        <v>5135</v>
+        <v>5988</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B131">
-        <v>5002</v>
+        <v>5949</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B132">
-        <v>4897</v>
+        <v>5760</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B133">
-        <v>4835</v>
+        <v>5682</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B134">
-        <v>4678</v>
+        <v>5476</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B135">
-        <v>4545</v>
+        <v>5369</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B136">
-        <v>4417</v>
+        <v>5205</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B137">
-        <v>4404</v>
+        <v>5101</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B138">
-        <v>4309</v>
+        <v>4911</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>4801</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>4778</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>4749</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>4798</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>4794</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>4708</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>16.04.202694</t>
-  </si>
-  <si>
-    <t>16.04.202695</t>
-  </si>
-  <si>
-    <t>16.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -602,6 +314,870 @@
   </si>
   <si>
     <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +1558,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
-        <v>5313</v>
+        <v>5273</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +1572,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>5241</v>
+        <v>5261</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1586,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>5160</v>
+        <v>5164</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1600,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>5179</v>
+        <v>5196</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1614,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>5160</v>
+        <v>5246</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1628,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>5166</v>
+        <v>5257</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1642,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>5106</v>
+        <v>5211</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1656,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>5126</v>
+        <v>5182</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1670,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>5160</v>
+        <v>5193</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1684,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>5167</v>
+        <v>5166</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1698,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>5130</v>
+        <v>5192</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1712,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>5089</v>
+        <v>5200</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1726,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>5167</v>
+        <v>5193</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1740,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>5176</v>
+        <v>5179</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1754,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>5154</v>
+        <v>5208</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1768,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>5235</v>
+        <v>5272</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1782,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>5326</v>
+        <v>5309</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1796,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>5378</v>
+        <v>5322</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1810,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>5386</v>
+        <v>5408</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1824,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>5489</v>
+        <v>5504</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1838,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>5606</v>
+        <v>5541</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1852,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>5715</v>
+        <v>5646</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1866,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>5779</v>
+        <v>5675</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1880,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>5891</v>
+        <v>5801</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1894,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>6128</v>
+        <v>6041</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1908,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>6273</v>
+        <v>6216</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1922,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>6297</v>
+        <v>6119</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1936,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>6285</v>
+        <v>6140</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1950,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>6324</v>
+        <v>5946</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1964,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>6296</v>
+        <v>6182</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1978,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>6208</v>
+        <v>6075</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1992,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>6064</v>
+        <v>6042</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +2006,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>5977</v>
+        <v>5988</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +2020,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>5859</v>
+        <v>5949</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +2034,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>5753</v>
+        <v>5760</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +2048,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>5539</v>
+        <v>5682</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +2062,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>5307</v>
+        <v>5476</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +2076,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>5161</v>
+        <v>5369</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +2090,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>4995</v>
+        <v>5205</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +2104,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>4871</v>
+        <v>5101</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +2118,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>4656</v>
+        <v>4911</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +2132,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>4546</v>
+        <v>4801</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +2146,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>4443</v>
+        <v>4778</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +2160,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>4340</v>
+        <v>4749</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +2174,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>4040</v>
+        <v>4798</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +2188,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>4069</v>
+        <v>4794</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +2202,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>4010</v>
+        <v>4708</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +2216,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>4003</v>
+        <v>4700</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +2230,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>4047</v>
+        <v>4727</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +2244,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>4138</v>
+        <v>4509</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +2258,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>4022</v>
+        <v>4594</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +2272,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>4012</v>
+        <v>4549</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +2286,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>4150</v>
+        <v>4482</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +2300,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>4182</v>
+        <v>4343</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +2314,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>4213</v>
+        <v>4421</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +2328,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>4198</v>
+        <v>4470</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +2342,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>4214</v>
+        <v>4306</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +2356,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>4316</v>
+        <v>4365</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +2370,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>4319</v>
+        <v>4478</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +2384,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>4350</v>
+        <v>4614</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +2398,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>4595</v>
+        <v>4520</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +2412,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>4613</v>
+        <v>4683</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +2426,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>4763</v>
+        <v>4842</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +2440,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>4883</v>
+        <v>4923</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +2454,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>5107</v>
+        <v>5086</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +2468,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>5212</v>
+        <v>5241</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +2482,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>5421</v>
+        <v>5455</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +2496,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>5479</v>
+        <v>5545</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +2510,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>5707</v>
+        <v>5758</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +2524,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>5896</v>
+        <v>5804</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +2538,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>6040</v>
+        <v>5981</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +2552,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>6228</v>
+        <v>6063</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +2566,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>6347</v>
+        <v>6194</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2580,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>6525</v>
+        <v>6310</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2594,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>6666</v>
+        <v>6496</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2608,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>6739</v>
+        <v>6573</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2622,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>6885</v>
+        <v>6660</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2636,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>7111</v>
+        <v>6787</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2650,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>7187</v>
+        <v>6933</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2664,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>7223</v>
+        <v>6931</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2678,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>7216</v>
+        <v>6843</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2692,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>7161</v>
+        <v>6841</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2706,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>7026</v>
+        <v>6751</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2720,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>6864</v>
+        <v>6649</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2734,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>6751</v>
+        <v>6424</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2748,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>6617</v>
+        <v>6393</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2762,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>6426</v>
+        <v>6208</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2776,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>6257</v>
+        <v>6078</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2790,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>6049</v>
+        <v>5932</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2804,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>5949</v>
+        <v>5845</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2818,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>5805</v>
+        <v>5702</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2832,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>5700</v>
+        <v>5636</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2846,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>5543</v>
+        <v>5489</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2860,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>5454</v>
+        <v>5434</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2874,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>5372</v>
+        <v>5382</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2888,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>5332</v>
+        <v>5371</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2902,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
-        <v>5273</v>
+        <v>5222</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2916,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B99">
-        <v>5261</v>
+        <v>5180</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2930,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B100">
-        <v>5164</v>
+        <v>5205</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2944,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B101">
-        <v>5196</v>
+        <v>5110</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B102">
-        <v>5246</v>
+        <v>5081</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2972,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B103">
-        <v>5257</v>
+        <v>5024</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2986,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B104">
-        <v>5211</v>
+        <v>5086</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +3000,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B105">
-        <v>5182</v>
+        <v>5062</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +3014,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B106">
-        <v>5193</v>
+        <v>5053</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +3028,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B107">
-        <v>5166</v>
+        <v>5032</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +3042,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B108">
-        <v>5192</v>
+        <v>5039</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +3056,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B109">
-        <v>5200</v>
+        <v>5013</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +3070,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B110">
-        <v>5193</v>
+        <v>5018</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +3084,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B111">
-        <v>5179</v>
+        <v>4995</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +3098,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B112">
-        <v>5208</v>
+        <v>5025</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +3112,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B113">
-        <v>5272</v>
+        <v>4990</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +3126,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B114">
-        <v>5309</v>
+        <v>5043</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +3140,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B115">
-        <v>5322</v>
+        <v>5035</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +3154,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B116">
-        <v>5408</v>
+        <v>5147</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +3168,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B117">
-        <v>5504</v>
+        <v>5153</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +3182,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B118">
-        <v>5541</v>
+        <v>5190</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +3196,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B119">
-        <v>5646</v>
+        <v>5237</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +3210,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B120">
-        <v>5675</v>
+        <v>5224</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +3224,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B121">
-        <v>5801</v>
+        <v>5239</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +3238,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B122">
-        <v>6041</v>
+        <v>5296</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +3252,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B123">
-        <v>6216</v>
+        <v>5308</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +3266,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B124">
-        <v>6119</v>
+        <v>5320</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +3280,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B125">
-        <v>6140</v>
+        <v>5326</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +3294,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B126">
-        <v>5946</v>
+        <v>5369</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +3308,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B127">
-        <v>6182</v>
+        <v>5188</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +3322,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B128">
-        <v>6075</v>
+        <v>5191</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +3336,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B129">
-        <v>6042</v>
+        <v>5089</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +3350,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B130">
-        <v>5988</v>
+        <v>4974</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +3364,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B131">
-        <v>5949</v>
+        <v>4951</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +3378,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B132">
-        <v>5760</v>
+        <v>4805</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +3392,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B133">
-        <v>5682</v>
+        <v>4530</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +3406,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B134">
-        <v>5476</v>
+        <v>4438</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +3420,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B135">
-        <v>5369</v>
+        <v>4347</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +3434,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B136">
-        <v>5205</v>
+        <v>4373</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +3448,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B137">
-        <v>5101</v>
+        <v>4320</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +3462,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B138">
-        <v>4911</v>
+        <v>4183</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +3476,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B139">
-        <v>4801</v>
+        <v>4120</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +3490,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B140">
-        <v>4778</v>
+        <v>4107</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +3504,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B141">
-        <v>4749</v>
+        <v>4016</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +3518,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B142">
-        <v>4798</v>
+        <v>3959</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +3532,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B143">
-        <v>4794</v>
+        <v>3902</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +3546,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B144">
-        <v>4708</v>
+        <v>3870</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +3560,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B145">
-        <v>4700</v>
+        <v>3945</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +3574,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>3892</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3588,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3602,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>3785</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3616,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>3730</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3630,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>3807</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3644,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>3796</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3658,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>3820</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3672,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>3894</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3686,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>4034</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3700,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>4120</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3714,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>4131</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3728,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>4223</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3742,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>4262</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3756,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>4333</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3770,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>4451</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3784,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>4631</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3798,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>4691</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3812,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>4825</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3826,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>5004</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3840,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>5125</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3854,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>5338</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3868,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>5437</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3882,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>5553</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3896,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>5668</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3910,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>5717</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3924,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>5862</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3938,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>5993</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3952,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>6166</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3966,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>6286</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3980,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>6402</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3994,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>6560</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +4008,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>6632</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +4022,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>6642</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +4036,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>6548</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +4050,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>6499</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +4064,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6388</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +4078,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>6203</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +4092,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>6106</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +4106,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>6064</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +4120,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>5981</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +4134,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>5889</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +4148,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5788</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +4162,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>5650</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +4176,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>5554</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +4190,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>5291</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +4204,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>5162</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +4218,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>5123</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +4232,2704 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>5036</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B194">
+        <v>4904</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4939</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4932</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B197">
+        <v>4820</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4757</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4813</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B200">
+        <v>4747</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4771</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4762</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B203">
+        <v>4693</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4680</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4694</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B206">
+        <v>4709</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4702</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4667</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B209">
+        <v>4689</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4711</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4729</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B212">
+        <v>4809</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>4775</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4768</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B215">
+        <v>4800</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>4735</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>4720</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B218">
+        <v>4821</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>4759</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>4738</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B221">
+        <v>4658</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>4581</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>4364</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B224">
+        <v>4235</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>4145</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>3946</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B227">
+        <v>3846</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>3694</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>3587</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B230">
+        <v>3333</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>3304</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3136</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B233">
+        <v>3021</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>2986</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>2892</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B236">
+        <v>2872</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>2865</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>2895</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B239">
+        <v>2839</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>2876</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>2846</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B242">
+        <v>2814</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>2781</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>2836</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B245">
+        <v>2928</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>2876</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>2930</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B248">
+        <v>2987</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>3033</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>2991</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B251">
+        <v>3047</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>3168</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>3270</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B254">
+        <v>3422</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>3475</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>3614</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B257">
+        <v>3690</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>3840</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>3928</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B260">
+        <v>4095</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>4329</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>4637</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B263">
+        <v>4816</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>4990</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>5103</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B266">
+        <v>5158</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>5366</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>5444</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B269">
+        <v>5623</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>5770</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>5909</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B272">
+        <v>6124</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>6123</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>6099</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B275">
+        <v>6132</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>6032</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>5960</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B278">
+        <v>5848</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>5716</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5595</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B281">
+        <v>5526</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5356</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5292</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B284">
+        <v>5165</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>5076</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>5006</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B287">
+        <v>4870</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4841</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4774</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B290">
+        <v>4827</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4752</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4717</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B293">
+        <v>4727</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4706</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B296">
+        <v>4690</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4649</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4636</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B299">
+        <v>4671</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4578</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4572</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B302">
+        <v>4582</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4595</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4676</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B305">
+        <v>4711</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4840</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4858</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5067</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5141</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B311">
+        <v>5344</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5454</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5652</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B314">
+        <v>5846</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>5946</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>6028</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B317">
+        <v>6060</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6135</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>6216</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B320">
+        <v>6192</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>20.04.202694</t>
-  </si>
-  <si>
-    <t>20.04.202695</t>
-  </si>
-  <si>
-    <t>20.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>21.04.202696</t>
+  </si>
+  <si>
+    <t>22.04.20261</t>
+  </si>
+  <si>
+    <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
+    <t>22.04.202695</t>
+  </si>
+  <si>
+    <t>22.04.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>4827</v>
+        <v>5156</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>4752</v>
+        <v>5120</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
-        <v>4717</v>
+        <v>5163</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
-        <v>4727</v>
+        <v>5220</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
-        <v>4706</v>
+        <v>5273</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>5132</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
-        <v>4690</v>
+        <v>5283</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
-        <v>4649</v>
+        <v>5213</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>4636</v>
+        <v>5058</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>4671</v>
+        <v>5141</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>4578</v>
+        <v>5066</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>4572</v>
+        <v>5048</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>4582</v>
+        <v>5025</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>4595</v>
+        <v>5023</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>4676</v>
+        <v>5063</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>4711</v>
+        <v>5104</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>4840</v>
+        <v>5131</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>4858</v>
+        <v>5221</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>5304</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>5067</v>
+        <v>5353</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>5141</v>
+        <v>5556</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>5344</v>
+        <v>5629</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>5454</v>
+        <v>5691</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>5652</v>
+        <v>5823</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>5846</v>
+        <v>6057</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>5946</v>
+        <v>6215</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>6028</v>
+        <v>6269</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>6060</v>
+        <v>6321</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>6135</v>
+        <v>6391</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>6216</v>
+        <v>6497</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>6192</v>
+        <v>6474</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>6058</v>
+        <v>6434</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>6015</v>
+        <v>6480</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>5966</v>
+        <v>6371</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>5875</v>
+        <v>6332</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>5770</v>
+        <v>6222</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>5498</v>
+        <v>6108</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>5423</v>
+        <v>6068</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>5366</v>
+        <v>5930</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>5295</v>
+        <v>5848</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>5258</v>
+        <v>5745</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>5057</v>
+        <v>5764</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>4990</v>
+        <v>5737</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>4967</v>
+        <v>5702</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>5015</v>
+        <v>5713</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>5029</v>
+        <v>5825</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>5134</v>
+        <v>5832</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>5128</v>
+        <v>5943</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>5053</v>
+        <v>5831</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>5065</v>
+        <v>5882</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>4999</v>
+        <v>5867</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>5053</v>
+        <v>5874</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>5159</v>
+        <v>5752</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>5151</v>
+        <v>5698</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>4971</v>
+        <v>5708</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>4981</v>
+        <v>5756</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>5067</v>
+        <v>5900</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>5140</v>
+        <v>5872</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>5187</v>
+        <v>5809</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>5292</v>
+        <v>5720</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>5330</v>
+        <v>5848</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>5388</v>
+        <v>5959</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>5490</v>
+        <v>5993</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>5663</v>
+        <v>6006</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>5756</v>
+        <v>6165</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>5904</v>
+        <v>6197</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>6002</v>
+        <v>6346</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>6043</v>
+        <v>6309</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>6121</v>
+        <v>6404</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>6268</v>
+        <v>6576</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>6359</v>
+        <v>6648</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>6550</v>
+        <v>6694</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>6656</v>
+        <v>6838</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>6822</v>
+        <v>6904</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>6919</v>
+        <v>7049</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>6879</v>
+        <v>7086</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>6973</v>
+        <v>7193</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>7074</v>
+        <v>7325</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>7131</v>
+        <v>7347</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>7067</v>
+        <v>7247</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>6974</v>
+        <v>7201</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>6886</v>
+        <v>7057</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>6758</v>
+        <v>6914</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>6543</v>
+        <v>6779</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>6405</v>
+        <v>6580</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>6425</v>
+        <v>6413</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>6313</v>
+        <v>6297</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>6192</v>
+        <v>6169</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>5957</v>
+        <v>6067</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>5778</v>
+        <v>5957</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>5666</v>
+        <v>5824</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>5466</v>
+        <v>5734</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>5363</v>
+        <v>5656</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>5313</v>
+        <v>5618</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>5265</v>
+        <v>5516</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
-        <v>5156</v>
+        <v>5438</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B99">
-        <v>5120</v>
+        <v>5392</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B100">
-        <v>5163</v>
+        <v>5358</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B101">
-        <v>5220</v>
+        <v>5296</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B102">
-        <v>5273</v>
+        <v>5303</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B103">
-        <v>5132</v>
+        <v>5319</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B104">
-        <v>5283</v>
+        <v>5306</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B105">
-        <v>5213</v>
+        <v>5328</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B106">
-        <v>5058</v>
+        <v>5336</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B107">
-        <v>5141</v>
+        <v>5282</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B108">
-        <v>5066</v>
+        <v>5288</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B109">
-        <v>5048</v>
+        <v>5312</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B110">
-        <v>5025</v>
+        <v>5316</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B111">
-        <v>5023</v>
+        <v>5325</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B112">
-        <v>5063</v>
+        <v>5341</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B113">
-        <v>5104</v>
+        <v>5397</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B114">
-        <v>5131</v>
+        <v>5558</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B115">
-        <v>5221</v>
+        <v>5597</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B116">
-        <v>5304</v>
+        <v>5656</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B117">
-        <v>5353</v>
+        <v>5703</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B118">
-        <v>5556</v>
+        <v>5801</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B119">
-        <v>5629</v>
+        <v>5848</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B120">
-        <v>5691</v>
+        <v>5977</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B121">
-        <v>5823</v>
+        <v>6097</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B122">
-        <v>6057</v>
+        <v>6287</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B123">
-        <v>6215</v>
+        <v>6467</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B124">
-        <v>6269</v>
+        <v>6531</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B125">
-        <v>6321</v>
+        <v>6504</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B126">
-        <v>6391</v>
+        <v>6521</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B127">
-        <v>6497</v>
+        <v>6574</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B128">
-        <v>6474</v>
+        <v>6504</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>6442</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>6305</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>6319</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>6197</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>6152</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>5932</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>5855</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>5754</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>5625</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>5499</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,580 +28,1156 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.04.20261</t>
-  </si>
-  <si>
-    <t>21.04.20262</t>
-  </si>
-  <si>
-    <t>21.04.20263</t>
-  </si>
-  <si>
-    <t>21.04.20264</t>
-  </si>
-  <si>
-    <t>21.04.20265</t>
-  </si>
-  <si>
-    <t>21.04.20266</t>
-  </si>
-  <si>
-    <t>21.04.20267</t>
-  </si>
-  <si>
-    <t>21.04.20268</t>
-  </si>
-  <si>
-    <t>21.04.20269</t>
-  </si>
-  <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>21.04.202625</t>
-  </si>
-  <si>
-    <t>21.04.202626</t>
-  </si>
-  <si>
-    <t>21.04.202627</t>
-  </si>
-  <si>
-    <t>21.04.202628</t>
-  </si>
-  <si>
-    <t>21.04.202629</t>
-  </si>
-  <si>
-    <t>21.04.202630</t>
-  </si>
-  <si>
-    <t>21.04.202631</t>
-  </si>
-  <si>
-    <t>21.04.202632</t>
-  </si>
-  <si>
-    <t>21.04.202633</t>
-  </si>
-  <si>
-    <t>21.04.202634</t>
-  </si>
-  <si>
-    <t>21.04.202635</t>
-  </si>
-  <si>
-    <t>21.04.202636</t>
-  </si>
-  <si>
-    <t>21.04.202637</t>
-  </si>
-  <si>
-    <t>21.04.202638</t>
-  </si>
-  <si>
-    <t>21.04.202639</t>
-  </si>
-  <si>
-    <t>21.04.202640</t>
-  </si>
-  <si>
-    <t>21.04.202641</t>
-  </si>
-  <si>
-    <t>21.04.202642</t>
-  </si>
-  <si>
-    <t>21.04.202643</t>
-  </si>
-  <si>
-    <t>21.04.202644</t>
-  </si>
-  <si>
-    <t>21.04.202645</t>
-  </si>
-  <si>
-    <t>21.04.202646</t>
-  </si>
-  <si>
-    <t>21.04.202647</t>
-  </si>
-  <si>
-    <t>21.04.202648</t>
-  </si>
-  <si>
-    <t>21.04.202649</t>
-  </si>
-  <si>
-    <t>21.04.202650</t>
-  </si>
-  <si>
-    <t>21.04.202651</t>
-  </si>
-  <si>
-    <t>21.04.202652</t>
-  </si>
-  <si>
-    <t>21.04.202653</t>
-  </si>
-  <si>
-    <t>21.04.202654</t>
-  </si>
-  <si>
-    <t>21.04.202655</t>
-  </si>
-  <si>
-    <t>21.04.202656</t>
-  </si>
-  <si>
-    <t>21.04.202657</t>
-  </si>
-  <si>
-    <t>21.04.202658</t>
-  </si>
-  <si>
-    <t>21.04.202659</t>
-  </si>
-  <si>
-    <t>21.04.202660</t>
-  </si>
-  <si>
-    <t>21.04.202661</t>
-  </si>
-  <si>
-    <t>21.04.202662</t>
-  </si>
-  <si>
-    <t>21.04.202663</t>
-  </si>
-  <si>
-    <t>21.04.202664</t>
-  </si>
-  <si>
-    <t>21.04.202665</t>
-  </si>
-  <si>
-    <t>21.04.202666</t>
-  </si>
-  <si>
-    <t>21.04.202667</t>
-  </si>
-  <si>
-    <t>21.04.202668</t>
-  </si>
-  <si>
-    <t>21.04.202669</t>
-  </si>
-  <si>
-    <t>21.04.202670</t>
-  </si>
-  <si>
-    <t>21.04.202671</t>
-  </si>
-  <si>
-    <t>21.04.202672</t>
-  </si>
-  <si>
-    <t>21.04.202673</t>
-  </si>
-  <si>
-    <t>21.04.202674</t>
-  </si>
-  <si>
-    <t>21.04.202675</t>
-  </si>
-  <si>
-    <t>21.04.202676</t>
-  </si>
-  <si>
-    <t>21.04.202677</t>
-  </si>
-  <si>
-    <t>21.04.202678</t>
-  </si>
-  <si>
-    <t>21.04.202679</t>
-  </si>
-  <si>
-    <t>21.04.202680</t>
-  </si>
-  <si>
-    <t>21.04.202681</t>
-  </si>
-  <si>
-    <t>21.04.202682</t>
-  </si>
-  <si>
-    <t>21.04.202683</t>
-  </si>
-  <si>
-    <t>21.04.202684</t>
-  </si>
-  <si>
-    <t>21.04.202685</t>
-  </si>
-  <si>
-    <t>21.04.202686</t>
-  </si>
-  <si>
-    <t>21.04.202687</t>
-  </si>
-  <si>
-    <t>21.04.202688</t>
-  </si>
-  <si>
-    <t>21.04.202689</t>
-  </si>
-  <si>
-    <t>21.04.202690</t>
-  </si>
-  <si>
-    <t>21.04.202691</t>
-  </si>
-  <si>
-    <t>21.04.202692</t>
-  </si>
-  <si>
-    <t>21.04.202693</t>
-  </si>
-  <si>
-    <t>21.04.202694</t>
-  </si>
-  <si>
-    <t>21.04.202695</t>
-  </si>
-  <si>
-    <t>21.04.202696</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.202625</t>
-  </si>
-  <si>
-    <t>22.04.202626</t>
-  </si>
-  <si>
-    <t>22.04.202627</t>
-  </si>
-  <si>
-    <t>22.04.202628</t>
-  </si>
-  <si>
-    <t>22.04.202629</t>
-  </si>
-  <si>
-    <t>22.04.202630</t>
-  </si>
-  <si>
-    <t>22.04.202631</t>
-  </si>
-  <si>
-    <t>22.04.202632</t>
-  </si>
-  <si>
-    <t>22.04.202633</t>
-  </si>
-  <si>
-    <t>22.04.202634</t>
-  </si>
-  <si>
-    <t>22.04.202635</t>
-  </si>
-  <si>
-    <t>22.04.202636</t>
-  </si>
-  <si>
-    <t>22.04.202637</t>
-  </si>
-  <si>
-    <t>22.04.202638</t>
-  </si>
-  <si>
-    <t>22.04.202639</t>
-  </si>
-  <si>
-    <t>22.04.202640</t>
-  </si>
-  <si>
-    <t>22.04.202641</t>
-  </si>
-  <si>
-    <t>22.04.202642</t>
-  </si>
-  <si>
-    <t>22.04.202643</t>
-  </si>
-  <si>
-    <t>22.04.202644</t>
-  </si>
-  <si>
-    <t>22.04.202645</t>
-  </si>
-  <si>
-    <t>22.04.202646</t>
-  </si>
-  <si>
-    <t>22.04.202647</t>
-  </si>
-  <si>
-    <t>22.04.202648</t>
-  </si>
-  <si>
-    <t>22.04.202649</t>
-  </si>
-  <si>
-    <t>22.04.202650</t>
-  </si>
-  <si>
-    <t>22.04.202651</t>
-  </si>
-  <si>
-    <t>22.04.202652</t>
-  </si>
-  <si>
-    <t>22.04.202653</t>
-  </si>
-  <si>
-    <t>22.04.202654</t>
-  </si>
-  <si>
-    <t>22.04.202655</t>
-  </si>
-  <si>
-    <t>22.04.202656</t>
-  </si>
-  <si>
-    <t>22.04.202657</t>
-  </si>
-  <si>
-    <t>22.04.202658</t>
-  </si>
-  <si>
-    <t>22.04.202659</t>
-  </si>
-  <si>
-    <t>22.04.202660</t>
-  </si>
-  <si>
-    <t>22.04.202661</t>
-  </si>
-  <si>
-    <t>22.04.202662</t>
-  </si>
-  <si>
-    <t>22.04.202663</t>
-  </si>
-  <si>
-    <t>22.04.202664</t>
-  </si>
-  <si>
-    <t>22.04.202665</t>
-  </si>
-  <si>
-    <t>22.04.202666</t>
-  </si>
-  <si>
-    <t>22.04.202667</t>
-  </si>
-  <si>
-    <t>22.04.202668</t>
-  </si>
-  <si>
-    <t>22.04.202669</t>
-  </si>
-  <si>
-    <t>22.04.202670</t>
-  </si>
-  <si>
-    <t>22.04.202671</t>
-  </si>
-  <si>
-    <t>22.04.202672</t>
-  </si>
-  <si>
-    <t>22.04.202673</t>
-  </si>
-  <si>
-    <t>22.04.202674</t>
-  </si>
-  <si>
-    <t>22.04.202675</t>
-  </si>
-  <si>
-    <t>22.04.202676</t>
-  </si>
-  <si>
-    <t>22.04.202677</t>
-  </si>
-  <si>
-    <t>22.04.202678</t>
-  </si>
-  <si>
-    <t>22.04.202679</t>
-  </si>
-  <si>
-    <t>22.04.202680</t>
-  </si>
-  <si>
-    <t>22.04.202681</t>
-  </si>
-  <si>
-    <t>22.04.202682</t>
-  </si>
-  <si>
-    <t>22.04.202683</t>
-  </si>
-  <si>
-    <t>22.04.202684</t>
-  </si>
-  <si>
-    <t>22.04.202685</t>
-  </si>
-  <si>
-    <t>22.04.202686</t>
-  </si>
-  <si>
-    <t>22.04.202687</t>
-  </si>
-  <si>
-    <t>22.04.202688</t>
-  </si>
-  <si>
-    <t>22.04.202689</t>
-  </si>
-  <si>
-    <t>22.04.202690</t>
-  </si>
-  <si>
-    <t>22.04.202691</t>
-  </si>
-  <si>
-    <t>22.04.202692</t>
-  </si>
-  <si>
-    <t>22.04.202693</t>
-  </si>
-  <si>
-    <t>22.04.202694</t>
-  </si>
-  <si>
-    <t>22.04.202695</t>
-  </si>
-  <si>
-    <t>22.04.202696</t>
+    <t>24.04.20261</t>
+  </si>
+  <si>
+    <t>24.04.20262</t>
+  </si>
+  <si>
+    <t>24.04.20263</t>
+  </si>
+  <si>
+    <t>24.04.20264</t>
+  </si>
+  <si>
+    <t>24.04.20265</t>
+  </si>
+  <si>
+    <t>24.04.20266</t>
+  </si>
+  <si>
+    <t>24.04.20267</t>
+  </si>
+  <si>
+    <t>24.04.20268</t>
+  </si>
+  <si>
+    <t>24.04.20269</t>
+  </si>
+  <si>
+    <t>24.04.202610</t>
+  </si>
+  <si>
+    <t>24.04.202611</t>
+  </si>
+  <si>
+    <t>24.04.202612</t>
+  </si>
+  <si>
+    <t>24.04.202613</t>
+  </si>
+  <si>
+    <t>24.04.202614</t>
+  </si>
+  <si>
+    <t>24.04.202615</t>
+  </si>
+  <si>
+    <t>24.04.202616</t>
+  </si>
+  <si>
+    <t>24.04.202617</t>
+  </si>
+  <si>
+    <t>24.04.202618</t>
+  </si>
+  <si>
+    <t>24.04.202619</t>
+  </si>
+  <si>
+    <t>24.04.202620</t>
+  </si>
+  <si>
+    <t>24.04.202621</t>
+  </si>
+  <si>
+    <t>24.04.202622</t>
+  </si>
+  <si>
+    <t>24.04.202623</t>
+  </si>
+  <si>
+    <t>24.04.202624</t>
+  </si>
+  <si>
+    <t>24.04.202625</t>
+  </si>
+  <si>
+    <t>24.04.202626</t>
+  </si>
+  <si>
+    <t>24.04.202627</t>
+  </si>
+  <si>
+    <t>24.04.202628</t>
+  </si>
+  <si>
+    <t>24.04.202629</t>
+  </si>
+  <si>
+    <t>24.04.202630</t>
+  </si>
+  <si>
+    <t>24.04.202631</t>
+  </si>
+  <si>
+    <t>24.04.202632</t>
+  </si>
+  <si>
+    <t>24.04.202633</t>
+  </si>
+  <si>
+    <t>24.04.202634</t>
+  </si>
+  <si>
+    <t>24.04.202635</t>
+  </si>
+  <si>
+    <t>24.04.202636</t>
+  </si>
+  <si>
+    <t>24.04.202637</t>
+  </si>
+  <si>
+    <t>24.04.202638</t>
+  </si>
+  <si>
+    <t>24.04.202639</t>
+  </si>
+  <si>
+    <t>24.04.202640</t>
+  </si>
+  <si>
+    <t>24.04.202641</t>
+  </si>
+  <si>
+    <t>24.04.202642</t>
+  </si>
+  <si>
+    <t>24.04.202643</t>
+  </si>
+  <si>
+    <t>24.04.202644</t>
+  </si>
+  <si>
+    <t>24.04.202645</t>
+  </si>
+  <si>
+    <t>24.04.202646</t>
+  </si>
+  <si>
+    <t>24.04.202647</t>
+  </si>
+  <si>
+    <t>24.04.202648</t>
+  </si>
+  <si>
+    <t>24.04.202649</t>
+  </si>
+  <si>
+    <t>24.04.202650</t>
+  </si>
+  <si>
+    <t>24.04.202651</t>
+  </si>
+  <si>
+    <t>24.04.202652</t>
+  </si>
+  <si>
+    <t>24.04.202653</t>
+  </si>
+  <si>
+    <t>24.04.202654</t>
+  </si>
+  <si>
+    <t>24.04.202655</t>
+  </si>
+  <si>
+    <t>24.04.202656</t>
+  </si>
+  <si>
+    <t>24.04.202657</t>
+  </si>
+  <si>
+    <t>24.04.202658</t>
+  </si>
+  <si>
+    <t>24.04.202659</t>
+  </si>
+  <si>
+    <t>24.04.202660</t>
+  </si>
+  <si>
+    <t>24.04.202661</t>
+  </si>
+  <si>
+    <t>24.04.202662</t>
+  </si>
+  <si>
+    <t>24.04.202663</t>
+  </si>
+  <si>
+    <t>24.04.202664</t>
+  </si>
+  <si>
+    <t>24.04.202665</t>
+  </si>
+  <si>
+    <t>24.04.202666</t>
+  </si>
+  <si>
+    <t>24.04.202667</t>
+  </si>
+  <si>
+    <t>24.04.202668</t>
+  </si>
+  <si>
+    <t>24.04.202669</t>
+  </si>
+  <si>
+    <t>24.04.202670</t>
+  </si>
+  <si>
+    <t>24.04.202671</t>
+  </si>
+  <si>
+    <t>24.04.202672</t>
+  </si>
+  <si>
+    <t>24.04.202673</t>
+  </si>
+  <si>
+    <t>24.04.202674</t>
+  </si>
+  <si>
+    <t>24.04.202675</t>
+  </si>
+  <si>
+    <t>24.04.202676</t>
+  </si>
+  <si>
+    <t>24.04.202677</t>
+  </si>
+  <si>
+    <t>24.04.202678</t>
+  </si>
+  <si>
+    <t>24.04.202679</t>
+  </si>
+  <si>
+    <t>24.04.202680</t>
+  </si>
+  <si>
+    <t>24.04.202681</t>
+  </si>
+  <si>
+    <t>24.04.202682</t>
+  </si>
+  <si>
+    <t>24.04.202683</t>
+  </si>
+  <si>
+    <t>24.04.202684</t>
+  </si>
+  <si>
+    <t>24.04.202685</t>
+  </si>
+  <si>
+    <t>24.04.202686</t>
+  </si>
+  <si>
+    <t>24.04.202687</t>
+  </si>
+  <si>
+    <t>24.04.202688</t>
+  </si>
+  <si>
+    <t>24.04.202689</t>
+  </si>
+  <si>
+    <t>24.04.202690</t>
+  </si>
+  <si>
+    <t>24.04.202691</t>
+  </si>
+  <si>
+    <t>24.04.202692</t>
+  </si>
+  <si>
+    <t>24.04.202693</t>
+  </si>
+  <si>
+    <t>24.04.202694</t>
+  </si>
+  <si>
+    <t>24.04.202695</t>
+  </si>
+  <si>
+    <t>24.04.202696</t>
+  </si>
+  <si>
+    <t>25.04.20261</t>
+  </si>
+  <si>
+    <t>25.04.20262</t>
+  </si>
+  <si>
+    <t>25.04.20263</t>
+  </si>
+  <si>
+    <t>25.04.20264</t>
+  </si>
+  <si>
+    <t>25.04.20265</t>
+  </si>
+  <si>
+    <t>25.04.20266</t>
+  </si>
+  <si>
+    <t>25.04.20267</t>
+  </si>
+  <si>
+    <t>25.04.20268</t>
+  </si>
+  <si>
+    <t>25.04.20269</t>
+  </si>
+  <si>
+    <t>25.04.202610</t>
+  </si>
+  <si>
+    <t>25.04.202611</t>
+  </si>
+  <si>
+    <t>25.04.202612</t>
+  </si>
+  <si>
+    <t>25.04.202613</t>
+  </si>
+  <si>
+    <t>25.04.202614</t>
+  </si>
+  <si>
+    <t>25.04.202615</t>
+  </si>
+  <si>
+    <t>25.04.202616</t>
+  </si>
+  <si>
+    <t>25.04.202617</t>
+  </si>
+  <si>
+    <t>25.04.202618</t>
+  </si>
+  <si>
+    <t>25.04.202619</t>
+  </si>
+  <si>
+    <t>25.04.202620</t>
+  </si>
+  <si>
+    <t>25.04.202621</t>
+  </si>
+  <si>
+    <t>25.04.202622</t>
+  </si>
+  <si>
+    <t>25.04.202623</t>
+  </si>
+  <si>
+    <t>25.04.202624</t>
+  </si>
+  <si>
+    <t>25.04.202625</t>
+  </si>
+  <si>
+    <t>25.04.202626</t>
+  </si>
+  <si>
+    <t>25.04.202627</t>
+  </si>
+  <si>
+    <t>25.04.202628</t>
+  </si>
+  <si>
+    <t>25.04.202629</t>
+  </si>
+  <si>
+    <t>25.04.202630</t>
+  </si>
+  <si>
+    <t>25.04.202631</t>
+  </si>
+  <si>
+    <t>25.04.202632</t>
+  </si>
+  <si>
+    <t>25.04.202633</t>
+  </si>
+  <si>
+    <t>25.04.202634</t>
+  </si>
+  <si>
+    <t>25.04.202635</t>
+  </si>
+  <si>
+    <t>25.04.202636</t>
+  </si>
+  <si>
+    <t>25.04.202637</t>
+  </si>
+  <si>
+    <t>25.04.202638</t>
+  </si>
+  <si>
+    <t>25.04.202639</t>
+  </si>
+  <si>
+    <t>25.04.202640</t>
+  </si>
+  <si>
+    <t>25.04.202641</t>
+  </si>
+  <si>
+    <t>25.04.202642</t>
+  </si>
+  <si>
+    <t>25.04.202643</t>
+  </si>
+  <si>
+    <t>25.04.202644</t>
+  </si>
+  <si>
+    <t>25.04.202645</t>
+  </si>
+  <si>
+    <t>25.04.202646</t>
+  </si>
+  <si>
+    <t>25.04.202647</t>
+  </si>
+  <si>
+    <t>25.04.202648</t>
+  </si>
+  <si>
+    <t>25.04.202649</t>
+  </si>
+  <si>
+    <t>25.04.202650</t>
+  </si>
+  <si>
+    <t>25.04.202651</t>
+  </si>
+  <si>
+    <t>25.04.202652</t>
+  </si>
+  <si>
+    <t>25.04.202653</t>
+  </si>
+  <si>
+    <t>25.04.202654</t>
+  </si>
+  <si>
+    <t>25.04.202655</t>
+  </si>
+  <si>
+    <t>25.04.202656</t>
+  </si>
+  <si>
+    <t>25.04.202657</t>
+  </si>
+  <si>
+    <t>25.04.202658</t>
+  </si>
+  <si>
+    <t>25.04.202659</t>
+  </si>
+  <si>
+    <t>25.04.202660</t>
+  </si>
+  <si>
+    <t>25.04.202661</t>
+  </si>
+  <si>
+    <t>25.04.202662</t>
+  </si>
+  <si>
+    <t>25.04.202663</t>
+  </si>
+  <si>
+    <t>25.04.202664</t>
+  </si>
+  <si>
+    <t>25.04.202665</t>
+  </si>
+  <si>
+    <t>25.04.202666</t>
+  </si>
+  <si>
+    <t>25.04.202667</t>
+  </si>
+  <si>
+    <t>25.04.202668</t>
+  </si>
+  <si>
+    <t>25.04.202669</t>
+  </si>
+  <si>
+    <t>25.04.202670</t>
+  </si>
+  <si>
+    <t>25.04.202671</t>
+  </si>
+  <si>
+    <t>25.04.202672</t>
+  </si>
+  <si>
+    <t>25.04.202673</t>
+  </si>
+  <si>
+    <t>25.04.202674</t>
+  </si>
+  <si>
+    <t>25.04.202675</t>
+  </si>
+  <si>
+    <t>25.04.202676</t>
+  </si>
+  <si>
+    <t>25.04.202677</t>
+  </si>
+  <si>
+    <t>25.04.202678</t>
+  </si>
+  <si>
+    <t>25.04.202679</t>
+  </si>
+  <si>
+    <t>25.04.202680</t>
+  </si>
+  <si>
+    <t>25.04.202681</t>
+  </si>
+  <si>
+    <t>25.04.202682</t>
+  </si>
+  <si>
+    <t>25.04.202683</t>
+  </si>
+  <si>
+    <t>25.04.202684</t>
+  </si>
+  <si>
+    <t>25.04.202685</t>
+  </si>
+  <si>
+    <t>25.04.202686</t>
+  </si>
+  <si>
+    <t>25.04.202687</t>
+  </si>
+  <si>
+    <t>25.04.202688</t>
+  </si>
+  <si>
+    <t>25.04.202689</t>
+  </si>
+  <si>
+    <t>25.04.202690</t>
+  </si>
+  <si>
+    <t>25.04.202691</t>
+  </si>
+  <si>
+    <t>25.04.202692</t>
+  </si>
+  <si>
+    <t>25.04.202693</t>
+  </si>
+  <si>
+    <t>25.04.202694</t>
+  </si>
+  <si>
+    <t>25.04.202695</t>
+  </si>
+  <si>
+    <t>25.04.202696</t>
+  </si>
+  <si>
+    <t>26.04.20261</t>
+  </si>
+  <si>
+    <t>26.04.20262</t>
+  </si>
+  <si>
+    <t>26.04.20263</t>
+  </si>
+  <si>
+    <t>26.04.20264</t>
+  </si>
+  <si>
+    <t>26.04.20265</t>
+  </si>
+  <si>
+    <t>26.04.20266</t>
+  </si>
+  <si>
+    <t>26.04.20267</t>
+  </si>
+  <si>
+    <t>26.04.20268</t>
+  </si>
+  <si>
+    <t>26.04.20269</t>
+  </si>
+  <si>
+    <t>26.04.202610</t>
+  </si>
+  <si>
+    <t>26.04.202611</t>
+  </si>
+  <si>
+    <t>26.04.202612</t>
+  </si>
+  <si>
+    <t>26.04.202613</t>
+  </si>
+  <si>
+    <t>26.04.202614</t>
+  </si>
+  <si>
+    <t>26.04.202615</t>
+  </si>
+  <si>
+    <t>26.04.202616</t>
+  </si>
+  <si>
+    <t>26.04.202617</t>
+  </si>
+  <si>
+    <t>26.04.202618</t>
+  </si>
+  <si>
+    <t>26.04.202619</t>
+  </si>
+  <si>
+    <t>26.04.202620</t>
+  </si>
+  <si>
+    <t>26.04.202621</t>
+  </si>
+  <si>
+    <t>26.04.202622</t>
+  </si>
+  <si>
+    <t>26.04.202623</t>
+  </si>
+  <si>
+    <t>26.04.202624</t>
+  </si>
+  <si>
+    <t>26.04.202625</t>
+  </si>
+  <si>
+    <t>26.04.202626</t>
+  </si>
+  <si>
+    <t>26.04.202627</t>
+  </si>
+  <si>
+    <t>26.04.202628</t>
+  </si>
+  <si>
+    <t>26.04.202629</t>
+  </si>
+  <si>
+    <t>26.04.202630</t>
+  </si>
+  <si>
+    <t>26.04.202631</t>
+  </si>
+  <si>
+    <t>26.04.202632</t>
+  </si>
+  <si>
+    <t>26.04.202633</t>
+  </si>
+  <si>
+    <t>26.04.202634</t>
+  </si>
+  <si>
+    <t>26.04.202635</t>
+  </si>
+  <si>
+    <t>26.04.202636</t>
+  </si>
+  <si>
+    <t>26.04.202637</t>
+  </si>
+  <si>
+    <t>26.04.202638</t>
+  </si>
+  <si>
+    <t>26.04.202639</t>
+  </si>
+  <si>
+    <t>26.04.202640</t>
+  </si>
+  <si>
+    <t>26.04.202641</t>
+  </si>
+  <si>
+    <t>26.04.202642</t>
+  </si>
+  <si>
+    <t>26.04.202643</t>
+  </si>
+  <si>
+    <t>26.04.202644</t>
+  </si>
+  <si>
+    <t>26.04.202645</t>
+  </si>
+  <si>
+    <t>26.04.202646</t>
+  </si>
+  <si>
+    <t>26.04.202647</t>
+  </si>
+  <si>
+    <t>26.04.202648</t>
+  </si>
+  <si>
+    <t>26.04.202649</t>
+  </si>
+  <si>
+    <t>26.04.202650</t>
+  </si>
+  <si>
+    <t>26.04.202651</t>
+  </si>
+  <si>
+    <t>26.04.202652</t>
+  </si>
+  <si>
+    <t>26.04.202653</t>
+  </si>
+  <si>
+    <t>26.04.202654</t>
+  </si>
+  <si>
+    <t>26.04.202655</t>
+  </si>
+  <si>
+    <t>26.04.202656</t>
+  </si>
+  <si>
+    <t>26.04.202657</t>
+  </si>
+  <si>
+    <t>26.04.202658</t>
+  </si>
+  <si>
+    <t>26.04.202659</t>
+  </si>
+  <si>
+    <t>26.04.202660</t>
+  </si>
+  <si>
+    <t>26.04.202661</t>
+  </si>
+  <si>
+    <t>26.04.202662</t>
+  </si>
+  <si>
+    <t>26.04.202663</t>
+  </si>
+  <si>
+    <t>26.04.202664</t>
+  </si>
+  <si>
+    <t>26.04.202665</t>
+  </si>
+  <si>
+    <t>26.04.202666</t>
+  </si>
+  <si>
+    <t>26.04.202667</t>
+  </si>
+  <si>
+    <t>26.04.202668</t>
+  </si>
+  <si>
+    <t>26.04.202669</t>
+  </si>
+  <si>
+    <t>26.04.202670</t>
+  </si>
+  <si>
+    <t>26.04.202671</t>
+  </si>
+  <si>
+    <t>26.04.202672</t>
+  </si>
+  <si>
+    <t>26.04.202673</t>
+  </si>
+  <si>
+    <t>26.04.202674</t>
+  </si>
+  <si>
+    <t>26.04.202675</t>
+  </si>
+  <si>
+    <t>26.04.202676</t>
+  </si>
+  <si>
+    <t>26.04.202677</t>
+  </si>
+  <si>
+    <t>26.04.202678</t>
+  </si>
+  <si>
+    <t>26.04.202679</t>
+  </si>
+  <si>
+    <t>26.04.202680</t>
+  </si>
+  <si>
+    <t>26.04.202681</t>
+  </si>
+  <si>
+    <t>26.04.202682</t>
+  </si>
+  <si>
+    <t>26.04.202683</t>
+  </si>
+  <si>
+    <t>26.04.202684</t>
+  </si>
+  <si>
+    <t>26.04.202685</t>
+  </si>
+  <si>
+    <t>26.04.202686</t>
+  </si>
+  <si>
+    <t>26.04.202687</t>
+  </si>
+  <si>
+    <t>26.04.202688</t>
+  </si>
+  <si>
+    <t>26.04.202689</t>
+  </si>
+  <si>
+    <t>26.04.202690</t>
+  </si>
+  <si>
+    <t>26.04.202691</t>
+  </si>
+  <si>
+    <t>26.04.202692</t>
+  </si>
+  <si>
+    <t>26.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202694</t>
+  </si>
+  <si>
+    <t>26.04.202695</t>
+  </si>
+  <si>
+    <t>26.04.202696</t>
+  </si>
+  <si>
+    <t>27.04.20261</t>
+  </si>
+  <si>
+    <t>27.04.20262</t>
+  </si>
+  <si>
+    <t>27.04.20263</t>
+  </si>
+  <si>
+    <t>27.04.20264</t>
+  </si>
+  <si>
+    <t>27.04.20265</t>
+  </si>
+  <si>
+    <t>27.04.20266</t>
+  </si>
+  <si>
+    <t>27.04.20267</t>
+  </si>
+  <si>
+    <t>27.04.20268</t>
+  </si>
+  <si>
+    <t>27.04.20269</t>
+  </si>
+  <si>
+    <t>27.04.202610</t>
+  </si>
+  <si>
+    <t>27.04.202611</t>
+  </si>
+  <si>
+    <t>27.04.202612</t>
+  </si>
+  <si>
+    <t>27.04.202613</t>
+  </si>
+  <si>
+    <t>27.04.202614</t>
+  </si>
+  <si>
+    <t>27.04.202615</t>
+  </si>
+  <si>
+    <t>27.04.202616</t>
+  </si>
+  <si>
+    <t>27.04.202617</t>
+  </si>
+  <si>
+    <t>27.04.202618</t>
+  </si>
+  <si>
+    <t>27.04.202619</t>
+  </si>
+  <si>
+    <t>27.04.202620</t>
+  </si>
+  <si>
+    <t>27.04.202621</t>
+  </si>
+  <si>
+    <t>27.04.202622</t>
+  </si>
+  <si>
+    <t>27.04.202623</t>
+  </si>
+  <si>
+    <t>27.04.202624</t>
+  </si>
+  <si>
+    <t>27.04.202625</t>
+  </si>
+  <si>
+    <t>27.04.202626</t>
+  </si>
+  <si>
+    <t>27.04.202627</t>
+  </si>
+  <si>
+    <t>27.04.202628</t>
+  </si>
+  <si>
+    <t>27.04.202629</t>
+  </si>
+  <si>
+    <t>27.04.202630</t>
+  </si>
+  <si>
+    <t>27.04.202631</t>
+  </si>
+  <si>
+    <t>27.04.202632</t>
+  </si>
+  <si>
+    <t>27.04.202633</t>
+  </si>
+  <si>
+    <t>27.04.202634</t>
+  </si>
+  <si>
+    <t>27.04.202635</t>
+  </si>
+  <si>
+    <t>27.04.202636</t>
+  </si>
+  <si>
+    <t>27.04.202637</t>
+  </si>
+  <si>
+    <t>27.04.202638</t>
+  </si>
+  <si>
+    <t>27.04.202639</t>
+  </si>
+  <si>
+    <t>27.04.202640</t>
+  </si>
+  <si>
+    <t>27.04.202641</t>
+  </si>
+  <si>
+    <t>27.04.202642</t>
+  </si>
+  <si>
+    <t>27.04.202643</t>
+  </si>
+  <si>
+    <t>27.04.202644</t>
+  </si>
+  <si>
+    <t>27.04.202645</t>
+  </si>
+  <si>
+    <t>27.04.202646</t>
+  </si>
+  <si>
+    <t>27.04.202647</t>
+  </si>
+  <si>
+    <t>27.04.202648</t>
+  </si>
+  <si>
+    <t>27.04.202649</t>
+  </si>
+  <si>
+    <t>27.04.202650</t>
+  </si>
+  <si>
+    <t>27.04.202651</t>
+  </si>
+  <si>
+    <t>27.04.202652</t>
+  </si>
+  <si>
+    <t>27.04.202653</t>
+  </si>
+  <si>
+    <t>27.04.202654</t>
+  </si>
+  <si>
+    <t>27.04.202655</t>
+  </si>
+  <si>
+    <t>27.04.202656</t>
+  </si>
+  <si>
+    <t>27.04.202657</t>
+  </si>
+  <si>
+    <t>27.04.202658</t>
+  </si>
+  <si>
+    <t>27.04.202659</t>
+  </si>
+  <si>
+    <t>27.04.202660</t>
+  </si>
+  <si>
+    <t>27.04.202661</t>
+  </si>
+  <si>
+    <t>27.04.202662</t>
+  </si>
+  <si>
+    <t>27.04.202663</t>
+  </si>
+  <si>
+    <t>27.04.202664</t>
+  </si>
+  <si>
+    <t>27.04.202665</t>
+  </si>
+  <si>
+    <t>27.04.202666</t>
+  </si>
+  <si>
+    <t>27.04.202667</t>
+  </si>
+  <si>
+    <t>27.04.202668</t>
+  </si>
+  <si>
+    <t>27.04.202669</t>
+  </si>
+  <si>
+    <t>27.04.202670</t>
+  </si>
+  <si>
+    <t>27.04.202671</t>
+  </si>
+  <si>
+    <t>27.04.202672</t>
+  </si>
+  <si>
+    <t>27.04.202673</t>
+  </si>
+  <si>
+    <t>27.04.202674</t>
+  </si>
+  <si>
+    <t>27.04.202675</t>
+  </si>
+  <si>
+    <t>27.04.202676</t>
+  </si>
+  <si>
+    <t>27.04.202677</t>
+  </si>
+  <si>
+    <t>27.04.202678</t>
+  </si>
+  <si>
+    <t>27.04.202679</t>
+  </si>
+  <si>
+    <t>27.04.202680</t>
+  </si>
+  <si>
+    <t>27.04.202681</t>
+  </si>
+  <si>
+    <t>27.04.202682</t>
+  </si>
+  <si>
+    <t>27.04.202683</t>
+  </si>
+  <si>
+    <t>27.04.202684</t>
+  </si>
+  <si>
+    <t>27.04.202685</t>
+  </si>
+  <si>
+    <t>27.04.202686</t>
+  </si>
+  <si>
+    <t>27.04.202687</t>
+  </si>
+  <si>
+    <t>27.04.202688</t>
+  </si>
+  <si>
+    <t>27.04.202689</t>
+  </si>
+  <si>
+    <t>27.04.202690</t>
+  </si>
+  <si>
+    <t>27.04.202691</t>
+  </si>
+  <si>
+    <t>27.04.202692</t>
+  </si>
+  <si>
+    <t>27.04.202693</t>
+  </si>
+  <si>
+    <t>27.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202695</t>
+  </si>
+  <si>
+    <t>27.04.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +1558,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2">
-        <v>5156</v>
+        <v>5386</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +1572,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46136.01041666666</v>
       </c>
       <c r="B3">
-        <v>5120</v>
+        <v>5390</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1586,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46136.02083333334</v>
       </c>
       <c r="B4">
-        <v>5163</v>
+        <v>5354</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1600,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46136.03125</v>
       </c>
       <c r="B5">
-        <v>5220</v>
+        <v>5332</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1614,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46136.04166666666</v>
       </c>
       <c r="B6">
-        <v>5273</v>
+        <v>5315</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1628,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46136.05208333334</v>
       </c>
       <c r="B7">
-        <v>5132</v>
+        <v>5328</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1642,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46136.0625</v>
       </c>
       <c r="B8">
-        <v>5283</v>
+        <v>5285</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1656,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46136.07291666666</v>
       </c>
       <c r="B9">
-        <v>5213</v>
+        <v>5259</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1670,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46136.08333333334</v>
       </c>
       <c r="B10">
-        <v>5058</v>
+        <v>5216</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1684,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46136.09375</v>
       </c>
       <c r="B11">
-        <v>5141</v>
+        <v>5228</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1698,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46136.10416666666</v>
       </c>
       <c r="B12">
-        <v>5066</v>
+        <v>5306</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1712,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46136.11458333334</v>
       </c>
       <c r="B13">
-        <v>5048</v>
+        <v>5307</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1726,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46136.125</v>
       </c>
       <c r="B14">
-        <v>5025</v>
+        <v>5291</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1740,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46136.13541666666</v>
       </c>
       <c r="B15">
-        <v>5023</v>
+        <v>5363</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1754,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46136.14583333334</v>
       </c>
       <c r="B16">
-        <v>5063</v>
+        <v>5370</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1768,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46136.15625</v>
       </c>
       <c r="B17">
-        <v>5104</v>
+        <v>5441</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1782,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46136.16666666666</v>
       </c>
       <c r="B18">
-        <v>5131</v>
+        <v>5438</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1796,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46136.17708333334</v>
       </c>
       <c r="B19">
-        <v>5221</v>
+        <v>5498</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1810,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46136.1875</v>
       </c>
       <c r="B20">
-        <v>5304</v>
+        <v>5597</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1824,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46136.19791666666</v>
       </c>
       <c r="B21">
-        <v>5353</v>
+        <v>5704</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1838,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46136.20833333334</v>
       </c>
       <c r="B22">
-        <v>5556</v>
+        <v>5667</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1852,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46136.21875</v>
       </c>
       <c r="B23">
-        <v>5629</v>
+        <v>5728</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1866,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46136.22916666666</v>
       </c>
       <c r="B24">
-        <v>5691</v>
+        <v>5833</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1880,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46136.23958333334</v>
       </c>
       <c r="B25">
-        <v>5823</v>
+        <v>5962</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1894,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46136.25</v>
       </c>
       <c r="B26">
-        <v>6057</v>
+        <v>6140</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1908,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46136.26041666666</v>
       </c>
       <c r="B27">
-        <v>6215</v>
+        <v>6228</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1922,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46136.27083333334</v>
       </c>
       <c r="B28">
-        <v>6269</v>
+        <v>6285</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1936,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46136.28125</v>
       </c>
       <c r="B29">
-        <v>6321</v>
+        <v>6227</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1950,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46136.29166666666</v>
       </c>
       <c r="B30">
-        <v>6391</v>
+        <v>6226</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1964,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46136.30208333334</v>
       </c>
       <c r="B31">
-        <v>6497</v>
+        <v>6106</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1978,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46136.3125</v>
       </c>
       <c r="B32">
-        <v>6474</v>
+        <v>6020</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1992,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46136.32291666666</v>
       </c>
       <c r="B33">
-        <v>6434</v>
+        <v>5953</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +2006,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46136.33333333334</v>
       </c>
       <c r="B34">
-        <v>6480</v>
+        <v>5784</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +2020,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46136.34375</v>
       </c>
       <c r="B35">
-        <v>6371</v>
+        <v>5706</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +2034,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46136.35416666666</v>
       </c>
       <c r="B36">
-        <v>6332</v>
+        <v>5540</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +2048,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46136.36458333334</v>
       </c>
       <c r="B37">
-        <v>6222</v>
+        <v>5269</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +2062,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46136.375</v>
       </c>
       <c r="B38">
-        <v>6108</v>
+        <v>5127</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +2076,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="B39">
-        <v>6068</v>
+        <v>4890</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +2090,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46136.39583333334</v>
       </c>
       <c r="B40">
-        <v>5930</v>
+        <v>4754</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +2104,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46136.40625</v>
       </c>
       <c r="B41">
-        <v>5848</v>
+        <v>4660</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +2118,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46136.41666666666</v>
       </c>
       <c r="B42">
-        <v>5745</v>
+        <v>4552</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +2132,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46136.42708333334</v>
       </c>
       <c r="B43">
-        <v>5764</v>
+        <v>4342</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +2146,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46136.4375</v>
       </c>
       <c r="B44">
-        <v>5737</v>
+        <v>4300</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +2160,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46136.44791666666</v>
       </c>
       <c r="B45">
-        <v>5702</v>
+        <v>4286</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +2174,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46136.45833333334</v>
       </c>
       <c r="B46">
-        <v>5713</v>
+        <v>4221</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +2188,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46136.46875</v>
       </c>
       <c r="B47">
-        <v>5825</v>
+        <v>4272</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +2202,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46136.47916666666</v>
       </c>
       <c r="B48">
-        <v>5832</v>
+        <v>4318</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +2216,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46136.48958333334</v>
       </c>
       <c r="B49">
-        <v>5943</v>
+        <v>4349</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +2230,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46136.5</v>
       </c>
       <c r="B50">
-        <v>5784</v>
+        <v>4340</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +2244,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46136.51041666666</v>
       </c>
       <c r="B51">
-        <v>5831</v>
+        <v>4326</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +2258,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46136.52083333334</v>
       </c>
       <c r="B52">
-        <v>5882</v>
+        <v>4304</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +2272,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46136.53125</v>
       </c>
       <c r="B53">
-        <v>5867</v>
+        <v>4438</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +2286,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46136.54166666666</v>
       </c>
       <c r="B54">
-        <v>5874</v>
+        <v>4488</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +2300,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="B55">
-        <v>5752</v>
+        <v>4470</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +2314,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46136.5625</v>
       </c>
       <c r="B56">
-        <v>5698</v>
+        <v>4495</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +2328,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46136.57291666666</v>
       </c>
       <c r="B57">
-        <v>5708</v>
+        <v>4519</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +2342,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46136.58333333334</v>
       </c>
       <c r="B58">
-        <v>5756</v>
+        <v>4560</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +2356,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46136.59375</v>
       </c>
       <c r="B59">
-        <v>5900</v>
+        <v>4505</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +2370,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46136.60416666666</v>
       </c>
       <c r="B60">
-        <v>5872</v>
+        <v>4486</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +2384,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46136.61458333334</v>
       </c>
       <c r="B61">
-        <v>5809</v>
+        <v>4570</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +2398,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46136.625</v>
       </c>
       <c r="B62">
-        <v>5720</v>
+        <v>4635</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +2412,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46136.63541666666</v>
       </c>
       <c r="B63">
-        <v>5848</v>
+        <v>4717</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +2426,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46136.64583333334</v>
       </c>
       <c r="B64">
-        <v>5959</v>
+        <v>4789</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +2440,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46136.65625</v>
       </c>
       <c r="B65">
-        <v>5993</v>
+        <v>4929</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +2454,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46136.66666666666</v>
       </c>
       <c r="B66">
-        <v>6006</v>
+        <v>5111</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +2468,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46136.67708333334</v>
       </c>
       <c r="B67">
-        <v>6165</v>
+        <v>5271</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +2482,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46136.6875</v>
       </c>
       <c r="B68">
-        <v>6197</v>
+        <v>5410</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +2496,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46136.69791666666</v>
       </c>
       <c r="B69">
-        <v>6346</v>
+        <v>5411</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +2510,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="B70">
-        <v>6309</v>
+        <v>5654</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +2524,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46136.71875</v>
       </c>
       <c r="B71">
-        <v>6404</v>
+        <v>5816</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +2538,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46136.72916666666</v>
       </c>
       <c r="B72">
-        <v>6576</v>
+        <v>5894</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +2552,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46136.73958333334</v>
       </c>
       <c r="B73">
-        <v>6648</v>
+        <v>6066</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +2566,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46136.75</v>
       </c>
       <c r="B74">
-        <v>6694</v>
+        <v>6219</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2580,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B75">
-        <v>6838</v>
+        <v>6377</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2594,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="B76">
-        <v>6904</v>
+        <v>6491</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2608,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46136.78125</v>
       </c>
       <c r="B77">
-        <v>7049</v>
+        <v>6622</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2622,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46136.79166666666</v>
       </c>
       <c r="B78">
-        <v>7086</v>
+        <v>6694</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2636,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46136.80208333334</v>
       </c>
       <c r="B79">
-        <v>7193</v>
+        <v>6893</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2650,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46136.8125</v>
       </c>
       <c r="B80">
-        <v>7325</v>
+        <v>6981</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2664,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46136.82291666666</v>
       </c>
       <c r="B81">
-        <v>7347</v>
+        <v>7112</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2678,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46136.83333333334</v>
       </c>
       <c r="B82">
-        <v>7247</v>
+        <v>7095</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2692,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46136.84375</v>
       </c>
       <c r="B83">
-        <v>7201</v>
+        <v>7077</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2706,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46136.85416666666</v>
       </c>
       <c r="B84">
-        <v>7057</v>
+        <v>6919</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2720,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46136.86458333334</v>
       </c>
       <c r="B85">
-        <v>6914</v>
+        <v>6831</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2734,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46136.875</v>
       </c>
       <c r="B86">
-        <v>6779</v>
+        <v>6638</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2748,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46136.88541666666</v>
       </c>
       <c r="B87">
-        <v>6580</v>
+        <v>6497</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2762,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46136.89583333334</v>
       </c>
       <c r="B88">
-        <v>6413</v>
+        <v>6287</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2776,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46136.90625</v>
       </c>
       <c r="B89">
-        <v>6297</v>
+        <v>6192</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2790,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46136.91666666666</v>
       </c>
       <c r="B90">
-        <v>6169</v>
+        <v>6043</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2804,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46136.92708333334</v>
       </c>
       <c r="B91">
-        <v>6067</v>
+        <v>5947</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2818,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46136.9375</v>
       </c>
       <c r="B92">
-        <v>5957</v>
+        <v>5800</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2832,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46136.94791666666</v>
       </c>
       <c r="B93">
-        <v>5824</v>
+        <v>5743</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2846,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46136.95833333334</v>
       </c>
       <c r="B94">
-        <v>5734</v>
+        <v>5610</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2860,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46136.96875</v>
       </c>
       <c r="B95">
-        <v>5656</v>
+        <v>5525</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2874,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46136.97916666666</v>
       </c>
       <c r="B96">
-        <v>5618</v>
+        <v>5402</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2888,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46136.98958333334</v>
       </c>
       <c r="B97">
-        <v>5516</v>
+        <v>5360</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2902,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B98">
-        <v>5438</v>
+        <v>5308</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2916,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46134.01041666666</v>
+        <v>46137.01041666666</v>
       </c>
       <c r="B99">
-        <v>5392</v>
+        <v>5289</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2930,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46134.02083333334</v>
+        <v>46137.02083333334</v>
       </c>
       <c r="B100">
-        <v>5358</v>
+        <v>5225</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2944,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46134.03125</v>
+        <v>46137.03125</v>
       </c>
       <c r="B101">
-        <v>5296</v>
+        <v>5176</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46134.04166666666</v>
+        <v>46137.04166666666</v>
       </c>
       <c r="B102">
-        <v>5303</v>
+        <v>5151</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2972,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46134.05208333334</v>
+        <v>46137.05208333334</v>
       </c>
       <c r="B103">
-        <v>5319</v>
+        <v>5123</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2986,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46134.0625</v>
+        <v>46137.0625</v>
       </c>
       <c r="B104">
-        <v>5306</v>
+        <v>5090</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +3000,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46134.07291666666</v>
+        <v>46137.07291666666</v>
       </c>
       <c r="B105">
-        <v>5328</v>
+        <v>5025</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +3014,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46134.08333333334</v>
+        <v>46137.08333333334</v>
       </c>
       <c r="B106">
-        <v>5336</v>
+        <v>5121</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +3028,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46134.09375</v>
+        <v>46137.09375</v>
       </c>
       <c r="B107">
-        <v>5282</v>
+        <v>5110</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +3042,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46134.10416666666</v>
+        <v>46137.10416666666</v>
       </c>
       <c r="B108">
-        <v>5288</v>
+        <v>5106</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +3056,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46134.11458333334</v>
+        <v>46137.11458333334</v>
       </c>
       <c r="B109">
-        <v>5312</v>
+        <v>5077</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +3070,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46134.125</v>
+        <v>46137.125</v>
       </c>
       <c r="B110">
-        <v>5316</v>
+        <v>5097</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +3084,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46134.13541666666</v>
+        <v>46137.13541666666</v>
       </c>
       <c r="B111">
-        <v>5325</v>
+        <v>5106</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +3098,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46134.14583333334</v>
+        <v>46137.14583333334</v>
       </c>
       <c r="B112">
-        <v>5341</v>
+        <v>5120</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +3112,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46134.15625</v>
+        <v>46137.15625</v>
       </c>
       <c r="B113">
-        <v>5397</v>
+        <v>5054</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +3126,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46134.16666666666</v>
+        <v>46137.16666666666</v>
       </c>
       <c r="B114">
-        <v>5558</v>
+        <v>5077</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +3140,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46134.17708333334</v>
+        <v>46137.17708333334</v>
       </c>
       <c r="B115">
-        <v>5597</v>
+        <v>4755</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +3154,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46134.1875</v>
+        <v>46137.1875</v>
       </c>
       <c r="B116">
-        <v>5656</v>
+        <v>4782</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +3168,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46134.19791666666</v>
+        <v>46137.19791666666</v>
       </c>
       <c r="B117">
-        <v>5703</v>
+        <v>4767</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +3182,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46134.20833333334</v>
+        <v>46137.20833333334</v>
       </c>
       <c r="B118">
-        <v>5801</v>
+        <v>4815</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +3196,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46134.21875</v>
+        <v>46137.21875</v>
       </c>
       <c r="B119">
-        <v>5848</v>
+        <v>4814</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +3210,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46134.22916666666</v>
+        <v>46137.22916666666</v>
       </c>
       <c r="B120">
-        <v>5977</v>
+        <v>5035</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +3224,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46134.23958333334</v>
+        <v>46137.23958333334</v>
       </c>
       <c r="B121">
-        <v>6097</v>
+        <v>5213</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +3238,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46134.25</v>
+        <v>46137.25</v>
       </c>
       <c r="B122">
-        <v>6287</v>
+        <v>5206</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +3252,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46134.26041666666</v>
+        <v>46137.26041666666</v>
       </c>
       <c r="B123">
-        <v>6467</v>
+        <v>5215</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +3266,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46134.27083333334</v>
+        <v>46137.27083333334</v>
       </c>
       <c r="B124">
-        <v>6531</v>
+        <v>5198</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +3280,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46134.28125</v>
+        <v>46137.28125</v>
       </c>
       <c r="B125">
-        <v>6504</v>
+        <v>5123</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +3294,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46134.29166666666</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="B126">
-        <v>6521</v>
+        <v>5079</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +3308,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46134.30208333334</v>
+        <v>46137.30208333334</v>
       </c>
       <c r="B127">
-        <v>6574</v>
+        <v>5037</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +3322,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46134.3125</v>
+        <v>46137.3125</v>
       </c>
       <c r="B128">
-        <v>6504</v>
+        <v>4999</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +3336,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46134.32291666666</v>
+        <v>46137.32291666666</v>
       </c>
       <c r="B129">
-        <v>6442</v>
+        <v>4913</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +3350,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46134.33333333334</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="B130">
-        <v>6305</v>
+        <v>4757</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +3364,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46134.34375</v>
+        <v>46137.34375</v>
       </c>
       <c r="B131">
-        <v>6319</v>
+        <v>4684</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +3378,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46134.35416666666</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="B132">
-        <v>6197</v>
+        <v>4520</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +3392,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46134.36458333334</v>
+        <v>46137.36458333334</v>
       </c>
       <c r="B133">
-        <v>6152</v>
+        <v>4424</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +3406,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46134.375</v>
+        <v>46137.375</v>
       </c>
       <c r="B134">
-        <v>5932</v>
+        <v>4235</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +3420,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46134.38541666666</v>
+        <v>46137.38541666666</v>
       </c>
       <c r="B135">
-        <v>5855</v>
+        <v>4117</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +3434,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46134.39583333334</v>
+        <v>46137.39583333334</v>
       </c>
       <c r="B136">
-        <v>5754</v>
+        <v>4074</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +3448,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46134.40625</v>
+        <v>46137.40625</v>
       </c>
       <c r="B137">
-        <v>5625</v>
+        <v>3958</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +3462,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46134.41666666666</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="B138">
-        <v>5499</v>
+        <v>3950</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +3476,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46134.42708333334</v>
+        <v>46137.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>3929</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +3490,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46134.4375</v>
+        <v>46137.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>3825</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +3504,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46134.44791666666</v>
+        <v>46137.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>3797</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +3518,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46134.45833333334</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>3741</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +3532,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46134.46875</v>
+        <v>46137.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>3736</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +3546,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46134.47916666666</v>
+        <v>46137.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>3763</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +3560,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46134.48958333334</v>
+        <v>46137.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>3689</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,7 +3574,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46134.5</v>
+        <v>46137.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,10 +3588,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46134.51041666666</v>
+        <v>46137.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>3649</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3602,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46134.52083333334</v>
+        <v>46137.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3616,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46134.53125</v>
+        <v>46137.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>3580</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3630,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46134.54166666666</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>3625</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3644,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46134.55208333334</v>
+        <v>46137.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>3702</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3658,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46134.5625</v>
+        <v>46137.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>3775</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3672,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46134.57291666666</v>
+        <v>46137.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>3847</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3686,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46134.58333333334</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>3952</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3700,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46134.59375</v>
+        <v>46137.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>3927</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3714,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46134.60416666666</v>
+        <v>46137.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>3857</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3728,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46134.61458333334</v>
+        <v>46137.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>3808</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3742,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46134.625</v>
+        <v>46137.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>3859</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3756,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46134.63541666666</v>
+        <v>46137.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>3918</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3770,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46134.64583333334</v>
+        <v>46137.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>4033</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3784,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46134.65625</v>
+        <v>46137.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>4094</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3798,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46134.66666666666</v>
+        <v>46137.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>4288</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3812,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46134.67708333334</v>
+        <v>46137.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>4409</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3826,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46134.6875</v>
+        <v>46137.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>4610</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3840,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46134.69791666666</v>
+        <v>46137.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>4733</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3854,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46134.70833333334</v>
+        <v>46137.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>5055</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3868,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46134.71875</v>
+        <v>46137.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>5075</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3882,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46134.72916666666</v>
+        <v>46137.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>5239</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3896,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46134.73958333334</v>
+        <v>46137.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>5402</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3910,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46134.75</v>
+        <v>46137.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>5621</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3924,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46134.76041666666</v>
+        <v>46137.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>5754</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3938,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46134.77083333334</v>
+        <v>46137.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>5817</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3952,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46134.78125</v>
+        <v>46137.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>5914</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3966,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46134.79166666666</v>
+        <v>46137.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>5983</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3980,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46134.80208333334</v>
+        <v>46137.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>6130</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3994,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46134.8125</v>
+        <v>46137.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>6285</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +4008,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46134.82291666666</v>
+        <v>46137.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>6460</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +4022,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46134.83333333334</v>
+        <v>46137.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>6481</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +4036,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46134.84375</v>
+        <v>46137.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>6445</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +4050,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46134.85416666666</v>
+        <v>46137.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>6364</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +4064,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46134.86458333334</v>
+        <v>46137.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6296</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +4078,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46134.875</v>
+        <v>46137.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>6172</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +4092,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46134.88541666666</v>
+        <v>46137.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>6081</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +4106,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46134.89583333334</v>
+        <v>46137.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>5921</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +4120,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46134.90625</v>
+        <v>46137.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>5857</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +4134,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46134.91666666666</v>
+        <v>46137.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>5684</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +4148,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46134.92708333334</v>
+        <v>46137.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5577</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +4162,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46134.9375</v>
+        <v>46137.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>5395</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +4176,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46134.94791666666</v>
+        <v>46137.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>5328</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +4190,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46134.95833333334</v>
+        <v>46137.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>5202</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +4204,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46134.96875</v>
+        <v>46137.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>5143</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +4218,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46134.97916666666</v>
+        <v>46137.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>5015</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +4232,2704 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46134.98958333334</v>
+        <v>46137.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>5003</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B194">
+        <v>4934</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46138.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4887</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46138.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4775</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46138.03125</v>
+      </c>
+      <c r="B197">
+        <v>4760</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46138.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4731</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46138.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4737</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46138.0625</v>
+      </c>
+      <c r="B200">
+        <v>4693</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46138.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4664</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46138.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4702</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46138.09375</v>
+      </c>
+      <c r="B203">
+        <v>4690</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46138.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4619</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46138.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4641</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46138.125</v>
+      </c>
+      <c r="B206">
+        <v>4669</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46138.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4666</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46138.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4679</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46138.15625</v>
+      </c>
+      <c r="B209">
+        <v>4675</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46138.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4656</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46138.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4652</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46138.1875</v>
+      </c>
+      <c r="B212">
+        <v>4635</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46138.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>4610</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46138.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4573</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46138.21875</v>
+      </c>
+      <c r="B215">
+        <v>4642</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46138.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>4630</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46138.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>4526</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46138.25</v>
+      </c>
+      <c r="B218">
+        <v>4505</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46138.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>4479</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46138.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>4426</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46138.28125</v>
+      </c>
+      <c r="B221">
+        <v>4365</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46138.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>4275</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46138.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>4166</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46138.3125</v>
+      </c>
+      <c r="B224">
+        <v>4012</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46138.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>3887</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>3775</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46138.34375</v>
+      </c>
+      <c r="B227">
+        <v>3634</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46138.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>3566</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46138.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>3473</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46138.375</v>
+      </c>
+      <c r="B230">
+        <v>3366</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46138.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>3269</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46138.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3192</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46138.40625</v>
+      </c>
+      <c r="B233">
+        <v>3076</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>2973</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46138.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>2991</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46138.4375</v>
+      </c>
+      <c r="B236">
+        <v>2944</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46138.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>2907</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46138.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>2931</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46138.46875</v>
+      </c>
+      <c r="B239">
+        <v>2914</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46138.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>2890</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46138.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>2930</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46138.5</v>
+      </c>
+      <c r="B242">
+        <v>3001</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46138.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>3036</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46138.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>3059</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46138.53125</v>
+      </c>
+      <c r="B245">
+        <v>2994</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46138.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>3034</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46138.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>3006</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46138.5625</v>
+      </c>
+      <c r="B248">
+        <v>2951</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46138.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>2925</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>2941</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46138.59375</v>
+      </c>
+      <c r="B251">
+        <v>2937</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46138.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>2979</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46138.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>3011</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46138.625</v>
+      </c>
+      <c r="B254">
+        <v>3094</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46138.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>3158</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46138.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>3273</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46138.65625</v>
+      </c>
+      <c r="B257">
+        <v>3411</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46138.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>3549</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46138.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>3771</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46138.6875</v>
+      </c>
+      <c r="B260">
+        <v>3932</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46138.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>4105</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46138.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>4516</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46138.71875</v>
+      </c>
+      <c r="B263">
+        <v>4502</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46138.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>4601</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46138.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>4834</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46138.75</v>
+      </c>
+      <c r="B266">
+        <v>5051</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46138.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>5250</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46138.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>5417</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46138.78125</v>
+      </c>
+      <c r="B269">
+        <v>5564</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46138.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>5662</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46138.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>5796</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46138.8125</v>
+      </c>
+      <c r="B272">
+        <v>5983</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46138.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>6086</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46138.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>6129</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46138.84375</v>
+      </c>
+      <c r="B275">
+        <v>6128</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46138.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>6087</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46138.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>6042</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46138.875</v>
+      </c>
+      <c r="B278">
+        <v>5870</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46138.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>5803</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46138.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5704</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46138.90625</v>
+      </c>
+      <c r="B281">
+        <v>5611</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46138.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5419</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46138.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5283</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46138.9375</v>
+      </c>
+      <c r="B284">
+        <v>5184</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46138.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>5111</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46138.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>5011</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46138.96875</v>
+      </c>
+      <c r="B287">
+        <v>4949</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46138.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4889</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46138.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4899</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B290">
+        <v>4796</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46139.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4722</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46139.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4754</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46139.03125</v>
+      </c>
+      <c r="B293">
+        <v>4712</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46139.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4752</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46139.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4742</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46139.0625</v>
+      </c>
+      <c r="B296">
+        <v>4691</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46139.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4718</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4799</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46139.09375</v>
+      </c>
+      <c r="B299">
+        <v>4807</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4722</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46139.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4745</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46139.125</v>
+      </c>
+      <c r="B302">
+        <v>4758</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46139.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4735</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46139.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4666</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46139.15625</v>
+      </c>
+      <c r="B305">
+        <v>4689</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46139.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4782</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46139.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4839</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46139.1875</v>
+      </c>
+      <c r="B308">
+        <v>4929</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46139.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>5025</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46139.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>5223</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46139.21875</v>
+      </c>
+      <c r="B311">
+        <v>5336</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46139.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5468</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46139.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5622</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46139.25</v>
+      </c>
+      <c r="B314">
+        <v>5856</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46139.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>5967</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46139.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>5969</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46139.28125</v>
+      </c>
+      <c r="B317">
+        <v>5985</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46139.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>6071</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46139.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>6032</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46139.3125</v>
+      </c>
+      <c r="B320">
+        <v>5947</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46139.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>5757</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46139.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>5571</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46139.34375</v>
+      </c>
+      <c r="B323">
+        <v>5425</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46139.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>5187</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46139.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>5075</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46139.375</v>
+      </c>
+      <c r="B326">
+        <v>4876</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46139.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>4765</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46139.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>4560</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46139.40625</v>
+      </c>
+      <c r="B329">
+        <v>4442</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46139.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>4349</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46139.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4153</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B332">
+        <v>4053</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>3989</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>4008</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46139.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46139.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46139.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46139.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46139.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46139.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46139.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46139.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46139.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46139.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46139.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46139.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46139.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46139.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46139.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46139.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46139.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46139.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46139.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46139.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46139.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46139.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46139.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46139.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46139.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46139.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46139.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46139.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46139.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46139.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46139.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46139.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46139.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46139.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46139.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46139.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46139.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46139.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46139.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46139.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46139.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46139.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,1156 +28,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.202625</t>
-  </si>
-  <si>
-    <t>24.04.202626</t>
-  </si>
-  <si>
-    <t>24.04.202627</t>
-  </si>
-  <si>
-    <t>24.04.202628</t>
-  </si>
-  <si>
-    <t>24.04.202629</t>
-  </si>
-  <si>
-    <t>24.04.202630</t>
-  </si>
-  <si>
-    <t>24.04.202631</t>
-  </si>
-  <si>
-    <t>24.04.202632</t>
-  </si>
-  <si>
-    <t>24.04.202633</t>
-  </si>
-  <si>
-    <t>24.04.202634</t>
-  </si>
-  <si>
-    <t>24.04.202635</t>
-  </si>
-  <si>
-    <t>24.04.202636</t>
-  </si>
-  <si>
-    <t>24.04.202637</t>
-  </si>
-  <si>
-    <t>24.04.202638</t>
-  </si>
-  <si>
-    <t>24.04.202639</t>
-  </si>
-  <si>
-    <t>24.04.202640</t>
-  </si>
-  <si>
-    <t>24.04.202641</t>
-  </si>
-  <si>
-    <t>24.04.202642</t>
-  </si>
-  <si>
-    <t>24.04.202643</t>
-  </si>
-  <si>
-    <t>24.04.202644</t>
-  </si>
-  <si>
-    <t>24.04.202645</t>
-  </si>
-  <si>
-    <t>24.04.202646</t>
-  </si>
-  <si>
-    <t>24.04.202647</t>
-  </si>
-  <si>
-    <t>24.04.202648</t>
-  </si>
-  <si>
-    <t>24.04.202649</t>
-  </si>
-  <si>
-    <t>24.04.202650</t>
-  </si>
-  <si>
-    <t>24.04.202651</t>
-  </si>
-  <si>
-    <t>24.04.202652</t>
-  </si>
-  <si>
-    <t>24.04.202653</t>
-  </si>
-  <si>
-    <t>24.04.202654</t>
-  </si>
-  <si>
-    <t>24.04.202655</t>
-  </si>
-  <si>
-    <t>24.04.202656</t>
-  </si>
-  <si>
-    <t>24.04.202657</t>
-  </si>
-  <si>
-    <t>24.04.202658</t>
-  </si>
-  <si>
-    <t>24.04.202659</t>
-  </si>
-  <si>
-    <t>24.04.202660</t>
-  </si>
-  <si>
-    <t>24.04.202661</t>
-  </si>
-  <si>
-    <t>24.04.202662</t>
-  </si>
-  <si>
-    <t>24.04.202663</t>
-  </si>
-  <si>
-    <t>24.04.202664</t>
-  </si>
-  <si>
-    <t>24.04.202665</t>
-  </si>
-  <si>
-    <t>24.04.202666</t>
-  </si>
-  <si>
-    <t>24.04.202667</t>
-  </si>
-  <si>
-    <t>24.04.202668</t>
-  </si>
-  <si>
-    <t>24.04.202669</t>
-  </si>
-  <si>
-    <t>24.04.202670</t>
-  </si>
-  <si>
-    <t>24.04.202671</t>
-  </si>
-  <si>
-    <t>24.04.202672</t>
-  </si>
-  <si>
-    <t>24.04.202673</t>
-  </si>
-  <si>
-    <t>24.04.202674</t>
-  </si>
-  <si>
-    <t>24.04.202675</t>
-  </si>
-  <si>
-    <t>24.04.202676</t>
-  </si>
-  <si>
-    <t>24.04.202677</t>
-  </si>
-  <si>
-    <t>24.04.202678</t>
-  </si>
-  <si>
-    <t>24.04.202679</t>
-  </si>
-  <si>
-    <t>24.04.202680</t>
-  </si>
-  <si>
-    <t>24.04.202681</t>
-  </si>
-  <si>
-    <t>24.04.202682</t>
-  </si>
-  <si>
-    <t>24.04.202683</t>
-  </si>
-  <si>
-    <t>24.04.202684</t>
-  </si>
-  <si>
-    <t>24.04.202685</t>
-  </si>
-  <si>
-    <t>24.04.202686</t>
-  </si>
-  <si>
-    <t>24.04.202687</t>
-  </si>
-  <si>
-    <t>24.04.202688</t>
-  </si>
-  <si>
-    <t>24.04.202689</t>
-  </si>
-  <si>
-    <t>24.04.202690</t>
-  </si>
-  <si>
-    <t>24.04.202691</t>
-  </si>
-  <si>
-    <t>24.04.202692</t>
-  </si>
-  <si>
-    <t>24.04.202693</t>
-  </si>
-  <si>
-    <t>24.04.202694</t>
-  </si>
-  <si>
-    <t>24.04.202695</t>
-  </si>
-  <si>
-    <t>24.04.202696</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.202625</t>
-  </si>
-  <si>
-    <t>25.04.202626</t>
-  </si>
-  <si>
-    <t>25.04.202627</t>
-  </si>
-  <si>
-    <t>25.04.202628</t>
-  </si>
-  <si>
-    <t>25.04.202629</t>
-  </si>
-  <si>
-    <t>25.04.202630</t>
-  </si>
-  <si>
-    <t>25.04.202631</t>
-  </si>
-  <si>
-    <t>25.04.202632</t>
-  </si>
-  <si>
-    <t>25.04.202633</t>
-  </si>
-  <si>
-    <t>25.04.202634</t>
-  </si>
-  <si>
-    <t>25.04.202635</t>
-  </si>
-  <si>
-    <t>25.04.202636</t>
-  </si>
-  <si>
-    <t>25.04.202637</t>
-  </si>
-  <si>
-    <t>25.04.202638</t>
-  </si>
-  <si>
-    <t>25.04.202639</t>
-  </si>
-  <si>
-    <t>25.04.202640</t>
-  </si>
-  <si>
-    <t>25.04.202641</t>
-  </si>
-  <si>
-    <t>25.04.202642</t>
-  </si>
-  <si>
-    <t>25.04.202643</t>
-  </si>
-  <si>
-    <t>25.04.202644</t>
-  </si>
-  <si>
-    <t>25.04.202645</t>
-  </si>
-  <si>
-    <t>25.04.202646</t>
-  </si>
-  <si>
-    <t>25.04.202647</t>
-  </si>
-  <si>
-    <t>25.04.202648</t>
-  </si>
-  <si>
-    <t>25.04.202649</t>
-  </si>
-  <si>
-    <t>25.04.202650</t>
-  </si>
-  <si>
-    <t>25.04.202651</t>
-  </si>
-  <si>
-    <t>25.04.202652</t>
-  </si>
-  <si>
-    <t>25.04.202653</t>
-  </si>
-  <si>
-    <t>25.04.202654</t>
-  </si>
-  <si>
-    <t>25.04.202655</t>
-  </si>
-  <si>
-    <t>25.04.202656</t>
-  </si>
-  <si>
-    <t>25.04.202657</t>
-  </si>
-  <si>
-    <t>25.04.202658</t>
-  </si>
-  <si>
-    <t>25.04.202659</t>
-  </si>
-  <si>
-    <t>25.04.202660</t>
-  </si>
-  <si>
-    <t>25.04.202661</t>
-  </si>
-  <si>
-    <t>25.04.202662</t>
-  </si>
-  <si>
-    <t>25.04.202663</t>
-  </si>
-  <si>
-    <t>25.04.202664</t>
-  </si>
-  <si>
-    <t>25.04.202665</t>
-  </si>
-  <si>
-    <t>25.04.202666</t>
-  </si>
-  <si>
-    <t>25.04.202667</t>
-  </si>
-  <si>
-    <t>25.04.202668</t>
-  </si>
-  <si>
-    <t>25.04.202669</t>
-  </si>
-  <si>
-    <t>25.04.202670</t>
-  </si>
-  <si>
-    <t>25.04.202671</t>
-  </si>
-  <si>
-    <t>25.04.202672</t>
-  </si>
-  <si>
-    <t>25.04.202673</t>
-  </si>
-  <si>
-    <t>25.04.202674</t>
-  </si>
-  <si>
-    <t>25.04.202675</t>
-  </si>
-  <si>
-    <t>25.04.202676</t>
-  </si>
-  <si>
-    <t>25.04.202677</t>
-  </si>
-  <si>
-    <t>25.04.202678</t>
-  </si>
-  <si>
-    <t>25.04.202679</t>
-  </si>
-  <si>
-    <t>25.04.202680</t>
-  </si>
-  <si>
-    <t>25.04.202681</t>
-  </si>
-  <si>
-    <t>25.04.202682</t>
-  </si>
-  <si>
-    <t>25.04.202683</t>
-  </si>
-  <si>
-    <t>25.04.202684</t>
-  </si>
-  <si>
-    <t>25.04.202685</t>
-  </si>
-  <si>
-    <t>25.04.202686</t>
-  </si>
-  <si>
-    <t>25.04.202687</t>
-  </si>
-  <si>
-    <t>25.04.202688</t>
-  </si>
-  <si>
-    <t>25.04.202689</t>
-  </si>
-  <si>
-    <t>25.04.202690</t>
-  </si>
-  <si>
-    <t>25.04.202691</t>
-  </si>
-  <si>
-    <t>25.04.202692</t>
-  </si>
-  <si>
-    <t>25.04.202693</t>
-  </si>
-  <si>
-    <t>25.04.202694</t>
-  </si>
-  <si>
-    <t>25.04.202695</t>
-  </si>
-  <si>
-    <t>25.04.202696</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.202625</t>
-  </si>
-  <si>
-    <t>26.04.202626</t>
-  </si>
-  <si>
-    <t>26.04.202627</t>
-  </si>
-  <si>
-    <t>26.04.202628</t>
-  </si>
-  <si>
-    <t>26.04.202629</t>
-  </si>
-  <si>
-    <t>26.04.202630</t>
-  </si>
-  <si>
-    <t>26.04.202631</t>
-  </si>
-  <si>
-    <t>26.04.202632</t>
-  </si>
-  <si>
-    <t>26.04.202633</t>
-  </si>
-  <si>
-    <t>26.04.202634</t>
-  </si>
-  <si>
-    <t>26.04.202635</t>
-  </si>
-  <si>
-    <t>26.04.202636</t>
-  </si>
-  <si>
-    <t>26.04.202637</t>
-  </si>
-  <si>
-    <t>26.04.202638</t>
-  </si>
-  <si>
-    <t>26.04.202639</t>
-  </si>
-  <si>
-    <t>26.04.202640</t>
-  </si>
-  <si>
-    <t>26.04.202641</t>
-  </si>
-  <si>
-    <t>26.04.202642</t>
-  </si>
-  <si>
-    <t>26.04.202643</t>
-  </si>
-  <si>
-    <t>26.04.202644</t>
-  </si>
-  <si>
-    <t>26.04.202645</t>
-  </si>
-  <si>
-    <t>26.04.202646</t>
-  </si>
-  <si>
-    <t>26.04.202647</t>
-  </si>
-  <si>
-    <t>26.04.202648</t>
-  </si>
-  <si>
-    <t>26.04.202649</t>
-  </si>
-  <si>
-    <t>26.04.202650</t>
-  </si>
-  <si>
-    <t>26.04.202651</t>
-  </si>
-  <si>
-    <t>26.04.202652</t>
-  </si>
-  <si>
-    <t>26.04.202653</t>
-  </si>
-  <si>
-    <t>26.04.202654</t>
-  </si>
-  <si>
-    <t>26.04.202655</t>
-  </si>
-  <si>
-    <t>26.04.202656</t>
-  </si>
-  <si>
-    <t>26.04.202657</t>
-  </si>
-  <si>
-    <t>26.04.202658</t>
-  </si>
-  <si>
-    <t>26.04.202659</t>
-  </si>
-  <si>
-    <t>26.04.202660</t>
-  </si>
-  <si>
-    <t>26.04.202661</t>
-  </si>
-  <si>
-    <t>26.04.202662</t>
-  </si>
-  <si>
-    <t>26.04.202663</t>
-  </si>
-  <si>
-    <t>26.04.202664</t>
-  </si>
-  <si>
-    <t>26.04.202665</t>
-  </si>
-  <si>
-    <t>26.04.202666</t>
-  </si>
-  <si>
-    <t>26.04.202667</t>
-  </si>
-  <si>
-    <t>26.04.202668</t>
-  </si>
-  <si>
-    <t>26.04.202669</t>
-  </si>
-  <si>
-    <t>26.04.202670</t>
-  </si>
-  <si>
-    <t>26.04.202671</t>
-  </si>
-  <si>
-    <t>26.04.202672</t>
-  </si>
-  <si>
-    <t>26.04.202673</t>
-  </si>
-  <si>
-    <t>26.04.202674</t>
-  </si>
-  <si>
-    <t>26.04.202675</t>
-  </si>
-  <si>
-    <t>26.04.202676</t>
-  </si>
-  <si>
-    <t>26.04.202677</t>
-  </si>
-  <si>
-    <t>26.04.202678</t>
-  </si>
-  <si>
-    <t>26.04.202679</t>
-  </si>
-  <si>
-    <t>26.04.202680</t>
-  </si>
-  <si>
-    <t>26.04.202681</t>
-  </si>
-  <si>
-    <t>26.04.202682</t>
-  </si>
-  <si>
-    <t>26.04.202683</t>
-  </si>
-  <si>
-    <t>26.04.202684</t>
-  </si>
-  <si>
-    <t>26.04.202685</t>
-  </si>
-  <si>
-    <t>26.04.202686</t>
-  </si>
-  <si>
-    <t>26.04.202687</t>
-  </si>
-  <si>
-    <t>26.04.202688</t>
-  </si>
-  <si>
-    <t>26.04.202689</t>
-  </si>
-  <si>
-    <t>26.04.202690</t>
-  </si>
-  <si>
-    <t>26.04.202691</t>
-  </si>
-  <si>
-    <t>26.04.202692</t>
-  </si>
-  <si>
-    <t>26.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202694</t>
-  </si>
-  <si>
-    <t>26.04.202695</t>
-  </si>
-  <si>
-    <t>26.04.202696</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.202625</t>
-  </si>
-  <si>
-    <t>27.04.202626</t>
-  </si>
-  <si>
-    <t>27.04.202627</t>
-  </si>
-  <si>
-    <t>27.04.202628</t>
-  </si>
-  <si>
-    <t>27.04.202629</t>
-  </si>
-  <si>
-    <t>27.04.202630</t>
-  </si>
-  <si>
-    <t>27.04.202631</t>
-  </si>
-  <si>
-    <t>27.04.202632</t>
-  </si>
-  <si>
-    <t>27.04.202633</t>
-  </si>
-  <si>
-    <t>27.04.202634</t>
-  </si>
-  <si>
-    <t>27.04.202635</t>
-  </si>
-  <si>
-    <t>27.04.202636</t>
-  </si>
-  <si>
-    <t>27.04.202637</t>
-  </si>
-  <si>
-    <t>27.04.202638</t>
-  </si>
-  <si>
-    <t>27.04.202639</t>
-  </si>
-  <si>
-    <t>27.04.202640</t>
-  </si>
-  <si>
-    <t>27.04.202641</t>
-  </si>
-  <si>
-    <t>27.04.202642</t>
-  </si>
-  <si>
-    <t>27.04.202643</t>
-  </si>
-  <si>
-    <t>27.04.202644</t>
-  </si>
-  <si>
-    <t>27.04.202645</t>
-  </si>
-  <si>
-    <t>27.04.202646</t>
-  </si>
-  <si>
-    <t>27.04.202647</t>
-  </si>
-  <si>
-    <t>27.04.202648</t>
-  </si>
-  <si>
-    <t>27.04.202649</t>
-  </si>
-  <si>
-    <t>27.04.202650</t>
-  </si>
-  <si>
-    <t>27.04.202651</t>
-  </si>
-  <si>
-    <t>27.04.202652</t>
-  </si>
-  <si>
-    <t>27.04.202653</t>
-  </si>
-  <si>
-    <t>27.04.202654</t>
-  </si>
-  <si>
-    <t>27.04.202655</t>
-  </si>
-  <si>
-    <t>27.04.202656</t>
-  </si>
-  <si>
-    <t>27.04.202657</t>
-  </si>
-  <si>
-    <t>27.04.202658</t>
-  </si>
-  <si>
-    <t>27.04.202659</t>
-  </si>
-  <si>
-    <t>27.04.202660</t>
-  </si>
-  <si>
-    <t>27.04.202661</t>
-  </si>
-  <si>
-    <t>27.04.202662</t>
-  </si>
-  <si>
-    <t>27.04.202663</t>
-  </si>
-  <si>
-    <t>27.04.202664</t>
-  </si>
-  <si>
-    <t>27.04.202665</t>
-  </si>
-  <si>
-    <t>27.04.202666</t>
-  </si>
-  <si>
-    <t>27.04.202667</t>
-  </si>
-  <si>
-    <t>27.04.202668</t>
-  </si>
-  <si>
-    <t>27.04.202669</t>
-  </si>
-  <si>
-    <t>27.04.202670</t>
-  </si>
-  <si>
-    <t>27.04.202671</t>
-  </si>
-  <si>
-    <t>27.04.202672</t>
-  </si>
-  <si>
-    <t>27.04.202673</t>
-  </si>
-  <si>
-    <t>27.04.202674</t>
-  </si>
-  <si>
-    <t>27.04.202675</t>
-  </si>
-  <si>
-    <t>27.04.202676</t>
-  </si>
-  <si>
-    <t>27.04.202677</t>
-  </si>
-  <si>
-    <t>27.04.202678</t>
-  </si>
-  <si>
-    <t>27.04.202679</t>
-  </si>
-  <si>
-    <t>27.04.202680</t>
-  </si>
-  <si>
-    <t>27.04.202681</t>
-  </si>
-  <si>
-    <t>27.04.202682</t>
-  </si>
-  <si>
-    <t>27.04.202683</t>
-  </si>
-  <si>
-    <t>27.04.202684</t>
-  </si>
-  <si>
-    <t>27.04.202685</t>
-  </si>
-  <si>
-    <t>27.04.202686</t>
-  </si>
-  <si>
-    <t>27.04.202687</t>
-  </si>
-  <si>
-    <t>27.04.202688</t>
-  </si>
-  <si>
-    <t>27.04.202689</t>
-  </si>
-  <si>
-    <t>27.04.202690</t>
-  </si>
-  <si>
-    <t>27.04.202691</t>
-  </si>
-  <si>
-    <t>27.04.202692</t>
-  </si>
-  <si>
-    <t>27.04.202693</t>
-  </si>
-  <si>
-    <t>27.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202695</t>
-  </si>
-  <si>
-    <t>27.04.202696</t>
+    <t>28.04.20261</t>
+  </si>
+  <si>
+    <t>28.04.20262</t>
+  </si>
+  <si>
+    <t>28.04.20263</t>
+  </si>
+  <si>
+    <t>28.04.20264</t>
+  </si>
+  <si>
+    <t>28.04.20265</t>
+  </si>
+  <si>
+    <t>28.04.20266</t>
+  </si>
+  <si>
+    <t>28.04.20267</t>
+  </si>
+  <si>
+    <t>28.04.20268</t>
+  </si>
+  <si>
+    <t>28.04.20269</t>
+  </si>
+  <si>
+    <t>28.04.202610</t>
+  </si>
+  <si>
+    <t>28.04.202611</t>
+  </si>
+  <si>
+    <t>28.04.202612</t>
+  </si>
+  <si>
+    <t>28.04.202613</t>
+  </si>
+  <si>
+    <t>28.04.202614</t>
+  </si>
+  <si>
+    <t>28.04.202615</t>
+  </si>
+  <si>
+    <t>28.04.202616</t>
+  </si>
+  <si>
+    <t>28.04.202617</t>
+  </si>
+  <si>
+    <t>28.04.202618</t>
+  </si>
+  <si>
+    <t>28.04.202619</t>
+  </si>
+  <si>
+    <t>28.04.202620</t>
+  </si>
+  <si>
+    <t>28.04.202621</t>
+  </si>
+  <si>
+    <t>28.04.202622</t>
+  </si>
+  <si>
+    <t>28.04.202623</t>
+  </si>
+  <si>
+    <t>28.04.202624</t>
+  </si>
+  <si>
+    <t>28.04.202625</t>
+  </si>
+  <si>
+    <t>28.04.202626</t>
+  </si>
+  <si>
+    <t>28.04.202627</t>
+  </si>
+  <si>
+    <t>28.04.202628</t>
+  </si>
+  <si>
+    <t>28.04.202629</t>
+  </si>
+  <si>
+    <t>28.04.202630</t>
+  </si>
+  <si>
+    <t>28.04.202631</t>
+  </si>
+  <si>
+    <t>28.04.202632</t>
+  </si>
+  <si>
+    <t>28.04.202633</t>
+  </si>
+  <si>
+    <t>28.04.202634</t>
+  </si>
+  <si>
+    <t>28.04.202635</t>
+  </si>
+  <si>
+    <t>28.04.202636</t>
+  </si>
+  <si>
+    <t>28.04.202637</t>
+  </si>
+  <si>
+    <t>28.04.202638</t>
+  </si>
+  <si>
+    <t>28.04.202639</t>
+  </si>
+  <si>
+    <t>28.04.202640</t>
+  </si>
+  <si>
+    <t>28.04.202641</t>
+  </si>
+  <si>
+    <t>28.04.202642</t>
+  </si>
+  <si>
+    <t>28.04.202643</t>
+  </si>
+  <si>
+    <t>28.04.202644</t>
+  </si>
+  <si>
+    <t>28.04.202645</t>
+  </si>
+  <si>
+    <t>28.04.202646</t>
+  </si>
+  <si>
+    <t>28.04.202647</t>
+  </si>
+  <si>
+    <t>28.04.202648</t>
+  </si>
+  <si>
+    <t>28.04.202649</t>
+  </si>
+  <si>
+    <t>28.04.202650</t>
+  </si>
+  <si>
+    <t>28.04.202651</t>
+  </si>
+  <si>
+    <t>28.04.202652</t>
+  </si>
+  <si>
+    <t>28.04.202653</t>
+  </si>
+  <si>
+    <t>28.04.202654</t>
+  </si>
+  <si>
+    <t>28.04.202655</t>
+  </si>
+  <si>
+    <t>28.04.202656</t>
+  </si>
+  <si>
+    <t>28.04.202657</t>
+  </si>
+  <si>
+    <t>28.04.202658</t>
+  </si>
+  <si>
+    <t>28.04.202659</t>
+  </si>
+  <si>
+    <t>28.04.202660</t>
+  </si>
+  <si>
+    <t>28.04.202661</t>
+  </si>
+  <si>
+    <t>28.04.202662</t>
+  </si>
+  <si>
+    <t>28.04.202663</t>
+  </si>
+  <si>
+    <t>28.04.202664</t>
+  </si>
+  <si>
+    <t>28.04.202665</t>
+  </si>
+  <si>
+    <t>28.04.202666</t>
+  </si>
+  <si>
+    <t>28.04.202667</t>
+  </si>
+  <si>
+    <t>28.04.202668</t>
+  </si>
+  <si>
+    <t>28.04.202669</t>
+  </si>
+  <si>
+    <t>28.04.202670</t>
+  </si>
+  <si>
+    <t>28.04.202671</t>
+  </si>
+  <si>
+    <t>28.04.202672</t>
+  </si>
+  <si>
+    <t>28.04.202673</t>
+  </si>
+  <si>
+    <t>28.04.202674</t>
+  </si>
+  <si>
+    <t>28.04.202675</t>
+  </si>
+  <si>
+    <t>28.04.202676</t>
+  </si>
+  <si>
+    <t>28.04.202677</t>
+  </si>
+  <si>
+    <t>28.04.202678</t>
+  </si>
+  <si>
+    <t>28.04.202679</t>
+  </si>
+  <si>
+    <t>28.04.202680</t>
+  </si>
+  <si>
+    <t>28.04.202681</t>
+  </si>
+  <si>
+    <t>28.04.202682</t>
+  </si>
+  <si>
+    <t>28.04.202683</t>
+  </si>
+  <si>
+    <t>28.04.202684</t>
+  </si>
+  <si>
+    <t>28.04.202685</t>
+  </si>
+  <si>
+    <t>28.04.202686</t>
+  </si>
+  <si>
+    <t>28.04.202687</t>
+  </si>
+  <si>
+    <t>28.04.202688</t>
+  </si>
+  <si>
+    <t>28.04.202689</t>
+  </si>
+  <si>
+    <t>28.04.202690</t>
+  </si>
+  <si>
+    <t>28.04.202691</t>
+  </si>
+  <si>
+    <t>28.04.202692</t>
+  </si>
+  <si>
+    <t>28.04.202693</t>
+  </si>
+  <si>
+    <t>28.04.202694</t>
+  </si>
+  <si>
+    <t>28.04.202695</t>
+  </si>
+  <si>
+    <t>28.04.202696</t>
+  </si>
+  <si>
+    <t>29.04.20261</t>
+  </si>
+  <si>
+    <t>29.04.20262</t>
+  </si>
+  <si>
+    <t>29.04.20263</t>
+  </si>
+  <si>
+    <t>29.04.20264</t>
+  </si>
+  <si>
+    <t>29.04.20265</t>
+  </si>
+  <si>
+    <t>29.04.20266</t>
+  </si>
+  <si>
+    <t>29.04.20267</t>
+  </si>
+  <si>
+    <t>29.04.20268</t>
+  </si>
+  <si>
+    <t>29.04.20269</t>
+  </si>
+  <si>
+    <t>29.04.202610</t>
+  </si>
+  <si>
+    <t>29.04.202611</t>
+  </si>
+  <si>
+    <t>29.04.202612</t>
+  </si>
+  <si>
+    <t>29.04.202613</t>
+  </si>
+  <si>
+    <t>29.04.202614</t>
+  </si>
+  <si>
+    <t>29.04.202615</t>
+  </si>
+  <si>
+    <t>29.04.202616</t>
+  </si>
+  <si>
+    <t>29.04.202617</t>
+  </si>
+  <si>
+    <t>29.04.202618</t>
+  </si>
+  <si>
+    <t>29.04.202619</t>
+  </si>
+  <si>
+    <t>29.04.202620</t>
+  </si>
+  <si>
+    <t>29.04.202621</t>
+  </si>
+  <si>
+    <t>29.04.202622</t>
+  </si>
+  <si>
+    <t>29.04.202623</t>
+  </si>
+  <si>
+    <t>29.04.202624</t>
+  </si>
+  <si>
+    <t>29.04.202625</t>
+  </si>
+  <si>
+    <t>29.04.202626</t>
+  </si>
+  <si>
+    <t>29.04.202627</t>
+  </si>
+  <si>
+    <t>29.04.202628</t>
+  </si>
+  <si>
+    <t>29.04.202629</t>
+  </si>
+  <si>
+    <t>29.04.202630</t>
+  </si>
+  <si>
+    <t>29.04.202631</t>
+  </si>
+  <si>
+    <t>29.04.202632</t>
+  </si>
+  <si>
+    <t>29.04.202633</t>
+  </si>
+  <si>
+    <t>29.04.202634</t>
+  </si>
+  <si>
+    <t>29.04.202635</t>
+  </si>
+  <si>
+    <t>29.04.202636</t>
+  </si>
+  <si>
+    <t>29.04.202637</t>
+  </si>
+  <si>
+    <t>29.04.202638</t>
+  </si>
+  <si>
+    <t>29.04.202639</t>
+  </si>
+  <si>
+    <t>29.04.202640</t>
+  </si>
+  <si>
+    <t>29.04.202641</t>
+  </si>
+  <si>
+    <t>29.04.202642</t>
+  </si>
+  <si>
+    <t>29.04.202643</t>
+  </si>
+  <si>
+    <t>29.04.202644</t>
+  </si>
+  <si>
+    <t>29.04.202645</t>
+  </si>
+  <si>
+    <t>29.04.202646</t>
+  </si>
+  <si>
+    <t>29.04.202647</t>
+  </si>
+  <si>
+    <t>29.04.202648</t>
+  </si>
+  <si>
+    <t>29.04.202649</t>
+  </si>
+  <si>
+    <t>29.04.202650</t>
+  </si>
+  <si>
+    <t>29.04.202651</t>
+  </si>
+  <si>
+    <t>29.04.202652</t>
+  </si>
+  <si>
+    <t>29.04.202653</t>
+  </si>
+  <si>
+    <t>29.04.202654</t>
+  </si>
+  <si>
+    <t>29.04.202655</t>
+  </si>
+  <si>
+    <t>29.04.202656</t>
+  </si>
+  <si>
+    <t>29.04.202657</t>
+  </si>
+  <si>
+    <t>29.04.202658</t>
+  </si>
+  <si>
+    <t>29.04.202659</t>
+  </si>
+  <si>
+    <t>29.04.202660</t>
+  </si>
+  <si>
+    <t>29.04.202661</t>
+  </si>
+  <si>
+    <t>29.04.202662</t>
+  </si>
+  <si>
+    <t>29.04.202663</t>
+  </si>
+  <si>
+    <t>29.04.202664</t>
+  </si>
+  <si>
+    <t>29.04.202665</t>
+  </si>
+  <si>
+    <t>29.04.202666</t>
+  </si>
+  <si>
+    <t>29.04.202667</t>
+  </si>
+  <si>
+    <t>29.04.202668</t>
+  </si>
+  <si>
+    <t>29.04.202669</t>
+  </si>
+  <si>
+    <t>29.04.202670</t>
+  </si>
+  <si>
+    <t>29.04.202671</t>
+  </si>
+  <si>
+    <t>29.04.202672</t>
+  </si>
+  <si>
+    <t>29.04.202673</t>
+  </si>
+  <si>
+    <t>29.04.202674</t>
+  </si>
+  <si>
+    <t>29.04.202675</t>
+  </si>
+  <si>
+    <t>29.04.202676</t>
+  </si>
+  <si>
+    <t>29.04.202677</t>
+  </si>
+  <si>
+    <t>29.04.202678</t>
+  </si>
+  <si>
+    <t>29.04.202679</t>
+  </si>
+  <si>
+    <t>29.04.202680</t>
+  </si>
+  <si>
+    <t>29.04.202681</t>
+  </si>
+  <si>
+    <t>29.04.202682</t>
+  </si>
+  <si>
+    <t>29.04.202683</t>
+  </si>
+  <si>
+    <t>29.04.202684</t>
+  </si>
+  <si>
+    <t>29.04.202685</t>
+  </si>
+  <si>
+    <t>29.04.202686</t>
+  </si>
+  <si>
+    <t>29.04.202687</t>
+  </si>
+  <si>
+    <t>29.04.202688</t>
+  </si>
+  <si>
+    <t>29.04.202689</t>
+  </si>
+  <si>
+    <t>29.04.202690</t>
+  </si>
+  <si>
+    <t>29.04.202691</t>
+  </si>
+  <si>
+    <t>29.04.202692</t>
+  </si>
+  <si>
+    <t>29.04.202693</t>
+  </si>
+  <si>
+    <t>29.04.202694</t>
+  </si>
+  <si>
+    <t>29.04.202695</t>
+  </si>
+  <si>
+    <t>29.04.202696</t>
+  </si>
+  <si>
+    <t>30.04.20261</t>
+  </si>
+  <si>
+    <t>30.04.20262</t>
+  </si>
+  <si>
+    <t>30.04.20263</t>
+  </si>
+  <si>
+    <t>30.04.20264</t>
+  </si>
+  <si>
+    <t>30.04.20265</t>
+  </si>
+  <si>
+    <t>30.04.20266</t>
+  </si>
+  <si>
+    <t>30.04.20267</t>
+  </si>
+  <si>
+    <t>30.04.20268</t>
+  </si>
+  <si>
+    <t>30.04.20269</t>
+  </si>
+  <si>
+    <t>30.04.202610</t>
+  </si>
+  <si>
+    <t>30.04.202611</t>
+  </si>
+  <si>
+    <t>30.04.202612</t>
+  </si>
+  <si>
+    <t>30.04.202613</t>
+  </si>
+  <si>
+    <t>30.04.202614</t>
+  </si>
+  <si>
+    <t>30.04.202615</t>
+  </si>
+  <si>
+    <t>30.04.202616</t>
+  </si>
+  <si>
+    <t>30.04.202617</t>
+  </si>
+  <si>
+    <t>30.04.202618</t>
+  </si>
+  <si>
+    <t>30.04.202619</t>
+  </si>
+  <si>
+    <t>30.04.202620</t>
+  </si>
+  <si>
+    <t>30.04.202621</t>
+  </si>
+  <si>
+    <t>30.04.202622</t>
+  </si>
+  <si>
+    <t>30.04.202623</t>
+  </si>
+  <si>
+    <t>30.04.202624</t>
+  </si>
+  <si>
+    <t>30.04.202625</t>
+  </si>
+  <si>
+    <t>30.04.202626</t>
+  </si>
+  <si>
+    <t>30.04.202627</t>
+  </si>
+  <si>
+    <t>30.04.202628</t>
+  </si>
+  <si>
+    <t>30.04.202629</t>
+  </si>
+  <si>
+    <t>30.04.202630</t>
+  </si>
+  <si>
+    <t>30.04.202631</t>
+  </si>
+  <si>
+    <t>30.04.202632</t>
+  </si>
+  <si>
+    <t>30.04.202633</t>
+  </si>
+  <si>
+    <t>30.04.202634</t>
+  </si>
+  <si>
+    <t>30.04.202635</t>
+  </si>
+  <si>
+    <t>30.04.202636</t>
+  </si>
+  <si>
+    <t>30.04.202637</t>
+  </si>
+  <si>
+    <t>30.04.202638</t>
+  </si>
+  <si>
+    <t>30.04.202639</t>
+  </si>
+  <si>
+    <t>30.04.202640</t>
+  </si>
+  <si>
+    <t>30.04.202641</t>
+  </si>
+  <si>
+    <t>30.04.202642</t>
+  </si>
+  <si>
+    <t>30.04.202643</t>
+  </si>
+  <si>
+    <t>30.04.202644</t>
+  </si>
+  <si>
+    <t>30.04.202645</t>
+  </si>
+  <si>
+    <t>30.04.202646</t>
+  </si>
+  <si>
+    <t>30.04.202647</t>
+  </si>
+  <si>
+    <t>30.04.202648</t>
+  </si>
+  <si>
+    <t>30.04.202649</t>
+  </si>
+  <si>
+    <t>30.04.202650</t>
+  </si>
+  <si>
+    <t>30.04.202651</t>
+  </si>
+  <si>
+    <t>30.04.202652</t>
+  </si>
+  <si>
+    <t>30.04.202653</t>
+  </si>
+  <si>
+    <t>30.04.202654</t>
+  </si>
+  <si>
+    <t>30.04.202655</t>
+  </si>
+  <si>
+    <t>30.04.202656</t>
+  </si>
+  <si>
+    <t>30.04.202657</t>
+  </si>
+  <si>
+    <t>30.04.202658</t>
+  </si>
+  <si>
+    <t>30.04.202659</t>
+  </si>
+  <si>
+    <t>30.04.202660</t>
+  </si>
+  <si>
+    <t>30.04.202661</t>
+  </si>
+  <si>
+    <t>30.04.202662</t>
+  </si>
+  <si>
+    <t>30.04.202663</t>
+  </si>
+  <si>
+    <t>30.04.202664</t>
+  </si>
+  <si>
+    <t>30.04.202665</t>
+  </si>
+  <si>
+    <t>30.04.202666</t>
+  </si>
+  <si>
+    <t>30.04.202667</t>
+  </si>
+  <si>
+    <t>30.04.202668</t>
+  </si>
+  <si>
+    <t>30.04.202669</t>
+  </si>
+  <si>
+    <t>30.04.202670</t>
+  </si>
+  <si>
+    <t>30.04.202671</t>
+  </si>
+  <si>
+    <t>30.04.202672</t>
+  </si>
+  <si>
+    <t>30.04.202673</t>
+  </si>
+  <si>
+    <t>30.04.202674</t>
+  </si>
+  <si>
+    <t>30.04.202675</t>
+  </si>
+  <si>
+    <t>30.04.202676</t>
+  </si>
+  <si>
+    <t>30.04.202677</t>
+  </si>
+  <si>
+    <t>30.04.202678</t>
+  </si>
+  <si>
+    <t>30.04.202679</t>
+  </si>
+  <si>
+    <t>30.04.202680</t>
+  </si>
+  <si>
+    <t>30.04.202681</t>
+  </si>
+  <si>
+    <t>30.04.202682</t>
+  </si>
+  <si>
+    <t>30.04.202683</t>
+  </si>
+  <si>
+    <t>30.04.202684</t>
+  </si>
+  <si>
+    <t>30.04.202685</t>
+  </si>
+  <si>
+    <t>30.04.202686</t>
+  </si>
+  <si>
+    <t>30.04.202687</t>
+  </si>
+  <si>
+    <t>30.04.202688</t>
+  </si>
+  <si>
+    <t>30.04.202689</t>
+  </si>
+  <si>
+    <t>30.04.202690</t>
+  </si>
+  <si>
+    <t>30.04.202691</t>
+  </si>
+  <si>
+    <t>30.04.202692</t>
+  </si>
+  <si>
+    <t>30.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202694</t>
+  </si>
+  <si>
+    <t>30.04.202695</t>
+  </si>
+  <si>
+    <t>30.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D385"/>
+  <dimension ref="A1:D289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1558,10 +1270,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B2">
-        <v>5386</v>
+        <v>5367</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1572,10 +1284,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46136.01041666666</v>
+        <v>46140.01041666666</v>
       </c>
       <c r="B3">
-        <v>5390</v>
+        <v>5325</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1586,10 +1298,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46136.02083333334</v>
+        <v>46140.02083333334</v>
       </c>
       <c r="B4">
-        <v>5354</v>
+        <v>5256</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1600,10 +1312,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46136.03125</v>
+        <v>46140.03125</v>
       </c>
       <c r="B5">
-        <v>5332</v>
+        <v>5179</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1614,10 +1326,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46136.04166666666</v>
+        <v>46140.04166666666</v>
       </c>
       <c r="B6">
-        <v>5315</v>
+        <v>5228</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1628,10 +1340,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46136.05208333334</v>
+        <v>46140.05208333334</v>
       </c>
       <c r="B7">
-        <v>5328</v>
+        <v>5175</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1642,10 +1354,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46136.0625</v>
+        <v>46140.0625</v>
       </c>
       <c r="B8">
-        <v>5285</v>
+        <v>5168</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1656,10 +1368,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46136.07291666666</v>
+        <v>46140.07291666666</v>
       </c>
       <c r="B9">
-        <v>5259</v>
+        <v>5183</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1670,10 +1382,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46136.08333333334</v>
+        <v>46140.08333333334</v>
       </c>
       <c r="B10">
-        <v>5216</v>
+        <v>5125</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1684,10 +1396,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46136.09375</v>
+        <v>46140.09375</v>
       </c>
       <c r="B11">
-        <v>5228</v>
+        <v>5149</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1698,10 +1410,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46136.10416666666</v>
+        <v>46140.10416666666</v>
       </c>
       <c r="B12">
-        <v>5306</v>
+        <v>5130</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1712,10 +1424,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46136.11458333334</v>
+        <v>46140.11458333334</v>
       </c>
       <c r="B13">
-        <v>5307</v>
+        <v>5131</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1726,10 +1438,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46136.125</v>
+        <v>46140.125</v>
       </c>
       <c r="B14">
-        <v>5291</v>
+        <v>5252</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1740,10 +1452,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46136.13541666666</v>
+        <v>46140.13541666666</v>
       </c>
       <c r="B15">
-        <v>5363</v>
+        <v>5235</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1754,10 +1466,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46136.14583333334</v>
+        <v>46140.14583333334</v>
       </c>
       <c r="B16">
-        <v>5370</v>
+        <v>5308</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1768,10 +1480,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46136.15625</v>
+        <v>46140.15625</v>
       </c>
       <c r="B17">
-        <v>5441</v>
+        <v>5307</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1782,10 +1494,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46136.16666666666</v>
+        <v>46140.16666666666</v>
       </c>
       <c r="B18">
-        <v>5438</v>
+        <v>5320</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1796,10 +1508,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46136.17708333334</v>
+        <v>46140.17708333334</v>
       </c>
       <c r="B19">
-        <v>5498</v>
+        <v>5385</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1810,10 +1522,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46136.1875</v>
+        <v>46140.1875</v>
       </c>
       <c r="B20">
-        <v>5597</v>
+        <v>5490</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1824,10 +1536,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46136.19791666666</v>
+        <v>46140.19791666666</v>
       </c>
       <c r="B21">
-        <v>5704</v>
+        <v>5539</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1838,10 +1550,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46136.20833333334</v>
+        <v>46140.20833333334</v>
       </c>
       <c r="B22">
-        <v>5667</v>
+        <v>5575</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1852,10 +1564,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46136.21875</v>
+        <v>46140.21875</v>
       </c>
       <c r="B23">
-        <v>5728</v>
+        <v>5610</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1866,10 +1578,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46136.22916666666</v>
+        <v>46140.22916666666</v>
       </c>
       <c r="B24">
-        <v>5833</v>
+        <v>5686</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1880,10 +1592,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46136.23958333334</v>
+        <v>46140.23958333334</v>
       </c>
       <c r="B25">
-        <v>5962</v>
+        <v>5837</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1894,10 +1606,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46136.25</v>
+        <v>46140.25</v>
       </c>
       <c r="B26">
-        <v>6140</v>
+        <v>6066</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1908,10 +1620,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46136.26041666666</v>
+        <v>46140.26041666666</v>
       </c>
       <c r="B27">
-        <v>6228</v>
+        <v>6161</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1922,10 +1634,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46136.27083333334</v>
+        <v>46140.27083333334</v>
       </c>
       <c r="B28">
-        <v>6285</v>
+        <v>6105</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1936,10 +1648,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46136.28125</v>
+        <v>46140.28125</v>
       </c>
       <c r="B29">
-        <v>6227</v>
+        <v>6049</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1950,10 +1662,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46136.29166666666</v>
+        <v>46140.29166666666</v>
       </c>
       <c r="B30">
-        <v>6226</v>
+        <v>6114</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1964,10 +1676,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46136.30208333334</v>
+        <v>46140.30208333334</v>
       </c>
       <c r="B31">
-        <v>6106</v>
+        <v>6035</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1978,10 +1690,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46136.3125</v>
+        <v>46140.3125</v>
       </c>
       <c r="B32">
-        <v>6020</v>
+        <v>5971</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1992,10 +1704,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46136.32291666666</v>
+        <v>46140.32291666666</v>
       </c>
       <c r="B33">
-        <v>5953</v>
+        <v>5911</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -2006,10 +1718,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46136.33333333334</v>
+        <v>46140.33333333334</v>
       </c>
       <c r="B34">
-        <v>5784</v>
+        <v>5583</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -2020,10 +1732,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46136.34375</v>
+        <v>46140.34375</v>
       </c>
       <c r="B35">
-        <v>5706</v>
+        <v>5373</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -2034,10 +1746,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46136.35416666666</v>
+        <v>46140.35416666666</v>
       </c>
       <c r="B36">
-        <v>5540</v>
+        <v>5209</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -2048,10 +1760,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46136.36458333334</v>
+        <v>46140.36458333334</v>
       </c>
       <c r="B37">
-        <v>5269</v>
+        <v>5047</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -2062,10 +1774,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46136.375</v>
+        <v>46140.375</v>
       </c>
       <c r="B38">
-        <v>5127</v>
+        <v>4831</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -2076,10 +1788,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46136.38541666666</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="B39">
-        <v>4890</v>
+        <v>4665</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -2090,10 +1802,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46136.39583333334</v>
+        <v>46140.39583333334</v>
       </c>
       <c r="B40">
-        <v>4754</v>
+        <v>4517</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -2104,10 +1816,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46136.40625</v>
+        <v>46140.40625</v>
       </c>
       <c r="B41">
-        <v>4660</v>
+        <v>4419</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -2118,10 +1830,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46136.41666666666</v>
+        <v>46140.41666666666</v>
       </c>
       <c r="B42">
-        <v>4552</v>
+        <v>4331</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -2132,10 +1844,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46136.42708333334</v>
+        <v>46140.42708333334</v>
       </c>
       <c r="B43">
-        <v>4342</v>
+        <v>4228</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -2146,10 +1858,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46136.4375</v>
+        <v>46140.4375</v>
       </c>
       <c r="B44">
-        <v>4300</v>
+        <v>4112</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -2160,10 +1872,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46136.44791666666</v>
+        <v>46140.44791666666</v>
       </c>
       <c r="B45">
-        <v>4286</v>
+        <v>4019</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -2174,10 +1886,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46136.45833333334</v>
+        <v>46140.45833333334</v>
       </c>
       <c r="B46">
-        <v>4221</v>
+        <v>4008</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -2188,10 +1900,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46136.46875</v>
+        <v>46140.46875</v>
       </c>
       <c r="B47">
-        <v>4272</v>
+        <v>3948</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -2202,10 +1914,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46136.47916666666</v>
+        <v>46140.47916666666</v>
       </c>
       <c r="B48">
-        <v>4318</v>
+        <v>0</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -2216,10 +1928,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46136.48958333334</v>
+        <v>46140.48958333334</v>
       </c>
       <c r="B49">
-        <v>4349</v>
+        <v>3954</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -2230,10 +1942,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46136.5</v>
+        <v>46140.5</v>
       </c>
       <c r="B50">
-        <v>4340</v>
+        <v>3964</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -2244,10 +1956,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46136.51041666666</v>
+        <v>46140.51041666666</v>
       </c>
       <c r="B51">
-        <v>4326</v>
+        <v>3952</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -2258,10 +1970,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46136.52083333334</v>
+        <v>46140.52083333334</v>
       </c>
       <c r="B52">
-        <v>4304</v>
+        <v>3960</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -2272,10 +1984,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46136.53125</v>
+        <v>46140.53125</v>
       </c>
       <c r="B53">
-        <v>4438</v>
+        <v>3937</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -2286,10 +1998,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46136.54166666666</v>
+        <v>46140.54166666666</v>
       </c>
       <c r="B54">
-        <v>4488</v>
+        <v>4084</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -2300,10 +2012,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46136.55208333334</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="B55">
-        <v>4470</v>
+        <v>4079</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -2314,10 +2026,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46136.5625</v>
+        <v>46140.5625</v>
       </c>
       <c r="B56">
-        <v>4495</v>
+        <v>4119</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -2328,10 +2040,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46136.57291666666</v>
+        <v>46140.57291666666</v>
       </c>
       <c r="B57">
-        <v>4519</v>
+        <v>4064</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -2342,10 +2054,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46136.58333333334</v>
+        <v>46140.58333333334</v>
       </c>
       <c r="B58">
-        <v>4560</v>
+        <v>4062</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -2356,10 +2068,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46136.59375</v>
+        <v>46140.59375</v>
       </c>
       <c r="B59">
-        <v>4505</v>
+        <v>4134</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -2370,10 +2082,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46136.60416666666</v>
+        <v>46140.60416666666</v>
       </c>
       <c r="B60">
-        <v>4486</v>
+        <v>4194</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -2384,10 +2096,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46136.61458333334</v>
+        <v>46140.61458333334</v>
       </c>
       <c r="B61">
-        <v>4570</v>
+        <v>4264</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -2398,10 +2110,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46136.625</v>
+        <v>46140.625</v>
       </c>
       <c r="B62">
-        <v>4635</v>
+        <v>4372</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -2412,10 +2124,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46136.63541666666</v>
+        <v>46140.63541666666</v>
       </c>
       <c r="B63">
-        <v>4717</v>
+        <v>4457</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -2426,10 +2138,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46136.64583333334</v>
+        <v>46140.64583333334</v>
       </c>
       <c r="B64">
-        <v>4789</v>
+        <v>4579</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -2440,10 +2152,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46136.65625</v>
+        <v>46140.65625</v>
       </c>
       <c r="B65">
-        <v>4929</v>
+        <v>4613</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -2454,10 +2166,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46136.66666666666</v>
+        <v>46140.66666666666</v>
       </c>
       <c r="B66">
-        <v>5111</v>
+        <v>4794</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -2468,10 +2180,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46136.67708333334</v>
+        <v>46140.67708333334</v>
       </c>
       <c r="B67">
-        <v>5271</v>
+        <v>4884</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -2482,10 +2194,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46136.6875</v>
+        <v>46140.6875</v>
       </c>
       <c r="B68">
-        <v>5410</v>
+        <v>5062</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -2496,10 +2208,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46136.69791666666</v>
+        <v>46140.69791666666</v>
       </c>
       <c r="B69">
-        <v>5411</v>
+        <v>5373</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -2510,10 +2222,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46136.70833333334</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="B70">
-        <v>5654</v>
+        <v>5530</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -2524,10 +2236,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46136.71875</v>
+        <v>46140.71875</v>
       </c>
       <c r="B71">
-        <v>5816</v>
+        <v>5667</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -2538,10 +2250,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46136.72916666666</v>
+        <v>46140.72916666666</v>
       </c>
       <c r="B72">
-        <v>5894</v>
+        <v>5940</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -2552,10 +2264,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46136.73958333334</v>
+        <v>46140.73958333334</v>
       </c>
       <c r="B73">
-        <v>6066</v>
+        <v>6060</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2566,10 +2278,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46136.75</v>
+        <v>46140.75</v>
       </c>
       <c r="B74">
-        <v>6219</v>
+        <v>6232</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2580,10 +2292,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46136.76041666666</v>
+        <v>46140.76041666666</v>
       </c>
       <c r="B75">
-        <v>6377</v>
+        <v>6350</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2594,10 +2306,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46136.77083333334</v>
+        <v>46140.77083333334</v>
       </c>
       <c r="B76">
-        <v>6491</v>
+        <v>6535</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2608,10 +2320,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46136.78125</v>
+        <v>46140.78125</v>
       </c>
       <c r="B77">
-        <v>6622</v>
+        <v>6683</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2622,10 +2334,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46136.79166666666</v>
+        <v>46140.79166666666</v>
       </c>
       <c r="B78">
-        <v>6694</v>
+        <v>6801</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2636,10 +2348,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46136.80208333334</v>
+        <v>46140.80208333334</v>
       </c>
       <c r="B79">
-        <v>6893</v>
+        <v>6960</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2650,10 +2362,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46136.8125</v>
+        <v>46140.8125</v>
       </c>
       <c r="B80">
-        <v>6981</v>
+        <v>7052</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2664,10 +2376,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46136.82291666666</v>
+        <v>46140.82291666666</v>
       </c>
       <c r="B81">
-        <v>7112</v>
+        <v>7087</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2678,10 +2390,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46136.83333333334</v>
+        <v>46140.83333333334</v>
       </c>
       <c r="B82">
-        <v>7095</v>
+        <v>7136</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2692,10 +2404,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46136.84375</v>
+        <v>46140.84375</v>
       </c>
       <c r="B83">
-        <v>7077</v>
+        <v>7116</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2706,10 +2418,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46136.85416666666</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="B84">
-        <v>6919</v>
+        <v>7036</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2720,10 +2432,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46136.86458333334</v>
+        <v>46140.86458333334</v>
       </c>
       <c r="B85">
-        <v>6831</v>
+        <v>6882</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2734,10 +2446,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46136.875</v>
+        <v>46140.875</v>
       </c>
       <c r="B86">
-        <v>6638</v>
+        <v>6694</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2748,10 +2460,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46136.88541666666</v>
+        <v>46140.88541666666</v>
       </c>
       <c r="B87">
-        <v>6497</v>
+        <v>6483</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2762,10 +2474,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46136.89583333334</v>
+        <v>46140.89583333334</v>
       </c>
       <c r="B88">
-        <v>6287</v>
+        <v>6329</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2776,10 +2488,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46136.90625</v>
+        <v>46140.90625</v>
       </c>
       <c r="B89">
-        <v>6192</v>
+        <v>6207</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2790,10 +2502,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46136.91666666666</v>
+        <v>46140.91666666666</v>
       </c>
       <c r="B90">
-        <v>6043</v>
+        <v>6150</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2804,10 +2516,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46136.92708333334</v>
+        <v>46140.92708333334</v>
       </c>
       <c r="B91">
-        <v>5947</v>
+        <v>5957</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2818,10 +2530,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46136.9375</v>
+        <v>46140.9375</v>
       </c>
       <c r="B92">
-        <v>5800</v>
+        <v>5818</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2832,10 +2544,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46136.94791666666</v>
+        <v>46140.94791666666</v>
       </c>
       <c r="B93">
-        <v>5743</v>
+        <v>5716</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2846,10 +2558,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46136.95833333334</v>
+        <v>46140.95833333334</v>
       </c>
       <c r="B94">
-        <v>5610</v>
+        <v>5578</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2860,10 +2572,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46136.96875</v>
+        <v>46140.96875</v>
       </c>
       <c r="B95">
-        <v>5525</v>
+        <v>5508</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2874,10 +2586,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46136.97916666666</v>
+        <v>46140.97916666666</v>
       </c>
       <c r="B96">
-        <v>5402</v>
+        <v>5483</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2888,10 +2600,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46136.98958333334</v>
+        <v>46140.98958333334</v>
       </c>
       <c r="B97">
-        <v>5360</v>
+        <v>5394</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2902,10 +2614,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="B98">
-        <v>5308</v>
+        <v>5351</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2916,10 +2628,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46137.01041666666</v>
+        <v>46141.01041666666</v>
       </c>
       <c r="B99">
-        <v>5289</v>
+        <v>5227</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2930,10 +2642,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46137.02083333334</v>
+        <v>46141.02083333334</v>
       </c>
       <c r="B100">
-        <v>5225</v>
+        <v>5199</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2944,10 +2656,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46137.03125</v>
+        <v>46141.03125</v>
       </c>
       <c r="B101">
-        <v>5176</v>
+        <v>5198</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2958,10 +2670,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46137.04166666666</v>
+        <v>46141.04166666666</v>
       </c>
       <c r="B102">
-        <v>5151</v>
+        <v>5266</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2972,10 +2684,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46137.05208333334</v>
+        <v>46141.05208333334</v>
       </c>
       <c r="B103">
-        <v>5123</v>
+        <v>5254</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2986,10 +2698,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46137.0625</v>
+        <v>46141.0625</v>
       </c>
       <c r="B104">
-        <v>5090</v>
+        <v>5217</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -3000,10 +2712,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46137.07291666666</v>
+        <v>46141.07291666666</v>
       </c>
       <c r="B105">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -3014,10 +2726,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46137.08333333334</v>
+        <v>46141.08333333334</v>
       </c>
       <c r="B106">
-        <v>5121</v>
+        <v>5197</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -3028,10 +2740,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46137.09375</v>
+        <v>46141.09375</v>
       </c>
       <c r="B107">
-        <v>5110</v>
+        <v>5233</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -3042,10 +2754,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46137.10416666666</v>
+        <v>46141.10416666666</v>
       </c>
       <c r="B108">
-        <v>5106</v>
+        <v>5221</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -3056,10 +2768,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46137.11458333334</v>
+        <v>46141.11458333334</v>
       </c>
       <c r="B109">
-        <v>5077</v>
+        <v>5196</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -3070,10 +2782,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46137.125</v>
+        <v>46141.125</v>
       </c>
       <c r="B110">
-        <v>5097</v>
+        <v>5187</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -3084,10 +2796,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46137.13541666666</v>
+        <v>46141.13541666666</v>
       </c>
       <c r="B111">
-        <v>5106</v>
+        <v>5236</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -3098,10 +2810,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46137.14583333334</v>
+        <v>46141.14583333334</v>
       </c>
       <c r="B112">
-        <v>5120</v>
+        <v>5305</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -3112,10 +2824,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46137.15625</v>
+        <v>46141.15625</v>
       </c>
       <c r="B113">
-        <v>5054</v>
+        <v>5319</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -3126,10 +2838,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46137.16666666666</v>
+        <v>46141.16666666666</v>
       </c>
       <c r="B114">
-        <v>5077</v>
+        <v>5451</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -3140,10 +2852,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46137.17708333334</v>
+        <v>46141.17708333334</v>
       </c>
       <c r="B115">
-        <v>4755</v>
+        <v>5533</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -3154,10 +2866,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46137.1875</v>
+        <v>46141.1875</v>
       </c>
       <c r="B116">
-        <v>4782</v>
+        <v>5575</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -3168,10 +2880,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46137.19791666666</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="B117">
-        <v>4767</v>
+        <v>5655</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -3182,10 +2894,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46137.20833333334</v>
+        <v>46141.20833333334</v>
       </c>
       <c r="B118">
-        <v>4815</v>
+        <v>5600</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -3196,10 +2908,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46137.21875</v>
+        <v>46141.21875</v>
       </c>
       <c r="B119">
-        <v>4814</v>
+        <v>5685</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -3210,10 +2922,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46137.22916666666</v>
+        <v>46141.22916666666</v>
       </c>
       <c r="B120">
-        <v>5035</v>
+        <v>5722</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -3224,10 +2936,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46137.23958333334</v>
+        <v>46141.23958333334</v>
       </c>
       <c r="B121">
-        <v>5213</v>
+        <v>5864</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -3238,10 +2950,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46137.25</v>
+        <v>46141.25</v>
       </c>
       <c r="B122">
-        <v>5206</v>
+        <v>6109</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -3252,10 +2964,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46137.26041666666</v>
+        <v>46141.26041666666</v>
       </c>
       <c r="B123">
-        <v>5215</v>
+        <v>6167</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -3266,10 +2978,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46137.27083333334</v>
+        <v>46141.27083333334</v>
       </c>
       <c r="B124">
-        <v>5198</v>
+        <v>6218</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -3280,10 +2992,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46137.28125</v>
+        <v>46141.28125</v>
       </c>
       <c r="B125">
-        <v>5123</v>
+        <v>6203</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -3294,10 +3006,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46137.29166666666</v>
+        <v>46141.29166666666</v>
       </c>
       <c r="B126">
-        <v>5079</v>
+        <v>6303</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -3308,10 +3020,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46137.30208333334</v>
+        <v>46141.30208333334</v>
       </c>
       <c r="B127">
-        <v>5037</v>
+        <v>6325</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -3322,10 +3034,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46137.3125</v>
+        <v>46141.3125</v>
       </c>
       <c r="B128">
-        <v>4999</v>
+        <v>6304</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -3336,10 +3048,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46137.32291666666</v>
+        <v>46141.32291666666</v>
       </c>
       <c r="B129">
-        <v>4913</v>
+        <v>6218</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -3350,10 +3062,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46137.33333333334</v>
+        <v>46141.33333333334</v>
       </c>
       <c r="B130">
-        <v>4757</v>
+        <v>6079</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -3364,10 +3076,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46137.34375</v>
+        <v>46141.34375</v>
       </c>
       <c r="B131">
-        <v>4684</v>
+        <v>6020</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -3378,10 +3090,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46137.35416666666</v>
+        <v>46141.35416666666</v>
       </c>
       <c r="B132">
-        <v>4520</v>
+        <v>6004</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -3392,10 +3104,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46137.36458333334</v>
+        <v>46141.36458333334</v>
       </c>
       <c r="B133">
-        <v>4424</v>
+        <v>5852</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -3406,10 +3118,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46137.375</v>
+        <v>46141.375</v>
       </c>
       <c r="B134">
-        <v>4235</v>
+        <v>5796</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -3420,10 +3132,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46137.38541666666</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="B135">
-        <v>4117</v>
+        <v>5755</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -3434,10 +3146,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46137.39583333334</v>
+        <v>46141.39583333334</v>
       </c>
       <c r="B136">
-        <v>4074</v>
+        <v>5661</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -3448,10 +3160,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46137.40625</v>
+        <v>46141.40625</v>
       </c>
       <c r="B137">
-        <v>3958</v>
+        <v>5619</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -3462,10 +3174,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46137.41666666666</v>
+        <v>46141.41666666666</v>
       </c>
       <c r="B138">
-        <v>3950</v>
+        <v>5370</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -3476,10 +3188,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46137.42708333334</v>
+        <v>46141.42708333334</v>
       </c>
       <c r="B139">
-        <v>3929</v>
+        <v>5326</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -3490,10 +3202,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46137.4375</v>
+        <v>46141.4375</v>
       </c>
       <c r="B140">
-        <v>3825</v>
+        <v>5051</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -3504,10 +3216,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46137.44791666666</v>
+        <v>46141.44791666666</v>
       </c>
       <c r="B141">
-        <v>3797</v>
+        <v>4890</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -3518,10 +3230,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46137.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="B142">
-        <v>3741</v>
+        <v>4711</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -3532,10 +3244,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46137.46875</v>
+        <v>46141.46875</v>
       </c>
       <c r="B143">
-        <v>3736</v>
+        <v>4709</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -3546,10 +3258,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46137.47916666666</v>
+        <v>46141.47916666666</v>
       </c>
       <c r="B144">
-        <v>3763</v>
+        <v>4691</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -3560,10 +3272,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46137.48958333334</v>
+        <v>46141.48958333334</v>
       </c>
       <c r="B145">
-        <v>3689</v>
+        <v>4608</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3574,10 +3286,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46137.5</v>
+        <v>46141.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>4641</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3588,10 +3300,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46137.51041666666</v>
+        <v>46141.51041666666</v>
       </c>
       <c r="B147">
-        <v>3649</v>
+        <v>4786</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3602,10 +3314,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46137.52083333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B148">
-        <v>3600</v>
+        <v>4760</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3616,10 +3328,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46137.53125</v>
+        <v>46141.53125</v>
       </c>
       <c r="B149">
-        <v>3580</v>
+        <v>4622</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3630,10 +3342,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46137.54166666666</v>
+        <v>46141.54166666666</v>
       </c>
       <c r="B150">
-        <v>3625</v>
+        <v>4676</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3644,10 +3356,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46137.55208333334</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="B151">
-        <v>3702</v>
+        <v>4697</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3658,10 +3370,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46137.5625</v>
+        <v>46141.5625</v>
       </c>
       <c r="B152">
-        <v>3775</v>
+        <v>4730</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3672,10 +3384,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46137.57291666666</v>
+        <v>46141.57291666666</v>
       </c>
       <c r="B153">
-        <v>3847</v>
+        <v>4765</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3686,10 +3398,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46137.58333333334</v>
+        <v>46141.58333333334</v>
       </c>
       <c r="B154">
-        <v>3952</v>
+        <v>4829</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3700,10 +3412,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46137.59375</v>
+        <v>46141.59375</v>
       </c>
       <c r="B155">
-        <v>3927</v>
+        <v>4969</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3714,10 +3426,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46137.60416666666</v>
+        <v>46141.60416666666</v>
       </c>
       <c r="B156">
-        <v>3857</v>
+        <v>4988</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3728,10 +3440,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46137.61458333334</v>
+        <v>46141.61458333334</v>
       </c>
       <c r="B157">
-        <v>3808</v>
+        <v>5042</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3742,10 +3454,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46137.625</v>
+        <v>46141.625</v>
       </c>
       <c r="B158">
-        <v>3859</v>
+        <v>5195</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3756,10 +3468,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46137.63541666666</v>
+        <v>46141.63541666666</v>
       </c>
       <c r="B159">
-        <v>3918</v>
+        <v>5256</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3770,10 +3482,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46137.64583333334</v>
+        <v>46141.64583333334</v>
       </c>
       <c r="B160">
-        <v>4033</v>
+        <v>5321</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3784,10 +3496,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46137.65625</v>
+        <v>46141.65625</v>
       </c>
       <c r="B161">
-        <v>4094</v>
+        <v>5367</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3798,10 +3510,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46137.66666666666</v>
+        <v>46141.66666666666</v>
       </c>
       <c r="B162">
-        <v>4288</v>
+        <v>5561</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3812,10 +3524,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46137.67708333334</v>
+        <v>46141.67708333334</v>
       </c>
       <c r="B163">
-        <v>4409</v>
+        <v>5671</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3826,10 +3538,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46137.6875</v>
+        <v>46141.6875</v>
       </c>
       <c r="B164">
-        <v>4610</v>
+        <v>5820</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3840,10 +3552,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46137.69791666666</v>
+        <v>46141.69791666666</v>
       </c>
       <c r="B165">
-        <v>4733</v>
+        <v>5918</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3854,10 +3566,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46137.70833333334</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="B166">
-        <v>5055</v>
+        <v>5978</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3868,10 +3580,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46137.71875</v>
+        <v>46141.71875</v>
       </c>
       <c r="B167">
-        <v>5075</v>
+        <v>6125</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3882,10 +3594,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46137.72916666666</v>
+        <v>46141.72916666666</v>
       </c>
       <c r="B168">
-        <v>5239</v>
+        <v>6304</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3896,10 +3608,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46137.73958333334</v>
+        <v>46141.73958333334</v>
       </c>
       <c r="B169">
-        <v>5402</v>
+        <v>6379</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3910,10 +3622,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46137.75</v>
+        <v>46141.75</v>
       </c>
       <c r="B170">
-        <v>5621</v>
+        <v>6532</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3924,10 +3636,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46137.76041666666</v>
+        <v>46141.76041666666</v>
       </c>
       <c r="B171">
-        <v>5754</v>
+        <v>6611</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3938,10 +3650,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46137.77083333334</v>
+        <v>46141.77083333334</v>
       </c>
       <c r="B172">
-        <v>5817</v>
+        <v>6725</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3952,10 +3664,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46137.78125</v>
+        <v>46141.78125</v>
       </c>
       <c r="B173">
-        <v>5914</v>
+        <v>6848</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3966,10 +3678,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46137.79166666666</v>
+        <v>46141.79166666666</v>
       </c>
       <c r="B174">
-        <v>5983</v>
+        <v>6953</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3980,10 +3692,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46137.80208333334</v>
+        <v>46141.80208333334</v>
       </c>
       <c r="B175">
-        <v>6130</v>
+        <v>7003</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3994,10 +3706,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46137.8125</v>
+        <v>46141.8125</v>
       </c>
       <c r="B176">
-        <v>6285</v>
+        <v>7107</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -4008,10 +3720,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46137.82291666666</v>
+        <v>46141.82291666666</v>
       </c>
       <c r="B177">
-        <v>6460</v>
+        <v>7237</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -4022,10 +3734,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46137.83333333334</v>
+        <v>46141.83333333334</v>
       </c>
       <c r="B178">
-        <v>6481</v>
+        <v>7165</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -4036,10 +3748,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46137.84375</v>
+        <v>46141.84375</v>
       </c>
       <c r="B179">
-        <v>6445</v>
+        <v>7115</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -4050,10 +3762,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46137.85416666666</v>
+        <v>46141.85416666666</v>
       </c>
       <c r="B180">
-        <v>6364</v>
+        <v>6981</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -4064,10 +3776,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46137.86458333334</v>
+        <v>46141.86458333334</v>
       </c>
       <c r="B181">
-        <v>6296</v>
+        <v>6877</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -4078,10 +3790,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46137.875</v>
+        <v>46141.875</v>
       </c>
       <c r="B182">
-        <v>6172</v>
+        <v>6779</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -4092,10 +3804,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46137.88541666666</v>
+        <v>46141.88541666666</v>
       </c>
       <c r="B183">
-        <v>6081</v>
+        <v>6639</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -4106,10 +3818,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46137.89583333334</v>
+        <v>46141.89583333334</v>
       </c>
       <c r="B184">
-        <v>5921</v>
+        <v>6531</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -4120,10 +3832,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46137.90625</v>
+        <v>46141.90625</v>
       </c>
       <c r="B185">
-        <v>5857</v>
+        <v>6324</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -4134,10 +3846,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46137.91666666666</v>
+        <v>46141.91666666666</v>
       </c>
       <c r="B186">
-        <v>5684</v>
+        <v>6128</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -4148,10 +3860,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46137.92708333334</v>
+        <v>46141.92708333334</v>
       </c>
       <c r="B187">
-        <v>5577</v>
+        <v>6012</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -4162,10 +3874,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46137.9375</v>
+        <v>46141.9375</v>
       </c>
       <c r="B188">
-        <v>5395</v>
+        <v>5901</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -4176,10 +3888,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46137.94791666666</v>
+        <v>46141.94791666666</v>
       </c>
       <c r="B189">
-        <v>5328</v>
+        <v>5721</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -4190,10 +3902,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46137.95833333334</v>
+        <v>46141.95833333334</v>
       </c>
       <c r="B190">
-        <v>5202</v>
+        <v>5673</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -4204,10 +3916,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46137.96875</v>
+        <v>46141.96875</v>
       </c>
       <c r="B191">
-        <v>5143</v>
+        <v>5580</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -4218,10 +3930,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46137.97916666666</v>
+        <v>46141.97916666666</v>
       </c>
       <c r="B192">
-        <v>5015</v>
+        <v>5531</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -4232,10 +3944,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46137.98958333334</v>
+        <v>46141.98958333334</v>
       </c>
       <c r="B193">
-        <v>5003</v>
+        <v>5468</v>
       </c>
       <c r="C193">
         <v>96</v>
@@ -4246,10 +3958,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="2">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B194">
-        <v>4934</v>
+        <v>5379</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -4260,10 +3972,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="2">
-        <v>46138.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B195">
-        <v>4887</v>
+        <v>5308</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -4274,10 +3986,10 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="2">
-        <v>46138.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B196">
-        <v>4775</v>
+        <v>5299</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -4288,10 +4000,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="2">
-        <v>46138.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B197">
-        <v>4760</v>
+        <v>5318</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -4302,10 +4014,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="2">
-        <v>46138.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B198">
-        <v>4731</v>
+        <v>0</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -4316,10 +4028,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="2">
-        <v>46138.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B199">
-        <v>4737</v>
+        <v>5260</v>
       </c>
       <c r="C199">
         <v>6</v>
@@ -4330,10 +4042,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="2">
-        <v>46138.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B200">
-        <v>4693</v>
+        <v>5279</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -4344,10 +4056,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="2">
-        <v>46138.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B201">
-        <v>4664</v>
+        <v>5241</v>
       </c>
       <c r="C201">
         <v>8</v>
@@ -4358,10 +4070,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="2">
-        <v>46138.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B202">
-        <v>4702</v>
+        <v>5021</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -4372,10 +4084,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="2">
-        <v>46138.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B203">
-        <v>4690</v>
+        <v>4859</v>
       </c>
       <c r="C203">
         <v>10</v>
@@ -4386,10 +4098,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="2">
-        <v>46138.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B204">
-        <v>4619</v>
+        <v>4872</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -4400,10 +4112,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="2">
-        <v>46138.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B205">
-        <v>4641</v>
+        <v>4867</v>
       </c>
       <c r="C205">
         <v>12</v>
@@ -4414,10 +4126,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="2">
-        <v>46138.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B206">
-        <v>4669</v>
+        <v>4837</v>
       </c>
       <c r="C206">
         <v>13</v>
@@ -4428,10 +4140,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="2">
-        <v>46138.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B207">
-        <v>4666</v>
+        <v>4872</v>
       </c>
       <c r="C207">
         <v>14</v>
@@ -4442,10 +4154,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="2">
-        <v>46138.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B208">
-        <v>4679</v>
+        <v>4930</v>
       </c>
       <c r="C208">
         <v>15</v>
@@ -4456,10 +4168,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="2">
-        <v>46138.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B209">
-        <v>4675</v>
+        <v>4865</v>
       </c>
       <c r="C209">
         <v>16</v>
@@ -4470,10 +4182,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="2">
-        <v>46138.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B210">
-        <v>4656</v>
+        <v>4874</v>
       </c>
       <c r="C210">
         <v>17</v>
@@ -4484,10 +4196,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="2">
-        <v>46138.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B211">
-        <v>4652</v>
+        <v>5437</v>
       </c>
       <c r="C211">
         <v>18</v>
@@ -4498,10 +4210,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="2">
-        <v>46138.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B212">
-        <v>4635</v>
+        <v>5576</v>
       </c>
       <c r="C212">
         <v>19</v>
@@ -4512,10 +4224,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="2">
-        <v>46138.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B213">
-        <v>4610</v>
+        <v>5596</v>
       </c>
       <c r="C213">
         <v>20</v>
@@ -4526,10 +4238,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="2">
-        <v>46138.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B214">
-        <v>4573</v>
+        <v>5609</v>
       </c>
       <c r="C214">
         <v>21</v>
@@ -4540,10 +4252,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="2">
-        <v>46138.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B215">
-        <v>4642</v>
+        <v>5724</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -4554,10 +4266,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="2">
-        <v>46138.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B216">
-        <v>4630</v>
+        <v>5907</v>
       </c>
       <c r="C216">
         <v>23</v>
@@ -4568,10 +4280,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="2">
-        <v>46138.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B217">
-        <v>4526</v>
+        <v>6050</v>
       </c>
       <c r="C217">
         <v>24</v>
@@ -4582,10 +4294,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="2">
-        <v>46138.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B218">
-        <v>4505</v>
+        <v>6319</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -4596,10 +4308,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="2">
-        <v>46138.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B219">
-        <v>4479</v>
+        <v>6425</v>
       </c>
       <c r="C219">
         <v>26</v>
@@ -4610,10 +4322,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="2">
-        <v>46138.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B220">
-        <v>4426</v>
+        <v>6508</v>
       </c>
       <c r="C220">
         <v>27</v>
@@ -4624,10 +4336,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="2">
-        <v>46138.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B221">
-        <v>4365</v>
+        <v>6573</v>
       </c>
       <c r="C221">
         <v>28</v>
@@ -4638,10 +4350,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="2">
-        <v>46138.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B222">
-        <v>4275</v>
+        <v>6712</v>
       </c>
       <c r="C222">
         <v>29</v>
@@ -4652,10 +4364,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="2">
-        <v>46138.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B223">
-        <v>4166</v>
+        <v>6887</v>
       </c>
       <c r="C223">
         <v>30</v>
@@ -4666,10 +4378,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="2">
-        <v>46138.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B224">
-        <v>4012</v>
+        <v>6879</v>
       </c>
       <c r="C224">
         <v>31</v>
@@ -4680,10 +4392,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="2">
-        <v>46138.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B225">
-        <v>3887</v>
+        <v>6788</v>
       </c>
       <c r="C225">
         <v>32</v>
@@ -4694,10 +4406,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="2">
-        <v>46138.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B226">
-        <v>3775</v>
+        <v>6738</v>
       </c>
       <c r="C226">
         <v>33</v>
@@ -4708,10 +4420,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="2">
-        <v>46138.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B227">
-        <v>3634</v>
+        <v>6813</v>
       </c>
       <c r="C227">
         <v>34</v>
@@ -4722,10 +4434,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="2">
-        <v>46138.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B228">
-        <v>3566</v>
+        <v>6723</v>
       </c>
       <c r="C228">
         <v>35</v>
@@ -4736,10 +4448,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="2">
-        <v>46138.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B229">
-        <v>3473</v>
+        <v>6650</v>
       </c>
       <c r="C229">
         <v>36</v>
@@ -4750,10 +4462,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="2">
-        <v>46138.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B230">
-        <v>3366</v>
+        <v>6630</v>
       </c>
       <c r="C230">
         <v>37</v>
@@ -4764,10 +4476,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="2">
-        <v>46138.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B231">
-        <v>3269</v>
+        <v>6540</v>
       </c>
       <c r="C231">
         <v>38</v>
@@ -4778,10 +4490,10 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="2">
-        <v>46138.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B232">
-        <v>3192</v>
+        <v>6409</v>
       </c>
       <c r="C232">
         <v>39</v>
@@ -4792,10 +4504,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="2">
-        <v>46138.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B233">
-        <v>3076</v>
+        <v>6429</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -4806,10 +4518,10 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="2">
-        <v>46138.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B234">
-        <v>2973</v>
+        <v>6245</v>
       </c>
       <c r="C234">
         <v>41</v>
@@ -4820,10 +4532,10 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="2">
-        <v>46138.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B235">
-        <v>2991</v>
+        <v>6260</v>
       </c>
       <c r="C235">
         <v>42</v>
@@ -4834,10 +4546,10 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="2">
-        <v>46138.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B236">
-        <v>2944</v>
+        <v>6170</v>
       </c>
       <c r="C236">
         <v>43</v>
@@ -4848,10 +4560,10 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="2">
-        <v>46138.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B237">
-        <v>2907</v>
+        <v>6093</v>
       </c>
       <c r="C237">
         <v>44</v>
@@ -4862,10 +4574,10 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="2">
-        <v>46138.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B238">
-        <v>2931</v>
+        <v>6089</v>
       </c>
       <c r="C238">
         <v>45</v>
@@ -4876,10 +4588,10 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="2">
-        <v>46138.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B239">
-        <v>2914</v>
+        <v>0</v>
       </c>
       <c r="C239">
         <v>46</v>
@@ -4890,10 +4602,10 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="2">
-        <v>46138.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B240">
-        <v>2890</v>
+        <v>0</v>
       </c>
       <c r="C240">
         <v>47</v>
@@ -4904,10 +4616,10 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="2">
-        <v>46138.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B241">
-        <v>2930</v>
+        <v>0</v>
       </c>
       <c r="C241">
         <v>48</v>
@@ -4918,10 +4630,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="2">
-        <v>46138.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B242">
-        <v>3001</v>
+        <v>0</v>
       </c>
       <c r="C242">
         <v>49</v>
@@ -4932,10 +4644,10 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="2">
-        <v>46138.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B243">
-        <v>3036</v>
+        <v>0</v>
       </c>
       <c r="C243">
         <v>50</v>
@@ -4946,10 +4658,10 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="2">
-        <v>46138.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B244">
-        <v>3059</v>
+        <v>0</v>
       </c>
       <c r="C244">
         <v>51</v>
@@ -4960,10 +4672,10 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="2">
-        <v>46138.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B245">
-        <v>2994</v>
+        <v>0</v>
       </c>
       <c r="C245">
         <v>52</v>
@@ -4974,10 +4686,10 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="2">
-        <v>46138.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B246">
-        <v>3034</v>
+        <v>0</v>
       </c>
       <c r="C246">
         <v>53</v>
@@ -4988,10 +4700,10 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="2">
-        <v>46138.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B247">
-        <v>3006</v>
+        <v>0</v>
       </c>
       <c r="C247">
         <v>54</v>
@@ -5002,10 +4714,10 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="2">
-        <v>46138.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B248">
-        <v>2951</v>
+        <v>0</v>
       </c>
       <c r="C248">
         <v>55</v>
@@ -5016,10 +4728,10 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="2">
-        <v>46138.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B249">
-        <v>2925</v>
+        <v>0</v>
       </c>
       <c r="C249">
         <v>56</v>
@@ -5030,10 +4742,10 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="2">
-        <v>46138.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B250">
-        <v>2941</v>
+        <v>0</v>
       </c>
       <c r="C250">
         <v>57</v>
@@ -5044,10 +4756,10 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="2">
-        <v>46138.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B251">
-        <v>2937</v>
+        <v>0</v>
       </c>
       <c r="C251">
         <v>58</v>
@@ -5058,10 +4770,10 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="2">
-        <v>46138.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B252">
-        <v>2979</v>
+        <v>0</v>
       </c>
       <c r="C252">
         <v>59</v>
@@ -5072,10 +4784,10 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="2">
-        <v>46138.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B253">
-        <v>3011</v>
+        <v>0</v>
       </c>
       <c r="C253">
         <v>60</v>
@@ -5086,10 +4798,10 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="2">
-        <v>46138.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B254">
-        <v>3094</v>
+        <v>0</v>
       </c>
       <c r="C254">
         <v>61</v>
@@ -5100,10 +4812,10 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="2">
-        <v>46138.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B255">
-        <v>3158</v>
+        <v>0</v>
       </c>
       <c r="C255">
         <v>62</v>
@@ -5114,10 +4826,10 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="2">
-        <v>46138.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B256">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="C256">
         <v>63</v>
@@ -5128,10 +4840,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="2">
-        <v>46138.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B257">
-        <v>3411</v>
+        <v>0</v>
       </c>
       <c r="C257">
         <v>64</v>
@@ -5142,10 +4854,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="2">
-        <v>46138.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B258">
-        <v>3549</v>
+        <v>0</v>
       </c>
       <c r="C258">
         <v>65</v>
@@ -5156,10 +4868,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="2">
-        <v>46138.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B259">
-        <v>3771</v>
+        <v>0</v>
       </c>
       <c r="C259">
         <v>66</v>
@@ -5170,10 +4882,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="2">
-        <v>46138.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B260">
-        <v>3932</v>
+        <v>0</v>
       </c>
       <c r="C260">
         <v>67</v>
@@ -5184,10 +4896,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="2">
-        <v>46138.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B261">
-        <v>4105</v>
+        <v>0</v>
       </c>
       <c r="C261">
         <v>68</v>
@@ -5198,10 +4910,10 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="2">
-        <v>46138.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B262">
-        <v>4516</v>
+        <v>0</v>
       </c>
       <c r="C262">
         <v>69</v>
@@ -5212,10 +4924,10 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="2">
-        <v>46138.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B263">
-        <v>4502</v>
+        <v>0</v>
       </c>
       <c r="C263">
         <v>70</v>
@@ -5226,10 +4938,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="2">
-        <v>46138.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B264">
-        <v>4601</v>
+        <v>0</v>
       </c>
       <c r="C264">
         <v>71</v>
@@ -5240,10 +4952,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="2">
-        <v>46138.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B265">
-        <v>4834</v>
+        <v>0</v>
       </c>
       <c r="C265">
         <v>72</v>
@@ -5254,10 +4966,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="2">
-        <v>46138.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B266">
-        <v>5051</v>
+        <v>0</v>
       </c>
       <c r="C266">
         <v>73</v>
@@ -5268,10 +4980,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="2">
-        <v>46138.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B267">
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="C267">
         <v>74</v>
@@ -5282,10 +4994,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="2">
-        <v>46138.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B268">
-        <v>5417</v>
+        <v>0</v>
       </c>
       <c r="C268">
         <v>75</v>
@@ -5296,10 +5008,10 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="2">
-        <v>46138.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B269">
-        <v>5564</v>
+        <v>0</v>
       </c>
       <c r="C269">
         <v>76</v>
@@ -5310,10 +5022,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="2">
-        <v>46138.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B270">
-        <v>5662</v>
+        <v>0</v>
       </c>
       <c r="C270">
         <v>77</v>
@@ -5324,10 +5036,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="2">
-        <v>46138.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B271">
-        <v>5796</v>
+        <v>0</v>
       </c>
       <c r="C271">
         <v>78</v>
@@ -5338,10 +5050,10 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="2">
-        <v>46138.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B272">
-        <v>5983</v>
+        <v>0</v>
       </c>
       <c r="C272">
         <v>79</v>
@@ -5352,10 +5064,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="2">
-        <v>46138.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B273">
-        <v>6086</v>
+        <v>0</v>
       </c>
       <c r="C273">
         <v>80</v>
@@ -5366,10 +5078,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="2">
-        <v>46138.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B274">
-        <v>6129</v>
+        <v>0</v>
       </c>
       <c r="C274">
         <v>81</v>
@@ -5380,10 +5092,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="2">
-        <v>46138.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B275">
-        <v>6128</v>
+        <v>0</v>
       </c>
       <c r="C275">
         <v>82</v>
@@ -5394,10 +5106,10 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="2">
-        <v>46138.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B276">
-        <v>6087</v>
+        <v>0</v>
       </c>
       <c r="C276">
         <v>83</v>
@@ -5408,10 +5120,10 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="2">
-        <v>46138.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B277">
-        <v>6042</v>
+        <v>0</v>
       </c>
       <c r="C277">
         <v>84</v>
@@ -5422,10 +5134,10 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="2">
-        <v>46138.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B278">
-        <v>5870</v>
+        <v>0</v>
       </c>
       <c r="C278">
         <v>85</v>
@@ -5436,10 +5148,10 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="2">
-        <v>46138.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B279">
-        <v>5803</v>
+        <v>0</v>
       </c>
       <c r="C279">
         <v>86</v>
@@ -5450,10 +5162,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="2">
-        <v>46138.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B280">
-        <v>5704</v>
+        <v>0</v>
       </c>
       <c r="C280">
         <v>87</v>
@@ -5464,10 +5176,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="2">
-        <v>46138.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B281">
-        <v>5611</v>
+        <v>0</v>
       </c>
       <c r="C281">
         <v>88</v>
@@ -5478,10 +5190,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="2">
-        <v>46138.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B282">
-        <v>5419</v>
+        <v>0</v>
       </c>
       <c r="C282">
         <v>89</v>
@@ -5492,10 +5204,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="2">
-        <v>46138.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B283">
-        <v>5283</v>
+        <v>0</v>
       </c>
       <c r="C283">
         <v>90</v>
@@ -5506,10 +5218,10 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="2">
-        <v>46138.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B284">
-        <v>5184</v>
+        <v>0</v>
       </c>
       <c r="C284">
         <v>91</v>
@@ -5520,10 +5232,10 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="2">
-        <v>46138.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B285">
-        <v>5111</v>
+        <v>0</v>
       </c>
       <c r="C285">
         <v>92</v>
@@ -5534,10 +5246,10 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="2">
-        <v>46138.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B286">
-        <v>5011</v>
+        <v>0</v>
       </c>
       <c r="C286">
         <v>93</v>
@@ -5548,10 +5260,10 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="2">
-        <v>46138.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B287">
-        <v>4949</v>
+        <v>0</v>
       </c>
       <c r="C287">
         <v>94</v>
@@ -5562,10 +5274,10 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="2">
-        <v>46138.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B288">
-        <v>4889</v>
+        <v>0</v>
       </c>
       <c r="C288">
         <v>95</v>
@@ -5576,1360 +5288,16 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="2">
-        <v>46138.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B289">
-        <v>4899</v>
+        <v>0</v>
       </c>
       <c r="C289">
         <v>96</v>
       </c>
       <c r="D289" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4">
-      <c r="A290" s="2">
-        <v>46139</v>
-      </c>
-      <c r="B290">
-        <v>4796</v>
-      </c>
-      <c r="C290">
-        <v>1</v>
-      </c>
-      <c r="D290" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4">
-      <c r="A291" s="2">
-        <v>46139.01041666666</v>
-      </c>
-      <c r="B291">
-        <v>4722</v>
-      </c>
-      <c r="C291">
-        <v>2</v>
-      </c>
-      <c r="D291" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
-      <c r="A292" s="2">
-        <v>46139.02083333334</v>
-      </c>
-      <c r="B292">
-        <v>4754</v>
-      </c>
-      <c r="C292">
-        <v>3</v>
-      </c>
-      <c r="D292" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
-      <c r="A293" s="2">
-        <v>46139.03125</v>
-      </c>
-      <c r="B293">
-        <v>4712</v>
-      </c>
-      <c r="C293">
-        <v>4</v>
-      </c>
-      <c r="D293" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
-      <c r="A294" s="2">
-        <v>46139.04166666666</v>
-      </c>
-      <c r="B294">
-        <v>4752</v>
-      </c>
-      <c r="C294">
-        <v>5</v>
-      </c>
-      <c r="D294" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
-      <c r="A295" s="2">
-        <v>46139.05208333334</v>
-      </c>
-      <c r="B295">
-        <v>4742</v>
-      </c>
-      <c r="C295">
-        <v>6</v>
-      </c>
-      <c r="D295" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
-      <c r="A296" s="2">
-        <v>46139.0625</v>
-      </c>
-      <c r="B296">
-        <v>4691</v>
-      </c>
-      <c r="C296">
-        <v>7</v>
-      </c>
-      <c r="D296" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4">
-      <c r="A297" s="2">
-        <v>46139.07291666666</v>
-      </c>
-      <c r="B297">
-        <v>4718</v>
-      </c>
-      <c r="C297">
-        <v>8</v>
-      </c>
-      <c r="D297" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4">
-      <c r="A298" s="2">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="B298">
-        <v>4799</v>
-      </c>
-      <c r="C298">
-        <v>9</v>
-      </c>
-      <c r="D298" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
-      <c r="A299" s="2">
-        <v>46139.09375</v>
-      </c>
-      <c r="B299">
-        <v>4807</v>
-      </c>
-      <c r="C299">
-        <v>10</v>
-      </c>
-      <c r="D299" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4">
-      <c r="A300" s="2">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="B300">
-        <v>4722</v>
-      </c>
-      <c r="C300">
-        <v>11</v>
-      </c>
-      <c r="D300" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4">
-      <c r="A301" s="2">
-        <v>46139.11458333334</v>
-      </c>
-      <c r="B301">
-        <v>4745</v>
-      </c>
-      <c r="C301">
-        <v>12</v>
-      </c>
-      <c r="D301" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
-      <c r="A302" s="2">
-        <v>46139.125</v>
-      </c>
-      <c r="B302">
-        <v>4758</v>
-      </c>
-      <c r="C302">
-        <v>13</v>
-      </c>
-      <c r="D302" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
-      <c r="A303" s="2">
-        <v>46139.13541666666</v>
-      </c>
-      <c r="B303">
-        <v>4735</v>
-      </c>
-      <c r="C303">
-        <v>14</v>
-      </c>
-      <c r="D303" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4">
-      <c r="A304" s="2">
-        <v>46139.14583333334</v>
-      </c>
-      <c r="B304">
-        <v>4666</v>
-      </c>
-      <c r="C304">
-        <v>15</v>
-      </c>
-      <c r="D304" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4">
-      <c r="A305" s="2">
-        <v>46139.15625</v>
-      </c>
-      <c r="B305">
-        <v>4689</v>
-      </c>
-      <c r="C305">
-        <v>16</v>
-      </c>
-      <c r="D305" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4">
-      <c r="A306" s="2">
-        <v>46139.16666666666</v>
-      </c>
-      <c r="B306">
-        <v>4782</v>
-      </c>
-      <c r="C306">
-        <v>17</v>
-      </c>
-      <c r="D306" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4">
-      <c r="A307" s="2">
-        <v>46139.17708333334</v>
-      </c>
-      <c r="B307">
-        <v>4839</v>
-      </c>
-      <c r="C307">
-        <v>18</v>
-      </c>
-      <c r="D307" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4">
-      <c r="A308" s="2">
-        <v>46139.1875</v>
-      </c>
-      <c r="B308">
-        <v>4929</v>
-      </c>
-      <c r="C308">
-        <v>19</v>
-      </c>
-      <c r="D308" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
-      <c r="A309" s="2">
-        <v>46139.19791666666</v>
-      </c>
-      <c r="B309">
-        <v>5025</v>
-      </c>
-      <c r="C309">
-        <v>20</v>
-      </c>
-      <c r="D309" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4">
-      <c r="A310" s="2">
-        <v>46139.20833333334</v>
-      </c>
-      <c r="B310">
-        <v>5223</v>
-      </c>
-      <c r="C310">
-        <v>21</v>
-      </c>
-      <c r="D310" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
-      <c r="A311" s="2">
-        <v>46139.21875</v>
-      </c>
-      <c r="B311">
-        <v>5336</v>
-      </c>
-      <c r="C311">
-        <v>22</v>
-      </c>
-      <c r="D311" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4">
-      <c r="A312" s="2">
-        <v>46139.22916666666</v>
-      </c>
-      <c r="B312">
-        <v>5468</v>
-      </c>
-      <c r="C312">
-        <v>23</v>
-      </c>
-      <c r="D312" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4">
-      <c r="A313" s="2">
-        <v>46139.23958333334</v>
-      </c>
-      <c r="B313">
-        <v>5622</v>
-      </c>
-      <c r="C313">
-        <v>24</v>
-      </c>
-      <c r="D313" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4">
-      <c r="A314" s="2">
-        <v>46139.25</v>
-      </c>
-      <c r="B314">
-        <v>5856</v>
-      </c>
-      <c r="C314">
-        <v>25</v>
-      </c>
-      <c r="D314" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4">
-      <c r="A315" s="2">
-        <v>46139.26041666666</v>
-      </c>
-      <c r="B315">
-        <v>5967</v>
-      </c>
-      <c r="C315">
-        <v>26</v>
-      </c>
-      <c r="D315" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4">
-      <c r="A316" s="2">
-        <v>46139.27083333334</v>
-      </c>
-      <c r="B316">
-        <v>5969</v>
-      </c>
-      <c r="C316">
-        <v>27</v>
-      </c>
-      <c r="D316" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4">
-      <c r="A317" s="2">
-        <v>46139.28125</v>
-      </c>
-      <c r="B317">
-        <v>5985</v>
-      </c>
-      <c r="C317">
-        <v>28</v>
-      </c>
-      <c r="D317" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4">
-      <c r="A318" s="2">
-        <v>46139.29166666666</v>
-      </c>
-      <c r="B318">
-        <v>6071</v>
-      </c>
-      <c r="C318">
-        <v>29</v>
-      </c>
-      <c r="D318" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4">
-      <c r="A319" s="2">
-        <v>46139.30208333334</v>
-      </c>
-      <c r="B319">
-        <v>6032</v>
-      </c>
-      <c r="C319">
-        <v>30</v>
-      </c>
-      <c r="D319" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4">
-      <c r="A320" s="2">
-        <v>46139.3125</v>
-      </c>
-      <c r="B320">
-        <v>5947</v>
-      </c>
-      <c r="C320">
-        <v>31</v>
-      </c>
-      <c r="D320" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4">
-      <c r="A321" s="2">
-        <v>46139.32291666666</v>
-      </c>
-      <c r="B321">
-        <v>5757</v>
-      </c>
-      <c r="C321">
-        <v>32</v>
-      </c>
-      <c r="D321" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4">
-      <c r="A322" s="2">
-        <v>46139.33333333334</v>
-      </c>
-      <c r="B322">
-        <v>5571</v>
-      </c>
-      <c r="C322">
-        <v>33</v>
-      </c>
-      <c r="D322" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4">
-      <c r="A323" s="2">
-        <v>46139.34375</v>
-      </c>
-      <c r="B323">
-        <v>5425</v>
-      </c>
-      <c r="C323">
-        <v>34</v>
-      </c>
-      <c r="D323" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4">
-      <c r="A324" s="2">
-        <v>46139.35416666666</v>
-      </c>
-      <c r="B324">
-        <v>5187</v>
-      </c>
-      <c r="C324">
-        <v>35</v>
-      </c>
-      <c r="D324" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4">
-      <c r="A325" s="2">
-        <v>46139.36458333334</v>
-      </c>
-      <c r="B325">
-        <v>5075</v>
-      </c>
-      <c r="C325">
-        <v>36</v>
-      </c>
-      <c r="D325" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4">
-      <c r="A326" s="2">
-        <v>46139.375</v>
-      </c>
-      <c r="B326">
-        <v>4876</v>
-      </c>
-      <c r="C326">
-        <v>37</v>
-      </c>
-      <c r="D326" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4">
-      <c r="A327" s="2">
-        <v>46139.38541666666</v>
-      </c>
-      <c r="B327">
-        <v>4765</v>
-      </c>
-      <c r="C327">
-        <v>38</v>
-      </c>
-      <c r="D327" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4">
-      <c r="A328" s="2">
-        <v>46139.39583333334</v>
-      </c>
-      <c r="B328">
-        <v>4560</v>
-      </c>
-      <c r="C328">
-        <v>39</v>
-      </c>
-      <c r="D328" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4">
-      <c r="A329" s="2">
-        <v>46139.40625</v>
-      </c>
-      <c r="B329">
-        <v>4442</v>
-      </c>
-      <c r="C329">
-        <v>40</v>
-      </c>
-      <c r="D329" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4">
-      <c r="A330" s="2">
-        <v>46139.41666666666</v>
-      </c>
-      <c r="B330">
-        <v>4349</v>
-      </c>
-      <c r="C330">
-        <v>41</v>
-      </c>
-      <c r="D330" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4">
-      <c r="A331" s="2">
-        <v>46139.42708333334</v>
-      </c>
-      <c r="B331">
-        <v>4153</v>
-      </c>
-      <c r="C331">
-        <v>42</v>
-      </c>
-      <c r="D331" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4">
-      <c r="A332" s="2">
-        <v>46139.4375</v>
-      </c>
-      <c r="B332">
-        <v>4053</v>
-      </c>
-      <c r="C332">
-        <v>43</v>
-      </c>
-      <c r="D332" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4">
-      <c r="A333" s="2">
-        <v>46139.44791666666</v>
-      </c>
-      <c r="B333">
-        <v>3989</v>
-      </c>
-      <c r="C333">
-        <v>44</v>
-      </c>
-      <c r="D333" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4">
-      <c r="A334" s="2">
-        <v>46139.45833333334</v>
-      </c>
-      <c r="B334">
-        <v>4008</v>
-      </c>
-      <c r="C334">
-        <v>45</v>
-      </c>
-      <c r="D334" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4">
-      <c r="A335" s="2">
-        <v>46139.46875</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-      <c r="C335">
-        <v>46</v>
-      </c>
-      <c r="D335" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4">
-      <c r="A336" s="2">
-        <v>46139.47916666666</v>
-      </c>
-      <c r="B336">
-        <v>0</v>
-      </c>
-      <c r="C336">
-        <v>47</v>
-      </c>
-      <c r="D336" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4">
-      <c r="A337" s="2">
-        <v>46139.48958333334</v>
-      </c>
-      <c r="B337">
-        <v>0</v>
-      </c>
-      <c r="C337">
-        <v>48</v>
-      </c>
-      <c r="D337" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4">
-      <c r="A338" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B338">
-        <v>0</v>
-      </c>
-      <c r="C338">
-        <v>49</v>
-      </c>
-      <c r="D338" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4">
-      <c r="A339" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B339">
-        <v>0</v>
-      </c>
-      <c r="C339">
-        <v>50</v>
-      </c>
-      <c r="D339" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4">
-      <c r="A340" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B340">
-        <v>0</v>
-      </c>
-      <c r="C340">
-        <v>51</v>
-      </c>
-      <c r="D340" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4">
-      <c r="A341" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B341">
-        <v>0</v>
-      </c>
-      <c r="C341">
-        <v>52</v>
-      </c>
-      <c r="D341" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4">
-      <c r="A342" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B342">
-        <v>0</v>
-      </c>
-      <c r="C342">
-        <v>53</v>
-      </c>
-      <c r="D342" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4">
-      <c r="A343" s="2">
-        <v>46139.55208333334</v>
-      </c>
-      <c r="B343">
-        <v>0</v>
-      </c>
-      <c r="C343">
-        <v>54</v>
-      </c>
-      <c r="D343" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4">
-      <c r="A344" s="2">
-        <v>46139.5625</v>
-      </c>
-      <c r="B344">
-        <v>0</v>
-      </c>
-      <c r="C344">
-        <v>55</v>
-      </c>
-      <c r="D344" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4">
-      <c r="A345" s="2">
-        <v>46139.57291666666</v>
-      </c>
-      <c r="B345">
-        <v>0</v>
-      </c>
-      <c r="C345">
-        <v>56</v>
-      </c>
-      <c r="D345" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4">
-      <c r="A346" s="2">
-        <v>46139.58333333334</v>
-      </c>
-      <c r="B346">
-        <v>0</v>
-      </c>
-      <c r="C346">
-        <v>57</v>
-      </c>
-      <c r="D346" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4">
-      <c r="A347" s="2">
-        <v>46139.59375</v>
-      </c>
-      <c r="B347">
-        <v>0</v>
-      </c>
-      <c r="C347">
-        <v>58</v>
-      </c>
-      <c r="D347" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4">
-      <c r="A348" s="2">
-        <v>46139.60416666666</v>
-      </c>
-      <c r="B348">
-        <v>0</v>
-      </c>
-      <c r="C348">
-        <v>59</v>
-      </c>
-      <c r="D348" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4">
-      <c r="A349" s="2">
-        <v>46139.61458333334</v>
-      </c>
-      <c r="B349">
-        <v>0</v>
-      </c>
-      <c r="C349">
-        <v>60</v>
-      </c>
-      <c r="D349" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4">
-      <c r="A350" s="2">
-        <v>46139.625</v>
-      </c>
-      <c r="B350">
-        <v>0</v>
-      </c>
-      <c r="C350">
-        <v>61</v>
-      </c>
-      <c r="D350" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4">
-      <c r="A351" s="2">
-        <v>46139.63541666666</v>
-      </c>
-      <c r="B351">
-        <v>0</v>
-      </c>
-      <c r="C351">
-        <v>62</v>
-      </c>
-      <c r="D351" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4">
-      <c r="A352" s="2">
-        <v>46139.64583333334</v>
-      </c>
-      <c r="B352">
-        <v>0</v>
-      </c>
-      <c r="C352">
-        <v>63</v>
-      </c>
-      <c r="D352" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4">
-      <c r="A353" s="2">
-        <v>46139.65625</v>
-      </c>
-      <c r="B353">
-        <v>0</v>
-      </c>
-      <c r="C353">
-        <v>64</v>
-      </c>
-      <c r="D353" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4">
-      <c r="A354" s="2">
-        <v>46139.66666666666</v>
-      </c>
-      <c r="B354">
-        <v>0</v>
-      </c>
-      <c r="C354">
-        <v>65</v>
-      </c>
-      <c r="D354" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4">
-      <c r="A355" s="2">
-        <v>46139.67708333334</v>
-      </c>
-      <c r="B355">
-        <v>0</v>
-      </c>
-      <c r="C355">
-        <v>66</v>
-      </c>
-      <c r="D355" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4">
-      <c r="A356" s="2">
-        <v>46139.6875</v>
-      </c>
-      <c r="B356">
-        <v>0</v>
-      </c>
-      <c r="C356">
-        <v>67</v>
-      </c>
-      <c r="D356" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4">
-      <c r="A357" s="2">
-        <v>46139.69791666666</v>
-      </c>
-      <c r="B357">
-        <v>0</v>
-      </c>
-      <c r="C357">
-        <v>68</v>
-      </c>
-      <c r="D357" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4">
-      <c r="A358" s="2">
-        <v>46139.70833333334</v>
-      </c>
-      <c r="B358">
-        <v>0</v>
-      </c>
-      <c r="C358">
-        <v>69</v>
-      </c>
-      <c r="D358" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4">
-      <c r="A359" s="2">
-        <v>46139.71875</v>
-      </c>
-      <c r="B359">
-        <v>0</v>
-      </c>
-      <c r="C359">
-        <v>70</v>
-      </c>
-      <c r="D359" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4">
-      <c r="A360" s="2">
-        <v>46139.72916666666</v>
-      </c>
-      <c r="B360">
-        <v>0</v>
-      </c>
-      <c r="C360">
-        <v>71</v>
-      </c>
-      <c r="D360" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4">
-      <c r="A361" s="2">
-        <v>46139.73958333334</v>
-      </c>
-      <c r="B361">
-        <v>0</v>
-      </c>
-      <c r="C361">
-        <v>72</v>
-      </c>
-      <c r="D361" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4">
-      <c r="A362" s="2">
-        <v>46139.75</v>
-      </c>
-      <c r="B362">
-        <v>0</v>
-      </c>
-      <c r="C362">
-        <v>73</v>
-      </c>
-      <c r="D362" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4">
-      <c r="A363" s="2">
-        <v>46139.76041666666</v>
-      </c>
-      <c r="B363">
-        <v>0</v>
-      </c>
-      <c r="C363">
-        <v>74</v>
-      </c>
-      <c r="D363" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4">
-      <c r="A364" s="2">
-        <v>46139.77083333334</v>
-      </c>
-      <c r="B364">
-        <v>0</v>
-      </c>
-      <c r="C364">
-        <v>75</v>
-      </c>
-      <c r="D364" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4">
-      <c r="A365" s="2">
-        <v>46139.78125</v>
-      </c>
-      <c r="B365">
-        <v>0</v>
-      </c>
-      <c r="C365">
-        <v>76</v>
-      </c>
-      <c r="D365" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4">
-      <c r="A366" s="2">
-        <v>46139.79166666666</v>
-      </c>
-      <c r="B366">
-        <v>0</v>
-      </c>
-      <c r="C366">
-        <v>77</v>
-      </c>
-      <c r="D366" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4">
-      <c r="A367" s="2">
-        <v>46139.80208333334</v>
-      </c>
-      <c r="B367">
-        <v>0</v>
-      </c>
-      <c r="C367">
-        <v>78</v>
-      </c>
-      <c r="D367" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4">
-      <c r="A368" s="2">
-        <v>46139.8125</v>
-      </c>
-      <c r="B368">
-        <v>0</v>
-      </c>
-      <c r="C368">
-        <v>79</v>
-      </c>
-      <c r="D368" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4">
-      <c r="A369" s="2">
-        <v>46139.82291666666</v>
-      </c>
-      <c r="B369">
-        <v>0</v>
-      </c>
-      <c r="C369">
-        <v>80</v>
-      </c>
-      <c r="D369" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4">
-      <c r="A370" s="2">
-        <v>46139.83333333334</v>
-      </c>
-      <c r="B370">
-        <v>0</v>
-      </c>
-      <c r="C370">
-        <v>81</v>
-      </c>
-      <c r="D370" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4">
-      <c r="A371" s="2">
-        <v>46139.84375</v>
-      </c>
-      <c r="B371">
-        <v>0</v>
-      </c>
-      <c r="C371">
-        <v>82</v>
-      </c>
-      <c r="D371" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4">
-      <c r="A372" s="2">
-        <v>46139.85416666666</v>
-      </c>
-      <c r="B372">
-        <v>0</v>
-      </c>
-      <c r="C372">
-        <v>83</v>
-      </c>
-      <c r="D372" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4">
-      <c r="A373" s="2">
-        <v>46139.86458333334</v>
-      </c>
-      <c r="B373">
-        <v>0</v>
-      </c>
-      <c r="C373">
-        <v>84</v>
-      </c>
-      <c r="D373" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4">
-      <c r="A374" s="2">
-        <v>46139.875</v>
-      </c>
-      <c r="B374">
-        <v>0</v>
-      </c>
-      <c r="C374">
-        <v>85</v>
-      </c>
-      <c r="D374" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4">
-      <c r="A375" s="2">
-        <v>46139.88541666666</v>
-      </c>
-      <c r="B375">
-        <v>0</v>
-      </c>
-      <c r="C375">
-        <v>86</v>
-      </c>
-      <c r="D375" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4">
-      <c r="A376" s="2">
-        <v>46139.89583333334</v>
-      </c>
-      <c r="B376">
-        <v>0</v>
-      </c>
-      <c r="C376">
-        <v>87</v>
-      </c>
-      <c r="D376" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4">
-      <c r="A377" s="2">
-        <v>46139.90625</v>
-      </c>
-      <c r="B377">
-        <v>0</v>
-      </c>
-      <c r="C377">
-        <v>88</v>
-      </c>
-      <c r="D377" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4">
-      <c r="A378" s="2">
-        <v>46139.91666666666</v>
-      </c>
-      <c r="B378">
-        <v>0</v>
-      </c>
-      <c r="C378">
-        <v>89</v>
-      </c>
-      <c r="D378" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4">
-      <c r="A379" s="2">
-        <v>46139.92708333334</v>
-      </c>
-      <c r="B379">
-        <v>0</v>
-      </c>
-      <c r="C379">
-        <v>90</v>
-      </c>
-      <c r="D379" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4">
-      <c r="A380" s="2">
-        <v>46139.9375</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380">
-        <v>91</v>
-      </c>
-      <c r="D380" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4">
-      <c r="A381" s="2">
-        <v>46139.94791666666</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381">
-        <v>92</v>
-      </c>
-      <c r="D381" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4">
-      <c r="A382" s="2">
-        <v>46139.95833333334</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-      <c r="C382">
-        <v>93</v>
-      </c>
-      <c r="D382" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4">
-      <c r="A383" s="2">
-        <v>46139.96875</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-      <c r="C383">
-        <v>94</v>
-      </c>
-      <c r="D383" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4">
-      <c r="A384" s="2">
-        <v>46139.97916666666</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384">
-        <v>95</v>
-      </c>
-      <c r="D384" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4">
-      <c r="A385" s="2">
-        <v>46139.98958333334</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385">
-        <v>96</v>
-      </c>
-      <c r="D385" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,582 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.04.20261</t>
-  </si>
-  <si>
-    <t>28.04.20262</t>
-  </si>
-  <si>
-    <t>28.04.20263</t>
-  </si>
-  <si>
-    <t>28.04.20264</t>
-  </si>
-  <si>
-    <t>28.04.20265</t>
-  </si>
-  <si>
-    <t>28.04.20266</t>
-  </si>
-  <si>
-    <t>28.04.20267</t>
-  </si>
-  <si>
-    <t>28.04.20268</t>
-  </si>
-  <si>
-    <t>28.04.20269</t>
-  </si>
-  <si>
-    <t>28.04.202610</t>
-  </si>
-  <si>
-    <t>28.04.202611</t>
-  </si>
-  <si>
-    <t>28.04.202612</t>
-  </si>
-  <si>
-    <t>28.04.202613</t>
-  </si>
-  <si>
-    <t>28.04.202614</t>
-  </si>
-  <si>
-    <t>28.04.202615</t>
-  </si>
-  <si>
-    <t>28.04.202616</t>
-  </si>
-  <si>
-    <t>28.04.202617</t>
-  </si>
-  <si>
-    <t>28.04.202618</t>
-  </si>
-  <si>
-    <t>28.04.202619</t>
-  </si>
-  <si>
-    <t>28.04.202620</t>
-  </si>
-  <si>
-    <t>28.04.202621</t>
-  </si>
-  <si>
-    <t>28.04.202622</t>
-  </si>
-  <si>
-    <t>28.04.202623</t>
-  </si>
-  <si>
-    <t>28.04.202624</t>
-  </si>
-  <si>
-    <t>28.04.202625</t>
-  </si>
-  <si>
-    <t>28.04.202626</t>
-  </si>
-  <si>
-    <t>28.04.202627</t>
-  </si>
-  <si>
-    <t>28.04.202628</t>
-  </si>
-  <si>
-    <t>28.04.202629</t>
-  </si>
-  <si>
-    <t>28.04.202630</t>
-  </si>
-  <si>
-    <t>28.04.202631</t>
-  </si>
-  <si>
-    <t>28.04.202632</t>
-  </si>
-  <si>
-    <t>28.04.202633</t>
-  </si>
-  <si>
-    <t>28.04.202634</t>
-  </si>
-  <si>
-    <t>28.04.202635</t>
-  </si>
-  <si>
-    <t>28.04.202636</t>
-  </si>
-  <si>
-    <t>28.04.202637</t>
-  </si>
-  <si>
-    <t>28.04.202638</t>
-  </si>
-  <si>
-    <t>28.04.202639</t>
-  </si>
-  <si>
-    <t>28.04.202640</t>
-  </si>
-  <si>
-    <t>28.04.202641</t>
-  </si>
-  <si>
-    <t>28.04.202642</t>
-  </si>
-  <si>
-    <t>28.04.202643</t>
-  </si>
-  <si>
-    <t>28.04.202644</t>
-  </si>
-  <si>
-    <t>28.04.202645</t>
-  </si>
-  <si>
-    <t>28.04.202646</t>
-  </si>
-  <si>
-    <t>28.04.202647</t>
-  </si>
-  <si>
-    <t>28.04.202648</t>
-  </si>
-  <si>
-    <t>28.04.202649</t>
-  </si>
-  <si>
-    <t>28.04.202650</t>
-  </si>
-  <si>
-    <t>28.04.202651</t>
-  </si>
-  <si>
-    <t>28.04.202652</t>
-  </si>
-  <si>
-    <t>28.04.202653</t>
-  </si>
-  <si>
-    <t>28.04.202654</t>
-  </si>
-  <si>
-    <t>28.04.202655</t>
-  </si>
-  <si>
-    <t>28.04.202656</t>
-  </si>
-  <si>
-    <t>28.04.202657</t>
-  </si>
-  <si>
-    <t>28.04.202658</t>
-  </si>
-  <si>
-    <t>28.04.202659</t>
-  </si>
-  <si>
-    <t>28.04.202660</t>
-  </si>
-  <si>
-    <t>28.04.202661</t>
-  </si>
-  <si>
-    <t>28.04.202662</t>
-  </si>
-  <si>
-    <t>28.04.202663</t>
-  </si>
-  <si>
-    <t>28.04.202664</t>
-  </si>
-  <si>
-    <t>28.04.202665</t>
-  </si>
-  <si>
-    <t>28.04.202666</t>
-  </si>
-  <si>
-    <t>28.04.202667</t>
-  </si>
-  <si>
-    <t>28.04.202668</t>
-  </si>
-  <si>
-    <t>28.04.202669</t>
-  </si>
-  <si>
-    <t>28.04.202670</t>
-  </si>
-  <si>
-    <t>28.04.202671</t>
-  </si>
-  <si>
-    <t>28.04.202672</t>
-  </si>
-  <si>
-    <t>28.04.202673</t>
-  </si>
-  <si>
-    <t>28.04.202674</t>
-  </si>
-  <si>
-    <t>28.04.202675</t>
-  </si>
-  <si>
-    <t>28.04.202676</t>
-  </si>
-  <si>
-    <t>28.04.202677</t>
-  </si>
-  <si>
-    <t>28.04.202678</t>
-  </si>
-  <si>
-    <t>28.04.202679</t>
-  </si>
-  <si>
-    <t>28.04.202680</t>
-  </si>
-  <si>
-    <t>28.04.202681</t>
-  </si>
-  <si>
-    <t>28.04.202682</t>
-  </si>
-  <si>
-    <t>28.04.202683</t>
-  </si>
-  <si>
-    <t>28.04.202684</t>
-  </si>
-  <si>
-    <t>28.04.202685</t>
-  </si>
-  <si>
-    <t>28.04.202686</t>
-  </si>
-  <si>
-    <t>28.04.202687</t>
-  </si>
-  <si>
-    <t>28.04.202688</t>
-  </si>
-  <si>
-    <t>28.04.202689</t>
-  </si>
-  <si>
-    <t>28.04.202690</t>
-  </si>
-  <si>
-    <t>28.04.202691</t>
-  </si>
-  <si>
-    <t>28.04.202692</t>
-  </si>
-  <si>
-    <t>28.04.202693</t>
-  </si>
-  <si>
-    <t>28.04.202694</t>
-  </si>
-  <si>
-    <t>28.04.202695</t>
-  </si>
-  <si>
-    <t>28.04.202696</t>
-  </si>
-  <si>
-    <t>29.04.20261</t>
-  </si>
-  <si>
-    <t>29.04.20262</t>
-  </si>
-  <si>
-    <t>29.04.20263</t>
-  </si>
-  <si>
-    <t>29.04.20264</t>
-  </si>
-  <si>
-    <t>29.04.20265</t>
-  </si>
-  <si>
-    <t>29.04.20266</t>
-  </si>
-  <si>
-    <t>29.04.20267</t>
-  </si>
-  <si>
-    <t>29.04.20268</t>
-  </si>
-  <si>
-    <t>29.04.20269</t>
-  </si>
-  <si>
-    <t>29.04.202610</t>
-  </si>
-  <si>
-    <t>29.04.202611</t>
-  </si>
-  <si>
-    <t>29.04.202612</t>
-  </si>
-  <si>
-    <t>29.04.202613</t>
-  </si>
-  <si>
-    <t>29.04.202614</t>
-  </si>
-  <si>
-    <t>29.04.202615</t>
-  </si>
-  <si>
-    <t>29.04.202616</t>
-  </si>
-  <si>
-    <t>29.04.202617</t>
-  </si>
-  <si>
-    <t>29.04.202618</t>
-  </si>
-  <si>
-    <t>29.04.202619</t>
-  </si>
-  <si>
-    <t>29.04.202620</t>
-  </si>
-  <si>
-    <t>29.04.202621</t>
-  </si>
-  <si>
-    <t>29.04.202622</t>
-  </si>
-  <si>
-    <t>29.04.202623</t>
-  </si>
-  <si>
-    <t>29.04.202624</t>
-  </si>
-  <si>
-    <t>29.04.202625</t>
-  </si>
-  <si>
-    <t>29.04.202626</t>
-  </si>
-  <si>
-    <t>29.04.202627</t>
-  </si>
-  <si>
-    <t>29.04.202628</t>
-  </si>
-  <si>
-    <t>29.04.202629</t>
-  </si>
-  <si>
-    <t>29.04.202630</t>
-  </si>
-  <si>
-    <t>29.04.202631</t>
-  </si>
-  <si>
-    <t>29.04.202632</t>
-  </si>
-  <si>
-    <t>29.04.202633</t>
-  </si>
-  <si>
-    <t>29.04.202634</t>
-  </si>
-  <si>
-    <t>29.04.202635</t>
-  </si>
-  <si>
-    <t>29.04.202636</t>
-  </si>
-  <si>
-    <t>29.04.202637</t>
-  </si>
-  <si>
-    <t>29.04.202638</t>
-  </si>
-  <si>
-    <t>29.04.202639</t>
-  </si>
-  <si>
-    <t>29.04.202640</t>
-  </si>
-  <si>
-    <t>29.04.202641</t>
-  </si>
-  <si>
-    <t>29.04.202642</t>
-  </si>
-  <si>
-    <t>29.04.202643</t>
-  </si>
-  <si>
-    <t>29.04.202644</t>
-  </si>
-  <si>
-    <t>29.04.202645</t>
-  </si>
-  <si>
-    <t>29.04.202646</t>
-  </si>
-  <si>
-    <t>29.04.202647</t>
-  </si>
-  <si>
-    <t>29.04.202648</t>
-  </si>
-  <si>
-    <t>29.04.202649</t>
-  </si>
-  <si>
-    <t>29.04.202650</t>
-  </si>
-  <si>
-    <t>29.04.202651</t>
-  </si>
-  <si>
-    <t>29.04.202652</t>
-  </si>
-  <si>
-    <t>29.04.202653</t>
-  </si>
-  <si>
-    <t>29.04.202654</t>
-  </si>
-  <si>
-    <t>29.04.202655</t>
-  </si>
-  <si>
-    <t>29.04.202656</t>
-  </si>
-  <si>
-    <t>29.04.202657</t>
-  </si>
-  <si>
-    <t>29.04.202658</t>
-  </si>
-  <si>
-    <t>29.04.202659</t>
-  </si>
-  <si>
-    <t>29.04.202660</t>
-  </si>
-  <si>
-    <t>29.04.202661</t>
-  </si>
-  <si>
-    <t>29.04.202662</t>
-  </si>
-  <si>
-    <t>29.04.202663</t>
-  </si>
-  <si>
-    <t>29.04.202664</t>
-  </si>
-  <si>
-    <t>29.04.202665</t>
-  </si>
-  <si>
-    <t>29.04.202666</t>
-  </si>
-  <si>
-    <t>29.04.202667</t>
-  </si>
-  <si>
-    <t>29.04.202668</t>
-  </si>
-  <si>
-    <t>29.04.202669</t>
-  </si>
-  <si>
-    <t>29.04.202670</t>
-  </si>
-  <si>
-    <t>29.04.202671</t>
-  </si>
-  <si>
-    <t>29.04.202672</t>
-  </si>
-  <si>
-    <t>29.04.202673</t>
-  </si>
-  <si>
-    <t>29.04.202674</t>
-  </si>
-  <si>
-    <t>29.04.202675</t>
-  </si>
-  <si>
-    <t>29.04.202676</t>
-  </si>
-  <si>
-    <t>29.04.202677</t>
-  </si>
-  <si>
-    <t>29.04.202678</t>
-  </si>
-  <si>
-    <t>29.04.202679</t>
-  </si>
-  <si>
-    <t>29.04.202680</t>
-  </si>
-  <si>
-    <t>29.04.202681</t>
-  </si>
-  <si>
-    <t>29.04.202682</t>
-  </si>
-  <si>
-    <t>29.04.202683</t>
-  </si>
-  <si>
-    <t>29.04.202684</t>
-  </si>
-  <si>
-    <t>29.04.202685</t>
-  </si>
-  <si>
-    <t>29.04.202686</t>
-  </si>
-  <si>
-    <t>29.04.202687</t>
-  </si>
-  <si>
-    <t>29.04.202688</t>
-  </si>
-  <si>
-    <t>29.04.202689</t>
-  </si>
-  <si>
-    <t>29.04.202690</t>
-  </si>
-  <si>
-    <t>29.04.202691</t>
-  </si>
-  <si>
-    <t>29.04.202692</t>
-  </si>
-  <si>
-    <t>29.04.202693</t>
-  </si>
-  <si>
-    <t>29.04.202694</t>
-  </si>
-  <si>
-    <t>29.04.202695</t>
-  </si>
-  <si>
-    <t>29.04.202696</t>
-  </si>
-  <si>
     <t>30.04.20261</t>
   </si>
   <si>
@@ -890,6 +314,1158 @@
   </si>
   <si>
     <t>30.04.202696</t>
+  </si>
+  <si>
+    <t>01.05.20261</t>
+  </si>
+  <si>
+    <t>01.05.20262</t>
+  </si>
+  <si>
+    <t>01.05.20263</t>
+  </si>
+  <si>
+    <t>01.05.20264</t>
+  </si>
+  <si>
+    <t>01.05.20265</t>
+  </si>
+  <si>
+    <t>01.05.20266</t>
+  </si>
+  <si>
+    <t>01.05.20267</t>
+  </si>
+  <si>
+    <t>01.05.20268</t>
+  </si>
+  <si>
+    <t>01.05.20269</t>
+  </si>
+  <si>
+    <t>01.05.202610</t>
+  </si>
+  <si>
+    <t>01.05.202611</t>
+  </si>
+  <si>
+    <t>01.05.202612</t>
+  </si>
+  <si>
+    <t>01.05.202613</t>
+  </si>
+  <si>
+    <t>01.05.202614</t>
+  </si>
+  <si>
+    <t>01.05.202615</t>
+  </si>
+  <si>
+    <t>01.05.202616</t>
+  </si>
+  <si>
+    <t>01.05.202617</t>
+  </si>
+  <si>
+    <t>01.05.202618</t>
+  </si>
+  <si>
+    <t>01.05.202619</t>
+  </si>
+  <si>
+    <t>01.05.202620</t>
+  </si>
+  <si>
+    <t>01.05.202621</t>
+  </si>
+  <si>
+    <t>01.05.202622</t>
+  </si>
+  <si>
+    <t>01.05.202623</t>
+  </si>
+  <si>
+    <t>01.05.202624</t>
+  </si>
+  <si>
+    <t>01.05.202625</t>
+  </si>
+  <si>
+    <t>01.05.202626</t>
+  </si>
+  <si>
+    <t>01.05.202627</t>
+  </si>
+  <si>
+    <t>01.05.202628</t>
+  </si>
+  <si>
+    <t>01.05.202629</t>
+  </si>
+  <si>
+    <t>01.05.202630</t>
+  </si>
+  <si>
+    <t>01.05.202631</t>
+  </si>
+  <si>
+    <t>01.05.202632</t>
+  </si>
+  <si>
+    <t>01.05.202633</t>
+  </si>
+  <si>
+    <t>01.05.202634</t>
+  </si>
+  <si>
+    <t>01.05.202635</t>
+  </si>
+  <si>
+    <t>01.05.202636</t>
+  </si>
+  <si>
+    <t>01.05.202637</t>
+  </si>
+  <si>
+    <t>01.05.202638</t>
+  </si>
+  <si>
+    <t>01.05.202639</t>
+  </si>
+  <si>
+    <t>01.05.202640</t>
+  </si>
+  <si>
+    <t>01.05.202641</t>
+  </si>
+  <si>
+    <t>01.05.202642</t>
+  </si>
+  <si>
+    <t>01.05.202643</t>
+  </si>
+  <si>
+    <t>01.05.202644</t>
+  </si>
+  <si>
+    <t>01.05.202645</t>
+  </si>
+  <si>
+    <t>01.05.202646</t>
+  </si>
+  <si>
+    <t>01.05.202647</t>
+  </si>
+  <si>
+    <t>01.05.202648</t>
+  </si>
+  <si>
+    <t>01.05.202649</t>
+  </si>
+  <si>
+    <t>01.05.202650</t>
+  </si>
+  <si>
+    <t>01.05.202651</t>
+  </si>
+  <si>
+    <t>01.05.202652</t>
+  </si>
+  <si>
+    <t>01.05.202653</t>
+  </si>
+  <si>
+    <t>01.05.202654</t>
+  </si>
+  <si>
+    <t>01.05.202655</t>
+  </si>
+  <si>
+    <t>01.05.202656</t>
+  </si>
+  <si>
+    <t>01.05.202657</t>
+  </si>
+  <si>
+    <t>01.05.202658</t>
+  </si>
+  <si>
+    <t>01.05.202659</t>
+  </si>
+  <si>
+    <t>01.05.202660</t>
+  </si>
+  <si>
+    <t>01.05.202661</t>
+  </si>
+  <si>
+    <t>01.05.202662</t>
+  </si>
+  <si>
+    <t>01.05.202663</t>
+  </si>
+  <si>
+    <t>01.05.202664</t>
+  </si>
+  <si>
+    <t>01.05.202665</t>
+  </si>
+  <si>
+    <t>01.05.202666</t>
+  </si>
+  <si>
+    <t>01.05.202667</t>
+  </si>
+  <si>
+    <t>01.05.202668</t>
+  </si>
+  <si>
+    <t>01.05.202669</t>
+  </si>
+  <si>
+    <t>01.05.202670</t>
+  </si>
+  <si>
+    <t>01.05.202671</t>
+  </si>
+  <si>
+    <t>01.05.202672</t>
+  </si>
+  <si>
+    <t>01.05.202673</t>
+  </si>
+  <si>
+    <t>01.05.202674</t>
+  </si>
+  <si>
+    <t>01.05.202675</t>
+  </si>
+  <si>
+    <t>01.05.202676</t>
+  </si>
+  <si>
+    <t>01.05.202677</t>
+  </si>
+  <si>
+    <t>01.05.202678</t>
+  </si>
+  <si>
+    <t>01.05.202679</t>
+  </si>
+  <si>
+    <t>01.05.202680</t>
+  </si>
+  <si>
+    <t>01.05.202681</t>
+  </si>
+  <si>
+    <t>01.05.202682</t>
+  </si>
+  <si>
+    <t>01.05.202683</t>
+  </si>
+  <si>
+    <t>01.05.202684</t>
+  </si>
+  <si>
+    <t>01.05.202685</t>
+  </si>
+  <si>
+    <t>01.05.202686</t>
+  </si>
+  <si>
+    <t>01.05.202687</t>
+  </si>
+  <si>
+    <t>01.05.202688</t>
+  </si>
+  <si>
+    <t>01.05.202689</t>
+  </si>
+  <si>
+    <t>01.05.202690</t>
+  </si>
+  <si>
+    <t>01.05.202691</t>
+  </si>
+  <si>
+    <t>01.05.202692</t>
+  </si>
+  <si>
+    <t>01.05.202693</t>
+  </si>
+  <si>
+    <t>01.05.202694</t>
+  </si>
+  <si>
+    <t>01.05.202695</t>
+  </si>
+  <si>
+    <t>01.05.202696</t>
+  </si>
+  <si>
+    <t>02.05.20261</t>
+  </si>
+  <si>
+    <t>02.05.20262</t>
+  </si>
+  <si>
+    <t>02.05.20263</t>
+  </si>
+  <si>
+    <t>02.05.20264</t>
+  </si>
+  <si>
+    <t>02.05.20265</t>
+  </si>
+  <si>
+    <t>02.05.20266</t>
+  </si>
+  <si>
+    <t>02.05.20267</t>
+  </si>
+  <si>
+    <t>02.05.20268</t>
+  </si>
+  <si>
+    <t>02.05.20269</t>
+  </si>
+  <si>
+    <t>02.05.202610</t>
+  </si>
+  <si>
+    <t>02.05.202611</t>
+  </si>
+  <si>
+    <t>02.05.202612</t>
+  </si>
+  <si>
+    <t>02.05.202613</t>
+  </si>
+  <si>
+    <t>02.05.202614</t>
+  </si>
+  <si>
+    <t>02.05.202615</t>
+  </si>
+  <si>
+    <t>02.05.202616</t>
+  </si>
+  <si>
+    <t>02.05.202617</t>
+  </si>
+  <si>
+    <t>02.05.202618</t>
+  </si>
+  <si>
+    <t>02.05.202619</t>
+  </si>
+  <si>
+    <t>02.05.202620</t>
+  </si>
+  <si>
+    <t>02.05.202621</t>
+  </si>
+  <si>
+    <t>02.05.202622</t>
+  </si>
+  <si>
+    <t>02.05.202623</t>
+  </si>
+  <si>
+    <t>02.05.202624</t>
+  </si>
+  <si>
+    <t>02.05.202625</t>
+  </si>
+  <si>
+    <t>02.05.202626</t>
+  </si>
+  <si>
+    <t>02.05.202627</t>
+  </si>
+  <si>
+    <t>02.05.202628</t>
+  </si>
+  <si>
+    <t>02.05.202629</t>
+  </si>
+  <si>
+    <t>02.05.202630</t>
+  </si>
+  <si>
+    <t>02.05.202631</t>
+  </si>
+  <si>
+    <t>02.05.202632</t>
+  </si>
+  <si>
+    <t>02.05.202633</t>
+  </si>
+  <si>
+    <t>02.05.202634</t>
+  </si>
+  <si>
+    <t>02.05.202635</t>
+  </si>
+  <si>
+    <t>02.05.202636</t>
+  </si>
+  <si>
+    <t>02.05.202637</t>
+  </si>
+  <si>
+    <t>02.05.202638</t>
+  </si>
+  <si>
+    <t>02.05.202639</t>
+  </si>
+  <si>
+    <t>02.05.202640</t>
+  </si>
+  <si>
+    <t>02.05.202641</t>
+  </si>
+  <si>
+    <t>02.05.202642</t>
+  </si>
+  <si>
+    <t>02.05.202643</t>
+  </si>
+  <si>
+    <t>02.05.202644</t>
+  </si>
+  <si>
+    <t>02.05.202645</t>
+  </si>
+  <si>
+    <t>02.05.202646</t>
+  </si>
+  <si>
+    <t>02.05.202647</t>
+  </si>
+  <si>
+    <t>02.05.202648</t>
+  </si>
+  <si>
+    <t>02.05.202649</t>
+  </si>
+  <si>
+    <t>02.05.202650</t>
+  </si>
+  <si>
+    <t>02.05.202651</t>
+  </si>
+  <si>
+    <t>02.05.202652</t>
+  </si>
+  <si>
+    <t>02.05.202653</t>
+  </si>
+  <si>
+    <t>02.05.202654</t>
+  </si>
+  <si>
+    <t>02.05.202655</t>
+  </si>
+  <si>
+    <t>02.05.202656</t>
+  </si>
+  <si>
+    <t>02.05.202657</t>
+  </si>
+  <si>
+    <t>02.05.202658</t>
+  </si>
+  <si>
+    <t>02.05.202659</t>
+  </si>
+  <si>
+    <t>02.05.202660</t>
+  </si>
+  <si>
+    <t>02.05.202661</t>
+  </si>
+  <si>
+    <t>02.05.202662</t>
+  </si>
+  <si>
+    <t>02.05.202663</t>
+  </si>
+  <si>
+    <t>02.05.202664</t>
+  </si>
+  <si>
+    <t>02.05.202665</t>
+  </si>
+  <si>
+    <t>02.05.202666</t>
+  </si>
+  <si>
+    <t>02.05.202667</t>
+  </si>
+  <si>
+    <t>02.05.202668</t>
+  </si>
+  <si>
+    <t>02.05.202669</t>
+  </si>
+  <si>
+    <t>02.05.202670</t>
+  </si>
+  <si>
+    <t>02.05.202671</t>
+  </si>
+  <si>
+    <t>02.05.202672</t>
+  </si>
+  <si>
+    <t>02.05.202673</t>
+  </si>
+  <si>
+    <t>02.05.202674</t>
+  </si>
+  <si>
+    <t>02.05.202675</t>
+  </si>
+  <si>
+    <t>02.05.202676</t>
+  </si>
+  <si>
+    <t>02.05.202677</t>
+  </si>
+  <si>
+    <t>02.05.202678</t>
+  </si>
+  <si>
+    <t>02.05.202679</t>
+  </si>
+  <si>
+    <t>02.05.202680</t>
+  </si>
+  <si>
+    <t>02.05.202681</t>
+  </si>
+  <si>
+    <t>02.05.202682</t>
+  </si>
+  <si>
+    <t>02.05.202683</t>
+  </si>
+  <si>
+    <t>02.05.202684</t>
+  </si>
+  <si>
+    <t>02.05.202685</t>
+  </si>
+  <si>
+    <t>02.05.202686</t>
+  </si>
+  <si>
+    <t>02.05.202687</t>
+  </si>
+  <si>
+    <t>02.05.202688</t>
+  </si>
+  <si>
+    <t>02.05.202689</t>
+  </si>
+  <si>
+    <t>02.05.202690</t>
+  </si>
+  <si>
+    <t>02.05.202691</t>
+  </si>
+  <si>
+    <t>02.05.202692</t>
+  </si>
+  <si>
+    <t>02.05.202693</t>
+  </si>
+  <si>
+    <t>02.05.202694</t>
+  </si>
+  <si>
+    <t>02.05.202695</t>
+  </si>
+  <si>
+    <t>02.05.202696</t>
+  </si>
+  <si>
+    <t>03.05.20261</t>
+  </si>
+  <si>
+    <t>03.05.20262</t>
+  </si>
+  <si>
+    <t>03.05.20263</t>
+  </si>
+  <si>
+    <t>03.05.20264</t>
+  </si>
+  <si>
+    <t>03.05.20265</t>
+  </si>
+  <si>
+    <t>03.05.20266</t>
+  </si>
+  <si>
+    <t>03.05.20267</t>
+  </si>
+  <si>
+    <t>03.05.20268</t>
+  </si>
+  <si>
+    <t>03.05.20269</t>
+  </si>
+  <si>
+    <t>03.05.202610</t>
+  </si>
+  <si>
+    <t>03.05.202611</t>
+  </si>
+  <si>
+    <t>03.05.202612</t>
+  </si>
+  <si>
+    <t>03.05.202613</t>
+  </si>
+  <si>
+    <t>03.05.202614</t>
+  </si>
+  <si>
+    <t>03.05.202615</t>
+  </si>
+  <si>
+    <t>03.05.202616</t>
+  </si>
+  <si>
+    <t>03.05.202617</t>
+  </si>
+  <si>
+    <t>03.05.202618</t>
+  </si>
+  <si>
+    <t>03.05.202619</t>
+  </si>
+  <si>
+    <t>03.05.202620</t>
+  </si>
+  <si>
+    <t>03.05.202621</t>
+  </si>
+  <si>
+    <t>03.05.202622</t>
+  </si>
+  <si>
+    <t>03.05.202623</t>
+  </si>
+  <si>
+    <t>03.05.202624</t>
+  </si>
+  <si>
+    <t>03.05.202625</t>
+  </si>
+  <si>
+    <t>03.05.202626</t>
+  </si>
+  <si>
+    <t>03.05.202627</t>
+  </si>
+  <si>
+    <t>03.05.202628</t>
+  </si>
+  <si>
+    <t>03.05.202629</t>
+  </si>
+  <si>
+    <t>03.05.202630</t>
+  </si>
+  <si>
+    <t>03.05.202631</t>
+  </si>
+  <si>
+    <t>03.05.202632</t>
+  </si>
+  <si>
+    <t>03.05.202633</t>
+  </si>
+  <si>
+    <t>03.05.202634</t>
+  </si>
+  <si>
+    <t>03.05.202635</t>
+  </si>
+  <si>
+    <t>03.05.202636</t>
+  </si>
+  <si>
+    <t>03.05.202637</t>
+  </si>
+  <si>
+    <t>03.05.202638</t>
+  </si>
+  <si>
+    <t>03.05.202639</t>
+  </si>
+  <si>
+    <t>03.05.202640</t>
+  </si>
+  <si>
+    <t>03.05.202641</t>
+  </si>
+  <si>
+    <t>03.05.202642</t>
+  </si>
+  <si>
+    <t>03.05.202643</t>
+  </si>
+  <si>
+    <t>03.05.202644</t>
+  </si>
+  <si>
+    <t>03.05.202645</t>
+  </si>
+  <si>
+    <t>03.05.202646</t>
+  </si>
+  <si>
+    <t>03.05.202647</t>
+  </si>
+  <si>
+    <t>03.05.202648</t>
+  </si>
+  <si>
+    <t>03.05.202649</t>
+  </si>
+  <si>
+    <t>03.05.202650</t>
+  </si>
+  <si>
+    <t>03.05.202651</t>
+  </si>
+  <si>
+    <t>03.05.202652</t>
+  </si>
+  <si>
+    <t>03.05.202653</t>
+  </si>
+  <si>
+    <t>03.05.202654</t>
+  </si>
+  <si>
+    <t>03.05.202655</t>
+  </si>
+  <si>
+    <t>03.05.202656</t>
+  </si>
+  <si>
+    <t>03.05.202657</t>
+  </si>
+  <si>
+    <t>03.05.202658</t>
+  </si>
+  <si>
+    <t>03.05.202659</t>
+  </si>
+  <si>
+    <t>03.05.202660</t>
+  </si>
+  <si>
+    <t>03.05.202661</t>
+  </si>
+  <si>
+    <t>03.05.202662</t>
+  </si>
+  <si>
+    <t>03.05.202663</t>
+  </si>
+  <si>
+    <t>03.05.202664</t>
+  </si>
+  <si>
+    <t>03.05.202665</t>
+  </si>
+  <si>
+    <t>03.05.202666</t>
+  </si>
+  <si>
+    <t>03.05.202667</t>
+  </si>
+  <si>
+    <t>03.05.202668</t>
+  </si>
+  <si>
+    <t>03.05.202669</t>
+  </si>
+  <si>
+    <t>03.05.202670</t>
+  </si>
+  <si>
+    <t>03.05.202671</t>
+  </si>
+  <si>
+    <t>03.05.202672</t>
+  </si>
+  <si>
+    <t>03.05.202673</t>
+  </si>
+  <si>
+    <t>03.05.202674</t>
+  </si>
+  <si>
+    <t>03.05.202675</t>
+  </si>
+  <si>
+    <t>03.05.202676</t>
+  </si>
+  <si>
+    <t>03.05.202677</t>
+  </si>
+  <si>
+    <t>03.05.202678</t>
+  </si>
+  <si>
+    <t>03.05.202679</t>
+  </si>
+  <si>
+    <t>03.05.202680</t>
+  </si>
+  <si>
+    <t>03.05.202681</t>
+  </si>
+  <si>
+    <t>03.05.202682</t>
+  </si>
+  <si>
+    <t>03.05.202683</t>
+  </si>
+  <si>
+    <t>03.05.202684</t>
+  </si>
+  <si>
+    <t>03.05.202685</t>
+  </si>
+  <si>
+    <t>03.05.202686</t>
+  </si>
+  <si>
+    <t>03.05.202687</t>
+  </si>
+  <si>
+    <t>03.05.202688</t>
+  </si>
+  <si>
+    <t>03.05.202689</t>
+  </si>
+  <si>
+    <t>03.05.202690</t>
+  </si>
+  <si>
+    <t>03.05.202691</t>
+  </si>
+  <si>
+    <t>03.05.202692</t>
+  </si>
+  <si>
+    <t>03.05.202693</t>
+  </si>
+  <si>
+    <t>03.05.202694</t>
+  </si>
+  <si>
+    <t>03.05.202695</t>
+  </si>
+  <si>
+    <t>03.05.202696</t>
+  </si>
+  <si>
+    <t>04.05.20261</t>
+  </si>
+  <si>
+    <t>04.05.20262</t>
+  </si>
+  <si>
+    <t>04.05.20263</t>
+  </si>
+  <si>
+    <t>04.05.20264</t>
+  </si>
+  <si>
+    <t>04.05.20265</t>
+  </si>
+  <si>
+    <t>04.05.20266</t>
+  </si>
+  <si>
+    <t>04.05.20267</t>
+  </si>
+  <si>
+    <t>04.05.20268</t>
+  </si>
+  <si>
+    <t>04.05.20269</t>
+  </si>
+  <si>
+    <t>04.05.202610</t>
+  </si>
+  <si>
+    <t>04.05.202611</t>
+  </si>
+  <si>
+    <t>04.05.202612</t>
+  </si>
+  <si>
+    <t>04.05.202613</t>
+  </si>
+  <si>
+    <t>04.05.202614</t>
+  </si>
+  <si>
+    <t>04.05.202615</t>
+  </si>
+  <si>
+    <t>04.05.202616</t>
+  </si>
+  <si>
+    <t>04.05.202617</t>
+  </si>
+  <si>
+    <t>04.05.202618</t>
+  </si>
+  <si>
+    <t>04.05.202619</t>
+  </si>
+  <si>
+    <t>04.05.202620</t>
+  </si>
+  <si>
+    <t>04.05.202621</t>
+  </si>
+  <si>
+    <t>04.05.202622</t>
+  </si>
+  <si>
+    <t>04.05.202623</t>
+  </si>
+  <si>
+    <t>04.05.202624</t>
+  </si>
+  <si>
+    <t>04.05.202625</t>
+  </si>
+  <si>
+    <t>04.05.202626</t>
+  </si>
+  <si>
+    <t>04.05.202627</t>
+  </si>
+  <si>
+    <t>04.05.202628</t>
+  </si>
+  <si>
+    <t>04.05.202629</t>
+  </si>
+  <si>
+    <t>04.05.202630</t>
+  </si>
+  <si>
+    <t>04.05.202631</t>
+  </si>
+  <si>
+    <t>04.05.202632</t>
+  </si>
+  <si>
+    <t>04.05.202633</t>
+  </si>
+  <si>
+    <t>04.05.202634</t>
+  </si>
+  <si>
+    <t>04.05.202635</t>
+  </si>
+  <si>
+    <t>04.05.202636</t>
+  </si>
+  <si>
+    <t>04.05.202637</t>
+  </si>
+  <si>
+    <t>04.05.202638</t>
+  </si>
+  <si>
+    <t>04.05.202639</t>
+  </si>
+  <si>
+    <t>04.05.202640</t>
+  </si>
+  <si>
+    <t>04.05.202641</t>
+  </si>
+  <si>
+    <t>04.05.202642</t>
+  </si>
+  <si>
+    <t>04.05.202643</t>
+  </si>
+  <si>
+    <t>04.05.202644</t>
+  </si>
+  <si>
+    <t>04.05.202645</t>
+  </si>
+  <si>
+    <t>04.05.202646</t>
+  </si>
+  <si>
+    <t>04.05.202647</t>
+  </si>
+  <si>
+    <t>04.05.202648</t>
+  </si>
+  <si>
+    <t>04.05.202649</t>
+  </si>
+  <si>
+    <t>04.05.202650</t>
+  </si>
+  <si>
+    <t>04.05.202651</t>
+  </si>
+  <si>
+    <t>04.05.202652</t>
+  </si>
+  <si>
+    <t>04.05.202653</t>
+  </si>
+  <si>
+    <t>04.05.202654</t>
+  </si>
+  <si>
+    <t>04.05.202655</t>
+  </si>
+  <si>
+    <t>04.05.202656</t>
+  </si>
+  <si>
+    <t>04.05.202657</t>
+  </si>
+  <si>
+    <t>04.05.202658</t>
+  </si>
+  <si>
+    <t>04.05.202659</t>
+  </si>
+  <si>
+    <t>04.05.202660</t>
+  </si>
+  <si>
+    <t>04.05.202661</t>
+  </si>
+  <si>
+    <t>04.05.202662</t>
+  </si>
+  <si>
+    <t>04.05.202663</t>
+  </si>
+  <si>
+    <t>04.05.202664</t>
+  </si>
+  <si>
+    <t>04.05.202665</t>
+  </si>
+  <si>
+    <t>04.05.202666</t>
+  </si>
+  <si>
+    <t>04.05.202667</t>
+  </si>
+  <si>
+    <t>04.05.202668</t>
+  </si>
+  <si>
+    <t>04.05.202669</t>
+  </si>
+  <si>
+    <t>04.05.202670</t>
+  </si>
+  <si>
+    <t>04.05.202671</t>
+  </si>
+  <si>
+    <t>04.05.202672</t>
+  </si>
+  <si>
+    <t>04.05.202673</t>
+  </si>
+  <si>
+    <t>04.05.202674</t>
+  </si>
+  <si>
+    <t>04.05.202675</t>
+  </si>
+  <si>
+    <t>04.05.202676</t>
+  </si>
+  <si>
+    <t>04.05.202677</t>
+  </si>
+  <si>
+    <t>04.05.202678</t>
+  </si>
+  <si>
+    <t>04.05.202679</t>
+  </si>
+  <si>
+    <t>04.05.202680</t>
+  </si>
+  <si>
+    <t>04.05.202681</t>
+  </si>
+  <si>
+    <t>04.05.202682</t>
+  </si>
+  <si>
+    <t>04.05.202683</t>
+  </si>
+  <si>
+    <t>04.05.202684</t>
+  </si>
+  <si>
+    <t>04.05.202685</t>
+  </si>
+  <si>
+    <t>04.05.202686</t>
+  </si>
+  <si>
+    <t>04.05.202687</t>
+  </si>
+  <si>
+    <t>04.05.202688</t>
+  </si>
+  <si>
+    <t>04.05.202689</t>
+  </si>
+  <si>
+    <t>04.05.202690</t>
+  </si>
+  <si>
+    <t>04.05.202691</t>
+  </si>
+  <si>
+    <t>04.05.202692</t>
+  </si>
+  <si>
+    <t>04.05.202693</t>
+  </si>
+  <si>
+    <t>04.05.202694</t>
+  </si>
+  <si>
+    <t>04.05.202695</t>
+  </si>
+  <si>
+    <t>04.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D289"/>
+  <dimension ref="A1:D481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1270,10 +1846,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B2">
-        <v>5367</v>
+        <v>5379</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1284,10 +1860,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46140.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B3">
-        <v>5325</v>
+        <v>5308</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1298,10 +1874,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46140.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B4">
-        <v>5256</v>
+        <v>5299</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1312,10 +1888,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46140.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B5">
-        <v>5179</v>
+        <v>5318</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1326,10 +1902,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46140.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B6">
-        <v>5228</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1340,10 +1916,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46140.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B7">
-        <v>5175</v>
+        <v>5260</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1354,10 +1930,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46140.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B8">
-        <v>5168</v>
+        <v>5279</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1368,10 +1944,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46140.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B9">
-        <v>5183</v>
+        <v>5241</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1382,10 +1958,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46140.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B10">
-        <v>5125</v>
+        <v>5021</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1396,10 +1972,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46140.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B11">
-        <v>5149</v>
+        <v>4859</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1410,10 +1986,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46140.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B12">
-        <v>5130</v>
+        <v>4872</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1424,10 +2000,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46140.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B13">
-        <v>5131</v>
+        <v>4867</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1438,10 +2014,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46140.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B14">
-        <v>5252</v>
+        <v>4837</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1452,10 +2028,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46140.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B15">
-        <v>5235</v>
+        <v>4872</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1466,10 +2042,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46140.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B16">
-        <v>5308</v>
+        <v>4930</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1480,10 +2056,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46140.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B17">
-        <v>5307</v>
+        <v>4865</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1494,10 +2070,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46140.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B18">
-        <v>5320</v>
+        <v>4874</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1508,10 +2084,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46140.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B19">
-        <v>5385</v>
+        <v>5437</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1522,10 +2098,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46140.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B20">
-        <v>5490</v>
+        <v>5576</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1536,10 +2112,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46140.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B21">
-        <v>5539</v>
+        <v>5596</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1550,10 +2126,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46140.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B22">
-        <v>5575</v>
+        <v>5609</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1564,10 +2140,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46140.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B23">
-        <v>5610</v>
+        <v>5724</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1578,10 +2154,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46140.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B24">
-        <v>5686</v>
+        <v>5907</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1592,10 +2168,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46140.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B25">
-        <v>5837</v>
+        <v>6050</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1606,10 +2182,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46140.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B26">
-        <v>6066</v>
+        <v>6319</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1620,10 +2196,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46140.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B27">
-        <v>6161</v>
+        <v>6425</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1634,10 +2210,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46140.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B28">
-        <v>6105</v>
+        <v>6508</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1648,10 +2224,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46140.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B29">
-        <v>6049</v>
+        <v>6573</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1662,10 +2238,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46140.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B30">
-        <v>6114</v>
+        <v>6712</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1676,10 +2252,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46140.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B31">
-        <v>6035</v>
+        <v>6887</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1690,10 +2266,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46140.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B32">
-        <v>5971</v>
+        <v>6879</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1704,10 +2280,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46140.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B33">
-        <v>5911</v>
+        <v>6788</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1718,10 +2294,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46140.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B34">
-        <v>5583</v>
+        <v>6738</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1732,10 +2308,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46140.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B35">
-        <v>5373</v>
+        <v>6813</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1746,10 +2322,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46140.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B36">
-        <v>5209</v>
+        <v>6723</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1760,10 +2336,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46140.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B37">
-        <v>5047</v>
+        <v>6650</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1774,10 +2350,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46140.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B38">
-        <v>4831</v>
+        <v>6630</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1788,10 +2364,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46140.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B39">
-        <v>4665</v>
+        <v>6540</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1802,10 +2378,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46140.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B40">
-        <v>4517</v>
+        <v>6409</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1816,10 +2392,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46140.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B41">
-        <v>4419</v>
+        <v>6429</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1830,10 +2406,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46140.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B42">
-        <v>4331</v>
+        <v>6245</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1844,10 +2420,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46140.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B43">
-        <v>4228</v>
+        <v>6260</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1858,10 +2434,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46140.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B44">
-        <v>4112</v>
+        <v>6170</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1872,10 +2448,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46140.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B45">
-        <v>4019</v>
+        <v>6093</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1886,10 +2462,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46140.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B46">
-        <v>4008</v>
+        <v>6089</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1900,10 +2476,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46140.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B47">
-        <v>3948</v>
+        <v>6135</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1914,10 +2490,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46140.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>6146</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1928,10 +2504,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46140.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B49">
-        <v>3954</v>
+        <v>6125</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1942,10 +2518,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46140.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B50">
-        <v>3964</v>
+        <v>6169</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1956,10 +2532,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46140.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B51">
-        <v>3952</v>
+        <v>6158</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1970,10 +2546,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46140.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B52">
-        <v>3960</v>
+        <v>6216</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1984,10 +2560,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46140.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B53">
-        <v>3937</v>
+        <v>6158</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1998,10 +2574,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46140.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B54">
-        <v>4084</v>
+        <v>6122</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -2012,10 +2588,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46140.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B55">
-        <v>4079</v>
+        <v>6032</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -2026,10 +2602,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46140.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B56">
-        <v>4119</v>
+        <v>5962</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -2040,10 +2616,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46140.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B57">
-        <v>4064</v>
+        <v>5895</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -2054,10 +2630,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46140.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B58">
-        <v>4062</v>
+        <v>5973</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -2068,10 +2644,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46140.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B59">
-        <v>4134</v>
+        <v>6008</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -2082,10 +2658,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46140.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B60">
-        <v>4194</v>
+        <v>6038</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -2096,10 +2672,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46140.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B61">
-        <v>4264</v>
+        <v>6064</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -2110,10 +2686,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46140.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B62">
-        <v>4372</v>
+        <v>5999</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -2124,10 +2700,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46140.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B63">
-        <v>4457</v>
+        <v>5973</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -2138,10 +2714,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46140.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B64">
-        <v>4579</v>
+        <v>6018</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -2152,10 +2728,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46140.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B65">
-        <v>4613</v>
+        <v>6080</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -2166,10 +2742,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46140.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B66">
-        <v>4794</v>
+        <v>6131</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -2180,10 +2756,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46140.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B67">
-        <v>4884</v>
+        <v>6204</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -2194,10 +2770,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46140.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B68">
-        <v>5062</v>
+        <v>6199</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -2208,10 +2784,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46140.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B69">
-        <v>5373</v>
+        <v>6297</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -2222,10 +2798,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46140.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B70">
-        <v>5530</v>
+        <v>6358</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -2236,10 +2812,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46140.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B71">
-        <v>5667</v>
+        <v>6559</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -2250,10 +2826,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46140.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B72">
-        <v>5940</v>
+        <v>6551</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -2264,10 +2840,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46140.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B73">
-        <v>6060</v>
+        <v>6609</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -2278,10 +2854,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46140.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B74">
-        <v>6232</v>
+        <v>6731</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2292,10 +2868,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46140.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B75">
-        <v>6350</v>
+        <v>6773</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2306,10 +2882,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46140.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B76">
-        <v>6535</v>
+        <v>6940</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2320,10 +2896,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46140.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B77">
-        <v>6683</v>
+        <v>7037</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2334,10 +2910,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46140.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B78">
-        <v>6801</v>
+        <v>7017</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2348,10 +2924,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46140.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B79">
-        <v>6960</v>
+        <v>7132</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2362,10 +2938,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46140.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B80">
-        <v>7052</v>
+        <v>7210</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2376,10 +2952,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46140.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B81">
-        <v>7087</v>
+        <v>7290</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2390,10 +2966,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46140.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B82">
-        <v>7136</v>
+        <v>7263</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2404,10 +2980,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46140.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B83">
-        <v>7116</v>
+        <v>7234</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2418,10 +2994,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46140.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B84">
-        <v>7036</v>
+        <v>7101</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2432,10 +3008,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46140.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B85">
-        <v>6882</v>
+        <v>7057</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2446,10 +3022,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46140.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B86">
-        <v>6694</v>
+        <v>6838</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2460,10 +3036,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46140.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B87">
-        <v>6483</v>
+        <v>6689</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2474,10 +3050,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46140.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B88">
-        <v>6329</v>
+        <v>6564</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2488,10 +3064,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46140.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B89">
-        <v>6207</v>
+        <v>6450</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2502,10 +3078,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46140.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B90">
-        <v>6150</v>
+        <v>6260</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2516,10 +3092,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46140.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B91">
-        <v>5957</v>
+        <v>6159</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2530,10 +3106,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46140.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B92">
-        <v>5818</v>
+        <v>5992</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2544,10 +3120,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46140.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B93">
-        <v>5716</v>
+        <v>5920</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2558,10 +3134,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46140.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B94">
-        <v>5578</v>
+        <v>5735</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2572,10 +3148,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46140.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B95">
-        <v>5508</v>
+        <v>5684</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2586,10 +3162,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46140.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B96">
-        <v>5483</v>
+        <v>5585</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2600,10 +3176,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46140.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B97">
-        <v>5394</v>
+        <v>5506</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2614,10 +3190,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B98">
-        <v>5351</v>
+        <v>5492</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2628,10 +3204,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46141.01041666666</v>
+        <v>46143.01041666666</v>
       </c>
       <c r="B99">
-        <v>5227</v>
+        <v>5458</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2642,10 +3218,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46141.02083333334</v>
+        <v>46143.02083333334</v>
       </c>
       <c r="B100">
-        <v>5199</v>
+        <v>5407</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2656,10 +3232,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46141.03125</v>
+        <v>46143.03125</v>
       </c>
       <c r="B101">
-        <v>5198</v>
+        <v>5332</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2670,10 +3246,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46141.04166666666</v>
+        <v>46143.04166666666</v>
       </c>
       <c r="B102">
-        <v>5266</v>
+        <v>5342</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2684,10 +3260,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46141.05208333334</v>
+        <v>46143.05208333334</v>
       </c>
       <c r="B103">
-        <v>5254</v>
+        <v>5271</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2698,10 +3274,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46141.0625</v>
+        <v>46143.0625</v>
       </c>
       <c r="B104">
-        <v>5217</v>
+        <v>5282</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2712,10 +3288,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46141.07291666666</v>
+        <v>46143.07291666666</v>
       </c>
       <c r="B105">
-        <v>5225</v>
+        <v>5215</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2726,10 +3302,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46141.08333333334</v>
+        <v>46143.08333333334</v>
       </c>
       <c r="B106">
-        <v>5197</v>
+        <v>5188</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2740,10 +3316,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46141.09375</v>
+        <v>46143.09375</v>
       </c>
       <c r="B107">
-        <v>5233</v>
+        <v>5219</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2754,10 +3330,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46141.10416666666</v>
+        <v>46143.10416666666</v>
       </c>
       <c r="B108">
-        <v>5221</v>
+        <v>5197</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2768,10 +3344,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46141.11458333334</v>
+        <v>46143.11458333334</v>
       </c>
       <c r="B109">
-        <v>5196</v>
+        <v>5232</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2782,10 +3358,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46141.125</v>
+        <v>46143.125</v>
       </c>
       <c r="B110">
-        <v>5187</v>
+        <v>5184</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2796,10 +3372,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46141.13541666666</v>
+        <v>46143.13541666666</v>
       </c>
       <c r="B111">
-        <v>5236</v>
+        <v>5354</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2810,10 +3386,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46141.14583333334</v>
+        <v>46143.14583333334</v>
       </c>
       <c r="B112">
-        <v>5305</v>
+        <v>5337</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2824,10 +3400,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46141.15625</v>
+        <v>46143.15625</v>
       </c>
       <c r="B113">
-        <v>5319</v>
+        <v>5378</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2838,10 +3414,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46141.16666666666</v>
+        <v>46143.16666666666</v>
       </c>
       <c r="B114">
-        <v>5451</v>
+        <v>5253</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2852,10 +3428,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46141.17708333334</v>
+        <v>46143.17708333334</v>
       </c>
       <c r="B115">
-        <v>5533</v>
+        <v>5334</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2866,10 +3442,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46141.1875</v>
+        <v>46143.1875</v>
       </c>
       <c r="B116">
-        <v>5575</v>
+        <v>5433</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2880,10 +3456,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46141.19791666666</v>
+        <v>46143.19791666666</v>
       </c>
       <c r="B117">
-        <v>5655</v>
+        <v>5385</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2894,10 +3470,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46141.20833333334</v>
+        <v>46143.20833333334</v>
       </c>
       <c r="B118">
-        <v>5600</v>
+        <v>5381</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2908,10 +3484,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46141.21875</v>
+        <v>46143.21875</v>
       </c>
       <c r="B119">
-        <v>5685</v>
+        <v>5304</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2922,10 +3498,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46141.22916666666</v>
+        <v>46143.22916666666</v>
       </c>
       <c r="B120">
-        <v>5722</v>
+        <v>5325</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2936,10 +3512,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46141.23958333334</v>
+        <v>46143.23958333334</v>
       </c>
       <c r="B121">
-        <v>5864</v>
+        <v>5304</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2950,10 +3526,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46141.25</v>
+        <v>46143.25</v>
       </c>
       <c r="B122">
-        <v>6109</v>
+        <v>5224</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2964,10 +3540,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46141.26041666666</v>
+        <v>46143.26041666666</v>
       </c>
       <c r="B123">
-        <v>6167</v>
+        <v>5199</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2978,10 +3554,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46141.27083333334</v>
+        <v>46143.27083333334</v>
       </c>
       <c r="B124">
-        <v>6218</v>
+        <v>5198</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2992,10 +3568,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46141.28125</v>
+        <v>46143.28125</v>
       </c>
       <c r="B125">
-        <v>6203</v>
+        <v>5178</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -3006,10 +3582,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46141.29166666666</v>
+        <v>46143.29166666666</v>
       </c>
       <c r="B126">
-        <v>6303</v>
+        <v>5156</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -3020,10 +3596,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46141.30208333334</v>
+        <v>46143.30208333334</v>
       </c>
       <c r="B127">
-        <v>6325</v>
+        <v>5002</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -3034,10 +3610,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46141.3125</v>
+        <v>46143.3125</v>
       </c>
       <c r="B128">
-        <v>6304</v>
+        <v>4932</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -3048,10 +3624,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46141.32291666666</v>
+        <v>46143.32291666666</v>
       </c>
       <c r="B129">
-        <v>6218</v>
+        <v>4801</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -3062,10 +3638,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46141.33333333334</v>
+        <v>46143.33333333334</v>
       </c>
       <c r="B130">
-        <v>6079</v>
+        <v>4666</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -3076,10 +3652,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46141.34375</v>
+        <v>46143.34375</v>
       </c>
       <c r="B131">
-        <v>6020</v>
+        <v>4433</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -3090,10 +3666,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46141.35416666666</v>
+        <v>46143.35416666666</v>
       </c>
       <c r="B132">
-        <v>6004</v>
+        <v>4335</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -3104,10 +3680,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46141.36458333334</v>
+        <v>46143.36458333334</v>
       </c>
       <c r="B133">
-        <v>5852</v>
+        <v>4230</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -3118,10 +3694,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46141.375</v>
+        <v>46143.375</v>
       </c>
       <c r="B134">
-        <v>5796</v>
+        <v>4097</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -3132,10 +3708,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46141.38541666666</v>
+        <v>46143.38541666666</v>
       </c>
       <c r="B135">
-        <v>5755</v>
+        <v>4006</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -3146,10 +3722,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46141.39583333334</v>
+        <v>46143.39583333334</v>
       </c>
       <c r="B136">
-        <v>5661</v>
+        <v>3885</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -3160,10 +3736,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46141.40625</v>
+        <v>46143.40625</v>
       </c>
       <c r="B137">
-        <v>5619</v>
+        <v>3758</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -3174,10 +3750,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46141.41666666666</v>
+        <v>46143.41666666666</v>
       </c>
       <c r="B138">
-        <v>5370</v>
+        <v>3746</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -3188,10 +3764,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46141.42708333334</v>
+        <v>46143.42708333334</v>
       </c>
       <c r="B139">
-        <v>5326</v>
+        <v>3674</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -3202,10 +3778,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46141.4375</v>
+        <v>46143.4375</v>
       </c>
       <c r="B140">
-        <v>5051</v>
+        <v>3714</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -3216,10 +3792,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46141.44791666666</v>
+        <v>46143.44791666666</v>
       </c>
       <c r="B141">
-        <v>4890</v>
+        <v>3689</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -3230,10 +3806,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46141.45833333334</v>
+        <v>46143.45833333334</v>
       </c>
       <c r="B142">
-        <v>4711</v>
+        <v>3729</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -3244,10 +3820,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46141.46875</v>
+        <v>46143.46875</v>
       </c>
       <c r="B143">
-        <v>4709</v>
+        <v>3709</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -3258,10 +3834,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46141.47916666666</v>
+        <v>46143.47916666666</v>
       </c>
       <c r="B144">
-        <v>4691</v>
+        <v>3761</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -3272,10 +3848,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46141.48958333334</v>
+        <v>46143.48958333334</v>
       </c>
       <c r="B145">
-        <v>4608</v>
+        <v>3770</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3286,10 +3862,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46141.5</v>
+        <v>46143.5</v>
       </c>
       <c r="B146">
-        <v>4641</v>
+        <v>3850</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3300,10 +3876,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46141.51041666666</v>
+        <v>46143.51041666666</v>
       </c>
       <c r="B147">
-        <v>4786</v>
+        <v>3917</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3314,10 +3890,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46141.52083333334</v>
+        <v>46143.52083333334</v>
       </c>
       <c r="B148">
-        <v>4760</v>
+        <v>3950</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3328,10 +3904,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46141.53125</v>
+        <v>46143.53125</v>
       </c>
       <c r="B149">
-        <v>4622</v>
+        <v>3975</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3342,10 +3918,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46141.54166666666</v>
+        <v>46143.54166666666</v>
       </c>
       <c r="B150">
-        <v>4676</v>
+        <v>3993</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3356,10 +3932,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46141.55208333334</v>
+        <v>46143.55208333334</v>
       </c>
       <c r="B151">
-        <v>4697</v>
+        <v>3974</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3370,10 +3946,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46141.5625</v>
+        <v>46143.5625</v>
       </c>
       <c r="B152">
-        <v>4730</v>
+        <v>3946</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3384,10 +3960,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46141.57291666666</v>
+        <v>46143.57291666666</v>
       </c>
       <c r="B153">
-        <v>4765</v>
+        <v>3968</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3398,10 +3974,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46141.58333333334</v>
+        <v>46143.58333333334</v>
       </c>
       <c r="B154">
-        <v>4829</v>
+        <v>3941</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3412,10 +3988,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46141.59375</v>
+        <v>46143.59375</v>
       </c>
       <c r="B155">
-        <v>4969</v>
+        <v>3996</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3426,10 +4002,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46141.60416666666</v>
+        <v>46143.60416666666</v>
       </c>
       <c r="B156">
-        <v>4988</v>
+        <v>4033</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3440,10 +4016,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46141.61458333334</v>
+        <v>46143.61458333334</v>
       </c>
       <c r="B157">
-        <v>5042</v>
+        <v>4021</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3454,10 +4030,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46141.625</v>
+        <v>46143.625</v>
       </c>
       <c r="B158">
-        <v>5195</v>
+        <v>3993</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3468,10 +4044,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46141.63541666666</v>
+        <v>46143.63541666666</v>
       </c>
       <c r="B159">
-        <v>5256</v>
+        <v>4080</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3482,10 +4058,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46141.64583333334</v>
+        <v>46143.64583333334</v>
       </c>
       <c r="B160">
-        <v>5321</v>
+        <v>4201</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3496,10 +4072,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46141.65625</v>
+        <v>46143.65625</v>
       </c>
       <c r="B161">
-        <v>5367</v>
+        <v>4250</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3510,10 +4086,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46141.66666666666</v>
+        <v>46143.66666666666</v>
       </c>
       <c r="B162">
-        <v>5561</v>
+        <v>4436</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3524,10 +4100,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46141.67708333334</v>
+        <v>46143.67708333334</v>
       </c>
       <c r="B163">
-        <v>5671</v>
+        <v>4518</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3538,10 +4114,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46141.6875</v>
+        <v>46143.6875</v>
       </c>
       <c r="B164">
-        <v>5820</v>
+        <v>4671</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3552,10 +4128,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46141.69791666666</v>
+        <v>46143.69791666666</v>
       </c>
       <c r="B165">
-        <v>5918</v>
+        <v>4841</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3566,10 +4142,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46141.70833333334</v>
+        <v>46143.70833333334</v>
       </c>
       <c r="B166">
-        <v>5978</v>
+        <v>5017</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3580,10 +4156,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46141.71875</v>
+        <v>46143.71875</v>
       </c>
       <c r="B167">
-        <v>6125</v>
+        <v>5142</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3594,10 +4170,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46141.72916666666</v>
+        <v>46143.72916666666</v>
       </c>
       <c r="B168">
-        <v>6304</v>
+        <v>5244</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3608,10 +4184,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46141.73958333334</v>
+        <v>46143.73958333334</v>
       </c>
       <c r="B169">
-        <v>6379</v>
+        <v>5409</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3622,10 +4198,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46141.75</v>
+        <v>46143.75</v>
       </c>
       <c r="B170">
-        <v>6532</v>
+        <v>5574</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3636,10 +4212,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46141.76041666666</v>
+        <v>46143.76041666666</v>
       </c>
       <c r="B171">
-        <v>6611</v>
+        <v>5721</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3650,10 +4226,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46141.77083333334</v>
+        <v>46143.77083333334</v>
       </c>
       <c r="B172">
-        <v>6725</v>
+        <v>5871</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3664,10 +4240,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46141.78125</v>
+        <v>46143.78125</v>
       </c>
       <c r="B173">
-        <v>6848</v>
+        <v>6011</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3678,10 +4254,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46141.79166666666</v>
+        <v>46143.79166666666</v>
       </c>
       <c r="B174">
-        <v>6953</v>
+        <v>6078</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3692,10 +4268,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46141.80208333334</v>
+        <v>46143.80208333334</v>
       </c>
       <c r="B175">
-        <v>7003</v>
+        <v>6188</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3706,10 +4282,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46141.8125</v>
+        <v>46143.8125</v>
       </c>
       <c r="B176">
-        <v>7107</v>
+        <v>6303</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3720,10 +4296,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46141.82291666666</v>
+        <v>46143.82291666666</v>
       </c>
       <c r="B177">
-        <v>7237</v>
+        <v>6391</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3734,10 +4310,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46141.83333333334</v>
+        <v>46143.83333333334</v>
       </c>
       <c r="B178">
-        <v>7165</v>
+        <v>6434</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3748,10 +4324,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46141.84375</v>
+        <v>46143.84375</v>
       </c>
       <c r="B179">
-        <v>7115</v>
+        <v>6394</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3762,10 +4338,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46141.85416666666</v>
+        <v>46143.85416666666</v>
       </c>
       <c r="B180">
-        <v>6981</v>
+        <v>6346</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3776,10 +4352,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46141.86458333334</v>
+        <v>46143.86458333334</v>
       </c>
       <c r="B181">
-        <v>6877</v>
+        <v>6281</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3790,10 +4366,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46141.875</v>
+        <v>46143.875</v>
       </c>
       <c r="B182">
-        <v>6779</v>
+        <v>6144</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3804,10 +4380,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46141.88541666666</v>
+        <v>46143.88541666666</v>
       </c>
       <c r="B183">
-        <v>6639</v>
+        <v>6011</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3818,10 +4394,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46141.89583333334</v>
+        <v>46143.89583333334</v>
       </c>
       <c r="B184">
-        <v>6531</v>
+        <v>5921</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3832,10 +4408,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46141.90625</v>
+        <v>46143.90625</v>
       </c>
       <c r="B185">
-        <v>6324</v>
+        <v>5954</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3846,10 +4422,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46141.91666666666</v>
+        <v>46143.91666666666</v>
       </c>
       <c r="B186">
-        <v>6128</v>
+        <v>5682</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3860,10 +4436,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46141.92708333334</v>
+        <v>46143.92708333334</v>
       </c>
       <c r="B187">
-        <v>6012</v>
+        <v>5580</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3874,10 +4450,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46141.9375</v>
+        <v>46143.9375</v>
       </c>
       <c r="B188">
-        <v>5901</v>
+        <v>5521</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3888,10 +4464,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46141.94791666666</v>
+        <v>46143.94791666666</v>
       </c>
       <c r="B189">
-        <v>5721</v>
+        <v>5419</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3902,10 +4478,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46141.95833333334</v>
+        <v>46143.95833333334</v>
       </c>
       <c r="B190">
-        <v>5673</v>
+        <v>5287</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3916,10 +4492,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46141.96875</v>
+        <v>46143.96875</v>
       </c>
       <c r="B191">
-        <v>5580</v>
+        <v>5206</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3930,10 +4506,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46141.97916666666</v>
+        <v>46143.97916666666</v>
       </c>
       <c r="B192">
-        <v>5531</v>
+        <v>5124</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3944,10 +4520,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46141.98958333334</v>
+        <v>46143.98958333334</v>
       </c>
       <c r="B193">
-        <v>5468</v>
+        <v>5101</v>
       </c>
       <c r="C193">
         <v>96</v>
@@ -3958,10 +4534,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="2">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B194">
-        <v>5379</v>
+        <v>4974</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -3972,10 +4548,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="2">
-        <v>46142.01041666666</v>
+        <v>46144.01041666666</v>
       </c>
       <c r="B195">
-        <v>5308</v>
+        <v>4904</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -3986,10 +4562,10 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="2">
-        <v>46142.02083333334</v>
+        <v>46144.02083333334</v>
       </c>
       <c r="B196">
-        <v>5299</v>
+        <v>4898</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -4000,10 +4576,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="2">
-        <v>46142.03125</v>
+        <v>46144.03125</v>
       </c>
       <c r="B197">
-        <v>5318</v>
+        <v>4867</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -4014,10 +4590,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="2">
-        <v>46142.04166666666</v>
+        <v>46144.04166666666</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>4844</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -4028,10 +4604,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="2">
-        <v>46142.05208333334</v>
+        <v>46144.05208333334</v>
       </c>
       <c r="B199">
-        <v>5260</v>
+        <v>4883</v>
       </c>
       <c r="C199">
         <v>6</v>
@@ -4042,10 +4618,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="2">
-        <v>46142.0625</v>
+        <v>46144.0625</v>
       </c>
       <c r="B200">
-        <v>5279</v>
+        <v>4832</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -4056,10 +4632,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="2">
-        <v>46142.07291666666</v>
+        <v>46144.07291666666</v>
       </c>
       <c r="B201">
-        <v>5241</v>
+        <v>4837</v>
       </c>
       <c r="C201">
         <v>8</v>
@@ -4070,10 +4646,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="2">
-        <v>46142.08333333334</v>
+        <v>46144.08333333334</v>
       </c>
       <c r="B202">
-        <v>5021</v>
+        <v>4778</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -4084,10 +4660,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="2">
-        <v>46142.09375</v>
+        <v>46144.09375</v>
       </c>
       <c r="B203">
-        <v>4859</v>
+        <v>4780</v>
       </c>
       <c r="C203">
         <v>10</v>
@@ -4098,10 +4674,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="2">
-        <v>46142.10416666666</v>
+        <v>46144.10416666666</v>
       </c>
       <c r="B204">
-        <v>4872</v>
+        <v>4763</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -4112,10 +4688,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="2">
-        <v>46142.11458333334</v>
+        <v>46144.11458333334</v>
       </c>
       <c r="B205">
-        <v>4867</v>
+        <v>4781</v>
       </c>
       <c r="C205">
         <v>12</v>
@@ -4126,10 +4702,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="2">
-        <v>46142.125</v>
+        <v>46144.125</v>
       </c>
       <c r="B206">
-        <v>4837</v>
+        <v>4688</v>
       </c>
       <c r="C206">
         <v>13</v>
@@ -4140,10 +4716,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="2">
-        <v>46142.13541666666</v>
+        <v>46144.13541666666</v>
       </c>
       <c r="B207">
-        <v>4872</v>
+        <v>4715</v>
       </c>
       <c r="C207">
         <v>14</v>
@@ -4154,10 +4730,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="2">
-        <v>46142.14583333334</v>
+        <v>46144.14583333334</v>
       </c>
       <c r="B208">
-        <v>4930</v>
+        <v>4753</v>
       </c>
       <c r="C208">
         <v>15</v>
@@ -4168,10 +4744,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="2">
-        <v>46142.15625</v>
+        <v>46144.15625</v>
       </c>
       <c r="B209">
-        <v>4865</v>
+        <v>4790</v>
       </c>
       <c r="C209">
         <v>16</v>
@@ -4182,10 +4758,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="2">
-        <v>46142.16666666666</v>
+        <v>46144.16666666666</v>
       </c>
       <c r="B210">
-        <v>4874</v>
+        <v>4755</v>
       </c>
       <c r="C210">
         <v>17</v>
@@ -4196,10 +4772,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="2">
-        <v>46142.17708333334</v>
+        <v>46144.17708333334</v>
       </c>
       <c r="B211">
-        <v>5437</v>
+        <v>4809</v>
       </c>
       <c r="C211">
         <v>18</v>
@@ -4210,10 +4786,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="2">
-        <v>46142.1875</v>
+        <v>46144.1875</v>
       </c>
       <c r="B212">
-        <v>5576</v>
+        <v>4801</v>
       </c>
       <c r="C212">
         <v>19</v>
@@ -4224,10 +4800,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="2">
-        <v>46142.19791666666</v>
+        <v>46144.19791666666</v>
       </c>
       <c r="B213">
-        <v>5596</v>
+        <v>4809</v>
       </c>
       <c r="C213">
         <v>20</v>
@@ -4238,10 +4814,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="2">
-        <v>46142.20833333334</v>
+        <v>46144.20833333334</v>
       </c>
       <c r="B214">
-        <v>5609</v>
+        <v>4799</v>
       </c>
       <c r="C214">
         <v>21</v>
@@ -4252,10 +4828,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="2">
-        <v>46142.21875</v>
+        <v>46144.21875</v>
       </c>
       <c r="B215">
-        <v>5724</v>
+        <v>4821</v>
       </c>
       <c r="C215">
         <v>22</v>
@@ -4266,10 +4842,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="2">
-        <v>46142.22916666666</v>
+        <v>46144.22916666666</v>
       </c>
       <c r="B216">
-        <v>5907</v>
+        <v>4835</v>
       </c>
       <c r="C216">
         <v>23</v>
@@ -4280,10 +4856,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="2">
-        <v>46142.23958333334</v>
+        <v>46144.23958333334</v>
       </c>
       <c r="B217">
-        <v>6050</v>
+        <v>4882</v>
       </c>
       <c r="C217">
         <v>24</v>
@@ -4294,10 +4870,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="2">
-        <v>46142.25</v>
+        <v>46144.25</v>
       </c>
       <c r="B218">
-        <v>6319</v>
+        <v>4937</v>
       </c>
       <c r="C218">
         <v>25</v>
@@ -4308,10 +4884,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="2">
-        <v>46142.26041666666</v>
+        <v>46144.26041666666</v>
       </c>
       <c r="B219">
-        <v>6425</v>
+        <v>4990</v>
       </c>
       <c r="C219">
         <v>26</v>
@@ -4322,10 +4898,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="2">
-        <v>46142.27083333334</v>
+        <v>46144.27083333334</v>
       </c>
       <c r="B220">
-        <v>6508</v>
+        <v>5011</v>
       </c>
       <c r="C220">
         <v>27</v>
@@ -4336,10 +4912,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="2">
-        <v>46142.28125</v>
+        <v>46144.28125</v>
       </c>
       <c r="B221">
-        <v>6573</v>
+        <v>5043</v>
       </c>
       <c r="C221">
         <v>28</v>
@@ -4350,10 +4926,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="2">
-        <v>46142.29166666666</v>
+        <v>46144.29166666666</v>
       </c>
       <c r="B222">
-        <v>6712</v>
+        <v>5039</v>
       </c>
       <c r="C222">
         <v>29</v>
@@ -4364,10 +4940,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="2">
-        <v>46142.30208333334</v>
+        <v>46144.30208333334</v>
       </c>
       <c r="B223">
-        <v>6887</v>
+        <v>5063</v>
       </c>
       <c r="C223">
         <v>30</v>
@@ -4378,10 +4954,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="2">
-        <v>46142.3125</v>
+        <v>46144.3125</v>
       </c>
       <c r="B224">
-        <v>6879</v>
+        <v>4955</v>
       </c>
       <c r="C224">
         <v>31</v>
@@ -4392,10 +4968,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="2">
-        <v>46142.32291666666</v>
+        <v>46144.32291666666</v>
       </c>
       <c r="B225">
-        <v>6788</v>
+        <v>4983</v>
       </c>
       <c r="C225">
         <v>32</v>
@@ -4406,10 +4982,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="2">
-        <v>46142.33333333334</v>
+        <v>46144.33333333334</v>
       </c>
       <c r="B226">
-        <v>6738</v>
+        <v>4865</v>
       </c>
       <c r="C226">
         <v>33</v>
@@ -4420,10 +4996,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="2">
-        <v>46142.34375</v>
+        <v>46144.34375</v>
       </c>
       <c r="B227">
-        <v>6813</v>
+        <v>4812</v>
       </c>
       <c r="C227">
         <v>34</v>
@@ -4434,10 +5010,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="2">
-        <v>46142.35416666666</v>
+        <v>46144.35416666666</v>
       </c>
       <c r="B228">
-        <v>6723</v>
+        <v>4679</v>
       </c>
       <c r="C228">
         <v>35</v>
@@ -4448,10 +5024,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="2">
-        <v>46142.36458333334</v>
+        <v>46144.36458333334</v>
       </c>
       <c r="B229">
-        <v>6650</v>
+        <v>4702</v>
       </c>
       <c r="C229">
         <v>36</v>
@@ -4462,10 +5038,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="2">
-        <v>46142.375</v>
+        <v>46144.375</v>
       </c>
       <c r="B230">
-        <v>6630</v>
+        <v>4535</v>
       </c>
       <c r="C230">
         <v>37</v>
@@ -4476,10 +5052,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="2">
-        <v>46142.38541666666</v>
+        <v>46144.38541666666</v>
       </c>
       <c r="B231">
-        <v>6540</v>
+        <v>4434</v>
       </c>
       <c r="C231">
         <v>38</v>
@@ -4490,10 +5066,10 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="2">
-        <v>46142.39583333334</v>
+        <v>46144.39583333334</v>
       </c>
       <c r="B232">
-        <v>6409</v>
+        <v>4475</v>
       </c>
       <c r="C232">
         <v>39</v>
@@ -4504,10 +5080,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="2">
-        <v>46142.40625</v>
+        <v>46144.40625</v>
       </c>
       <c r="B233">
-        <v>6429</v>
+        <v>4359</v>
       </c>
       <c r="C233">
         <v>40</v>
@@ -4518,10 +5094,10 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="2">
-        <v>46142.41666666666</v>
+        <v>46144.41666666666</v>
       </c>
       <c r="B234">
-        <v>6245</v>
+        <v>4286</v>
       </c>
       <c r="C234">
         <v>41</v>
@@ -4532,10 +5108,10 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="2">
-        <v>46142.42708333334</v>
+        <v>46144.42708333334</v>
       </c>
       <c r="B235">
-        <v>6260</v>
+        <v>4359</v>
       </c>
       <c r="C235">
         <v>42</v>
@@ -4546,10 +5122,10 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="2">
-        <v>46142.4375</v>
+        <v>46144.4375</v>
       </c>
       <c r="B236">
-        <v>6170</v>
+        <v>4301</v>
       </c>
       <c r="C236">
         <v>43</v>
@@ -4560,10 +5136,10 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="2">
-        <v>46142.44791666666</v>
+        <v>46144.44791666666</v>
       </c>
       <c r="B237">
-        <v>6093</v>
+        <v>4221</v>
       </c>
       <c r="C237">
         <v>44</v>
@@ -4574,10 +5150,10 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="2">
-        <v>46142.45833333334</v>
+        <v>46144.45833333334</v>
       </c>
       <c r="B238">
-        <v>6089</v>
+        <v>4189</v>
       </c>
       <c r="C238">
         <v>45</v>
@@ -4588,10 +5164,10 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="2">
-        <v>46142.46875</v>
+        <v>46144.46875</v>
       </c>
       <c r="B239">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="C239">
         <v>46</v>
@@ -4602,10 +5178,10 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="2">
-        <v>46142.47916666666</v>
+        <v>46144.47916666666</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>4149</v>
       </c>
       <c r="C240">
         <v>47</v>
@@ -4616,10 +5192,10 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="2">
-        <v>46142.48958333334</v>
+        <v>46144.48958333334</v>
       </c>
       <c r="B241">
-        <v>0</v>
+        <v>4135</v>
       </c>
       <c r="C241">
         <v>48</v>
@@ -4630,10 +5206,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="2">
-        <v>46142.5</v>
+        <v>46144.5</v>
       </c>
       <c r="B242">
-        <v>0</v>
+        <v>4136</v>
       </c>
       <c r="C242">
         <v>49</v>
@@ -4644,10 +5220,10 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="2">
-        <v>46142.51041666666</v>
+        <v>46144.51041666666</v>
       </c>
       <c r="B243">
-        <v>0</v>
+        <v>4187</v>
       </c>
       <c r="C243">
         <v>50</v>
@@ -4658,10 +5234,10 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="2">
-        <v>46142.52083333334</v>
+        <v>46144.52083333334</v>
       </c>
       <c r="B244">
-        <v>0</v>
+        <v>4245</v>
       </c>
       <c r="C244">
         <v>51</v>
@@ -4672,10 +5248,10 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="2">
-        <v>46142.53125</v>
+        <v>46144.53125</v>
       </c>
       <c r="B245">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="C245">
         <v>52</v>
@@ -4686,10 +5262,10 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="2">
-        <v>46142.54166666666</v>
+        <v>46144.54166666666</v>
       </c>
       <c r="B246">
-        <v>0</v>
+        <v>4050</v>
       </c>
       <c r="C246">
         <v>53</v>
@@ -4700,10 +5276,10 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="2">
-        <v>46142.55208333334</v>
+        <v>46144.55208333334</v>
       </c>
       <c r="B247">
-        <v>0</v>
+        <v>4052</v>
       </c>
       <c r="C247">
         <v>54</v>
@@ -4714,10 +5290,10 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="2">
-        <v>46142.5625</v>
+        <v>46144.5625</v>
       </c>
       <c r="B248">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="C248">
         <v>55</v>
@@ -4728,10 +5304,10 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="2">
-        <v>46142.57291666666</v>
+        <v>46144.57291666666</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="C249">
         <v>56</v>
@@ -4742,10 +5318,10 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="2">
-        <v>46142.58333333334</v>
+        <v>46144.58333333334</v>
       </c>
       <c r="B250">
-        <v>0</v>
+        <v>4259</v>
       </c>
       <c r="C250">
         <v>57</v>
@@ -4756,10 +5332,10 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="2">
-        <v>46142.59375</v>
+        <v>46144.59375</v>
       </c>
       <c r="B251">
-        <v>0</v>
+        <v>4217</v>
       </c>
       <c r="C251">
         <v>58</v>
@@ -4770,10 +5346,10 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="2">
-        <v>46142.60416666666</v>
+        <v>46144.60416666666</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>4259</v>
       </c>
       <c r="C252">
         <v>59</v>
@@ -4784,10 +5360,10 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="2">
-        <v>46142.61458333334</v>
+        <v>46144.61458333334</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>4355</v>
       </c>
       <c r="C253">
         <v>60</v>
@@ -4798,10 +5374,10 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="2">
-        <v>46142.625</v>
+        <v>46144.625</v>
       </c>
       <c r="B254">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="C254">
         <v>61</v>
@@ -4812,10 +5388,10 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="2">
-        <v>46142.63541666666</v>
+        <v>46144.63541666666</v>
       </c>
       <c r="B255">
-        <v>0</v>
+        <v>4234</v>
       </c>
       <c r="C255">
         <v>62</v>
@@ -4826,10 +5402,10 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="2">
-        <v>46142.64583333334</v>
+        <v>46144.64583333334</v>
       </c>
       <c r="B256">
-        <v>0</v>
+        <v>4424</v>
       </c>
       <c r="C256">
         <v>63</v>
@@ -4840,10 +5416,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="2">
-        <v>46142.65625</v>
+        <v>46144.65625</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>4538</v>
       </c>
       <c r="C257">
         <v>64</v>
@@ -4854,10 +5430,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="2">
-        <v>46142.66666666666</v>
+        <v>46144.66666666666</v>
       </c>
       <c r="B258">
-        <v>0</v>
+        <v>4705</v>
       </c>
       <c r="C258">
         <v>65</v>
@@ -4868,10 +5444,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="2">
-        <v>46142.67708333334</v>
+        <v>46144.67708333334</v>
       </c>
       <c r="B259">
-        <v>0</v>
+        <v>4841</v>
       </c>
       <c r="C259">
         <v>66</v>
@@ -4882,10 +5458,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="2">
-        <v>46142.6875</v>
+        <v>46144.6875</v>
       </c>
       <c r="B260">
-        <v>0</v>
+        <v>4950</v>
       </c>
       <c r="C260">
         <v>67</v>
@@ -4896,10 +5472,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="2">
-        <v>46142.69791666666</v>
+        <v>46144.69791666666</v>
       </c>
       <c r="B261">
-        <v>0</v>
+        <v>5032</v>
       </c>
       <c r="C261">
         <v>68</v>
@@ -4910,10 +5486,10 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="2">
-        <v>46142.70833333334</v>
+        <v>46144.70833333334</v>
       </c>
       <c r="B262">
-        <v>0</v>
+        <v>5054</v>
       </c>
       <c r="C262">
         <v>69</v>
@@ -4924,10 +5500,10 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="2">
-        <v>46142.71875</v>
+        <v>46144.71875</v>
       </c>
       <c r="B263">
-        <v>0</v>
+        <v>5186</v>
       </c>
       <c r="C263">
         <v>70</v>
@@ -4938,10 +5514,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="2">
-        <v>46142.72916666666</v>
+        <v>46144.72916666666</v>
       </c>
       <c r="B264">
-        <v>0</v>
+        <v>5355</v>
       </c>
       <c r="C264">
         <v>71</v>
@@ -4952,10 +5528,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="2">
-        <v>46142.73958333334</v>
+        <v>46144.73958333334</v>
       </c>
       <c r="B265">
-        <v>0</v>
+        <v>5491</v>
       </c>
       <c r="C265">
         <v>72</v>
@@ -4966,10 +5542,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="2">
-        <v>46142.75</v>
+        <v>46144.75</v>
       </c>
       <c r="B266">
-        <v>0</v>
+        <v>5605</v>
       </c>
       <c r="C266">
         <v>73</v>
@@ -4980,10 +5556,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="2">
-        <v>46142.76041666666</v>
+        <v>46144.76041666666</v>
       </c>
       <c r="B267">
-        <v>0</v>
+        <v>5770</v>
       </c>
       <c r="C267">
         <v>74</v>
@@ -4994,10 +5570,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="2">
-        <v>46142.77083333334</v>
+        <v>46144.77083333334</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>5909</v>
       </c>
       <c r="C268">
         <v>75</v>
@@ -5008,10 +5584,10 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="2">
-        <v>46142.78125</v>
+        <v>46144.78125</v>
       </c>
       <c r="B269">
-        <v>0</v>
+        <v>6052</v>
       </c>
       <c r="C269">
         <v>76</v>
@@ -5022,10 +5598,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="2">
-        <v>46142.79166666666</v>
+        <v>46144.79166666666</v>
       </c>
       <c r="B270">
-        <v>0</v>
+        <v>6134</v>
       </c>
       <c r="C270">
         <v>77</v>
@@ -5036,10 +5612,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="2">
-        <v>46142.80208333334</v>
+        <v>46144.80208333334</v>
       </c>
       <c r="B271">
-        <v>0</v>
+        <v>6260</v>
       </c>
       <c r="C271">
         <v>78</v>
@@ -5050,10 +5626,10 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="2">
-        <v>46142.8125</v>
+        <v>46144.8125</v>
       </c>
       <c r="B272">
-        <v>0</v>
+        <v>6371</v>
       </c>
       <c r="C272">
         <v>79</v>
@@ -5064,10 +5640,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="2">
-        <v>46142.82291666666</v>
+        <v>46144.82291666666</v>
       </c>
       <c r="B273">
-        <v>0</v>
+        <v>6441</v>
       </c>
       <c r="C273">
         <v>80</v>
@@ -5078,10 +5654,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="2">
-        <v>46142.83333333334</v>
+        <v>46144.83333333334</v>
       </c>
       <c r="B274">
-        <v>0</v>
+        <v>6525</v>
       </c>
       <c r="C274">
         <v>81</v>
@@ -5092,10 +5668,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="2">
-        <v>46142.84375</v>
+        <v>46144.84375</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>6442</v>
       </c>
       <c r="C275">
         <v>82</v>
@@ -5106,10 +5682,10 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="2">
-        <v>46142.85416666666</v>
+        <v>46144.85416666666</v>
       </c>
       <c r="B276">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="C276">
         <v>83</v>
@@ -5120,10 +5696,10 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="2">
-        <v>46142.86458333334</v>
+        <v>46144.86458333334</v>
       </c>
       <c r="B277">
-        <v>0</v>
+        <v>6409</v>
       </c>
       <c r="C277">
         <v>84</v>
@@ -5134,10 +5710,10 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="2">
-        <v>46142.875</v>
+        <v>46144.875</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>6319</v>
       </c>
       <c r="C278">
         <v>85</v>
@@ -5148,10 +5724,10 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="2">
-        <v>46142.88541666666</v>
+        <v>46144.88541666666</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>6125</v>
       </c>
       <c r="C279">
         <v>86</v>
@@ -5162,10 +5738,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="2">
-        <v>46142.89583333334</v>
+        <v>46144.89583333334</v>
       </c>
       <c r="B280">
-        <v>0</v>
+        <v>6056</v>
       </c>
       <c r="C280">
         <v>87</v>
@@ -5176,10 +5752,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="2">
-        <v>46142.90625</v>
+        <v>46144.90625</v>
       </c>
       <c r="B281">
-        <v>0</v>
+        <v>5914</v>
       </c>
       <c r="C281">
         <v>88</v>
@@ -5190,10 +5766,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="2">
-        <v>46142.91666666666</v>
+        <v>46144.91666666666</v>
       </c>
       <c r="B282">
-        <v>0</v>
+        <v>5795</v>
       </c>
       <c r="C282">
         <v>89</v>
@@ -5204,10 +5780,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="2">
-        <v>46142.92708333334</v>
+        <v>46144.92708333334</v>
       </c>
       <c r="B283">
-        <v>0</v>
+        <v>5669</v>
       </c>
       <c r="C283">
         <v>90</v>
@@ -5218,10 +5794,10 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="2">
-        <v>46142.9375</v>
+        <v>46144.9375</v>
       </c>
       <c r="B284">
-        <v>0</v>
+        <v>5585</v>
       </c>
       <c r="C284">
         <v>91</v>
@@ -5232,10 +5808,10 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="2">
-        <v>46142.94791666666</v>
+        <v>46144.94791666666</v>
       </c>
       <c r="B285">
-        <v>0</v>
+        <v>5460</v>
       </c>
       <c r="C285">
         <v>92</v>
@@ -5246,10 +5822,10 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="2">
-        <v>46142.95833333334</v>
+        <v>46144.95833333334</v>
       </c>
       <c r="B286">
-        <v>0</v>
+        <v>5227</v>
       </c>
       <c r="C286">
         <v>93</v>
@@ -5260,10 +5836,10 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="2">
-        <v>46142.96875</v>
+        <v>46144.96875</v>
       </c>
       <c r="B287">
-        <v>0</v>
+        <v>5148</v>
       </c>
       <c r="C287">
         <v>94</v>
@@ -5274,10 +5850,10 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="2">
-        <v>46142.97916666666</v>
+        <v>46144.97916666666</v>
       </c>
       <c r="B288">
-        <v>0</v>
+        <v>5168</v>
       </c>
       <c r="C288">
         <v>95</v>
@@ -5288,16 +5864,2704 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="2">
-        <v>46142.98958333334</v>
+        <v>46144.98958333334</v>
       </c>
       <c r="B289">
-        <v>0</v>
+        <v>5084</v>
       </c>
       <c r="C289">
         <v>96</v>
       </c>
       <c r="D289" t="s">
         <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B290">
+        <v>5000</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46145.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4893</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46145.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4926</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46145.03125</v>
+      </c>
+      <c r="B293">
+        <v>4881</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46145.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4901</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46145.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4868</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46145.0625</v>
+      </c>
+      <c r="B296">
+        <v>4815</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46145.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4813</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46145.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4814</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46145.09375</v>
+      </c>
+      <c r="B299">
+        <v>4820</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46145.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4775</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46145.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4787</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46145.125</v>
+      </c>
+      <c r="B302">
+        <v>4796</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46145.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4751</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46145.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4779</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46145.15625</v>
+      </c>
+      <c r="B305">
+        <v>4783</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46145.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4815</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46145.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4821</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46145.1875</v>
+      </c>
+      <c r="B308">
+        <v>4754</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46145.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>4781</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46145.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>4761</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46145.21875</v>
+      </c>
+      <c r="B311">
+        <v>4702</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46145.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>4737</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46145.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>4647</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46145.25</v>
+      </c>
+      <c r="B314">
+        <v>4668</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46145.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>4614</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46145.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>4456</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46145.28125</v>
+      </c>
+      <c r="B317">
+        <v>4407</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46145.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>4301</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46145.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>4195</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46145.3125</v>
+      </c>
+      <c r="B320">
+        <v>4065</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46145.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>3877</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46145.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>3790</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46145.34375</v>
+      </c>
+      <c r="B323">
+        <v>3655</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46145.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>3543</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46145.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>3410</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46145.375</v>
+      </c>
+      <c r="B326">
+        <v>3154</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46145.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>3034</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46145.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2956</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46145.40625</v>
+      </c>
+      <c r="B329">
+        <v>2885</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46145.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>2925</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46145.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>2879</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46145.4375</v>
+      </c>
+      <c r="B332">
+        <v>2855</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46145.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>2837</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46145.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>2832</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46145.46875</v>
+      </c>
+      <c r="B335">
+        <v>2894</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46145.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>2910</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46145.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>2993</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46145.5</v>
+      </c>
+      <c r="B338">
+        <v>2975</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46145.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>2995</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46145.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>2962</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46145.53125</v>
+      </c>
+      <c r="B341">
+        <v>2970</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46145.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>3032</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46145.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>3067</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46145.5625</v>
+      </c>
+      <c r="B344">
+        <v>3095</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46145.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>3098</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46145.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>3027</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46145.59375</v>
+      </c>
+      <c r="B347">
+        <v>3029</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46145.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>3125</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46145.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>3168</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46145.625</v>
+      </c>
+      <c r="B350">
+        <v>3060</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46145.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>3292</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46145.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>3350</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46145.65625</v>
+      </c>
+      <c r="B353">
+        <v>3451</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46145.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>3552</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46145.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>3682</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46145.6875</v>
+      </c>
+      <c r="B356">
+        <v>3866</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46145.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>4051</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46145.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>4385</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46145.71875</v>
+      </c>
+      <c r="B359">
+        <v>4501</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46145.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>4813</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46145.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>4898</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46145.75</v>
+      </c>
+      <c r="B362">
+        <v>5088</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46145.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>5248</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46145.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>5436</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46145.78125</v>
+      </c>
+      <c r="B365">
+        <v>5562</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46145.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>5680</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46145.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>5793</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46145.8125</v>
+      </c>
+      <c r="B368">
+        <v>6034</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46145.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>6209</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46145.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6219</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46145.84375</v>
+      </c>
+      <c r="B371">
+        <v>6193</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46145.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>6213</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46145.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6087</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46145.875</v>
+      </c>
+      <c r="B374">
+        <v>6032</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46145.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>5969</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46145.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>5836</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46145.90625</v>
+      </c>
+      <c r="B377">
+        <v>5727</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46145.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5563</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46145.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5430</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46145.9375</v>
+      </c>
+      <c r="B380">
+        <v>5359</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46145.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>5325</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46145.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>5113</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46145.96875</v>
+      </c>
+      <c r="B383">
+        <v>5028</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46145.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>4961</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46145.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>4947</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B386">
+        <v>4898</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46146.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>4875</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46146.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>4816</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46146.03125</v>
+      </c>
+      <c r="B389">
+        <v>4740</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46146.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>4743</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46146.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>4773</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46146.0625</v>
+      </c>
+      <c r="B392">
+        <v>4701</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46146.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>4750</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46146.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>4731</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46146.09375</v>
+      </c>
+      <c r="B395">
+        <v>4692</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46146.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>4703</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46146.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>4713</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46146.125</v>
+      </c>
+      <c r="B398">
+        <v>4784</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46146.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>4736</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46146.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>4802</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46146.15625</v>
+      </c>
+      <c r="B401">
+        <v>4888</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46146.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>4985</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46146.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>5025</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46146.1875</v>
+      </c>
+      <c r="B404">
+        <v>5049</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46146.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>5118</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46146.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>5225</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46146.21875</v>
+      </c>
+      <c r="B407">
+        <v>5310</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46146.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>5552</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46146.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>5709</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46146.25</v>
+      </c>
+      <c r="B410">
+        <v>5847</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46146.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>5918</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46146.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>5928</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46146.28125</v>
+      </c>
+      <c r="B413">
+        <v>5916</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46146.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>5925</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46146.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>5835</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46146.3125</v>
+      </c>
+      <c r="B416">
+        <v>5756</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46146.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>5622</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46146.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46146.34375</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46146.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46146.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46146.375</v>
+      </c>
+      <c r="B422">
+        <v>0</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46146.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46146.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46146.40625</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" s="2">
+        <v>46146.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+      <c r="C426">
+        <v>41</v>
+      </c>
+      <c r="D426" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" s="2">
+        <v>46146.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+      <c r="C427">
+        <v>42</v>
+      </c>
+      <c r="D427" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" s="2">
+        <v>46146.4375</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+      <c r="C428">
+        <v>43</v>
+      </c>
+      <c r="D428" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" s="2">
+        <v>46146.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+      <c r="C429">
+        <v>44</v>
+      </c>
+      <c r="D429" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="2">
+        <v>46146.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" s="2">
+        <v>46146.46875</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+      <c r="C431">
+        <v>46</v>
+      </c>
+      <c r="D431" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" s="2">
+        <v>46146.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+      <c r="C432">
+        <v>47</v>
+      </c>
+      <c r="D432" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" s="2">
+        <v>46146.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>48</v>
+      </c>
+      <c r="D433" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" s="2">
+        <v>46146.5</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+      <c r="C434">
+        <v>49</v>
+      </c>
+      <c r="D434" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" s="2">
+        <v>46146.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+      <c r="C435">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="2">
+        <v>46146.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+      <c r="C436">
+        <v>51</v>
+      </c>
+      <c r="D436" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" s="2">
+        <v>46146.53125</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+      <c r="C437">
+        <v>52</v>
+      </c>
+      <c r="D437" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="2">
+        <v>46146.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+      <c r="C438">
+        <v>53</v>
+      </c>
+      <c r="D438" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" s="2">
+        <v>46146.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+      <c r="C439">
+        <v>54</v>
+      </c>
+      <c r="D439" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="2">
+        <v>46146.5625</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440">
+        <v>55</v>
+      </c>
+      <c r="D440" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" s="2">
+        <v>46146.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+      <c r="C441">
+        <v>56</v>
+      </c>
+      <c r="D441" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" s="2">
+        <v>46146.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+      <c r="C442">
+        <v>57</v>
+      </c>
+      <c r="D442" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" s="2">
+        <v>46146.59375</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+      <c r="C443">
+        <v>58</v>
+      </c>
+      <c r="D443" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" s="2">
+        <v>46146.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+      <c r="C444">
+        <v>59</v>
+      </c>
+      <c r="D444" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" s="2">
+        <v>46146.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+      <c r="C445">
+        <v>60</v>
+      </c>
+      <c r="D445" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" s="2">
+        <v>46146.625</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>61</v>
+      </c>
+      <c r="D446" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" s="2">
+        <v>46146.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>62</v>
+      </c>
+      <c r="D447" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="2">
+        <v>46146.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+      <c r="C448">
+        <v>63</v>
+      </c>
+      <c r="D448" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="2">
+        <v>46146.65625</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+      <c r="C449">
+        <v>64</v>
+      </c>
+      <c r="D449" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" s="2">
+        <v>46146.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>65</v>
+      </c>
+      <c r="D450" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="2">
+        <v>46146.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>66</v>
+      </c>
+      <c r="D451" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="2">
+        <v>46146.6875</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>67</v>
+      </c>
+      <c r="D452" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" s="2">
+        <v>46146.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="2">
+        <v>46146.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+      <c r="C454">
+        <v>69</v>
+      </c>
+      <c r="D454" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" s="2">
+        <v>46146.71875</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+      <c r="C455">
+        <v>70</v>
+      </c>
+      <c r="D455" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="2">
+        <v>46146.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+      <c r="C456">
+        <v>71</v>
+      </c>
+      <c r="D456" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="2">
+        <v>46146.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <v>72</v>
+      </c>
+      <c r="D457" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" s="2">
+        <v>46146.75</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <v>73</v>
+      </c>
+      <c r="D458" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" s="2">
+        <v>46146.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+      <c r="C459">
+        <v>74</v>
+      </c>
+      <c r="D459" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" s="2">
+        <v>46146.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>75</v>
+      </c>
+      <c r="D460" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" s="2">
+        <v>46146.78125</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>76</v>
+      </c>
+      <c r="D461" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="2">
+        <v>46146.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>77</v>
+      </c>
+      <c r="D462" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" s="2">
+        <v>46146.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>78</v>
+      </c>
+      <c r="D463" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="2">
+        <v>46146.8125</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>79</v>
+      </c>
+      <c r="D464" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" s="2">
+        <v>46146.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+      <c r="D465" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="2">
+        <v>46146.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+      <c r="C466">
+        <v>81</v>
+      </c>
+      <c r="D466" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" s="2">
+        <v>46146.84375</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>82</v>
+      </c>
+      <c r="D467" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" s="2">
+        <v>46146.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>83</v>
+      </c>
+      <c r="D468" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" s="2">
+        <v>46146.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>84</v>
+      </c>
+      <c r="D469" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="2">
+        <v>46146.875</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>85</v>
+      </c>
+      <c r="D470" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="2">
+        <v>46146.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>86</v>
+      </c>
+      <c r="D471" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" s="2">
+        <v>46146.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>87</v>
+      </c>
+      <c r="D472" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" s="2">
+        <v>46146.90625</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>88</v>
+      </c>
+      <c r="D473" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" s="2">
+        <v>46146.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>89</v>
+      </c>
+      <c r="D474" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="2">
+        <v>46146.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>90</v>
+      </c>
+      <c r="D475" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" s="2">
+        <v>46146.9375</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>91</v>
+      </c>
+      <c r="D476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" s="2">
+        <v>46146.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>92</v>
+      </c>
+      <c r="D477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" s="2">
+        <v>46146.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>93</v>
+      </c>
+      <c r="D478" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" s="2">
+        <v>46146.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>94</v>
+      </c>
+      <c r="D479" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="2">
+        <v>46146.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>95</v>
+      </c>
+      <c r="D480" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" s="2">
+        <v>46146.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>96</v>
+      </c>
+      <c r="D481" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>05.05.202694</t>
-  </si>
-  <si>
-    <t>05.05.202695</t>
-  </si>
-  <si>
-    <t>05.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
+    <t>07.05.20261</t>
+  </si>
+  <si>
+    <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>07.05.202694</t>
+  </si>
+  <si>
+    <t>07.05.202695</t>
+  </si>
+  <si>
+    <t>07.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
-        <v>5295</v>
+        <v>5205</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.01041666666</v>
       </c>
       <c r="B3">
-        <v>5288</v>
+        <v>5196</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.02083333334</v>
       </c>
       <c r="B4">
-        <v>5260</v>
+        <v>5181</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
-        <v>5207</v>
+        <v>5189</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.04166666666</v>
       </c>
       <c r="B6">
-        <v>5128</v>
+        <v>5186</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.05208333334</v>
       </c>
       <c r="B7">
-        <v>5103</v>
+        <v>5191</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
-        <v>5060</v>
+        <v>5189</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.07291666666</v>
       </c>
       <c r="B9">
-        <v>5018</v>
+        <v>5158</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.08333333334</v>
       </c>
       <c r="B10">
-        <v>4990</v>
+        <v>5141</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
-        <v>5027</v>
+        <v>5149</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.10416666666</v>
       </c>
       <c r="B12">
-        <v>5058</v>
+        <v>5130</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.11458333334</v>
       </c>
       <c r="B13">
-        <v>5034</v>
+        <v>5171</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
-        <v>5095</v>
+        <v>5148</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.13541666666</v>
       </c>
       <c r="B15">
-        <v>5139</v>
+        <v>5189</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.14583333334</v>
       </c>
       <c r="B16">
-        <v>5199</v>
+        <v>5206</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
-        <v>5174</v>
+        <v>5268</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.16666666666</v>
       </c>
       <c r="B18">
-        <v>5185</v>
+        <v>5166</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.17708333334</v>
       </c>
       <c r="B19">
-        <v>5264</v>
+        <v>5231</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>5289</v>
+        <v>5250</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.19791666666</v>
       </c>
       <c r="B21">
-        <v>5365</v>
+        <v>5251</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.20833333334</v>
       </c>
       <c r="B22">
-        <v>5433</v>
+        <v>5342</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>5547</v>
+        <v>5441</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.22916666666</v>
       </c>
       <c r="B24">
-        <v>5581</v>
+        <v>5534</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.23958333334</v>
       </c>
       <c r="B25">
-        <v>5683</v>
+        <v>5618</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>5936</v>
+        <v>5808</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.26041666666</v>
       </c>
       <c r="B27">
-        <v>5982</v>
+        <v>5878</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.27083333334</v>
       </c>
       <c r="B28">
-        <v>5941</v>
+        <v>5915</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>5864</v>
+        <v>5880</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.29166666666</v>
       </c>
       <c r="B30">
-        <v>5846</v>
+        <v>5893</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.30208333334</v>
       </c>
       <c r="B31">
-        <v>5806</v>
+        <v>5801</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>5656</v>
+        <v>5781</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.32291666666</v>
       </c>
       <c r="B33">
-        <v>5476</v>
+        <v>5671</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.33333333334</v>
       </c>
       <c r="B34">
-        <v>5295</v>
+        <v>5582</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>5171</v>
+        <v>5477</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.35416666666</v>
       </c>
       <c r="B36">
-        <v>5017</v>
+        <v>5397</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.36458333334</v>
       </c>
       <c r="B37">
-        <v>4878</v>
+        <v>5288</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>4731</v>
+        <v>5228</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="B39">
-        <v>4568</v>
+        <v>5041</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.39583333334</v>
       </c>
       <c r="B40">
-        <v>4449</v>
+        <v>4986</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>4314</v>
+        <v>4861</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.41666666666</v>
       </c>
       <c r="B42">
-        <v>4187</v>
+        <v>4893</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.42708333334</v>
       </c>
       <c r="B43">
-        <v>4040</v>
+        <v>4839</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>4077</v>
+        <v>4784</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.44791666666</v>
       </c>
       <c r="B45">
-        <v>4000</v>
+        <v>4735</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="B46">
-        <v>3990</v>
+        <v>4587</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>3976</v>
+        <v>4582</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.47916666666</v>
       </c>
       <c r="B48">
-        <v>3895</v>
+        <v>4662</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.48958333334</v>
       </c>
       <c r="B49">
-        <v>3843</v>
+        <v>4699</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>4131</v>
+        <v>4728</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.51041666666</v>
       </c>
       <c r="B51">
-        <v>4087</v>
+        <v>4792</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.52083333334</v>
       </c>
       <c r="B52">
-        <v>3985</v>
+        <v>4824</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>3963</v>
+        <v>4818</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.54166666666</v>
       </c>
       <c r="B54">
-        <v>3953</v>
+        <v>4804</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="B55">
-        <v>3927</v>
+        <v>4845</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>3881</v>
+        <v>4816</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.57291666666</v>
       </c>
       <c r="B57">
-        <v>3965</v>
+        <v>4850</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.58333333334</v>
       </c>
       <c r="B58">
-        <v>3869</v>
+        <v>4705</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>3975</v>
+        <v>4865</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.60416666666</v>
       </c>
       <c r="B60">
-        <v>4052</v>
+        <v>4873</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.61458333334</v>
       </c>
       <c r="B61">
-        <v>4007</v>
+        <v>4940</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>4088</v>
+        <v>5085</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.63541666666</v>
       </c>
       <c r="B63">
-        <v>4214</v>
+        <v>5151</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B64">
-        <v>4371</v>
+        <v>5243</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>4576</v>
+        <v>5320</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.66666666666</v>
       </c>
       <c r="B66">
-        <v>4689</v>
+        <v>5558</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.67708333334</v>
       </c>
       <c r="B67">
-        <v>4873</v>
+        <v>5702</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>5138</v>
+        <v>5740</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.69791666666</v>
       </c>
       <c r="B69">
-        <v>5442</v>
+        <v>5826</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="B70">
-        <v>5711</v>
+        <v>5887</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>5898</v>
+        <v>5984</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.72916666666</v>
       </c>
       <c r="B72">
-        <v>6006</v>
+        <v>6116</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.73958333334</v>
       </c>
       <c r="B73">
-        <v>6145</v>
+        <v>6209</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>6128</v>
+        <v>6309</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.76041666666</v>
       </c>
       <c r="B75">
-        <v>6265</v>
+        <v>6480</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.77083333334</v>
       </c>
       <c r="B76">
-        <v>6351</v>
+        <v>6561</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>6496</v>
+        <v>6674</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.79166666666</v>
       </c>
       <c r="B78">
-        <v>6536</v>
+        <v>6725</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.80208333334</v>
       </c>
       <c r="B79">
-        <v>6654</v>
+        <v>6779</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>6741</v>
+        <v>6860</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.82291666666</v>
       </c>
       <c r="B81">
-        <v>6836</v>
+        <v>6940</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.83333333334</v>
       </c>
       <c r="B82">
-        <v>6956</v>
+        <v>7009</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>6936</v>
+        <v>6995</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.85416666666</v>
       </c>
       <c r="B84">
-        <v>6826</v>
+        <v>6910</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.86458333334</v>
       </c>
       <c r="B85">
-        <v>6749</v>
+        <v>6779</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
-        <v>6525</v>
+        <v>6627</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.88541666666</v>
       </c>
       <c r="B87">
-        <v>6444</v>
+        <v>6484</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.89583333334</v>
       </c>
       <c r="B88">
-        <v>6304</v>
+        <v>6315</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>6189</v>
+        <v>6140</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.91666666666</v>
       </c>
       <c r="B90">
-        <v>6009</v>
+        <v>5982</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.92708333334</v>
       </c>
       <c r="B91">
-        <v>5856</v>
+        <v>5842</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
-        <v>5764</v>
+        <v>5773</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.94791666666</v>
       </c>
       <c r="B93">
-        <v>5651</v>
+        <v>5644</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.95833333334</v>
       </c>
       <c r="B94">
-        <v>5415</v>
+        <v>5532</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
-        <v>5351</v>
+        <v>5458</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.97916666666</v>
       </c>
       <c r="B96">
-        <v>5266</v>
+        <v>5372</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.98958333334</v>
       </c>
       <c r="B97">
-        <v>5207</v>
+        <v>5340</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>5206</v>
+        <v>5294</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B99">
-        <v>5131</v>
+        <v>5229</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B100">
-        <v>5072</v>
+        <v>5132</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B101">
-        <v>5054</v>
+        <v>5183</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B102">
-        <v>5021</v>
+        <v>5245</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B103">
-        <v>5175</v>
+        <v>5252</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B104">
-        <v>5168</v>
+        <v>5211</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B105">
-        <v>5102</v>
+        <v>5185</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B106">
-        <v>5077</v>
+        <v>5201</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B107">
-        <v>5042</v>
+        <v>5217</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B108">
-        <v>5077</v>
+        <v>5162</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B109">
-        <v>5028</v>
+        <v>5205</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B110">
-        <v>5180</v>
+        <v>5164</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B111">
-        <v>5173</v>
+        <v>5211</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B112">
-        <v>5202</v>
+        <v>5174</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B113">
-        <v>5207</v>
+        <v>5199</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B114">
-        <v>5140</v>
+        <v>5191</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B115">
-        <v>5188</v>
+        <v>5260</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B116">
-        <v>5205</v>
+        <v>5320</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B117">
-        <v>5246</v>
+        <v>5321</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B118">
-        <v>5369</v>
+        <v>5393</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B119">
-        <v>5430</v>
+        <v>5473</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B120">
-        <v>5597</v>
+        <v>5548</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B121">
-        <v>5673</v>
+        <v>5646</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B122">
-        <v>5837</v>
+        <v>5899</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B123">
-        <v>5843</v>
+        <v>5924</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B124">
-        <v>5832</v>
+        <v>6030</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B125">
-        <v>5768</v>
+        <v>6070</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B126">
-        <v>5790</v>
+        <v>6104</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B127">
-        <v>5694</v>
+        <v>6004</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>6026</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202694</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>11.05.202694</t>
+  </si>
+  <si>
+    <t>11.05.202695</t>
+  </si>
+  <si>
+    <t>11.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>5205</v>
+        <v>4655</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46149.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>5196</v>
+        <v>4595</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46149.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>5181</v>
+        <v>4578</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>5189</v>
+        <v>4573</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46149.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>5186</v>
+        <v>4640</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46149.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>5191</v>
+        <v>4637</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>5189</v>
+        <v>4649</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46149.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>5158</v>
+        <v>4674</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46149.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>5141</v>
+        <v>4652</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>5149</v>
+        <v>4695</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46149.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
-        <v>5130</v>
+        <v>4691</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46149.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>5171</v>
+        <v>4694</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>5148</v>
+        <v>4693</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46149.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>5189</v>
+        <v>4749</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46149.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>5206</v>
+        <v>4740</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>5268</v>
+        <v>4766</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46149.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>5166</v>
+        <v>4781</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46149.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>5231</v>
+        <v>4808</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>5250</v>
+        <v>4843</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46149.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>5251</v>
+        <v>4881</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46149.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>5342</v>
+        <v>4967</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>5441</v>
+        <v>5128</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46149.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>5534</v>
+        <v>5250</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46149.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>5618</v>
+        <v>5373</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>5808</v>
+        <v>5566</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46149.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>5878</v>
+        <v>5608</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46149.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>5915</v>
+        <v>5672</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>5880</v>
+        <v>5600</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46149.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>5893</v>
+        <v>5595</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46149.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>5801</v>
+        <v>5628</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>5781</v>
+        <v>5459</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46149.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>5671</v>
+        <v>5368</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46149.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>5582</v>
+        <v>5215</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>5477</v>
+        <v>5207</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46149.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>5397</v>
+        <v>5031</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46149.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>5288</v>
+        <v>4939</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>5228</v>
+        <v>4780</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46149.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>5041</v>
+        <v>4599</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46149.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>4986</v>
+        <v>4532</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>4861</v>
+        <v>4540</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46149.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>4893</v>
+        <v>4395</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46149.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>4839</v>
+        <v>4285</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>4784</v>
+        <v>4343</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46149.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>4735</v>
+        <v>4255</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46149.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>4587</v>
+        <v>4278</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>4582</v>
+        <v>4258</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46149.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>4662</v>
+        <v>0</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46149.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>4699</v>
+        <v>4310</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>4728</v>
+        <v>4372</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46149.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>4792</v>
+        <v>4393</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46149.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>4824</v>
+        <v>4425</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>4818</v>
+        <v>4403</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46149.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>4804</v>
+        <v>4489</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46149.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>4845</v>
+        <v>4503</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>4816</v>
+        <v>4436</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46149.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>4850</v>
+        <v>4457</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46149.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>4705</v>
+        <v>4570</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>4865</v>
+        <v>4686</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46149.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>4873</v>
+        <v>4719</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46149.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>4940</v>
+        <v>4816</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>5085</v>
+        <v>4841</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46149.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>5151</v>
+        <v>4917</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46149.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>5243</v>
+        <v>4979</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>5320</v>
+        <v>5067</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46149.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>5558</v>
+        <v>5076</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46149.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>5702</v>
+        <v>5153</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>5740</v>
+        <v>5267</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46149.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>5826</v>
+        <v>5458</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46149.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>5887</v>
+        <v>5625</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>5984</v>
+        <v>5743</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46149.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>6116</v>
+        <v>5882</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46149.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>6209</v>
+        <v>6078</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>6309</v>
+        <v>6160</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46149.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>6480</v>
+        <v>6340</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46149.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>6561</v>
+        <v>6386</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>6674</v>
+        <v>6511</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46149.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>6725</v>
+        <v>6564</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46149.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>6779</v>
+        <v>6637</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>6860</v>
+        <v>6725</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46149.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>6940</v>
+        <v>6804</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46149.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>7009</v>
+        <v>6878</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>6995</v>
+        <v>6871</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46149.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>6910</v>
+        <v>6812</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46149.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>6779</v>
+        <v>6635</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>6627</v>
+        <v>6533</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46149.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>6484</v>
+        <v>6406</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46149.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>6315</v>
+        <v>6288</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>6140</v>
+        <v>6109</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46149.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>5982</v>
+        <v>5873</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46149.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>5842</v>
+        <v>5807</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>5773</v>
+        <v>5706</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46149.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>5644</v>
+        <v>5590</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46149.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>5532</v>
+        <v>5443</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>5458</v>
+        <v>5343</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46149.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>5372</v>
+        <v>5360</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46149.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>5340</v>
+        <v>5317</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
-        <v>5294</v>
+        <v>5239</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B99">
-        <v>5229</v>
+        <v>5163</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B100">
-        <v>5132</v>
+        <v>5099</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B101">
-        <v>5183</v>
+        <v>5149</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B102">
-        <v>5245</v>
+        <v>5097</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B103">
-        <v>5252</v>
+        <v>5087</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B104">
-        <v>5211</v>
+        <v>5024</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B105">
-        <v>5185</v>
+        <v>5047</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B106">
-        <v>5201</v>
+        <v>5077</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B107">
-        <v>5217</v>
+        <v>5138</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B108">
-        <v>5162</v>
+        <v>5116</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B109">
-        <v>5205</v>
+        <v>5022</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B110">
-        <v>5164</v>
+        <v>5038</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B111">
-        <v>5211</v>
+        <v>5107</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B112">
-        <v>5174</v>
+        <v>5113</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B113">
-        <v>5199</v>
+        <v>5116</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B114">
-        <v>5191</v>
+        <v>5013</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B115">
-        <v>5260</v>
+        <v>5093</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B116">
-        <v>5320</v>
+        <v>5083</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B117">
-        <v>5321</v>
+        <v>5148</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B118">
-        <v>5393</v>
+        <v>5269</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B119">
-        <v>5473</v>
+        <v>5338</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B120">
-        <v>5548</v>
+        <v>5414</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B121">
-        <v>5646</v>
+        <v>5525</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B122">
-        <v>5899</v>
+        <v>5670</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B123">
-        <v>5924</v>
+        <v>5926</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B124">
-        <v>6030</v>
+        <v>5891</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B125">
-        <v>6070</v>
+        <v>5950</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B126">
-        <v>6104</v>
+        <v>5946</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B127">
-        <v>6004</v>
+        <v>5980</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B128">
-        <v>6026</v>
+        <v>5887</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>5852</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>5815</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>5748</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>5689</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>5618</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>5522</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>5468</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>5312</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>5229</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>5086</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>5028</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>11.05.202694</t>
-  </si>
-  <si>
-    <t>11.05.202695</t>
-  </si>
-  <si>
-    <t>11.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202694</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>4655</v>
+        <v>5066</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>4595</v>
+        <v>5081</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>4578</v>
+        <v>5057</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>4573</v>
+        <v>4974</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>4640</v>
+        <v>5058</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>4637</v>
+        <v>5066</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>4649</v>
+        <v>5056</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>4674</v>
+        <v>4993</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>4652</v>
+        <v>4945</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>4695</v>
+        <v>4939</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>4691</v>
+        <v>4971</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>4694</v>
+        <v>5002</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>4693</v>
+        <v>4910</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>4749</v>
+        <v>4974</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>4740</v>
+        <v>5016</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>4766</v>
+        <v>4952</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>4781</v>
+        <v>5000</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>4808</v>
+        <v>5089</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>4843</v>
+        <v>5111</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>4881</v>
+        <v>5119</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>4967</v>
+        <v>5254</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>5128</v>
+        <v>5272</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>5250</v>
+        <v>5331</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>5373</v>
+        <v>5473</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>5566</v>
+        <v>5788</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>5608</v>
+        <v>5894</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>5672</v>
+        <v>5962</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>5600</v>
+        <v>6035</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>5595</v>
+        <v>6048</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>5628</v>
+        <v>6073</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>5459</v>
+        <v>6071</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>5368</v>
+        <v>6035</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>5215</v>
+        <v>5981</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>5207</v>
+        <v>5939</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>5031</v>
+        <v>5926</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>4939</v>
+        <v>5860</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>4780</v>
+        <v>5743</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>4599</v>
+        <v>5773</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>4532</v>
+        <v>5702</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>4540</v>
+        <v>5602</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>4395</v>
+        <v>5592</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>4285</v>
+        <v>5569</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>4343</v>
+        <v>5647</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>4255</v>
+        <v>5501</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>4278</v>
+        <v>5486</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>4258</v>
+        <v>5445</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>5509</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>4310</v>
+        <v>5405</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>4372</v>
+        <v>5506</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>4393</v>
+        <v>5674</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>4425</v>
+        <v>5687</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>4403</v>
+        <v>5641</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>4489</v>
+        <v>5389</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>4503</v>
+        <v>5404</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>4436</v>
+        <v>5398</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>4457</v>
+        <v>5353</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>4570</v>
+        <v>5296</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>4686</v>
+        <v>5318</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>4719</v>
+        <v>5306</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>4816</v>
+        <v>5385</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>4841</v>
+        <v>5321</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>4917</v>
+        <v>5326</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>4979</v>
+        <v>5428</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>5067</v>
+        <v>5468</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>5076</v>
+        <v>5584</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>5153</v>
+        <v>5620</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>5267</v>
+        <v>5670</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>5458</v>
+        <v>5758</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>5625</v>
+        <v>6095</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>5743</v>
+        <v>6046</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>5882</v>
+        <v>6306</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>6078</v>
+        <v>6201</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>6160</v>
+        <v>6353</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>6340</v>
+        <v>6472</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>6386</v>
+        <v>6554</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>6511</v>
+        <v>6574</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>6564</v>
+        <v>6578</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>6637</v>
+        <v>6730</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>6725</v>
+        <v>6780</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>6804</v>
+        <v>6860</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>6878</v>
+        <v>6839</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>6871</v>
+        <v>6925</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>6812</v>
+        <v>6823</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>6635</v>
+        <v>6713</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>6533</v>
+        <v>6511</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>6406</v>
+        <v>6375</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>6288</v>
+        <v>6176</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>6109</v>
+        <v>6022</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>5873</v>
+        <v>5885</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>5807</v>
+        <v>5768</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>5706</v>
+        <v>5707</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>5590</v>
+        <v>5548</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>5443</v>
+        <v>5462</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>5343</v>
+        <v>5368</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>5360</v>
+        <v>5339</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>5317</v>
+        <v>5262</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
         <v>5239</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
-        <v>5163</v>
+        <v>5141</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
-        <v>5099</v>
+        <v>5137</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
-        <v>5149</v>
+        <v>5064</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
-        <v>5097</v>
+        <v>5239</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
-        <v>5087</v>
+        <v>5177</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
-        <v>5024</v>
+        <v>5155</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
-        <v>5047</v>
+        <v>5169</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
-        <v>5077</v>
+        <v>5103</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
-        <v>5138</v>
+        <v>5073</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
-        <v>5116</v>
+        <v>5091</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
-        <v>5022</v>
+        <v>5155</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>5038</v>
+        <v>5177</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
-        <v>5107</v>
+        <v>5156</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
-        <v>5113</v>
+        <v>5091</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
         <v>5116</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>5013</v>
+        <v>5087</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>5093</v>
+        <v>5096</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>5083</v>
+        <v>5162</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>5148</v>
+        <v>5206</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>5269</v>
+        <v>5376</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>5338</v>
+        <v>5411</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>5414</v>
+        <v>5563</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>5525</v>
+        <v>5608</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>5670</v>
+        <v>5856</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>5926</v>
+        <v>5930</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>5891</v>
+        <v>5949</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>5950</v>
+        <v>5954</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>5946</v>
+        <v>5963</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>5980</v>
+        <v>5914</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>5887</v>
+        <v>5776</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>5852</v>
+        <v>5661</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>5815</v>
+        <v>5599</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>5748</v>
+        <v>5454</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>5689</v>
+        <v>5269</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>5618</v>
+        <v>5242</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>5522</v>
+        <v>5033</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>5468</v>
+        <v>4916</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>5312</v>
+        <v>4754</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>5229</v>
+        <v>4648</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>5086</v>
+        <v>4510</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>5028</v>
+        <v>0</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202694</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
-        <v>5066</v>
+        <v>5239</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
-        <v>5081</v>
+        <v>5141</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
-        <v>5057</v>
+        <v>5137</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
-        <v>4974</v>
+        <v>5064</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
-        <v>5058</v>
+        <v>5239</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
-        <v>5066</v>
+        <v>5177</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
-        <v>5056</v>
+        <v>5155</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
-        <v>4993</v>
+        <v>5169</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
-        <v>4945</v>
+        <v>5103</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
-        <v>4939</v>
+        <v>5073</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
-        <v>4971</v>
+        <v>5091</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
-        <v>5002</v>
+        <v>5155</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>4910</v>
+        <v>5177</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
-        <v>4974</v>
+        <v>5156</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
-        <v>5016</v>
+        <v>5091</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>4952</v>
+        <v>5116</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>5000</v>
+        <v>5087</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>5089</v>
+        <v>5096</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>5111</v>
+        <v>5162</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>5119</v>
+        <v>5206</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>5254</v>
+        <v>5376</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>5272</v>
+        <v>5411</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>5331</v>
+        <v>5563</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>5473</v>
+        <v>5608</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>5788</v>
+        <v>5856</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>5894</v>
+        <v>5930</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>5962</v>
+        <v>5949</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>6035</v>
+        <v>5954</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>6048</v>
+        <v>5963</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>6073</v>
+        <v>5914</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>6071</v>
+        <v>5776</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>6035</v>
+        <v>5661</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>5981</v>
+        <v>5599</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>5939</v>
+        <v>5454</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>5926</v>
+        <v>5269</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>5860</v>
+        <v>5242</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
-        <v>5743</v>
+        <v>5033</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
-        <v>5773</v>
+        <v>4916</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
-        <v>5702</v>
+        <v>4754</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>5602</v>
+        <v>4648</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>5592</v>
+        <v>4510</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>5569</v>
+        <v>4456</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>5647</v>
+        <v>4318</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>5501</v>
+        <v>4308</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>5486</v>
+        <v>4211</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>5445</v>
+        <v>4170</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>5509</v>
+        <v>4193</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
-        <v>5405</v>
+        <v>4192</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>5506</v>
+        <v>4257</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
-        <v>5674</v>
+        <v>4242</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>5687</v>
+        <v>4189</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>5641</v>
+        <v>4248</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>5389</v>
+        <v>4231</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>5404</v>
+        <v>4282</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>5398</v>
+        <v>4257</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>5353</v>
+        <v>4159</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
-        <v>5296</v>
+        <v>4149</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>5318</v>
+        <v>4204</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>5306</v>
+        <v>4226</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>5385</v>
+        <v>4295</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
-        <v>5321</v>
+        <v>4345</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
-        <v>5326</v>
+        <v>4445</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
-        <v>5428</v>
+        <v>4448</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>5468</v>
+        <v>4570</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>5584</v>
+        <v>4740</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>5620</v>
+        <v>4875</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>5670</v>
+        <v>4923</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>5758</v>
+        <v>5134</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>6095</v>
+        <v>5266</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>6046</v>
+        <v>5442</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>6306</v>
+        <v>5645</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>6201</v>
+        <v>5715</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>6353</v>
+        <v>5921</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>6472</v>
+        <v>6099</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>6554</v>
+        <v>6219</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>6574</v>
+        <v>6412</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>6578</v>
+        <v>6473</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>6730</v>
+        <v>6551</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>6780</v>
+        <v>6613</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>6860</v>
+        <v>6792</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>6839</v>
+        <v>6875</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>6925</v>
+        <v>6909</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>6823</v>
+        <v>6829</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>6713</v>
+        <v>6807</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>6511</v>
+        <v>6589</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>6375</v>
+        <v>6469</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>6176</v>
+        <v>6309</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>6022</v>
+        <v>6354</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>5885</v>
+        <v>6089</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
-        <v>5768</v>
+        <v>5994</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
-        <v>5707</v>
+        <v>5811</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
-        <v>5548</v>
+        <v>5714</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
-        <v>5462</v>
+        <v>5509</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
-        <v>5368</v>
+        <v>5477</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
-        <v>5339</v>
+        <v>5364</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
-        <v>5262</v>
+        <v>5271</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
-        <v>5239</v>
+        <v>5280</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B99">
-        <v>5141</v>
+        <v>5219</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B100">
-        <v>5137</v>
+        <v>5184</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B101">
-        <v>5064</v>
+        <v>5107</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B102">
-        <v>5239</v>
+        <v>5178</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B103">
-        <v>5177</v>
+        <v>5200</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B104">
-        <v>5155</v>
+        <v>5134</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B105">
-        <v>5169</v>
+        <v>5159</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B106">
-        <v>5103</v>
+        <v>5104</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B107">
-        <v>5073</v>
+        <v>5098</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B108">
-        <v>5091</v>
+        <v>5093</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B109">
-        <v>5155</v>
+        <v>5118</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B110">
-        <v>5177</v>
+        <v>5059</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B111">
-        <v>5156</v>
+        <v>5086</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B112">
-        <v>5091</v>
+        <v>5088</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B113">
-        <v>5116</v>
+        <v>5099</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B114">
-        <v>5087</v>
+        <v>5109</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B115">
-        <v>5096</v>
+        <v>5160</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B116">
-        <v>5162</v>
+        <v>5092</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B117">
-        <v>5206</v>
+        <v>5140</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B118">
-        <v>5376</v>
+        <v>5195</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B119">
-        <v>5411</v>
+        <v>5261</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B120">
-        <v>5563</v>
+        <v>5335</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B121">
-        <v>5608</v>
+        <v>5431</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B122">
-        <v>5856</v>
+        <v>5533</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B123">
-        <v>5930</v>
+        <v>5638</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B124">
-        <v>5949</v>
+        <v>5655</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B125">
-        <v>5954</v>
+        <v>5639</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B126">
-        <v>5963</v>
+        <v>5563</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B127">
-        <v>5914</v>
+        <v>5570</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B128">
-        <v>5776</v>
+        <v>5477</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B129">
-        <v>5661</v>
+        <v>5352</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B130">
-        <v>5599</v>
+        <v>5164</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B131">
-        <v>5454</v>
+        <v>5072</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B132">
-        <v>5269</v>
+        <v>4963</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B133">
-        <v>5242</v>
+        <v>4827</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B134">
-        <v>5033</v>
+        <v>4580</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B135">
-        <v>4916</v>
+        <v>4482</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B136">
-        <v>4754</v>
+        <v>4348</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B137">
-        <v>4648</v>
+        <v>4249</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B138">
-        <v>4510</v>
+        <v>4159</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>4037</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>3991</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>20.05.202694</t>
+  </si>
+  <si>
+    <t>20.05.202695</t>
+  </si>
+  <si>
+    <t>20.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
-        <v>5239</v>
+        <v>5127</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
-        <v>5141</v>
+        <v>5080</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
-        <v>5137</v>
+        <v>5046</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
-        <v>5064</v>
+        <v>4951</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
-        <v>5239</v>
+        <v>4998</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
-        <v>5177</v>
+        <v>4955</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
-        <v>5155</v>
+        <v>4945</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
-        <v>5169</v>
+        <v>4897</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
-        <v>5103</v>
+        <v>5024</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
-        <v>5073</v>
+        <v>5011</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
-        <v>5091</v>
+        <v>5041</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
-        <v>5155</v>
+        <v>5013</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>5177</v>
+        <v>5155</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
-        <v>5156</v>
+        <v>5170</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>5091</v>
+        <v>5211</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>5116</v>
+        <v>5166</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>5087</v>
+        <v>5133</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>5096</v>
+        <v>5152</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>5206</v>
+        <v>5181</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>5376</v>
+        <v>5145</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>5411</v>
+        <v>5247</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>5563</v>
+        <v>5333</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>5608</v>
+        <v>5445</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>5856</v>
+        <v>5580</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>5930</v>
+        <v>5718</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>5949</v>
+        <v>5758</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>5954</v>
+        <v>5793</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>5963</v>
+        <v>5744</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>5914</v>
+        <v>5778</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>5776</v>
+        <v>5698</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>5661</v>
+        <v>5540</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>5599</v>
+        <v>5483</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>5454</v>
+        <v>5437</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>5269</v>
+        <v>5336</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>5242</v>
+        <v>5246</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>5033</v>
+        <v>5120</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>4916</v>
+        <v>5035</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
-        <v>4754</v>
+        <v>4970</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>4648</v>
+        <v>4887</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>4510</v>
+        <v>4734</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>4456</v>
+        <v>4698</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>4318</v>
+        <v>4686</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
-        <v>4308</v>
+        <v>4621</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>4211</v>
+        <v>4550</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>4170</v>
+        <v>4572</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>4193</v>
+        <v>4648</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>4192</v>
+        <v>4578</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>4257</v>
+        <v>4598</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>4242</v>
+        <v>4563</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>4189</v>
+        <v>4553</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>4248</v>
+        <v>4543</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>4231</v>
+        <v>4675</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>4282</v>
+        <v>4676</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
-        <v>4257</v>
+        <v>4615</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>4159</v>
+        <v>4644</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>4149</v>
+        <v>4863</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>4204</v>
+        <v>4967</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>4226</v>
+        <v>4972</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>4295</v>
+        <v>5035</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>4345</v>
+        <v>5064</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>4445</v>
+        <v>5116</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
-        <v>4448</v>
+        <v>5262</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
-        <v>4570</v>
+        <v>5331</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>4740</v>
+        <v>5367</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>4875</v>
+        <v>5378</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>4923</v>
+        <v>5537</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>5134</v>
+        <v>5588</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>5266</v>
+        <v>5727</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>5442</v>
+        <v>5865</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>5645</v>
+        <v>6013</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>5715</v>
+        <v>6045</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>5921</v>
+        <v>6162</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>6099</v>
+        <v>6270</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>6219</v>
+        <v>6440</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>6412</v>
+        <v>6513</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>6473</v>
+        <v>6584</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>6551</v>
+        <v>6659</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>6613</v>
+        <v>6777</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>6792</v>
+        <v>6811</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>6875</v>
+        <v>6908</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>6909</v>
+        <v>6955</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>6829</v>
+        <v>6942</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>6807</v>
+        <v>6802</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>6589</v>
+        <v>6684</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>6469</v>
+        <v>6503</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>6309</v>
+        <v>6355</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>6354</v>
+        <v>6159</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>6089</v>
+        <v>6037</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>5994</v>
+        <v>5900</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
-        <v>5811</v>
+        <v>5788</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
-        <v>5714</v>
+        <v>5637</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
-        <v>5509</v>
+        <v>5447</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
-        <v>5477</v>
+        <v>5347</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
-        <v>5364</v>
+        <v>5295</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
-        <v>5271</v>
+        <v>5212</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>5280</v>
+        <v>5099</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B99">
-        <v>5219</v>
+        <v>5084</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B100">
-        <v>5184</v>
+        <v>5047</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B101">
-        <v>5107</v>
+        <v>5004</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B102">
-        <v>5178</v>
+        <v>5044</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B103">
-        <v>5200</v>
+        <v>5025</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B104">
-        <v>5134</v>
+        <v>5021</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B105">
-        <v>5159</v>
+        <v>4990</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B106">
-        <v>5104</v>
+        <v>4968</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B107">
-        <v>5098</v>
+        <v>4997</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B108">
-        <v>5093</v>
+        <v>4986</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B109">
-        <v>5118</v>
+        <v>5012</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B110">
-        <v>5059</v>
+        <v>4975</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B111">
-        <v>5086</v>
+        <v>5016</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B112">
-        <v>5088</v>
+        <v>5042</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B113">
-        <v>5099</v>
+        <v>5083</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B114">
-        <v>5109</v>
+        <v>5138</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B115">
-        <v>5160</v>
+        <v>5193</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B116">
-        <v>5092</v>
+        <v>5129</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B117">
-        <v>5140</v>
+        <v>5183</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B118">
-        <v>5195</v>
+        <v>5194</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B119">
-        <v>5261</v>
+        <v>5255</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B120">
-        <v>5335</v>
+        <v>5341</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B121">
-        <v>5431</v>
+        <v>5474</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B122">
-        <v>5533</v>
+        <v>5677</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B123">
-        <v>5638</v>
+        <v>5757</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B124">
-        <v>5655</v>
+        <v>5829</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B125">
-        <v>5639</v>
+        <v>5814</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B126">
-        <v>5563</v>
+        <v>5842</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B127">
-        <v>5570</v>
+        <v>5833</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B128">
-        <v>5477</v>
+        <v>5828</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B129">
-        <v>5352</v>
+        <v>5815</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B130">
-        <v>5164</v>
+        <v>5763</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B131">
-        <v>5072</v>
+        <v>5782</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B132">
-        <v>4963</v>
+        <v>5687</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B133">
-        <v>4827</v>
+        <v>5657</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B134">
-        <v>4580</v>
+        <v>5541</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B135">
-        <v>4482</v>
+        <v>5581</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B136">
-        <v>4348</v>
+        <v>5549</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B137">
-        <v>4249</v>
+        <v>5496</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B138">
-        <v>4159</v>
+        <v>5323</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B139">
-        <v>4037</v>
+        <v>5255</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B140">
-        <v>3991</v>
+        <v>5203</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>5220</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>5307</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>5294</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>5321</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>5355</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>5542</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>5604</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>5544</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>20.05.202694</t>
-  </si>
-  <si>
-    <t>20.05.202695</t>
-  </si>
-  <si>
-    <t>20.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>5127</v>
+        <v>5099</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>5080</v>
+        <v>5084</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>5046</v>
+        <v>5047</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>4951</v>
+        <v>5004</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>4998</v>
+        <v>5044</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>4955</v>
+        <v>5025</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>4945</v>
+        <v>5021</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>4897</v>
+        <v>4990</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>5024</v>
+        <v>4968</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>5011</v>
+        <v>4997</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>5041</v>
+        <v>4986</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>5155</v>
+        <v>4975</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
-        <v>5170</v>
+        <v>5016</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>5211</v>
+        <v>5042</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>5166</v>
+        <v>5083</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>5133</v>
+        <v>5138</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>5152</v>
+        <v>5193</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>5163</v>
+        <v>5129</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>5181</v>
+        <v>5183</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>5145</v>
+        <v>5194</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>5247</v>
+        <v>5255</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>5333</v>
+        <v>5341</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>5445</v>
+        <v>5474</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>5580</v>
+        <v>5677</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>5718</v>
+        <v>5757</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>5758</v>
+        <v>5829</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>5793</v>
+        <v>5814</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>5744</v>
+        <v>5842</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>5778</v>
+        <v>5833</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>5698</v>
+        <v>5828</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>5540</v>
+        <v>5815</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>5483</v>
+        <v>5763</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>5437</v>
+        <v>5782</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>5336</v>
+        <v>5687</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>5246</v>
+        <v>5657</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>5120</v>
+        <v>5541</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>5035</v>
+        <v>5581</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>4970</v>
+        <v>5549</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>4887</v>
+        <v>5496</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>4734</v>
+        <v>5323</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>4698</v>
+        <v>5255</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>4686</v>
+        <v>5203</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>4621</v>
+        <v>5220</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>4550</v>
+        <v>5307</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>4572</v>
+        <v>5294</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>4648</v>
+        <v>5321</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>4578</v>
+        <v>5355</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>4598</v>
+        <v>5542</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>4563</v>
+        <v>5604</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>4553</v>
+        <v>5544</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>4543</v>
+        <v>5580</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>4675</v>
+        <v>5490</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>4676</v>
+        <v>5521</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>4615</v>
+        <v>5544</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>4644</v>
+        <v>5582</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>4863</v>
+        <v>5516</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>4967</v>
+        <v>5612</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>4972</v>
+        <v>5665</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>5035</v>
+        <v>5649</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>5064</v>
+        <v>5434</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>5116</v>
+        <v>5559</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>5262</v>
+        <v>5504</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>5331</v>
+        <v>5448</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>5367</v>
+        <v>5525</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>5378</v>
+        <v>5483</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>5537</v>
+        <v>5530</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>5588</v>
+        <v>5625</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>5727</v>
+        <v>5735</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>5865</v>
+        <v>5833</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>6013</v>
+        <v>5963</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>6045</v>
+        <v>5959</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>6162</v>
+        <v>6059</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>6270</v>
+        <v>6171</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>6440</v>
+        <v>6197</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>6513</v>
+        <v>6261</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>6584</v>
+        <v>6299</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>6659</v>
+        <v>6376</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>6777</v>
+        <v>6432</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>6811</v>
+        <v>6526</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>6908</v>
+        <v>6580</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>6955</v>
+        <v>6568</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>6942</v>
+        <v>6567</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>6802</v>
+        <v>6504</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>6684</v>
+        <v>6366</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>6503</v>
+        <v>6242</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>6355</v>
+        <v>6064</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>6159</v>
+        <v>5924</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>6037</v>
+        <v>5819</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>5900</v>
+        <v>5658</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>5788</v>
+        <v>5582</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>5637</v>
+        <v>5506</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>5447</v>
+        <v>5332</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>5347</v>
+        <v>5259</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
-        <v>5295</v>
+        <v>5244</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
-        <v>5212</v>
+        <v>5161</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
-        <v>5099</v>
+        <v>5139</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B99">
-        <v>5084</v>
+        <v>5071</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B100">
-        <v>5047</v>
+        <v>5012</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B101">
-        <v>5004</v>
+        <v>4995</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B102">
-        <v>5044</v>
+        <v>5061</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B103">
-        <v>5025</v>
+        <v>5053</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B104">
-        <v>5021</v>
+        <v>5034</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B105">
-        <v>4990</v>
+        <v>5003</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B106">
-        <v>4968</v>
+        <v>4984</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B107">
-        <v>4997</v>
+        <v>5009</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B108">
-        <v>4986</v>
+        <v>5007</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B109">
-        <v>5012</v>
+        <v>5030</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B110">
-        <v>4975</v>
+        <v>5051</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B111">
-        <v>5016</v>
+        <v>5022</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B112">
-        <v>5042</v>
+        <v>4987</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B113">
-        <v>5083</v>
+        <v>5001</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B114">
-        <v>5138</v>
+        <v>5033</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B115">
-        <v>5193</v>
+        <v>5013</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B116">
-        <v>5129</v>
+        <v>5040</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B117">
-        <v>5183</v>
+        <v>5049</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B118">
-        <v>5194</v>
+        <v>5190</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B119">
-        <v>5255</v>
+        <v>5270</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B120">
-        <v>5341</v>
+        <v>5388</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B121">
-        <v>5474</v>
+        <v>5477</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B122">
-        <v>5677</v>
+        <v>5726</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B123">
-        <v>5757</v>
+        <v>5863</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B124">
-        <v>5829</v>
+        <v>5943</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B125">
-        <v>5814</v>
+        <v>6058</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B126">
-        <v>5842</v>
+        <v>6126</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B127">
-        <v>5833</v>
+        <v>6224</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B128">
-        <v>5828</v>
+        <v>6163</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B129">
-        <v>5815</v>
+        <v>6111</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B130">
-        <v>5763</v>
+        <v>6052</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B131">
-        <v>5782</v>
+        <v>5979</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B132">
-        <v>5687</v>
+        <v>5929</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B133">
-        <v>5657</v>
+        <v>5862</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B134">
-        <v>5541</v>
+        <v>5737</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B135">
-        <v>5581</v>
+        <v>5621</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B136">
-        <v>5549</v>
+        <v>5503</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B137">
-        <v>5496</v>
+        <v>5342</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B138">
-        <v>5323</v>
+        <v>5485</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B139">
-        <v>5255</v>
+        <v>5159</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B140">
-        <v>5203</v>
+        <v>5117</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B141">
-        <v>5220</v>
+        <v>5105</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B142">
-        <v>5307</v>
+        <v>5152</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B143">
-        <v>5294</v>
+        <v>5090</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B144">
-        <v>5321</v>
+        <v>5130</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B145">
-        <v>5355</v>
+        <v>5116</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B146">
-        <v>5542</v>
+        <v>5060</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B147">
-        <v>5604</v>
+        <v>0</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B148">
-        <v>5544</v>
+        <v>0</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,870 @@
   </si>
   <si>
     <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +1558,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>5099</v>
+        <v>5139</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +1572,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>5084</v>
+        <v>5071</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1586,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
-        <v>5047</v>
+        <v>5012</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1600,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>5004</v>
+        <v>4995</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1614,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>5044</v>
+        <v>5061</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1628,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>5025</v>
+        <v>5053</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1642,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>5021</v>
+        <v>5034</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1656,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>4990</v>
+        <v>5003</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1670,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>4968</v>
+        <v>4984</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1684,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>4997</v>
+        <v>5009</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1698,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>4986</v>
+        <v>5007</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1712,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>5012</v>
+        <v>5030</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1726,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>4975</v>
+        <v>5051</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1740,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>5016</v>
+        <v>5022</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1754,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>5042</v>
+        <v>4987</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1768,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>5083</v>
+        <v>5001</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1782,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>5138</v>
+        <v>5033</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1796,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>5193</v>
+        <v>5013</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1810,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>5129</v>
+        <v>5040</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1824,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>5183</v>
+        <v>5049</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1838,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>5194</v>
+        <v>5190</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1852,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>5255</v>
+        <v>5270</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1866,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>5341</v>
+        <v>5388</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1880,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>5474</v>
+        <v>5477</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1894,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>5677</v>
+        <v>5726</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1908,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>5757</v>
+        <v>5863</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1922,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>5829</v>
+        <v>5943</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1936,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>5814</v>
+        <v>6058</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1950,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>5842</v>
+        <v>6126</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1964,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>5833</v>
+        <v>6224</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1978,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>5828</v>
+        <v>6163</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1992,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>5815</v>
+        <v>6111</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +2006,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>5763</v>
+        <v>6052</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +2020,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>5782</v>
+        <v>5979</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +2034,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>5687</v>
+        <v>5929</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +2048,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>5657</v>
+        <v>5862</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +2062,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>5541</v>
+        <v>5737</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +2076,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>5581</v>
+        <v>5621</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +2090,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>5549</v>
+        <v>5503</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +2104,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>5496</v>
+        <v>5342</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +2118,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>5323</v>
+        <v>5485</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +2132,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>5255</v>
+        <v>5159</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +2146,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>5203</v>
+        <v>5117</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +2160,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>5220</v>
+        <v>5105</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +2174,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>5307</v>
+        <v>5152</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +2188,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>5294</v>
+        <v>5090</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +2202,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>5321</v>
+        <v>5130</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +2216,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>5355</v>
+        <v>5116</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +2230,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>5542</v>
+        <v>5060</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +2244,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>5604</v>
+        <v>5118</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +2258,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>5544</v>
+        <v>5097</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +2272,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>5580</v>
+        <v>4988</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +2286,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>5490</v>
+        <v>4857</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +2300,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>5521</v>
+        <v>4801</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +2314,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>5544</v>
+        <v>4812</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +2328,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>5582</v>
+        <v>4854</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +2342,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>5516</v>
+        <v>4775</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +2356,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>5612</v>
+        <v>4784</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +2370,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>5665</v>
+        <v>4737</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +2384,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>5649</v>
+        <v>4685</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +2398,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>5434</v>
+        <v>4750</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +2412,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>5559</v>
+        <v>4936</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +2426,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>5504</v>
+        <v>4930</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +2440,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>5448</v>
+        <v>4959</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +2454,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>5525</v>
+        <v>5122</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +2468,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>5483</v>
+        <v>5245</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +2482,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>5530</v>
+        <v>5305</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +2496,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>5625</v>
+        <v>5473</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +2510,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>5735</v>
+        <v>5679</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +2524,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>5833</v>
+        <v>5787</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +2538,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>5963</v>
+        <v>5880</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +2552,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>5959</v>
+        <v>5931</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +2566,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>6059</v>
+        <v>6050</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2580,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>6171</v>
+        <v>6114</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2594,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>6197</v>
+        <v>6217</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2608,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>6261</v>
+        <v>6340</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2622,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>6299</v>
+        <v>6362</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2636,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>6376</v>
+        <v>6415</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2650,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>6432</v>
+        <v>6528</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2664,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>6526</v>
+        <v>6597</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2678,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>6580</v>
+        <v>6678</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2692,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>6568</v>
+        <v>6664</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2706,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
-        <v>6567</v>
+        <v>6697</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2720,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>6504</v>
+        <v>6598</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2734,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>6366</v>
+        <v>6467</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2748,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>6242</v>
+        <v>6353</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2762,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>6064</v>
+        <v>6181</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2776,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>5924</v>
+        <v>6055</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2790,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>5819</v>
+        <v>5909</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2804,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>5658</v>
+        <v>5788</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2818,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>5582</v>
+        <v>5708</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2832,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>5506</v>
+        <v>5546</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2846,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>5332</v>
+        <v>5367</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2860,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>5259</v>
+        <v>5270</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2874,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>5244</v>
+        <v>5198</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2888,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>5161</v>
+        <v>5133</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2902,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>5139</v>
+        <v>5058</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2916,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B99">
-        <v>5071</v>
+        <v>5020</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2930,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B100">
-        <v>5012</v>
+        <v>4983</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2944,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B101">
-        <v>4995</v>
+        <v>4949</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B102">
-        <v>5061</v>
+        <v>4908</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2972,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B103">
-        <v>5053</v>
+        <v>4865</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2986,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B104">
-        <v>5034</v>
+        <v>4907</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +3000,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B105">
-        <v>5003</v>
+        <v>4857</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +3014,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B106">
-        <v>4984</v>
+        <v>4896</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +3028,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B107">
-        <v>5009</v>
+        <v>4868</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +3042,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B108">
-        <v>5007</v>
+        <v>4898</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +3056,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B109">
-        <v>5030</v>
+        <v>4841</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +3070,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B110">
-        <v>5051</v>
+        <v>4827</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +3084,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B111">
-        <v>5022</v>
+        <v>4823</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +3098,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B112">
-        <v>4987</v>
+        <v>4788</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +3112,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B113">
-        <v>5001</v>
+        <v>4826</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +3126,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B114">
-        <v>5033</v>
+        <v>4830</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +3140,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B115">
-        <v>5013</v>
+        <v>4757</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +3154,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B116">
-        <v>5040</v>
+        <v>4723</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +3168,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B117">
-        <v>5049</v>
+        <v>4710</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +3182,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B118">
-        <v>5190</v>
+        <v>4613</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +3196,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B119">
-        <v>5270</v>
+        <v>4669</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +3210,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B120">
-        <v>5388</v>
+        <v>4665</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +3224,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B121">
-        <v>5477</v>
+        <v>4654</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +3238,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B122">
-        <v>5726</v>
+        <v>4690</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +3252,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B123">
-        <v>5863</v>
+        <v>4731</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +3266,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B124">
-        <v>5943</v>
+        <v>4794</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +3280,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B125">
-        <v>6058</v>
+        <v>4810</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +3294,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B126">
-        <v>6126</v>
+        <v>4813</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +3308,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B127">
-        <v>6224</v>
+        <v>4750</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +3322,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B128">
-        <v>6163</v>
+        <v>4711</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +3336,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B129">
-        <v>6111</v>
+        <v>4669</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +3350,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B130">
-        <v>6052</v>
+        <v>4665</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +3364,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B131">
-        <v>5979</v>
+        <v>4591</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +3378,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B132">
-        <v>5929</v>
+        <v>4539</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +3392,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B133">
-        <v>5862</v>
+        <v>4449</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +3406,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B134">
-        <v>5737</v>
+        <v>4415</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +3420,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B135">
-        <v>5621</v>
+        <v>4315</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +3434,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B136">
-        <v>5503</v>
+        <v>4184</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +3448,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B137">
-        <v>5342</v>
+        <v>4269</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +3462,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B138">
-        <v>5485</v>
+        <v>3955</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +3476,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B139">
-        <v>5159</v>
+        <v>3896</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +3490,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B140">
-        <v>5117</v>
+        <v>3926</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +3504,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B141">
-        <v>5105</v>
+        <v>3778</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +3518,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B142">
-        <v>5152</v>
+        <v>3723</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +3532,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B143">
-        <v>5090</v>
+        <v>3597</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +3546,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B144">
-        <v>5130</v>
+        <v>3509</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +3560,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B145">
-        <v>5116</v>
+        <v>3521</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +3574,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B146">
-        <v>5060</v>
+        <v>3486</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3588,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>3444</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3602,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>3532</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3616,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>3450</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +3630,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>3464</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +3644,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>3446</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +3658,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>3440</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +3672,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>3487</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +3686,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>3502</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +3700,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>3565</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +3714,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>3557</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +3728,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>3638</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +3742,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>3827</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +3756,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>3881</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +3770,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>3851</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +3784,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>3969</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +3798,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>4201</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +3812,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>4234</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +3826,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>4355</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +3840,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>4480</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +3854,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>4603</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +3868,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>4703</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +3882,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>4887</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +3896,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>5019</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +3910,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>5241</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +3924,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>5351</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +3938,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>5476</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +3952,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>5575</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +3966,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>5682</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +3980,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>5790</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +3994,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>5915</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +4008,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>6036</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +4022,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>6027</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +4036,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>6131</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +4050,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>6144</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +4064,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6095</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +4078,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>6012</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +4092,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>5840</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +4106,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>5743</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +4120,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>5638</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +4134,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>5507</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +4148,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5399</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +4162,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>5226</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +4176,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>5122</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +4190,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +4204,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>4991</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +4218,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>5033</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +4232,2704 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>5009</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B194">
+        <v>4873</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4831</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4851</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B197">
+        <v>4804</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4659</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4596</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B200">
+        <v>4584</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4391</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4375</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B203">
+        <v>4303</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4296</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B206">
+        <v>4310</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4309</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4359</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B209">
+        <v>4333</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4315</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4271</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B212">
+        <v>4207</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>4163</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4169</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B215">
+        <v>4130</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>4086</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>4065</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B218">
+        <v>4068</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>4015</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>3949</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B221">
+        <v>3892</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>3845</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>3741</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B224">
+        <v>3638</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>3543</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>3440</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B227">
+        <v>3329</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>3321</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>3267</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B230">
+        <v>3162</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>3154</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3018</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B233">
+        <v>2935</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>2868</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>2853</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B236">
+        <v>2846</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>2828</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>2920</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B239">
+        <v>2928</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>2915</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>2916</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B242">
+        <v>2894</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>2852</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>2905</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B245">
+        <v>2894</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>2923</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>2935</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B248">
+        <v>2925</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>2975</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>2958</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B251">
+        <v>3055</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>3086</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>3119</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B254">
+        <v>3209</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>3221</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>3354</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B257">
+        <v>3435</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>3535</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>3634</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B260">
+        <v>3748</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>3910</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>4062</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B263">
+        <v>4193</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>4329</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>4495</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B266">
+        <v>4772</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>4925</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>5065</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B269">
+        <v>5154</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>5172</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>5271</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B272">
+        <v>5408</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>5487</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>5592</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B275">
+        <v>5685</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>5730</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>5690</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B278">
+        <v>5603</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>5500</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5372</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B281">
+        <v>5265</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5189</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>5079</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B284">
+        <v>4962</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>4857</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>4707</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B287">
+        <v>4636</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4583</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4524</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B290">
+        <v>4466</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4414</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4369</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B293">
+        <v>4350</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4401</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4379</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4364</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4367</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B299">
+        <v>4391</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4397</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4393</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B302">
+        <v>4426</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4536</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4568</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B305">
+        <v>4584</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4611</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4602</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B308">
+        <v>4607</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>4660</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>4692</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B311">
+        <v>4802</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>4913</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>5057</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B314">
+        <v>5199</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>5283</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>5293</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B317">
+        <v>5272</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>5294</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>5243</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B320">
+        <v>5191</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>5052</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>4941</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B323">
+        <v>4854</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>4726</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>4643</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B326">
+        <v>4497</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>4444</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>4329</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B329">
+        <v>4320</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>4232</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>4174</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B332">
+        <v>4129</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>25.05.202694</t>
-  </si>
-  <si>
-    <t>25.05.202695</t>
-  </si>
-  <si>
-    <t>25.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>26.05.202696</t>
+  </si>
+  <si>
+    <t>27.05.20261</t>
+  </si>
+  <si>
+    <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
+    <t>27.05.202695</t>
+  </si>
+  <si>
+    <t>27.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>4466</v>
+        <v>5068</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>4414</v>
+        <v>4985</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>4369</v>
+        <v>5002</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>4350</v>
+        <v>4986</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>4401</v>
+        <v>4973</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>4379</v>
+        <v>4937</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>4941</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>4364</v>
+        <v>4942</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>4367</v>
+        <v>4995</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>4391</v>
+        <v>5037</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>4397</v>
+        <v>5030</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
-        <v>4393</v>
+        <v>4983</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>4426</v>
+        <v>5016</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>4536</v>
+        <v>5025</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>4568</v>
+        <v>5002</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>4584</v>
+        <v>4886</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>4611</v>
+        <v>4892</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>4602</v>
+        <v>4869</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>4607</v>
+        <v>4830</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>4660</v>
+        <v>4865</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>4692</v>
+        <v>4996</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>4802</v>
+        <v>5116</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>4913</v>
+        <v>5154</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>5057</v>
+        <v>5208</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>5199</v>
+        <v>5388</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>5283</v>
+        <v>5498</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>5293</v>
+        <v>5463</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>5272</v>
+        <v>5438</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>5294</v>
+        <v>5382</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>5243</v>
+        <v>5321</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>5191</v>
+        <v>5254</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>5052</v>
+        <v>5163</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>4941</v>
+        <v>4993</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>4854</v>
+        <v>4857</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>4726</v>
+        <v>4734</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>4643</v>
+        <v>4586</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>4497</v>
+        <v>4446</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>4444</v>
+        <v>4278</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>4329</v>
+        <v>4168</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>4320</v>
+        <v>4272</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>4232</v>
+        <v>4020</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>4174</v>
+        <v>3986</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>4129</v>
+        <v>3932</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>4106</v>
+        <v>3883</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>4163</v>
+        <v>3938</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>4184</v>
+        <v>3903</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>4217</v>
+        <v>3850</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>4205</v>
+        <v>3825</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>4164</v>
+        <v>3882</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>4194</v>
+        <v>3860</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>4232</v>
+        <v>3927</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>4243</v>
+        <v>3888</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>4247</v>
+        <v>3927</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>4290</v>
+        <v>3922</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>4335</v>
+        <v>4002</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>4321</v>
+        <v>4005</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>4427</v>
+        <v>4008</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>4485</v>
+        <v>4012</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>4497</v>
+        <v>4104</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>4602</v>
+        <v>4206</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>4710</v>
+        <v>4160</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>4719</v>
+        <v>4268</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>4855</v>
+        <v>4316</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>4918</v>
+        <v>4457</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>5090</v>
+        <v>4647</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>5251</v>
+        <v>4722</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>5358</v>
+        <v>4972</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>5413</v>
+        <v>5122</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>5460</v>
+        <v>5348</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>5688</v>
+        <v>5548</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>5681</v>
+        <v>5787</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>5749</v>
+        <v>6026</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>5896</v>
+        <v>6118</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>6138</v>
+        <v>6263</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>6271</v>
+        <v>6349</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>6359</v>
+        <v>6486</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>6268</v>
+        <v>6488</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>6361</v>
+        <v>6480</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>6448</v>
+        <v>6582</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>6509</v>
+        <v>6559</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>6609</v>
+        <v>6621</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>6650</v>
+        <v>6708</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>6638</v>
+        <v>6729</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>6570</v>
+        <v>6697</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>6471</v>
+        <v>6616</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>6263</v>
+        <v>6445</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>6169</v>
+        <v>6218</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>6021</v>
+        <v>6024</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>5805</v>
+        <v>5924</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>5738</v>
+        <v>5846</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>5670</v>
+        <v>5697</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>5585</v>
+        <v>5726</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>5397</v>
+        <v>5575</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>5262</v>
+        <v>5496</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>5216</v>
+        <v>5432</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
-        <v>5171</v>
+        <v>5365</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>5068</v>
+        <v>5298</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B99">
-        <v>4985</v>
+        <v>5223</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B100">
-        <v>5002</v>
+        <v>5142</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B101">
-        <v>4986</v>
+        <v>5140</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B102">
-        <v>4973</v>
+        <v>4970</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B103">
-        <v>4937</v>
+        <v>4931</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B104">
-        <v>4941</v>
+        <v>4908</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B105">
-        <v>4942</v>
+        <v>4858</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B106">
-        <v>4995</v>
+        <v>4904</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B107">
-        <v>5037</v>
+        <v>4907</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B108">
-        <v>5030</v>
+        <v>4871</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B109">
-        <v>4983</v>
+        <v>4867</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B110">
-        <v>5016</v>
+        <v>4936</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B111">
-        <v>5025</v>
+        <v>4960</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B112">
-        <v>5002</v>
+        <v>4956</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B113">
-        <v>4886</v>
+        <v>4918</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B114">
-        <v>4892</v>
+        <v>4954</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B115">
-        <v>4869</v>
+        <v>0</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B116">
-        <v>4830</v>
+        <v>4974</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B117">
-        <v>4865</v>
+        <v>5006</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B118">
-        <v>4996</v>
+        <v>5036</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B119">
-        <v>5116</v>
+        <v>5113</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B120">
-        <v>5154</v>
+        <v>5201</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B121">
-        <v>5208</v>
+        <v>5345</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B122">
-        <v>5388</v>
+        <v>5482</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B123">
-        <v>5498</v>
+        <v>5542</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B124">
-        <v>5463</v>
+        <v>5577</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B125">
-        <v>5438</v>
+        <v>5505</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B126">
-        <v>5382</v>
+        <v>5539</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B127">
-        <v>5321</v>
+        <v>5477</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B128">
-        <v>5254</v>
+        <v>5355</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B129">
-        <v>5163</v>
+        <v>5230</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B130">
-        <v>4993</v>
+        <v>5164</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B131">
-        <v>4857</v>
+        <v>0</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B132">
-        <v>4734</v>
+        <v>0</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B133">
-        <v>4586</v>
+        <v>0</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>27.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>5068</v>
+        <v>5298</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>4985</v>
+        <v>5223</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
-        <v>5002</v>
+        <v>5142</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>4986</v>
+        <v>5140</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>4973</v>
+        <v>4970</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>4937</v>
+        <v>4931</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>4941</v>
+        <v>4908</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>4942</v>
+        <v>4858</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>4995</v>
+        <v>4904</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>5037</v>
+        <v>4907</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>5030</v>
+        <v>4871</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>4983</v>
+        <v>4867</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>5016</v>
+        <v>4936</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>5025</v>
+        <v>4960</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>5002</v>
+        <v>4956</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>4886</v>
+        <v>4918</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>4892</v>
+        <v>4954</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>4869</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>4830</v>
+        <v>4974</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>4865</v>
+        <v>5006</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>4996</v>
+        <v>5036</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>5116</v>
+        <v>5113</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>5154</v>
+        <v>5201</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>5208</v>
+        <v>5345</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>5388</v>
+        <v>5482</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>5498</v>
+        <v>5542</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>5463</v>
+        <v>5577</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>5438</v>
+        <v>5505</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>5382</v>
+        <v>5539</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>5321</v>
+        <v>5477</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>5254</v>
+        <v>5355</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>5163</v>
+        <v>5230</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>4993</v>
+        <v>5164</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>4857</v>
+        <v>5147</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>4734</v>
+        <v>4981</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>4586</v>
+        <v>4901</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>4446</v>
+        <v>4714</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>4278</v>
+        <v>4639</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>4168</v>
+        <v>4490</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>4272</v>
+        <v>4397</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>4020</v>
+        <v>4247</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>3986</v>
+        <v>4191</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>3932</v>
+        <v>4111</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>3883</v>
+        <v>4058</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>3938</v>
+        <v>4046</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>3903</v>
+        <v>4062</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>3850</v>
+        <v>4028</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>3825</v>
+        <v>4037</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>3882</v>
+        <v>4145</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>3860</v>
+        <v>4191</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>3927</v>
+        <v>4169</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>3888</v>
+        <v>4120</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>3927</v>
+        <v>4227</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>3922</v>
+        <v>4231</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>4002</v>
+        <v>4232</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>4005</v>
+        <v>4223</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>4008</v>
+        <v>4323</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>4012</v>
+        <v>4346</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>4104</v>
+        <v>4491</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>4206</v>
+        <v>4666</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>4160</v>
+        <v>4561</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>4268</v>
+        <v>4740</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>4316</v>
+        <v>4878</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>4457</v>
+        <v>5047</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>4647</v>
+        <v>5151</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>4722</v>
+        <v>5232</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>4972</v>
+        <v>5362</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>5122</v>
+        <v>5550</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>5348</v>
+        <v>5632</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>5548</v>
+        <v>5811</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>5787</v>
+        <v>5979</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>6026</v>
+        <v>6157</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>6118</v>
+        <v>6210</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>6263</v>
+        <v>6405</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>6349</v>
+        <v>6496</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>6488</v>
+        <v>6604</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>6480</v>
+        <v>6705</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>6582</v>
+        <v>6716</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>6559</v>
+        <v>6804</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>6621</v>
+        <v>6843</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>6708</v>
+        <v>6903</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>6729</v>
+        <v>6904</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>6697</v>
+        <v>6873</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>6616</v>
+        <v>6716</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>6445</v>
+        <v>6533</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>6218</v>
+        <v>6395</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>6024</v>
+        <v>6226</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>5924</v>
+        <v>6088</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>5846</v>
+        <v>5967</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>5697</v>
+        <v>5850</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>5726</v>
+        <v>5786</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>5575</v>
+        <v>5508</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>5496</v>
+        <v>5446</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>5432</v>
+        <v>5356</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>5365</v>
+        <v>5307</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>5298</v>
+        <v>5195</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>5223</v>
+        <v>5147</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
-        <v>5142</v>
+        <v>5091</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>5140</v>
+        <v>5058</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
-        <v>4970</v>
+        <v>4985</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
-        <v>4931</v>
+        <v>5004</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
-        <v>4908</v>
+        <v>4955</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
-        <v>4858</v>
+        <v>4950</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
-        <v>4904</v>
+        <v>4909</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
-        <v>4907</v>
+        <v>4949</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
-        <v>4871</v>
+        <v>4947</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
-        <v>4867</v>
+        <v>4940</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>4936</v>
+        <v>5133</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
-        <v>4960</v>
+        <v>5289</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>4956</v>
+        <v>5286</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>4918</v>
+        <v>5272</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>4954</v>
+        <v>5296</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>5279</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>4974</v>
+        <v>5300</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>5006</v>
+        <v>5288</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>5036</v>
+        <v>5118</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>5113</v>
+        <v>5247</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>5201</v>
+        <v>5313</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>5345</v>
+        <v>5417</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>5482</v>
+        <v>5580</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>5542</v>
+        <v>5705</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>5577</v>
+        <v>5686</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>5505</v>
+        <v>5706</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>5539</v>
+        <v>5654</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>5477</v>
+        <v>5694</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>5355</v>
+        <v>5667</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>5230</v>
+        <v>5557</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>5164</v>
+        <v>5408</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>5337</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>5162</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,294 @@
   </si>
   <si>
     <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>5298</v>
+        <v>5195</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>5223</v>
+        <v>5147</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
-        <v>5142</v>
+        <v>5091</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>5140</v>
+        <v>5058</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>4970</v>
+        <v>4985</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>4931</v>
+        <v>5004</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>4908</v>
+        <v>4955</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>4858</v>
+        <v>4950</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>4904</v>
+        <v>4909</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>4907</v>
+        <v>4949</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>4871</v>
+        <v>4947</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>4867</v>
+        <v>4940</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>4936</v>
+        <v>5133</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>4960</v>
+        <v>5289</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>4956</v>
+        <v>5286</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>4918</v>
+        <v>5272</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>4954</v>
+        <v>5296</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>5279</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>4974</v>
+        <v>5300</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>5006</v>
+        <v>5288</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>5036</v>
+        <v>5118</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>5113</v>
+        <v>5247</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>5201</v>
+        <v>5313</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>5345</v>
+        <v>5417</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>5482</v>
+        <v>5580</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>5542</v>
+        <v>5705</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>5577</v>
+        <v>5686</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>5505</v>
+        <v>5706</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>5539</v>
+        <v>5654</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>5477</v>
+        <v>5694</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>5355</v>
+        <v>5667</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>5230</v>
+        <v>5557</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>5164</v>
+        <v>5408</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>5147</v>
+        <v>5337</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>4981</v>
+        <v>5162</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>4901</v>
+        <v>5053</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>4714</v>
+        <v>4718</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>4639</v>
+        <v>4617</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>4490</v>
+        <v>4444</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>4397</v>
+        <v>4274</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>4247</v>
+        <v>4322</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>4191</v>
+        <v>4359</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>4111</v>
+        <v>4303</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>4058</v>
+        <v>4161</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>4046</v>
+        <v>4010</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>4062</v>
+        <v>4067</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>4028</v>
+        <v>4110</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>4037</v>
+        <v>4200</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>4145</v>
+        <v>4194</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>4191</v>
+        <v>4205</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>4169</v>
+        <v>4157</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>4120</v>
+        <v>4229</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>4227</v>
+        <v>4131</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>4231</v>
+        <v>4132</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>4232</v>
+        <v>4228</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>4223</v>
+        <v>4266</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>4323</v>
+        <v>4273</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>4346</v>
+        <v>4390</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>4491</v>
+        <v>4391</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>4666</v>
+        <v>4436</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>4561</v>
+        <v>4470</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>4740</v>
+        <v>4567</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>4878</v>
+        <v>4709</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>5047</v>
+        <v>4842</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>5151</v>
+        <v>5176</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>5232</v>
+        <v>5252</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>5362</v>
+        <v>5421</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>5550</v>
+        <v>5623</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>5632</v>
+        <v>5827</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
         <v>5811</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>5979</v>
+        <v>5888</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>6157</v>
+        <v>5948</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>6210</v>
+        <v>6134</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>6405</v>
+        <v>6269</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>6496</v>
+        <v>6365</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>6628</v>
+        <v>6454</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>6604</v>
+        <v>6450</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>6705</v>
+        <v>6546</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>6716</v>
+        <v>6645</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>6804</v>
+        <v>6686</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>6843</v>
+        <v>6679</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>6903</v>
+        <v>6773</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>6904</v>
+        <v>6767</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>6873</v>
+        <v>6688</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>6716</v>
+        <v>6484</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>6533</v>
+        <v>6404</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>6395</v>
+        <v>6253</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>6226</v>
+        <v>6177</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>6088</v>
+        <v>6020</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>5967</v>
+        <v>5924</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>5850</v>
+        <v>5733</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>5786</v>
+        <v>5632</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>5508</v>
+        <v>5444</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>5446</v>
+        <v>5333</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>5356</v>
+        <v>5263</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>5307</v>
+        <v>5247</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>5195</v>
+        <v>5151</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
-        <v>5147</v>
+        <v>5071</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
-        <v>5091</v>
+        <v>5037</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
-        <v>5058</v>
+        <v>5051</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
-        <v>4985</v>
+        <v>5006</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
-        <v>5004</v>
+        <v>4980</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
-        <v>4955</v>
+        <v>5045</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
-        <v>4950</v>
+        <v>4884</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
-        <v>4909</v>
+        <v>5049</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
-        <v>4949</v>
+        <v>4999</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
-        <v>4947</v>
+        <v>5002</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
-        <v>4940</v>
+        <v>5021</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>5133</v>
+        <v>5022</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
-        <v>5289</v>
+        <v>5055</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>5286</v>
+        <v>5065</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>5272</v>
+        <v>5048</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>5296</v>
+        <v>5029</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>5279</v>
+        <v>5010</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>5300</v>
+        <v>5019</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>5288</v>
+        <v>5046</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>5118</v>
+        <v>5026</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>5247</v>
+        <v>5093</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>5313</v>
+        <v>5136</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>5417</v>
+        <v>5189</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>5580</v>
+        <v>5354</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>5705</v>
+        <v>5414</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>5686</v>
+        <v>5393</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>5706</v>
+        <v>5389</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>5654</v>
+        <v>5380</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>5694</v>
+        <v>5267</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>5667</v>
+        <v>5126</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>5557</v>
+        <v>5025</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>5408</v>
+        <v>4847</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>5337</v>
+        <v>4741</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>5162</v>
+        <v>4626</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.05.20261</t>
-  </si>
-  <si>
-    <t>28.05.20262</t>
-  </si>
-  <si>
-    <t>28.05.20263</t>
-  </si>
-  <si>
-    <t>28.05.20264</t>
-  </si>
-  <si>
-    <t>28.05.20265</t>
-  </si>
-  <si>
-    <t>28.05.20266</t>
-  </si>
-  <si>
-    <t>28.05.20267</t>
-  </si>
-  <si>
-    <t>28.05.20268</t>
-  </si>
-  <si>
-    <t>28.05.20269</t>
-  </si>
-  <si>
-    <t>28.05.202610</t>
-  </si>
-  <si>
-    <t>28.05.202611</t>
-  </si>
-  <si>
-    <t>28.05.202612</t>
-  </si>
-  <si>
-    <t>28.05.202613</t>
-  </si>
-  <si>
-    <t>28.05.202614</t>
-  </si>
-  <si>
-    <t>28.05.202615</t>
-  </si>
-  <si>
-    <t>28.05.202616</t>
-  </si>
-  <si>
-    <t>28.05.202617</t>
-  </si>
-  <si>
-    <t>28.05.202618</t>
-  </si>
-  <si>
-    <t>28.05.202619</t>
-  </si>
-  <si>
-    <t>28.05.202620</t>
-  </si>
-  <si>
-    <t>28.05.202621</t>
-  </si>
-  <si>
-    <t>28.05.202622</t>
-  </si>
-  <si>
-    <t>28.05.202623</t>
-  </si>
-  <si>
-    <t>28.05.202624</t>
-  </si>
-  <si>
-    <t>28.05.202625</t>
-  </si>
-  <si>
-    <t>28.05.202626</t>
-  </si>
-  <si>
-    <t>28.05.202627</t>
-  </si>
-  <si>
-    <t>28.05.202628</t>
-  </si>
-  <si>
-    <t>28.05.202629</t>
-  </si>
-  <si>
-    <t>28.05.202630</t>
-  </si>
-  <si>
-    <t>28.05.202631</t>
-  </si>
-  <si>
-    <t>28.05.202632</t>
-  </si>
-  <si>
-    <t>28.05.202633</t>
-  </si>
-  <si>
-    <t>28.05.202634</t>
-  </si>
-  <si>
-    <t>28.05.202635</t>
-  </si>
-  <si>
-    <t>28.05.202636</t>
-  </si>
-  <si>
-    <t>28.05.202637</t>
-  </si>
-  <si>
-    <t>28.05.202638</t>
-  </si>
-  <si>
-    <t>28.05.202639</t>
-  </si>
-  <si>
-    <t>28.05.202640</t>
-  </si>
-  <si>
-    <t>28.05.202641</t>
-  </si>
-  <si>
-    <t>28.05.202642</t>
-  </si>
-  <si>
-    <t>28.05.202643</t>
-  </si>
-  <si>
-    <t>28.05.202644</t>
-  </si>
-  <si>
-    <t>28.05.202645</t>
-  </si>
-  <si>
-    <t>28.05.202646</t>
-  </si>
-  <si>
-    <t>28.05.202647</t>
-  </si>
-  <si>
-    <t>28.05.202648</t>
-  </si>
-  <si>
-    <t>28.05.202649</t>
-  </si>
-  <si>
-    <t>28.05.202650</t>
-  </si>
-  <si>
-    <t>28.05.202651</t>
-  </si>
-  <si>
-    <t>28.05.202652</t>
-  </si>
-  <si>
-    <t>28.05.202653</t>
-  </si>
-  <si>
-    <t>28.05.202654</t>
-  </si>
-  <si>
-    <t>28.05.202655</t>
-  </si>
-  <si>
-    <t>28.05.202656</t>
-  </si>
-  <si>
-    <t>28.05.202657</t>
-  </si>
-  <si>
-    <t>28.05.202658</t>
-  </si>
-  <si>
-    <t>28.05.202659</t>
-  </si>
-  <si>
-    <t>28.05.202660</t>
-  </si>
-  <si>
-    <t>28.05.202661</t>
-  </si>
-  <si>
-    <t>28.05.202662</t>
-  </si>
-  <si>
-    <t>28.05.202663</t>
-  </si>
-  <si>
-    <t>28.05.202664</t>
-  </si>
-  <si>
-    <t>28.05.202665</t>
-  </si>
-  <si>
-    <t>28.05.202666</t>
-  </si>
-  <si>
-    <t>28.05.202667</t>
-  </si>
-  <si>
-    <t>28.05.202668</t>
-  </si>
-  <si>
-    <t>28.05.202669</t>
-  </si>
-  <si>
-    <t>28.05.202670</t>
-  </si>
-  <si>
-    <t>28.05.202671</t>
-  </si>
-  <si>
-    <t>28.05.202672</t>
-  </si>
-  <si>
-    <t>28.05.202673</t>
-  </si>
-  <si>
-    <t>28.05.202674</t>
-  </si>
-  <si>
-    <t>28.05.202675</t>
-  </si>
-  <si>
-    <t>28.05.202676</t>
-  </si>
-  <si>
-    <t>28.05.202677</t>
-  </si>
-  <si>
-    <t>28.05.202678</t>
-  </si>
-  <si>
-    <t>28.05.202679</t>
-  </si>
-  <si>
-    <t>28.05.202680</t>
-  </si>
-  <si>
-    <t>28.05.202681</t>
-  </si>
-  <si>
-    <t>28.05.202682</t>
-  </si>
-  <si>
-    <t>28.05.202683</t>
-  </si>
-  <si>
-    <t>28.05.202684</t>
-  </si>
-  <si>
-    <t>28.05.202685</t>
-  </si>
-  <si>
-    <t>28.05.202686</t>
-  </si>
-  <si>
-    <t>28.05.202687</t>
-  </si>
-  <si>
-    <t>28.05.202688</t>
-  </si>
-  <si>
-    <t>28.05.202689</t>
-  </si>
-  <si>
-    <t>28.05.202690</t>
-  </si>
-  <si>
-    <t>28.05.202691</t>
-  </si>
-  <si>
-    <t>28.05.202692</t>
-  </si>
-  <si>
-    <t>28.05.202693</t>
-  </si>
-  <si>
-    <t>28.05.202694</t>
-  </si>
-  <si>
-    <t>28.05.202695</t>
-  </si>
-  <si>
-    <t>28.05.202696</t>
-  </si>
-  <si>
     <t>29.05.20261</t>
   </si>
   <si>
@@ -602,6 +314,1446 @@
   </si>
   <si>
     <t>29.05.202696</t>
+  </si>
+  <si>
+    <t>30.05.20261</t>
+  </si>
+  <si>
+    <t>30.05.20262</t>
+  </si>
+  <si>
+    <t>30.05.20263</t>
+  </si>
+  <si>
+    <t>30.05.20264</t>
+  </si>
+  <si>
+    <t>30.05.20265</t>
+  </si>
+  <si>
+    <t>30.05.20266</t>
+  </si>
+  <si>
+    <t>30.05.20267</t>
+  </si>
+  <si>
+    <t>30.05.20268</t>
+  </si>
+  <si>
+    <t>30.05.20269</t>
+  </si>
+  <si>
+    <t>30.05.202610</t>
+  </si>
+  <si>
+    <t>30.05.202611</t>
+  </si>
+  <si>
+    <t>30.05.202612</t>
+  </si>
+  <si>
+    <t>30.05.202613</t>
+  </si>
+  <si>
+    <t>30.05.202614</t>
+  </si>
+  <si>
+    <t>30.05.202615</t>
+  </si>
+  <si>
+    <t>30.05.202616</t>
+  </si>
+  <si>
+    <t>30.05.202617</t>
+  </si>
+  <si>
+    <t>30.05.202618</t>
+  </si>
+  <si>
+    <t>30.05.202619</t>
+  </si>
+  <si>
+    <t>30.05.202620</t>
+  </si>
+  <si>
+    <t>30.05.202621</t>
+  </si>
+  <si>
+    <t>30.05.202622</t>
+  </si>
+  <si>
+    <t>30.05.202623</t>
+  </si>
+  <si>
+    <t>30.05.202624</t>
+  </si>
+  <si>
+    <t>30.05.202625</t>
+  </si>
+  <si>
+    <t>30.05.202626</t>
+  </si>
+  <si>
+    <t>30.05.202627</t>
+  </si>
+  <si>
+    <t>30.05.202628</t>
+  </si>
+  <si>
+    <t>30.05.202629</t>
+  </si>
+  <si>
+    <t>30.05.202630</t>
+  </si>
+  <si>
+    <t>30.05.202631</t>
+  </si>
+  <si>
+    <t>30.05.202632</t>
+  </si>
+  <si>
+    <t>30.05.202633</t>
+  </si>
+  <si>
+    <t>30.05.202634</t>
+  </si>
+  <si>
+    <t>30.05.202635</t>
+  </si>
+  <si>
+    <t>30.05.202636</t>
+  </si>
+  <si>
+    <t>30.05.202637</t>
+  </si>
+  <si>
+    <t>30.05.202638</t>
+  </si>
+  <si>
+    <t>30.05.202639</t>
+  </si>
+  <si>
+    <t>30.05.202640</t>
+  </si>
+  <si>
+    <t>30.05.202641</t>
+  </si>
+  <si>
+    <t>30.05.202642</t>
+  </si>
+  <si>
+    <t>30.05.202643</t>
+  </si>
+  <si>
+    <t>30.05.202644</t>
+  </si>
+  <si>
+    <t>30.05.202645</t>
+  </si>
+  <si>
+    <t>30.05.202646</t>
+  </si>
+  <si>
+    <t>30.05.202647</t>
+  </si>
+  <si>
+    <t>30.05.202648</t>
+  </si>
+  <si>
+    <t>30.05.202649</t>
+  </si>
+  <si>
+    <t>30.05.202650</t>
+  </si>
+  <si>
+    <t>30.05.202651</t>
+  </si>
+  <si>
+    <t>30.05.202652</t>
+  </si>
+  <si>
+    <t>30.05.202653</t>
+  </si>
+  <si>
+    <t>30.05.202654</t>
+  </si>
+  <si>
+    <t>30.05.202655</t>
+  </si>
+  <si>
+    <t>30.05.202656</t>
+  </si>
+  <si>
+    <t>30.05.202657</t>
+  </si>
+  <si>
+    <t>30.05.202658</t>
+  </si>
+  <si>
+    <t>30.05.202659</t>
+  </si>
+  <si>
+    <t>30.05.202660</t>
+  </si>
+  <si>
+    <t>30.05.202661</t>
+  </si>
+  <si>
+    <t>30.05.202662</t>
+  </si>
+  <si>
+    <t>30.05.202663</t>
+  </si>
+  <si>
+    <t>30.05.202664</t>
+  </si>
+  <si>
+    <t>30.05.202665</t>
+  </si>
+  <si>
+    <t>30.05.202666</t>
+  </si>
+  <si>
+    <t>30.05.202667</t>
+  </si>
+  <si>
+    <t>30.05.202668</t>
+  </si>
+  <si>
+    <t>30.05.202669</t>
+  </si>
+  <si>
+    <t>30.05.202670</t>
+  </si>
+  <si>
+    <t>30.05.202671</t>
+  </si>
+  <si>
+    <t>30.05.202672</t>
+  </si>
+  <si>
+    <t>30.05.202673</t>
+  </si>
+  <si>
+    <t>30.05.202674</t>
+  </si>
+  <si>
+    <t>30.05.202675</t>
+  </si>
+  <si>
+    <t>30.05.202676</t>
+  </si>
+  <si>
+    <t>30.05.202677</t>
+  </si>
+  <si>
+    <t>30.05.202678</t>
+  </si>
+  <si>
+    <t>30.05.202679</t>
+  </si>
+  <si>
+    <t>30.05.202680</t>
+  </si>
+  <si>
+    <t>30.05.202681</t>
+  </si>
+  <si>
+    <t>30.05.202682</t>
+  </si>
+  <si>
+    <t>30.05.202683</t>
+  </si>
+  <si>
+    <t>30.05.202684</t>
+  </si>
+  <si>
+    <t>30.05.202685</t>
+  </si>
+  <si>
+    <t>30.05.202686</t>
+  </si>
+  <si>
+    <t>30.05.202687</t>
+  </si>
+  <si>
+    <t>30.05.202688</t>
+  </si>
+  <si>
+    <t>30.05.202689</t>
+  </si>
+  <si>
+    <t>30.05.202690</t>
+  </si>
+  <si>
+    <t>30.05.202691</t>
+  </si>
+  <si>
+    <t>30.05.202692</t>
+  </si>
+  <si>
+    <t>30.05.202693</t>
+  </si>
+  <si>
+    <t>30.05.202694</t>
+  </si>
+  <si>
+    <t>30.05.202695</t>
+  </si>
+  <si>
+    <t>30.05.202696</t>
+  </si>
+  <si>
+    <t>31.05.20261</t>
+  </si>
+  <si>
+    <t>31.05.20262</t>
+  </si>
+  <si>
+    <t>31.05.20263</t>
+  </si>
+  <si>
+    <t>31.05.20264</t>
+  </si>
+  <si>
+    <t>31.05.20265</t>
+  </si>
+  <si>
+    <t>31.05.20266</t>
+  </si>
+  <si>
+    <t>31.05.20267</t>
+  </si>
+  <si>
+    <t>31.05.20268</t>
+  </si>
+  <si>
+    <t>31.05.20269</t>
+  </si>
+  <si>
+    <t>31.05.202610</t>
+  </si>
+  <si>
+    <t>31.05.202611</t>
+  </si>
+  <si>
+    <t>31.05.202612</t>
+  </si>
+  <si>
+    <t>31.05.202613</t>
+  </si>
+  <si>
+    <t>31.05.202614</t>
+  </si>
+  <si>
+    <t>31.05.202615</t>
+  </si>
+  <si>
+    <t>31.05.202616</t>
+  </si>
+  <si>
+    <t>31.05.202617</t>
+  </si>
+  <si>
+    <t>31.05.202618</t>
+  </si>
+  <si>
+    <t>31.05.202619</t>
+  </si>
+  <si>
+    <t>31.05.202620</t>
+  </si>
+  <si>
+    <t>31.05.202621</t>
+  </si>
+  <si>
+    <t>31.05.202622</t>
+  </si>
+  <si>
+    <t>31.05.202623</t>
+  </si>
+  <si>
+    <t>31.05.202624</t>
+  </si>
+  <si>
+    <t>31.05.202625</t>
+  </si>
+  <si>
+    <t>31.05.202626</t>
+  </si>
+  <si>
+    <t>31.05.202627</t>
+  </si>
+  <si>
+    <t>31.05.202628</t>
+  </si>
+  <si>
+    <t>31.05.202629</t>
+  </si>
+  <si>
+    <t>31.05.202630</t>
+  </si>
+  <si>
+    <t>31.05.202631</t>
+  </si>
+  <si>
+    <t>31.05.202632</t>
+  </si>
+  <si>
+    <t>31.05.202633</t>
+  </si>
+  <si>
+    <t>31.05.202634</t>
+  </si>
+  <si>
+    <t>31.05.202635</t>
+  </si>
+  <si>
+    <t>31.05.202636</t>
+  </si>
+  <si>
+    <t>31.05.202637</t>
+  </si>
+  <si>
+    <t>31.05.202638</t>
+  </si>
+  <si>
+    <t>31.05.202639</t>
+  </si>
+  <si>
+    <t>31.05.202640</t>
+  </si>
+  <si>
+    <t>31.05.202641</t>
+  </si>
+  <si>
+    <t>31.05.202642</t>
+  </si>
+  <si>
+    <t>31.05.202643</t>
+  </si>
+  <si>
+    <t>31.05.202644</t>
+  </si>
+  <si>
+    <t>31.05.202645</t>
+  </si>
+  <si>
+    <t>31.05.202646</t>
+  </si>
+  <si>
+    <t>31.05.202647</t>
+  </si>
+  <si>
+    <t>31.05.202648</t>
+  </si>
+  <si>
+    <t>31.05.202649</t>
+  </si>
+  <si>
+    <t>31.05.202650</t>
+  </si>
+  <si>
+    <t>31.05.202651</t>
+  </si>
+  <si>
+    <t>31.05.202652</t>
+  </si>
+  <si>
+    <t>31.05.202653</t>
+  </si>
+  <si>
+    <t>31.05.202654</t>
+  </si>
+  <si>
+    <t>31.05.202655</t>
+  </si>
+  <si>
+    <t>31.05.202656</t>
+  </si>
+  <si>
+    <t>31.05.202657</t>
+  </si>
+  <si>
+    <t>31.05.202658</t>
+  </si>
+  <si>
+    <t>31.05.202659</t>
+  </si>
+  <si>
+    <t>31.05.202660</t>
+  </si>
+  <si>
+    <t>31.05.202661</t>
+  </si>
+  <si>
+    <t>31.05.202662</t>
+  </si>
+  <si>
+    <t>31.05.202663</t>
+  </si>
+  <si>
+    <t>31.05.202664</t>
+  </si>
+  <si>
+    <t>31.05.202665</t>
+  </si>
+  <si>
+    <t>31.05.202666</t>
+  </si>
+  <si>
+    <t>31.05.202667</t>
+  </si>
+  <si>
+    <t>31.05.202668</t>
+  </si>
+  <si>
+    <t>31.05.202669</t>
+  </si>
+  <si>
+    <t>31.05.202670</t>
+  </si>
+  <si>
+    <t>31.05.202671</t>
+  </si>
+  <si>
+    <t>31.05.202672</t>
+  </si>
+  <si>
+    <t>31.05.202673</t>
+  </si>
+  <si>
+    <t>31.05.202674</t>
+  </si>
+  <si>
+    <t>31.05.202675</t>
+  </si>
+  <si>
+    <t>31.05.202676</t>
+  </si>
+  <si>
+    <t>31.05.202677</t>
+  </si>
+  <si>
+    <t>31.05.202678</t>
+  </si>
+  <si>
+    <t>31.05.202679</t>
+  </si>
+  <si>
+    <t>31.05.202680</t>
+  </si>
+  <si>
+    <t>31.05.202681</t>
+  </si>
+  <si>
+    <t>31.05.202682</t>
+  </si>
+  <si>
+    <t>31.05.202683</t>
+  </si>
+  <si>
+    <t>31.05.202684</t>
+  </si>
+  <si>
+    <t>31.05.202685</t>
+  </si>
+  <si>
+    <t>31.05.202686</t>
+  </si>
+  <si>
+    <t>31.05.202687</t>
+  </si>
+  <si>
+    <t>31.05.202688</t>
+  </si>
+  <si>
+    <t>31.05.202689</t>
+  </si>
+  <si>
+    <t>31.05.202690</t>
+  </si>
+  <si>
+    <t>31.05.202691</t>
+  </si>
+  <si>
+    <t>31.05.202692</t>
+  </si>
+  <si>
+    <t>31.05.202693</t>
+  </si>
+  <si>
+    <t>31.05.202694</t>
+  </si>
+  <si>
+    <t>31.05.202695</t>
+  </si>
+  <si>
+    <t>31.05.202696</t>
+  </si>
+  <si>
+    <t>01.06.20261</t>
+  </si>
+  <si>
+    <t>01.06.20262</t>
+  </si>
+  <si>
+    <t>01.06.20263</t>
+  </si>
+  <si>
+    <t>01.06.20264</t>
+  </si>
+  <si>
+    <t>01.06.20265</t>
+  </si>
+  <si>
+    <t>01.06.20266</t>
+  </si>
+  <si>
+    <t>01.06.20267</t>
+  </si>
+  <si>
+    <t>01.06.20268</t>
+  </si>
+  <si>
+    <t>01.06.20269</t>
+  </si>
+  <si>
+    <t>01.06.202610</t>
+  </si>
+  <si>
+    <t>01.06.202611</t>
+  </si>
+  <si>
+    <t>01.06.202612</t>
+  </si>
+  <si>
+    <t>01.06.202613</t>
+  </si>
+  <si>
+    <t>01.06.202614</t>
+  </si>
+  <si>
+    <t>01.06.202615</t>
+  </si>
+  <si>
+    <t>01.06.202616</t>
+  </si>
+  <si>
+    <t>01.06.202617</t>
+  </si>
+  <si>
+    <t>01.06.202618</t>
+  </si>
+  <si>
+    <t>01.06.202619</t>
+  </si>
+  <si>
+    <t>01.06.202620</t>
+  </si>
+  <si>
+    <t>01.06.202621</t>
+  </si>
+  <si>
+    <t>01.06.202622</t>
+  </si>
+  <si>
+    <t>01.06.202623</t>
+  </si>
+  <si>
+    <t>01.06.202624</t>
+  </si>
+  <si>
+    <t>01.06.202625</t>
+  </si>
+  <si>
+    <t>01.06.202626</t>
+  </si>
+  <si>
+    <t>01.06.202627</t>
+  </si>
+  <si>
+    <t>01.06.202628</t>
+  </si>
+  <si>
+    <t>01.06.202629</t>
+  </si>
+  <si>
+    <t>01.06.202630</t>
+  </si>
+  <si>
+    <t>01.06.202631</t>
+  </si>
+  <si>
+    <t>01.06.202632</t>
+  </si>
+  <si>
+    <t>01.06.202633</t>
+  </si>
+  <si>
+    <t>01.06.202634</t>
+  </si>
+  <si>
+    <t>01.06.202635</t>
+  </si>
+  <si>
+    <t>01.06.202636</t>
+  </si>
+  <si>
+    <t>01.06.202637</t>
+  </si>
+  <si>
+    <t>01.06.202638</t>
+  </si>
+  <si>
+    <t>01.06.202639</t>
+  </si>
+  <si>
+    <t>01.06.202640</t>
+  </si>
+  <si>
+    <t>01.06.202641</t>
+  </si>
+  <si>
+    <t>01.06.202642</t>
+  </si>
+  <si>
+    <t>01.06.202643</t>
+  </si>
+  <si>
+    <t>01.06.202644</t>
+  </si>
+  <si>
+    <t>01.06.202645</t>
+  </si>
+  <si>
+    <t>01.06.202646</t>
+  </si>
+  <si>
+    <t>01.06.202647</t>
+  </si>
+  <si>
+    <t>01.06.202648</t>
+  </si>
+  <si>
+    <t>01.06.202649</t>
+  </si>
+  <si>
+    <t>01.06.202650</t>
+  </si>
+  <si>
+    <t>01.06.202651</t>
+  </si>
+  <si>
+    <t>01.06.202652</t>
+  </si>
+  <si>
+    <t>01.06.202653</t>
+  </si>
+  <si>
+    <t>01.06.202654</t>
+  </si>
+  <si>
+    <t>01.06.202655</t>
+  </si>
+  <si>
+    <t>01.06.202656</t>
+  </si>
+  <si>
+    <t>01.06.202657</t>
+  </si>
+  <si>
+    <t>01.06.202658</t>
+  </si>
+  <si>
+    <t>01.06.202659</t>
+  </si>
+  <si>
+    <t>01.06.202660</t>
+  </si>
+  <si>
+    <t>01.06.202661</t>
+  </si>
+  <si>
+    <t>01.06.202662</t>
+  </si>
+  <si>
+    <t>01.06.202663</t>
+  </si>
+  <si>
+    <t>01.06.202664</t>
+  </si>
+  <si>
+    <t>01.06.202665</t>
+  </si>
+  <si>
+    <t>01.06.202666</t>
+  </si>
+  <si>
+    <t>01.06.202667</t>
+  </si>
+  <si>
+    <t>01.06.202668</t>
+  </si>
+  <si>
+    <t>01.06.202669</t>
+  </si>
+  <si>
+    <t>01.06.202670</t>
+  </si>
+  <si>
+    <t>01.06.202671</t>
+  </si>
+  <si>
+    <t>01.06.202672</t>
+  </si>
+  <si>
+    <t>01.06.202673</t>
+  </si>
+  <si>
+    <t>01.06.202674</t>
+  </si>
+  <si>
+    <t>01.06.202675</t>
+  </si>
+  <si>
+    <t>01.06.202676</t>
+  </si>
+  <si>
+    <t>01.06.202677</t>
+  </si>
+  <si>
+    <t>01.06.202678</t>
+  </si>
+  <si>
+    <t>01.06.202679</t>
+  </si>
+  <si>
+    <t>01.06.202680</t>
+  </si>
+  <si>
+    <t>01.06.202681</t>
+  </si>
+  <si>
+    <t>01.06.202682</t>
+  </si>
+  <si>
+    <t>01.06.202683</t>
+  </si>
+  <si>
+    <t>01.06.202684</t>
+  </si>
+  <si>
+    <t>01.06.202685</t>
+  </si>
+  <si>
+    <t>01.06.202686</t>
+  </si>
+  <si>
+    <t>01.06.202687</t>
+  </si>
+  <si>
+    <t>01.06.202688</t>
+  </si>
+  <si>
+    <t>01.06.202689</t>
+  </si>
+  <si>
+    <t>01.06.202690</t>
+  </si>
+  <si>
+    <t>01.06.202691</t>
+  </si>
+  <si>
+    <t>01.06.202692</t>
+  </si>
+  <si>
+    <t>01.06.202693</t>
+  </si>
+  <si>
+    <t>01.06.202694</t>
+  </si>
+  <si>
+    <t>01.06.202695</t>
+  </si>
+  <si>
+    <t>01.06.202696</t>
+  </si>
+  <si>
+    <t>02.06.20261</t>
+  </si>
+  <si>
+    <t>02.06.20262</t>
+  </si>
+  <si>
+    <t>02.06.20263</t>
+  </si>
+  <si>
+    <t>02.06.20264</t>
+  </si>
+  <si>
+    <t>02.06.20265</t>
+  </si>
+  <si>
+    <t>02.06.20266</t>
+  </si>
+  <si>
+    <t>02.06.20267</t>
+  </si>
+  <si>
+    <t>02.06.20268</t>
+  </si>
+  <si>
+    <t>02.06.20269</t>
+  </si>
+  <si>
+    <t>02.06.202610</t>
+  </si>
+  <si>
+    <t>02.06.202611</t>
+  </si>
+  <si>
+    <t>02.06.202612</t>
+  </si>
+  <si>
+    <t>02.06.202613</t>
+  </si>
+  <si>
+    <t>02.06.202614</t>
+  </si>
+  <si>
+    <t>02.06.202615</t>
+  </si>
+  <si>
+    <t>02.06.202616</t>
+  </si>
+  <si>
+    <t>02.06.202617</t>
+  </si>
+  <si>
+    <t>02.06.202618</t>
+  </si>
+  <si>
+    <t>02.06.202619</t>
+  </si>
+  <si>
+    <t>02.06.202620</t>
+  </si>
+  <si>
+    <t>02.06.202621</t>
+  </si>
+  <si>
+    <t>02.06.202622</t>
+  </si>
+  <si>
+    <t>02.06.202623</t>
+  </si>
+  <si>
+    <t>02.06.202624</t>
+  </si>
+  <si>
+    <t>02.06.202625</t>
+  </si>
+  <si>
+    <t>02.06.202626</t>
+  </si>
+  <si>
+    <t>02.06.202627</t>
+  </si>
+  <si>
+    <t>02.06.202628</t>
+  </si>
+  <si>
+    <t>02.06.202629</t>
+  </si>
+  <si>
+    <t>02.06.202630</t>
+  </si>
+  <si>
+    <t>02.06.202631</t>
+  </si>
+  <si>
+    <t>02.06.202632</t>
+  </si>
+  <si>
+    <t>02.06.202633</t>
+  </si>
+  <si>
+    <t>02.06.202634</t>
+  </si>
+  <si>
+    <t>02.06.202635</t>
+  </si>
+  <si>
+    <t>02.06.202636</t>
+  </si>
+  <si>
+    <t>02.06.202637</t>
+  </si>
+  <si>
+    <t>02.06.202638</t>
+  </si>
+  <si>
+    <t>02.06.202639</t>
+  </si>
+  <si>
+    <t>02.06.202640</t>
+  </si>
+  <si>
+    <t>02.06.202641</t>
+  </si>
+  <si>
+    <t>02.06.202642</t>
+  </si>
+  <si>
+    <t>02.06.202643</t>
+  </si>
+  <si>
+    <t>02.06.202644</t>
+  </si>
+  <si>
+    <t>02.06.202645</t>
+  </si>
+  <si>
+    <t>02.06.202646</t>
+  </si>
+  <si>
+    <t>02.06.202647</t>
+  </si>
+  <si>
+    <t>02.06.202648</t>
+  </si>
+  <si>
+    <t>02.06.202649</t>
+  </si>
+  <si>
+    <t>02.06.202650</t>
+  </si>
+  <si>
+    <t>02.06.202651</t>
+  </si>
+  <si>
+    <t>02.06.202652</t>
+  </si>
+  <si>
+    <t>02.06.202653</t>
+  </si>
+  <si>
+    <t>02.06.202654</t>
+  </si>
+  <si>
+    <t>02.06.202655</t>
+  </si>
+  <si>
+    <t>02.06.202656</t>
+  </si>
+  <si>
+    <t>02.06.202657</t>
+  </si>
+  <si>
+    <t>02.06.202658</t>
+  </si>
+  <si>
+    <t>02.06.202659</t>
+  </si>
+  <si>
+    <t>02.06.202660</t>
+  </si>
+  <si>
+    <t>02.06.202661</t>
+  </si>
+  <si>
+    <t>02.06.202662</t>
+  </si>
+  <si>
+    <t>02.06.202663</t>
+  </si>
+  <si>
+    <t>02.06.202664</t>
+  </si>
+  <si>
+    <t>02.06.202665</t>
+  </si>
+  <si>
+    <t>02.06.202666</t>
+  </si>
+  <si>
+    <t>02.06.202667</t>
+  </si>
+  <si>
+    <t>02.06.202668</t>
+  </si>
+  <si>
+    <t>02.06.202669</t>
+  </si>
+  <si>
+    <t>02.06.202670</t>
+  </si>
+  <si>
+    <t>02.06.202671</t>
+  </si>
+  <si>
+    <t>02.06.202672</t>
+  </si>
+  <si>
+    <t>02.06.202673</t>
+  </si>
+  <si>
+    <t>02.06.202674</t>
+  </si>
+  <si>
+    <t>02.06.202675</t>
+  </si>
+  <si>
+    <t>02.06.202676</t>
+  </si>
+  <si>
+    <t>02.06.202677</t>
+  </si>
+  <si>
+    <t>02.06.202678</t>
+  </si>
+  <si>
+    <t>02.06.202679</t>
+  </si>
+  <si>
+    <t>02.06.202680</t>
+  </si>
+  <si>
+    <t>02.06.202681</t>
+  </si>
+  <si>
+    <t>02.06.202682</t>
+  </si>
+  <si>
+    <t>02.06.202683</t>
+  </si>
+  <si>
+    <t>02.06.202684</t>
+  </si>
+  <si>
+    <t>02.06.202685</t>
+  </si>
+  <si>
+    <t>02.06.202686</t>
+  </si>
+  <si>
+    <t>02.06.202687</t>
+  </si>
+  <si>
+    <t>02.06.202688</t>
+  </si>
+  <si>
+    <t>02.06.202689</t>
+  </si>
+  <si>
+    <t>02.06.202690</t>
+  </si>
+  <si>
+    <t>02.06.202691</t>
+  </si>
+  <si>
+    <t>02.06.202692</t>
+  </si>
+  <si>
+    <t>02.06.202693</t>
+  </si>
+  <si>
+    <t>02.06.202694</t>
+  </si>
+  <si>
+    <t>02.06.202695</t>
+  </si>
+  <si>
+    <t>02.06.202696</t>
+  </si>
+  <si>
+    <t>03.06.20261</t>
+  </si>
+  <si>
+    <t>03.06.20262</t>
+  </si>
+  <si>
+    <t>03.06.20263</t>
+  </si>
+  <si>
+    <t>03.06.20264</t>
+  </si>
+  <si>
+    <t>03.06.20265</t>
+  </si>
+  <si>
+    <t>03.06.20266</t>
+  </si>
+  <si>
+    <t>03.06.20267</t>
+  </si>
+  <si>
+    <t>03.06.20268</t>
+  </si>
+  <si>
+    <t>03.06.20269</t>
+  </si>
+  <si>
+    <t>03.06.202610</t>
+  </si>
+  <si>
+    <t>03.06.202611</t>
+  </si>
+  <si>
+    <t>03.06.202612</t>
+  </si>
+  <si>
+    <t>03.06.202613</t>
+  </si>
+  <si>
+    <t>03.06.202614</t>
+  </si>
+  <si>
+    <t>03.06.202615</t>
+  </si>
+  <si>
+    <t>03.06.202616</t>
+  </si>
+  <si>
+    <t>03.06.202617</t>
+  </si>
+  <si>
+    <t>03.06.202618</t>
+  </si>
+  <si>
+    <t>03.06.202619</t>
+  </si>
+  <si>
+    <t>03.06.202620</t>
+  </si>
+  <si>
+    <t>03.06.202621</t>
+  </si>
+  <si>
+    <t>03.06.202622</t>
+  </si>
+  <si>
+    <t>03.06.202623</t>
+  </si>
+  <si>
+    <t>03.06.202624</t>
+  </si>
+  <si>
+    <t>03.06.202625</t>
+  </si>
+  <si>
+    <t>03.06.202626</t>
+  </si>
+  <si>
+    <t>03.06.202627</t>
+  </si>
+  <si>
+    <t>03.06.202628</t>
+  </si>
+  <si>
+    <t>03.06.202629</t>
+  </si>
+  <si>
+    <t>03.06.202630</t>
+  </si>
+  <si>
+    <t>03.06.202631</t>
+  </si>
+  <si>
+    <t>03.06.202632</t>
+  </si>
+  <si>
+    <t>03.06.202633</t>
+  </si>
+  <si>
+    <t>03.06.202634</t>
+  </si>
+  <si>
+    <t>03.06.202635</t>
+  </si>
+  <si>
+    <t>03.06.202636</t>
+  </si>
+  <si>
+    <t>03.06.202637</t>
+  </si>
+  <si>
+    <t>03.06.202638</t>
+  </si>
+  <si>
+    <t>03.06.202639</t>
+  </si>
+  <si>
+    <t>03.06.202640</t>
+  </si>
+  <si>
+    <t>03.06.202641</t>
+  </si>
+  <si>
+    <t>03.06.202642</t>
+  </si>
+  <si>
+    <t>03.06.202643</t>
+  </si>
+  <si>
+    <t>03.06.202644</t>
+  </si>
+  <si>
+    <t>03.06.202645</t>
+  </si>
+  <si>
+    <t>03.06.202646</t>
+  </si>
+  <si>
+    <t>03.06.202647</t>
+  </si>
+  <si>
+    <t>03.06.202648</t>
+  </si>
+  <si>
+    <t>03.06.202649</t>
+  </si>
+  <si>
+    <t>03.06.202650</t>
+  </si>
+  <si>
+    <t>03.06.202651</t>
+  </si>
+  <si>
+    <t>03.06.202652</t>
+  </si>
+  <si>
+    <t>03.06.202653</t>
+  </si>
+  <si>
+    <t>03.06.202654</t>
+  </si>
+  <si>
+    <t>03.06.202655</t>
+  </si>
+  <si>
+    <t>03.06.202656</t>
+  </si>
+  <si>
+    <t>03.06.202657</t>
+  </si>
+  <si>
+    <t>03.06.202658</t>
+  </si>
+  <si>
+    <t>03.06.202659</t>
+  </si>
+  <si>
+    <t>03.06.202660</t>
+  </si>
+  <si>
+    <t>03.06.202661</t>
+  </si>
+  <si>
+    <t>03.06.202662</t>
+  </si>
+  <si>
+    <t>03.06.202663</t>
+  </si>
+  <si>
+    <t>03.06.202664</t>
+  </si>
+  <si>
+    <t>03.06.202665</t>
+  </si>
+  <si>
+    <t>03.06.202666</t>
+  </si>
+  <si>
+    <t>03.06.202667</t>
+  </si>
+  <si>
+    <t>03.06.202668</t>
+  </si>
+  <si>
+    <t>03.06.202669</t>
+  </si>
+  <si>
+    <t>03.06.202670</t>
+  </si>
+  <si>
+    <t>03.06.202671</t>
+  </si>
+  <si>
+    <t>03.06.202672</t>
+  </si>
+  <si>
+    <t>03.06.202673</t>
+  </si>
+  <si>
+    <t>03.06.202674</t>
+  </si>
+  <si>
+    <t>03.06.202675</t>
+  </si>
+  <si>
+    <t>03.06.202676</t>
+  </si>
+  <si>
+    <t>03.06.202677</t>
+  </si>
+  <si>
+    <t>03.06.202678</t>
+  </si>
+  <si>
+    <t>03.06.202679</t>
+  </si>
+  <si>
+    <t>03.06.202680</t>
+  </si>
+  <si>
+    <t>03.06.202681</t>
+  </si>
+  <si>
+    <t>03.06.202682</t>
+  </si>
+  <si>
+    <t>03.06.202683</t>
+  </si>
+  <si>
+    <t>03.06.202684</t>
+  </si>
+  <si>
+    <t>03.06.202685</t>
+  </si>
+  <si>
+    <t>03.06.202686</t>
+  </si>
+  <si>
+    <t>03.06.202687</t>
+  </si>
+  <si>
+    <t>03.06.202688</t>
+  </si>
+  <si>
+    <t>03.06.202689</t>
+  </si>
+  <si>
+    <t>03.06.202690</t>
+  </si>
+  <si>
+    <t>03.06.202691</t>
+  </si>
+  <si>
+    <t>03.06.202692</t>
+  </si>
+  <si>
+    <t>03.06.202693</t>
+  </si>
+  <si>
+    <t>03.06.202694</t>
+  </si>
+  <si>
+    <t>03.06.202695</t>
+  </si>
+  <si>
+    <t>03.06.202696</t>
   </si>
 </sst>
 </file>
@@ -963,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +2134,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B2">
-        <v>5195</v>
+        <v>5151</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +2148,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B3">
-        <v>5147</v>
+        <v>5071</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +2162,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B4">
-        <v>5091</v>
+        <v>5037</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +2176,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B5">
-        <v>5058</v>
+        <v>5051</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +2190,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B6">
-        <v>4985</v>
+        <v>5006</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +2204,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B7">
-        <v>5004</v>
+        <v>4980</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +2218,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B8">
-        <v>4955</v>
+        <v>5045</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +2232,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B9">
-        <v>4950</v>
+        <v>4884</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +2246,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B10">
-        <v>4909</v>
+        <v>5049</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +2260,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B11">
-        <v>4949</v>
+        <v>4999</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +2274,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B12">
-        <v>4947</v>
+        <v>5002</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +2288,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B13">
-        <v>4940</v>
+        <v>5021</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +2302,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B14">
-        <v>5133</v>
+        <v>5022</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +2316,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B15">
-        <v>5289</v>
+        <v>5055</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +2330,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B16">
-        <v>5286</v>
+        <v>5065</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +2344,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B17">
-        <v>5272</v>
+        <v>5048</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +2358,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B18">
-        <v>5296</v>
+        <v>5029</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +2372,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B19">
-        <v>5279</v>
+        <v>5010</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +2386,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B20">
-        <v>5300</v>
+        <v>5019</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +2400,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B21">
-        <v>5288</v>
+        <v>5046</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +2414,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B22">
-        <v>5118</v>
+        <v>5026</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +2428,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B23">
-        <v>5247</v>
+        <v>5093</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +2442,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B24">
-        <v>5313</v>
+        <v>5136</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +2456,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B25">
-        <v>5417</v>
+        <v>5189</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +2470,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B26">
-        <v>5580</v>
+        <v>5354</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +2484,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B27">
-        <v>5705</v>
+        <v>5414</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +2498,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B28">
-        <v>5686</v>
+        <v>5393</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +2512,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B29">
-        <v>5706</v>
+        <v>5389</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +2526,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B30">
-        <v>5654</v>
+        <v>5380</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +2540,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B31">
-        <v>5694</v>
+        <v>5267</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +2554,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B32">
-        <v>5667</v>
+        <v>5126</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +2568,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B33">
-        <v>5557</v>
+        <v>5025</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +2582,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B34">
-        <v>5408</v>
+        <v>4847</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +2596,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B35">
-        <v>5337</v>
+        <v>4741</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +2610,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B36">
-        <v>5162</v>
+        <v>4626</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +2624,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B37">
-        <v>5053</v>
+        <v>4457</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +2638,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B38">
-        <v>4718</v>
+        <v>4328</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +2652,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B39">
-        <v>4617</v>
+        <v>4260</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +2666,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B40">
-        <v>4444</v>
+        <v>4041</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +2680,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B41">
-        <v>4274</v>
+        <v>4012</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +2694,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B42">
-        <v>4322</v>
+        <v>3878</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +2708,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B43">
-        <v>4359</v>
+        <v>3800</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +2722,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B44">
-        <v>4303</v>
+        <v>3765</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +2736,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B45">
-        <v>4161</v>
+        <v>3764</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +2750,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B46">
-        <v>4010</v>
+        <v>3815</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +2764,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B47">
-        <v>4067</v>
+        <v>3761</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +2778,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B48">
-        <v>4110</v>
+        <v>3727</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +2792,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B49">
-        <v>4200</v>
+        <v>3766</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +2806,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B50">
-        <v>4194</v>
+        <v>3804</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +2820,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B51">
-        <v>4205</v>
+        <v>3847</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +2834,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B52">
-        <v>4157</v>
+        <v>3826</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +2848,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B53">
-        <v>4229</v>
+        <v>3810</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +2862,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B54">
-        <v>4131</v>
+        <v>3944</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +2876,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B55">
-        <v>4132</v>
+        <v>3971</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +2890,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B56">
-        <v>4228</v>
+        <v>3973</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +2904,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B57">
-        <v>4266</v>
+        <v>4043</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +2918,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B58">
-        <v>4273</v>
+        <v>3888</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +2932,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B59">
-        <v>4390</v>
+        <v>4014</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +2946,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B60">
-        <v>4391</v>
+        <v>4099</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +2960,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B61">
-        <v>4436</v>
+        <v>4185</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +2974,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B62">
-        <v>4470</v>
+        <v>4134</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +2988,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B63">
-        <v>4567</v>
+        <v>4189</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +3002,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B64">
-        <v>4709</v>
+        <v>4376</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +3016,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B65">
-        <v>4842</v>
+        <v>4451</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +3030,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B66">
-        <v>5176</v>
+        <v>4578</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +3044,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B67">
-        <v>5252</v>
+        <v>4673</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +3058,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B68">
-        <v>5421</v>
+        <v>4855</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +3072,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B69">
-        <v>5623</v>
+        <v>5083</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +3086,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B70">
-        <v>5827</v>
+        <v>5440</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +3100,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B71">
-        <v>5811</v>
+        <v>5448</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +3114,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B72">
-        <v>5888</v>
+        <v>5645</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +3128,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B73">
-        <v>5948</v>
+        <v>5753</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +3142,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B74">
-        <v>6134</v>
+        <v>5962</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +3156,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B75">
-        <v>6269</v>
+        <v>5922</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +3170,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B76">
-        <v>6365</v>
+        <v>6077</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +3184,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B77">
-        <v>6454</v>
+        <v>6202</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +3198,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B78">
-        <v>6450</v>
+        <v>6225</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +3212,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B79">
-        <v>6546</v>
+        <v>6313</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +3226,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B80">
-        <v>6645</v>
+        <v>6405</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +3240,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B81">
-        <v>6686</v>
+        <v>6441</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +3254,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B82">
-        <v>6679</v>
+        <v>6445</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +3268,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B83">
-        <v>6773</v>
+        <v>6550</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +3282,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B84">
-        <v>6767</v>
+        <v>6574</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +3296,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B85">
-        <v>6688</v>
+        <v>6536</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +3310,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B86">
-        <v>6484</v>
+        <v>6364</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +3324,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B87">
-        <v>6404</v>
+        <v>6251</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +3338,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B88">
-        <v>6253</v>
+        <v>6138</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +3352,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B89">
-        <v>6177</v>
+        <v>5966</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +3366,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B90">
-        <v>6020</v>
+        <v>5861</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +3380,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B91">
-        <v>5924</v>
+        <v>5770</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +3394,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B92">
-        <v>5733</v>
+        <v>5657</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +3408,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B93">
-        <v>5632</v>
+        <v>5549</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +3422,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B94">
-        <v>5444</v>
+        <v>5357</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +3436,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B95">
-        <v>5333</v>
+        <v>5220</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +3450,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B96">
-        <v>5263</v>
+        <v>5186</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +3464,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B97">
-        <v>5247</v>
+        <v>5067</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +3478,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B98">
-        <v>5151</v>
+        <v>4968</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +3492,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46171.01041666666</v>
+        <v>46172.01041666666</v>
       </c>
       <c r="B99">
-        <v>5071</v>
+        <v>4953</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +3506,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46171.02083333334</v>
+        <v>46172.02083333334</v>
       </c>
       <c r="B100">
-        <v>5037</v>
+        <v>4878</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +3520,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46171.03125</v>
+        <v>46172.03125</v>
       </c>
       <c r="B101">
-        <v>5051</v>
+        <v>4828</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +3534,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46171.04166666666</v>
+        <v>46172.04166666666</v>
       </c>
       <c r="B102">
-        <v>5006</v>
+        <v>4805</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +3548,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46171.05208333334</v>
+        <v>46172.05208333334</v>
       </c>
       <c r="B103">
-        <v>4980</v>
+        <v>4789</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +3562,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46171.0625</v>
+        <v>46172.0625</v>
       </c>
       <c r="B104">
-        <v>5045</v>
+        <v>4804</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +3576,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46171.07291666666</v>
+        <v>46172.07291666666</v>
       </c>
       <c r="B105">
-        <v>4884</v>
+        <v>4787</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +3590,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46171.08333333334</v>
+        <v>46172.08333333334</v>
       </c>
       <c r="B106">
-        <v>5049</v>
+        <v>4803</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +3604,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46171.09375</v>
+        <v>46172.09375</v>
       </c>
       <c r="B107">
-        <v>4999</v>
+        <v>4799</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +3618,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46171.10416666666</v>
+        <v>46172.10416666666</v>
       </c>
       <c r="B108">
-        <v>5002</v>
+        <v>4780</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +3632,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46171.11458333334</v>
+        <v>46172.11458333334</v>
       </c>
       <c r="B109">
-        <v>5021</v>
+        <v>4756</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +3646,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46171.125</v>
+        <v>46172.125</v>
       </c>
       <c r="B110">
-        <v>5022</v>
+        <v>4626</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +3660,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46171.13541666666</v>
+        <v>46172.13541666666</v>
       </c>
       <c r="B111">
-        <v>5055</v>
+        <v>4644</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +3674,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46171.14583333334</v>
+        <v>46172.14583333334</v>
       </c>
       <c r="B112">
-        <v>5065</v>
+        <v>4702</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +3688,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46171.15625</v>
+        <v>46172.15625</v>
       </c>
       <c r="B113">
-        <v>5048</v>
+        <v>4669</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +3702,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46171.16666666666</v>
+        <v>46172.16666666666</v>
       </c>
       <c r="B114">
-        <v>5029</v>
+        <v>4665</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +3716,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46171.17708333334</v>
+        <v>46172.17708333334</v>
       </c>
       <c r="B115">
-        <v>5010</v>
+        <v>4656</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +3730,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46171.1875</v>
+        <v>46172.1875</v>
       </c>
       <c r="B116">
-        <v>5019</v>
+        <v>4599</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +3744,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46171.19791666666</v>
+        <v>46172.19791666666</v>
       </c>
       <c r="B117">
-        <v>5046</v>
+        <v>4561</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +3758,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46171.20833333334</v>
+        <v>46172.20833333334</v>
       </c>
       <c r="B118">
-        <v>5026</v>
+        <v>4575</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +3772,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46171.21875</v>
+        <v>46172.21875</v>
       </c>
       <c r="B119">
-        <v>5093</v>
+        <v>4576</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +3786,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46171.22916666666</v>
+        <v>46172.22916666666</v>
       </c>
       <c r="B120">
-        <v>5136</v>
+        <v>4561</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +3800,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46171.23958333334</v>
+        <v>46172.23958333334</v>
       </c>
       <c r="B121">
-        <v>5189</v>
+        <v>4594</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +3814,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46171.25</v>
+        <v>46172.25</v>
       </c>
       <c r="B122">
-        <v>5354</v>
+        <v>4611</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +3828,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46171.26041666666</v>
+        <v>46172.26041666666</v>
       </c>
       <c r="B123">
-        <v>5414</v>
+        <v>4649</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +3842,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46171.27083333334</v>
+        <v>46172.27083333334</v>
       </c>
       <c r="B124">
-        <v>5393</v>
+        <v>4685</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +3856,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46171.28125</v>
+        <v>46172.28125</v>
       </c>
       <c r="B125">
-        <v>5389</v>
+        <v>4643</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +3870,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46171.29166666666</v>
+        <v>46172.29166666666</v>
       </c>
       <c r="B126">
-        <v>5380</v>
+        <v>4619</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +3884,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46171.30208333334</v>
+        <v>46172.30208333334</v>
       </c>
       <c r="B127">
-        <v>5267</v>
+        <v>4567</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +3898,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46171.3125</v>
+        <v>46172.3125</v>
       </c>
       <c r="B128">
-        <v>5126</v>
+        <v>4522</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +3912,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46171.32291666666</v>
+        <v>46172.32291666666</v>
       </c>
       <c r="B129">
-        <v>5025</v>
+        <v>4403</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +3926,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46171.33333333334</v>
+        <v>46172.33333333334</v>
       </c>
       <c r="B130">
-        <v>4847</v>
+        <v>4329</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +3940,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46171.34375</v>
+        <v>46172.34375</v>
       </c>
       <c r="B131">
-        <v>4741</v>
+        <v>4292</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +3954,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46171.35416666666</v>
+        <v>46172.35416666666</v>
       </c>
       <c r="B132">
-        <v>4626</v>
+        <v>4203</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +3968,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46171.36458333334</v>
+        <v>46172.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>4158</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +3982,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46171.375</v>
+        <v>46172.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>4064</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +3996,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46171.38541666666</v>
+        <v>46172.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>3957</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +4010,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46171.39583333334</v>
+        <v>46172.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>3928</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +4024,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46171.40625</v>
+        <v>46172.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>3945</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +4038,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46171.41666666666</v>
+        <v>46172.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>3947</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +4052,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46171.42708333334</v>
+        <v>46172.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>3889</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +4066,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46171.4375</v>
+        <v>46172.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>3869</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +4080,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46171.44791666666</v>
+        <v>46172.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>3847</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +4094,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46171.45833333334</v>
+        <v>46172.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>4064</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +4108,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46171.46875</v>
+        <v>46172.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>4074</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +4122,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46171.47916666666</v>
+        <v>46172.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>4067</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +4136,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46171.48958333334</v>
+        <v>46172.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>4033</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +4150,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46171.5</v>
+        <v>46172.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>3969</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +4164,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46171.51041666666</v>
+        <v>46172.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>3954</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +4178,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46171.52083333334</v>
+        <v>46172.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>3909</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +4192,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46171.53125</v>
+        <v>46172.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>3873</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,10 +4206,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46171.54166666666</v>
+        <v>46172.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="C150">
         <v>53</v>
@@ -3068,10 +4220,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46171.55208333334</v>
+        <v>46172.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>3818</v>
       </c>
       <c r="C151">
         <v>54</v>
@@ -3082,10 +4234,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46171.5625</v>
+        <v>46172.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>3763</v>
       </c>
       <c r="C152">
         <v>55</v>
@@ -3096,10 +4248,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46171.57291666666</v>
+        <v>46172.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>3751</v>
       </c>
       <c r="C153">
         <v>56</v>
@@ -3110,10 +4262,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46171.58333333334</v>
+        <v>46172.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>3719</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -3124,10 +4276,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46171.59375</v>
+        <v>46172.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="C155">
         <v>58</v>
@@ -3138,10 +4290,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46171.60416666666</v>
+        <v>46172.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>3862</v>
       </c>
       <c r="C156">
         <v>59</v>
@@ -3152,10 +4304,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46171.61458333334</v>
+        <v>46172.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>3878</v>
       </c>
       <c r="C157">
         <v>60</v>
@@ -3166,10 +4318,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46171.625</v>
+        <v>46172.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>3952</v>
       </c>
       <c r="C158">
         <v>61</v>
@@ -3180,10 +4332,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46171.63541666666</v>
+        <v>46172.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>3994</v>
       </c>
       <c r="C159">
         <v>62</v>
@@ -3194,10 +4346,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46171.64583333334</v>
+        <v>46172.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>4007</v>
       </c>
       <c r="C160">
         <v>63</v>
@@ -3208,10 +4360,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46171.65625</v>
+        <v>46172.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="C161">
         <v>64</v>
@@ -3222,10 +4374,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46171.66666666666</v>
+        <v>46172.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>4203</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -3236,10 +4388,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46171.67708333334</v>
+        <v>46172.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>4247</v>
       </c>
       <c r="C163">
         <v>66</v>
@@ -3250,10 +4402,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46171.6875</v>
+        <v>46172.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>4344</v>
       </c>
       <c r="C164">
         <v>67</v>
@@ -3264,10 +4416,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46171.69791666666</v>
+        <v>46172.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>4422</v>
       </c>
       <c r="C165">
         <v>68</v>
@@ -3278,10 +4430,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46171.70833333334</v>
+        <v>46172.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>4510</v>
       </c>
       <c r="C166">
         <v>69</v>
@@ -3292,10 +4444,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46171.71875</v>
+        <v>46172.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>4643</v>
       </c>
       <c r="C167">
         <v>70</v>
@@ -3306,10 +4458,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46171.72916666666</v>
+        <v>46172.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>4878</v>
       </c>
       <c r="C168">
         <v>71</v>
@@ -3320,10 +4472,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46171.73958333334</v>
+        <v>46172.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>5055</v>
       </c>
       <c r="C169">
         <v>72</v>
@@ -3334,10 +4486,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46171.75</v>
+        <v>46172.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>5320</v>
       </c>
       <c r="C170">
         <v>73</v>
@@ -3348,10 +4500,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46171.76041666666</v>
+        <v>46172.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>5496</v>
       </c>
       <c r="C171">
         <v>74</v>
@@ -3362,10 +4514,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46171.77083333334</v>
+        <v>46172.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>5651</v>
       </c>
       <c r="C172">
         <v>75</v>
@@ -3376,10 +4528,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46171.78125</v>
+        <v>46172.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>5724</v>
       </c>
       <c r="C173">
         <v>76</v>
@@ -3390,10 +4542,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46171.79166666666</v>
+        <v>46172.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>5781</v>
       </c>
       <c r="C174">
         <v>77</v>
@@ -3404,10 +4556,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46171.80208333334</v>
+        <v>46172.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>5803</v>
       </c>
       <c r="C175">
         <v>78</v>
@@ -3418,10 +4570,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46171.8125</v>
+        <v>46172.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>5901</v>
       </c>
       <c r="C176">
         <v>79</v>
@@ -3432,10 +4584,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46171.82291666666</v>
+        <v>46172.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>5971</v>
       </c>
       <c r="C177">
         <v>80</v>
@@ -3446,10 +4598,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46171.83333333334</v>
+        <v>46172.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>6016</v>
       </c>
       <c r="C178">
         <v>81</v>
@@ -3460,10 +4612,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46171.84375</v>
+        <v>46172.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>6076</v>
       </c>
       <c r="C179">
         <v>82</v>
@@ -3474,10 +4626,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46171.85416666666</v>
+        <v>46172.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>6042</v>
       </c>
       <c r="C180">
         <v>83</v>
@@ -3488,10 +4640,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46171.86458333334</v>
+        <v>46172.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>6020</v>
       </c>
       <c r="C181">
         <v>84</v>
@@ -3502,10 +4654,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46171.875</v>
+        <v>46172.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>5911</v>
       </c>
       <c r="C182">
         <v>85</v>
@@ -3516,10 +4668,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46171.88541666666</v>
+        <v>46172.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>5819</v>
       </c>
       <c r="C183">
         <v>86</v>
@@ -3530,10 +4682,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46171.89583333334</v>
+        <v>46172.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>5695</v>
       </c>
       <c r="C184">
         <v>87</v>
@@ -3544,10 +4696,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46171.90625</v>
+        <v>46172.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>5585</v>
       </c>
       <c r="C185">
         <v>88</v>
@@ -3558,10 +4710,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46171.91666666666</v>
+        <v>46172.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>5495</v>
       </c>
       <c r="C186">
         <v>89</v>
@@ -3572,10 +4724,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46171.92708333334</v>
+        <v>46172.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>5365</v>
       </c>
       <c r="C187">
         <v>90</v>
@@ -3586,10 +4738,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46171.9375</v>
+        <v>46172.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>5263</v>
       </c>
       <c r="C188">
         <v>91</v>
@@ -3600,10 +4752,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46171.94791666666</v>
+        <v>46172.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>5102</v>
       </c>
       <c r="C189">
         <v>92</v>
@@ -3614,10 +4766,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46171.95833333334</v>
+        <v>46172.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>5122</v>
       </c>
       <c r="C190">
         <v>93</v>
@@ -3628,10 +4780,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46171.96875</v>
+        <v>46172.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>5066</v>
       </c>
       <c r="C191">
         <v>94</v>
@@ -3642,10 +4794,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46171.97916666666</v>
+        <v>46172.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>5021</v>
       </c>
       <c r="C192">
         <v>95</v>
@@ -3656,16 +4808,5392 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46171.98958333334</v>
+        <v>46172.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>4967</v>
       </c>
       <c r="C193">
         <v>96</v>
       </c>
       <c r="D193" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B194">
+        <v>4836</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="2">
+        <v>46173.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>4767</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="2">
+        <v>46173.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>4710</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="2">
+        <v>46173.03125</v>
+      </c>
+      <c r="B197">
+        <v>4669</v>
+      </c>
+      <c r="C197">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="2">
+        <v>46173.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>4657</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="2">
+        <v>46173.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>4573</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="2">
+        <v>46173.0625</v>
+      </c>
+      <c r="B200">
+        <v>4399</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="2">
+        <v>46173.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>4352</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="2">
+        <v>46173.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>4380</v>
+      </c>
+      <c r="C202">
+        <v>9</v>
+      </c>
+      <c r="D202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="2">
+        <v>46173.09375</v>
+      </c>
+      <c r="B203">
+        <v>4293</v>
+      </c>
+      <c r="C203">
+        <v>10</v>
+      </c>
+      <c r="D203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="2">
+        <v>46173.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4243</v>
+      </c>
+      <c r="C204">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="2">
+        <v>46173.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>4240</v>
+      </c>
+      <c r="C205">
+        <v>12</v>
+      </c>
+      <c r="D205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="2">
+        <v>46173.125</v>
+      </c>
+      <c r="B206">
+        <v>4292</v>
+      </c>
+      <c r="C206">
+        <v>13</v>
+      </c>
+      <c r="D206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="2">
+        <v>46173.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>4288</v>
+      </c>
+      <c r="C207">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="2">
+        <v>46173.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4306</v>
+      </c>
+      <c r="C208">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="2">
+        <v>46173.15625</v>
+      </c>
+      <c r="B209">
+        <v>4263</v>
+      </c>
+      <c r="C209">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="2">
+        <v>46173.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>4446</v>
+      </c>
+      <c r="C210">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="2">
+        <v>46173.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>4420</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="2">
+        <v>46173.1875</v>
+      </c>
+      <c r="B212">
+        <v>4349</v>
+      </c>
+      <c r="C212">
+        <v>19</v>
+      </c>
+      <c r="D212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="2">
+        <v>46173.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>4287</v>
+      </c>
+      <c r="C213">
+        <v>20</v>
+      </c>
+      <c r="D213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="2">
+        <v>46173.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4267</v>
+      </c>
+      <c r="C214">
+        <v>21</v>
+      </c>
+      <c r="D214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="2">
+        <v>46173.21875</v>
+      </c>
+      <c r="B215">
+        <v>4259</v>
+      </c>
+      <c r="C215">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="2">
+        <v>46173.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>4267</v>
+      </c>
+      <c r="C216">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="2">
+        <v>46173.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>4263</v>
+      </c>
+      <c r="C217">
+        <v>24</v>
+      </c>
+      <c r="D217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="2">
+        <v>46173.25</v>
+      </c>
+      <c r="B218">
+        <v>4266</v>
+      </c>
+      <c r="C218">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="2">
+        <v>46173.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>4213</v>
+      </c>
+      <c r="C219">
+        <v>26</v>
+      </c>
+      <c r="D219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="2">
+        <v>46173.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>4083</v>
+      </c>
+      <c r="C220">
+        <v>27</v>
+      </c>
+      <c r="D220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="2">
+        <v>46173.28125</v>
+      </c>
+      <c r="B221">
+        <v>4098</v>
+      </c>
+      <c r="C221">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="2">
+        <v>46173.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>4050</v>
+      </c>
+      <c r="C222">
+        <v>29</v>
+      </c>
+      <c r="D222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="2">
+        <v>46173.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>3996</v>
+      </c>
+      <c r="C223">
+        <v>30</v>
+      </c>
+      <c r="D223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="2">
+        <v>46173.3125</v>
+      </c>
+      <c r="B224">
+        <v>3963</v>
+      </c>
+      <c r="C224">
+        <v>31</v>
+      </c>
+      <c r="D224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="2">
+        <v>46173.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>3922</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="2">
+        <v>46173.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>3905</v>
+      </c>
+      <c r="C226">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="2">
+        <v>46173.34375</v>
+      </c>
+      <c r="B227">
+        <v>3914</v>
+      </c>
+      <c r="C227">
+        <v>34</v>
+      </c>
+      <c r="D227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="2">
+        <v>46173.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>3797</v>
+      </c>
+      <c r="C228">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="2">
+        <v>46173.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>3673</v>
+      </c>
+      <c r="C229">
+        <v>36</v>
+      </c>
+      <c r="D229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="2">
+        <v>46173.375</v>
+      </c>
+      <c r="B230">
+        <v>3706</v>
+      </c>
+      <c r="C230">
+        <v>37</v>
+      </c>
+      <c r="D230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="2">
+        <v>46173.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>3654</v>
+      </c>
+      <c r="C231">
+        <v>38</v>
+      </c>
+      <c r="D231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="2">
+        <v>46173.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3558</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="2">
+        <v>46173.40625</v>
+      </c>
+      <c r="B233">
+        <v>3563</v>
+      </c>
+      <c r="C233">
+        <v>40</v>
+      </c>
+      <c r="D233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="2">
+        <v>46173.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>41</v>
+      </c>
+      <c r="D234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="2">
+        <v>46173.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>3490</v>
+      </c>
+      <c r="C235">
+        <v>42</v>
+      </c>
+      <c r="D235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="2">
+        <v>46173.4375</v>
+      </c>
+      <c r="B236">
+        <v>3400</v>
+      </c>
+      <c r="C236">
+        <v>43</v>
+      </c>
+      <c r="D236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="2">
+        <v>46173.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>3329</v>
+      </c>
+      <c r="C237">
+        <v>44</v>
+      </c>
+      <c r="D237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="2">
+        <v>46173.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>3131</v>
+      </c>
+      <c r="C238">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="2">
+        <v>46173.46875</v>
+      </c>
+      <c r="B239">
+        <v>3042</v>
+      </c>
+      <c r="C239">
+        <v>46</v>
+      </c>
+      <c r="D239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="2">
+        <v>46173.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>3027</v>
+      </c>
+      <c r="C240">
+        <v>47</v>
+      </c>
+      <c r="D240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="2">
+        <v>46173.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>3067</v>
+      </c>
+      <c r="C241">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="2">
+        <v>46173.5</v>
+      </c>
+      <c r="B242">
+        <v>3040</v>
+      </c>
+      <c r="C242">
+        <v>49</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="2">
+        <v>46173.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>3083</v>
+      </c>
+      <c r="C243">
+        <v>50</v>
+      </c>
+      <c r="D243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="2">
+        <v>46173.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>3089</v>
+      </c>
+      <c r="C244">
+        <v>51</v>
+      </c>
+      <c r="D244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="2">
+        <v>46173.53125</v>
+      </c>
+      <c r="B245">
+        <v>3039</v>
+      </c>
+      <c r="C245">
+        <v>52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="2">
+        <v>46173.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>3144</v>
+      </c>
+      <c r="C246">
+        <v>53</v>
+      </c>
+      <c r="D246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="2">
+        <v>46173.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>3154</v>
+      </c>
+      <c r="C247">
+        <v>54</v>
+      </c>
+      <c r="D247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="2">
+        <v>46173.5625</v>
+      </c>
+      <c r="B248">
+        <v>3168</v>
+      </c>
+      <c r="C248">
+        <v>55</v>
+      </c>
+      <c r="D248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="2">
+        <v>46173.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>3178</v>
+      </c>
+      <c r="C249">
+        <v>56</v>
+      </c>
+      <c r="D249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="2">
+        <v>46173.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>3254</v>
+      </c>
+      <c r="C250">
+        <v>57</v>
+      </c>
+      <c r="D250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="2">
+        <v>46173.59375</v>
+      </c>
+      <c r="B251">
+        <v>3338</v>
+      </c>
+      <c r="C251">
+        <v>58</v>
+      </c>
+      <c r="D251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="2">
+        <v>46173.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>3424</v>
+      </c>
+      <c r="C252">
+        <v>59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="2">
+        <v>46173.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>3545</v>
+      </c>
+      <c r="C253">
+        <v>60</v>
+      </c>
+      <c r="D253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="2">
+        <v>46173.625</v>
+      </c>
+      <c r="B254">
+        <v>3629</v>
+      </c>
+      <c r="C254">
+        <v>61</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="2">
+        <v>46173.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>3573</v>
+      </c>
+      <c r="C255">
+        <v>62</v>
+      </c>
+      <c r="D255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="2">
+        <v>46173.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>63</v>
+      </c>
+      <c r="D256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="2">
+        <v>46173.65625</v>
+      </c>
+      <c r="B257">
+        <v>3689</v>
+      </c>
+      <c r="C257">
+        <v>64</v>
+      </c>
+      <c r="D257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="2">
+        <v>46173.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>3713</v>
+      </c>
+      <c r="C258">
+        <v>65</v>
+      </c>
+      <c r="D258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="2">
+        <v>46173.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>3806</v>
+      </c>
+      <c r="C259">
+        <v>66</v>
+      </c>
+      <c r="D259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="2">
+        <v>46173.6875</v>
+      </c>
+      <c r="B260">
+        <v>4093</v>
+      </c>
+      <c r="C260">
+        <v>67</v>
+      </c>
+      <c r="D260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="2">
+        <v>46173.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>4289</v>
+      </c>
+      <c r="C261">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="2">
+        <v>46173.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>4263</v>
+      </c>
+      <c r="C262">
+        <v>69</v>
+      </c>
+      <c r="D262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="2">
+        <v>46173.71875</v>
+      </c>
+      <c r="B263">
+        <v>4358</v>
+      </c>
+      <c r="C263">
+        <v>70</v>
+      </c>
+      <c r="D263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="2">
+        <v>46173.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>4555</v>
+      </c>
+      <c r="C264">
+        <v>71</v>
+      </c>
+      <c r="D264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="2">
+        <v>46173.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>4636</v>
+      </c>
+      <c r="C265">
+        <v>72</v>
+      </c>
+      <c r="D265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="2">
+        <v>46173.75</v>
+      </c>
+      <c r="B266">
+        <v>4692</v>
+      </c>
+      <c r="C266">
+        <v>73</v>
+      </c>
+      <c r="D266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="2">
+        <v>46173.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>4747</v>
+      </c>
+      <c r="C267">
+        <v>74</v>
+      </c>
+      <c r="D267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="2">
+        <v>46173.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>4873</v>
+      </c>
+      <c r="C268">
+        <v>75</v>
+      </c>
+      <c r="D268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="2">
+        <v>46173.78125</v>
+      </c>
+      <c r="B269">
+        <v>4930</v>
+      </c>
+      <c r="C269">
+        <v>76</v>
+      </c>
+      <c r="D269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="2">
+        <v>46173.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>4952</v>
+      </c>
+      <c r="C270">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="2">
+        <v>46173.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>5060</v>
+      </c>
+      <c r="C271">
+        <v>78</v>
+      </c>
+      <c r="D271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="2">
+        <v>46173.8125</v>
+      </c>
+      <c r="B272">
+        <v>5135</v>
+      </c>
+      <c r="C272">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="2">
+        <v>46173.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>5202</v>
+      </c>
+      <c r="C273">
+        <v>80</v>
+      </c>
+      <c r="D273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="2">
+        <v>46173.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>5245</v>
+      </c>
+      <c r="C274">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="2">
+        <v>46173.84375</v>
+      </c>
+      <c r="B275">
+        <v>5367</v>
+      </c>
+      <c r="C275">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="2">
+        <v>46173.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>5442</v>
+      </c>
+      <c r="C276">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="2">
+        <v>46173.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>5387</v>
+      </c>
+      <c r="C277">
+        <v>84</v>
+      </c>
+      <c r="D277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="2">
+        <v>46173.875</v>
+      </c>
+      <c r="B278">
+        <v>5324</v>
+      </c>
+      <c r="C278">
+        <v>85</v>
+      </c>
+      <c r="D278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="2">
+        <v>46173.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>5260</v>
+      </c>
+      <c r="C279">
+        <v>86</v>
+      </c>
+      <c r="D279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="2">
+        <v>46173.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>5189</v>
+      </c>
+      <c r="C280">
+        <v>87</v>
+      </c>
+      <c r="D280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="2">
+        <v>46173.90625</v>
+      </c>
+      <c r="B281">
+        <v>5083</v>
+      </c>
+      <c r="C281">
+        <v>88</v>
+      </c>
+      <c r="D281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="2">
+        <v>46173.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>5034</v>
+      </c>
+      <c r="C282">
+        <v>89</v>
+      </c>
+      <c r="D282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2">
+        <v>46173.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>4962</v>
+      </c>
+      <c r="C283">
+        <v>90</v>
+      </c>
+      <c r="D283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="2">
+        <v>46173.9375</v>
+      </c>
+      <c r="B284">
+        <v>4879</v>
+      </c>
+      <c r="C284">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="2">
+        <v>46173.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>4755</v>
+      </c>
+      <c r="C285">
+        <v>92</v>
+      </c>
+      <c r="D285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="2">
+        <v>46173.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>4678</v>
+      </c>
+      <c r="C286">
+        <v>93</v>
+      </c>
+      <c r="D286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="2">
+        <v>46173.96875</v>
+      </c>
+      <c r="B287">
+        <v>4550</v>
+      </c>
+      <c r="C287">
+        <v>94</v>
+      </c>
+      <c r="D287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="2">
+        <v>46173.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4516</v>
+      </c>
+      <c r="C288">
+        <v>95</v>
+      </c>
+      <c r="D288" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="2">
+        <v>46173.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4436</v>
+      </c>
+      <c r="C289">
+        <v>96</v>
+      </c>
+      <c r="D289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B290">
+        <v>4386</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="2">
+        <v>46174.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>4355</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="2">
+        <v>46174.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>4459</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="2">
+        <v>46174.03125</v>
+      </c>
+      <c r="B293">
+        <v>4420</v>
+      </c>
+      <c r="C293">
+        <v>4</v>
+      </c>
+      <c r="D293" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="2">
+        <v>46174.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>4378</v>
+      </c>
+      <c r="C294">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="2">
+        <v>46174.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>4327</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="2">
+        <v>46174.0625</v>
+      </c>
+      <c r="B296">
+        <v>4305</v>
+      </c>
+      <c r="C296">
+        <v>7</v>
+      </c>
+      <c r="D296" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="2">
+        <v>46174.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>4277</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="2">
+        <v>46174.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>4265</v>
+      </c>
+      <c r="C298">
+        <v>9</v>
+      </c>
+      <c r="D298" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="2">
+        <v>46174.09375</v>
+      </c>
+      <c r="B299">
+        <v>4254</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="2">
+        <v>46174.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>4235</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="2">
+        <v>46174.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>4245</v>
+      </c>
+      <c r="C301">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="2">
+        <v>46174.125</v>
+      </c>
+      <c r="B302">
+        <v>4263</v>
+      </c>
+      <c r="C302">
+        <v>13</v>
+      </c>
+      <c r="D302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="2">
+        <v>46174.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>4271</v>
+      </c>
+      <c r="C303">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="2">
+        <v>46174.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>4269</v>
+      </c>
+      <c r="C304">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="2">
+        <v>46174.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>16</v>
+      </c>
+      <c r="D305" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" s="2">
+        <v>46174.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>4180</v>
+      </c>
+      <c r="C306">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" s="2">
+        <v>46174.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>4143</v>
+      </c>
+      <c r="C307">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" s="2">
+        <v>46174.1875</v>
+      </c>
+      <c r="B308">
+        <v>4150</v>
+      </c>
+      <c r="C308">
+        <v>19</v>
+      </c>
+      <c r="D308" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="2">
+        <v>46174.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>4145</v>
+      </c>
+      <c r="C309">
+        <v>20</v>
+      </c>
+      <c r="D309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="2">
+        <v>46174.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>4161</v>
+      </c>
+      <c r="C310">
+        <v>21</v>
+      </c>
+      <c r="D310" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="2">
+        <v>46174.21875</v>
+      </c>
+      <c r="B311">
+        <v>4164</v>
+      </c>
+      <c r="C311">
+        <v>22</v>
+      </c>
+      <c r="D311" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" s="2">
+        <v>46174.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>4114</v>
+      </c>
+      <c r="C312">
+        <v>23</v>
+      </c>
+      <c r="D312" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" s="2">
+        <v>46174.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>4093</v>
+      </c>
+      <c r="C313">
+        <v>24</v>
+      </c>
+      <c r="D313" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" s="2">
+        <v>46174.25</v>
+      </c>
+      <c r="B314">
+        <v>4136</v>
+      </c>
+      <c r="C314">
+        <v>25</v>
+      </c>
+      <c r="D314" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" s="2">
+        <v>46174.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>4161</v>
+      </c>
+      <c r="C315">
+        <v>26</v>
+      </c>
+      <c r="D315" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" s="2">
+        <v>46174.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>4165</v>
+      </c>
+      <c r="C316">
+        <v>27</v>
+      </c>
+      <c r="D316" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" s="2">
+        <v>46174.28125</v>
+      </c>
+      <c r="B317">
+        <v>4148</v>
+      </c>
+      <c r="C317">
+        <v>28</v>
+      </c>
+      <c r="D317" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" s="2">
+        <v>46174.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>4174</v>
+      </c>
+      <c r="C318">
+        <v>29</v>
+      </c>
+      <c r="D318" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" s="2">
+        <v>46174.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>4176</v>
+      </c>
+      <c r="C319">
+        <v>30</v>
+      </c>
+      <c r="D319" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" s="2">
+        <v>46174.3125</v>
+      </c>
+      <c r="B320">
+        <v>4187</v>
+      </c>
+      <c r="C320">
+        <v>31</v>
+      </c>
+      <c r="D320" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="2">
+        <v>46174.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>4197</v>
+      </c>
+      <c r="C321">
+        <v>32</v>
+      </c>
+      <c r="D321" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="2">
+        <v>46174.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>4171</v>
+      </c>
+      <c r="C322">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="2">
+        <v>46174.34375</v>
+      </c>
+      <c r="B323">
+        <v>4139</v>
+      </c>
+      <c r="C323">
+        <v>34</v>
+      </c>
+      <c r="D323" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="2">
+        <v>46174.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>4144</v>
+      </c>
+      <c r="C324">
+        <v>35</v>
+      </c>
+      <c r="D324" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="2">
+        <v>46174.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>4058</v>
+      </c>
+      <c r="C325">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="2">
+        <v>46174.375</v>
+      </c>
+      <c r="B326">
+        <v>3969</v>
+      </c>
+      <c r="C326">
+        <v>37</v>
+      </c>
+      <c r="D326" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="2">
+        <v>46174.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>4014</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="2">
+        <v>46174.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>4006</v>
+      </c>
+      <c r="C328">
+        <v>39</v>
+      </c>
+      <c r="D328" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="2">
+        <v>46174.40625</v>
+      </c>
+      <c r="B329">
+        <v>4003</v>
+      </c>
+      <c r="C329">
+        <v>40</v>
+      </c>
+      <c r="D329" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="2">
+        <v>46174.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>3898</v>
+      </c>
+      <c r="C330">
+        <v>41</v>
+      </c>
+      <c r="D330" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="2">
+        <v>46174.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>3852</v>
+      </c>
+      <c r="C331">
+        <v>42</v>
+      </c>
+      <c r="D331" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="2">
+        <v>46174.4375</v>
+      </c>
+      <c r="B332">
+        <v>3780</v>
+      </c>
+      <c r="C332">
+        <v>43</v>
+      </c>
+      <c r="D332" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="2">
+        <v>46174.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>3658</v>
+      </c>
+      <c r="C333">
+        <v>44</v>
+      </c>
+      <c r="D333" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="2">
+        <v>46174.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>3505</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="2">
+        <v>46174.46875</v>
+      </c>
+      <c r="B335">
+        <v>3513</v>
+      </c>
+      <c r="C335">
+        <v>46</v>
+      </c>
+      <c r="D335" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="2">
+        <v>46174.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>3479</v>
+      </c>
+      <c r="C336">
+        <v>47</v>
+      </c>
+      <c r="D336" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" s="2">
+        <v>46174.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>3469</v>
+      </c>
+      <c r="C337">
+        <v>48</v>
+      </c>
+      <c r="D337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" s="2">
+        <v>46174.5</v>
+      </c>
+      <c r="B338">
+        <v>3512</v>
+      </c>
+      <c r="C338">
+        <v>49</v>
+      </c>
+      <c r="D338" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" s="2">
+        <v>46174.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>3532</v>
+      </c>
+      <c r="C339">
+        <v>50</v>
+      </c>
+      <c r="D339" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" s="2">
+        <v>46174.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>3586</v>
+      </c>
+      <c r="C340">
+        <v>51</v>
+      </c>
+      <c r="D340" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" s="2">
+        <v>46174.53125</v>
+      </c>
+      <c r="B341">
+        <v>3655</v>
+      </c>
+      <c r="C341">
+        <v>52</v>
+      </c>
+      <c r="D341" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342" s="2">
+        <v>46174.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>3713</v>
+      </c>
+      <c r="C342">
+        <v>53</v>
+      </c>
+      <c r="D342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343" s="2">
+        <v>46174.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>3733</v>
+      </c>
+      <c r="C343">
+        <v>54</v>
+      </c>
+      <c r="D343" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344" s="2">
+        <v>46174.5625</v>
+      </c>
+      <c r="B344">
+        <v>3801</v>
+      </c>
+      <c r="C344">
+        <v>55</v>
+      </c>
+      <c r="D344" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345" s="2">
+        <v>46174.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>3854</v>
+      </c>
+      <c r="C345">
+        <v>56</v>
+      </c>
+      <c r="D345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346" s="2">
+        <v>46174.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>3911</v>
+      </c>
+      <c r="C346">
+        <v>57</v>
+      </c>
+      <c r="D346" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347" s="2">
+        <v>46174.59375</v>
+      </c>
+      <c r="B347">
+        <v>3906</v>
+      </c>
+      <c r="C347">
+        <v>58</v>
+      </c>
+      <c r="D347" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348" s="2">
+        <v>46174.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>3938</v>
+      </c>
+      <c r="C348">
+        <v>59</v>
+      </c>
+      <c r="D348" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349" s="2">
+        <v>46174.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>4074</v>
+      </c>
+      <c r="C349">
+        <v>60</v>
+      </c>
+      <c r="D349" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350" s="2">
+        <v>46174.625</v>
+      </c>
+      <c r="B350">
+        <v>4214</v>
+      </c>
+      <c r="C350">
+        <v>61</v>
+      </c>
+      <c r="D350" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351" s="2">
+        <v>46174.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>4277</v>
+      </c>
+      <c r="C351">
+        <v>62</v>
+      </c>
+      <c r="D351" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352" s="2">
+        <v>46174.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>4319</v>
+      </c>
+      <c r="C352">
+        <v>63</v>
+      </c>
+      <c r="D352" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353" s="2">
+        <v>46174.65625</v>
+      </c>
+      <c r="B353">
+        <v>4376</v>
+      </c>
+      <c r="C353">
+        <v>64</v>
+      </c>
+      <c r="D353" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354" s="2">
+        <v>46174.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>4509</v>
+      </c>
+      <c r="C354">
+        <v>65</v>
+      </c>
+      <c r="D354" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355" s="2">
+        <v>46174.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>4577</v>
+      </c>
+      <c r="C355">
+        <v>66</v>
+      </c>
+      <c r="D355" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356" s="2">
+        <v>46174.6875</v>
+      </c>
+      <c r="B356">
+        <v>4571</v>
+      </c>
+      <c r="C356">
+        <v>67</v>
+      </c>
+      <c r="D356" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357" s="2">
+        <v>46174.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>4664</v>
+      </c>
+      <c r="C357">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358" s="2">
+        <v>46174.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>4682</v>
+      </c>
+      <c r="C358">
+        <v>69</v>
+      </c>
+      <c r="D358" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359" s="2">
+        <v>46174.71875</v>
+      </c>
+      <c r="B359">
+        <v>4958</v>
+      </c>
+      <c r="C359">
+        <v>70</v>
+      </c>
+      <c r="D359" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360" s="2">
+        <v>46174.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>5088</v>
+      </c>
+      <c r="C360">
+        <v>71</v>
+      </c>
+      <c r="D360" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361" s="2">
+        <v>46174.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>5034</v>
+      </c>
+      <c r="C361">
+        <v>72</v>
+      </c>
+      <c r="D361" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362" s="2">
+        <v>46174.75</v>
+      </c>
+      <c r="B362">
+        <v>5123</v>
+      </c>
+      <c r="C362">
+        <v>73</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363" s="2">
+        <v>46174.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>5223</v>
+      </c>
+      <c r="C363">
+        <v>74</v>
+      </c>
+      <c r="D363" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364" s="2">
+        <v>46174.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>5319</v>
+      </c>
+      <c r="C364">
+        <v>75</v>
+      </c>
+      <c r="D364" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365" s="2">
+        <v>46174.78125</v>
+      </c>
+      <c r="B365">
+        <v>5425</v>
+      </c>
+      <c r="C365">
+        <v>76</v>
+      </c>
+      <c r="D365" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366" s="2">
+        <v>46174.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>5463</v>
+      </c>
+      <c r="C366">
+        <v>77</v>
+      </c>
+      <c r="D366" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367" s="2">
+        <v>46174.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>5512</v>
+      </c>
+      <c r="C367">
+        <v>78</v>
+      </c>
+      <c r="D367" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368" s="2">
+        <v>46174.8125</v>
+      </c>
+      <c r="B368">
+        <v>5568</v>
+      </c>
+      <c r="C368">
+        <v>79</v>
+      </c>
+      <c r="D368" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369" s="2">
+        <v>46174.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>5615</v>
+      </c>
+      <c r="C369">
+        <v>80</v>
+      </c>
+      <c r="D369" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370" s="2">
+        <v>46174.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>5669</v>
+      </c>
+      <c r="C370">
+        <v>81</v>
+      </c>
+      <c r="D370" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" s="2">
+        <v>46174.84375</v>
+      </c>
+      <c r="B371">
+        <v>5708</v>
+      </c>
+      <c r="C371">
+        <v>82</v>
+      </c>
+      <c r="D371" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372" s="2">
+        <v>46174.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>5719</v>
+      </c>
+      <c r="C372">
+        <v>83</v>
+      </c>
+      <c r="D372" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" s="2">
+        <v>46174.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>5686</v>
+      </c>
+      <c r="C373">
+        <v>84</v>
+      </c>
+      <c r="D373" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" s="2">
+        <v>46174.875</v>
+      </c>
+      <c r="B374">
+        <v>5574</v>
+      </c>
+      <c r="C374">
+        <v>85</v>
+      </c>
+      <c r="D374" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375" s="2">
+        <v>46174.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>5458</v>
+      </c>
+      <c r="C375">
+        <v>86</v>
+      </c>
+      <c r="D375" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376" s="2">
+        <v>46174.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>5359</v>
+      </c>
+      <c r="C376">
+        <v>87</v>
+      </c>
+      <c r="D376" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377" s="2">
+        <v>46174.90625</v>
+      </c>
+      <c r="B377">
+        <v>5279</v>
+      </c>
+      <c r="C377">
+        <v>88</v>
+      </c>
+      <c r="D377" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378" s="2">
+        <v>46174.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>5276</v>
+      </c>
+      <c r="C378">
+        <v>89</v>
+      </c>
+      <c r="D378" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379" s="2">
+        <v>46174.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>5169</v>
+      </c>
+      <c r="C379">
+        <v>90</v>
+      </c>
+      <c r="D379" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380" s="2">
+        <v>46174.9375</v>
+      </c>
+      <c r="B380">
+        <v>5018</v>
+      </c>
+      <c r="C380">
+        <v>91</v>
+      </c>
+      <c r="D380" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381" s="2">
+        <v>46174.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>4902</v>
+      </c>
+      <c r="C381">
+        <v>92</v>
+      </c>
+      <c r="D381" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382" s="2">
+        <v>46174.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>4689</v>
+      </c>
+      <c r="C382">
+        <v>93</v>
+      </c>
+      <c r="D382" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383" s="2">
+        <v>46174.96875</v>
+      </c>
+      <c r="B383">
+        <v>4607</v>
+      </c>
+      <c r="C383">
+        <v>94</v>
+      </c>
+      <c r="D383" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384" s="2">
+        <v>46174.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>4556</v>
+      </c>
+      <c r="C384">
+        <v>95</v>
+      </c>
+      <c r="D384" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385" s="2">
+        <v>46174.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>4519</v>
+      </c>
+      <c r="C385">
+        <v>96</v>
+      </c>
+      <c r="D385" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B386">
+        <v>4470</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387" s="2">
+        <v>46175.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>4427</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388" s="2">
+        <v>46175.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>4382</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="2">
+        <v>46175.03125</v>
+      </c>
+      <c r="B389">
+        <v>4364</v>
+      </c>
+      <c r="C389">
+        <v>4</v>
+      </c>
+      <c r="D389" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="2">
+        <v>46175.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>4401</v>
+      </c>
+      <c r="C390">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="2">
+        <v>46175.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>4398</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="2">
+        <v>46175.0625</v>
+      </c>
+      <c r="B392">
+        <v>4385</v>
+      </c>
+      <c r="C392">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="2">
+        <v>46175.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>4360</v>
+      </c>
+      <c r="C393">
+        <v>8</v>
+      </c>
+      <c r="D393" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="2">
+        <v>46175.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>4394</v>
+      </c>
+      <c r="C394">
+        <v>9</v>
+      </c>
+      <c r="D394" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="2">
+        <v>46175.09375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>10</v>
+      </c>
+      <c r="D395" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="2">
+        <v>46175.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>4382</v>
+      </c>
+      <c r="C396">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="2">
+        <v>46175.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>12</v>
+      </c>
+      <c r="D397" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="2">
+        <v>46175.125</v>
+      </c>
+      <c r="B398">
+        <v>4379</v>
+      </c>
+      <c r="C398">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="2">
+        <v>46175.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>4509</v>
+      </c>
+      <c r="C399">
+        <v>14</v>
+      </c>
+      <c r="D399" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="2">
+        <v>46175.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>4539</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="2">
+        <v>46175.15625</v>
+      </c>
+      <c r="B401">
+        <v>4573</v>
+      </c>
+      <c r="C401">
+        <v>16</v>
+      </c>
+      <c r="D401" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="2">
+        <v>46175.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>4385</v>
+      </c>
+      <c r="C402">
+        <v>17</v>
+      </c>
+      <c r="D402" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="2">
+        <v>46175.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>4388</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="2">
+        <v>46175.1875</v>
+      </c>
+      <c r="B404">
+        <v>4404</v>
+      </c>
+      <c r="C404">
+        <v>19</v>
+      </c>
+      <c r="D404" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="2">
+        <v>46175.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>4480</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="2">
+        <v>46175.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>4635</v>
+      </c>
+      <c r="C406">
+        <v>21</v>
+      </c>
+      <c r="D406" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="2">
+        <v>46175.21875</v>
+      </c>
+      <c r="B407">
+        <v>4775</v>
+      </c>
+      <c r="C407">
+        <v>22</v>
+      </c>
+      <c r="D407" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="2">
+        <v>46175.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>4931</v>
+      </c>
+      <c r="C408">
+        <v>23</v>
+      </c>
+      <c r="D408" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="2">
+        <v>46175.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>5123</v>
+      </c>
+      <c r="C409">
+        <v>24</v>
+      </c>
+      <c r="D409" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="2">
+        <v>46175.25</v>
+      </c>
+      <c r="B410">
+        <v>5439</v>
+      </c>
+      <c r="C410">
+        <v>25</v>
+      </c>
+      <c r="D410" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="2">
+        <v>46175.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>5621</v>
+      </c>
+      <c r="C411">
+        <v>26</v>
+      </c>
+      <c r="D411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="2">
+        <v>46175.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>5767</v>
+      </c>
+      <c r="C412">
+        <v>27</v>
+      </c>
+      <c r="D412" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="2">
+        <v>46175.28125</v>
+      </c>
+      <c r="B413">
+        <v>5844</v>
+      </c>
+      <c r="C413">
+        <v>28</v>
+      </c>
+      <c r="D413" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="2">
+        <v>46175.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>5990</v>
+      </c>
+      <c r="C414">
+        <v>29</v>
+      </c>
+      <c r="D414" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="2">
+        <v>46175.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>6116</v>
+      </c>
+      <c r="C415">
+        <v>30</v>
+      </c>
+      <c r="D415" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="2">
+        <v>46175.3125</v>
+      </c>
+      <c r="B416">
+        <v>6136</v>
+      </c>
+      <c r="C416">
+        <v>31</v>
+      </c>
+      <c r="D416" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="2">
+        <v>46175.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>6059</v>
+      </c>
+      <c r="C417">
+        <v>32</v>
+      </c>
+      <c r="D417" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="2">
+        <v>46175.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>6015</v>
+      </c>
+      <c r="C418">
+        <v>33</v>
+      </c>
+      <c r="D418" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
+      <c r="A419" s="2">
+        <v>46175.34375</v>
+      </c>
+      <c r="B419">
+        <v>6033</v>
+      </c>
+      <c r="C419">
+        <v>34</v>
+      </c>
+      <c r="D419" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4">
+      <c r="A420" s="2">
+        <v>46175.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>6059</v>
+      </c>
+      <c r="C420">
+        <v>35</v>
+      </c>
+      <c r="D420" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4">
+      <c r="A421" s="2">
+        <v>46175.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>5996</v>
+      </c>
+      <c r="C421">
+        <v>36</v>
+      </c>
+      <c r="D421" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
+      <c r="A422" s="2">
+        <v>46175.375</v>
+      </c>
+      <c r="B422">
+        <v>5980</v>
+      </c>
+      <c r="C422">
+        <v>37</v>
+      </c>
+      <c r="D422" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
+      <c r="A423" s="2">
+        <v>46175.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>5913</v>
+      </c>
+      <c r="C423">
+        <v>38</v>
+      </c>
+      <c r="D423" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
+      <c r="A424" s="2">
+        <v>46175.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>5785</v>
+      </c>
+      <c r="C424">
+        <v>39</v>
+      </c>
+      <c r="D424" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4">
+      <c r="A425" s="2">
+        <v>46175.40625</v>
+      </c>
+      <c r="B425">
+        <v>5679</v>
+      </c>
+      <c r="C425">
+        <v>40</v>
+      </c>
+      <c r="D425" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
+      <c r="A426" s="2">
+        <v>46175.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>5644</v>
+      </c>
+      <c r="C426">
+        <v>41</v>
+      </c>
+      <c r="D426" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
+      <c r="A427" s="2">
+        <v>46175.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>5702</v>
+      </c>
+      <c r="C427">
+        <v>42</v>
+      </c>
+      <c r="D427" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4">
+      <c r="A428" s="2">
+        <v>46175.4375</v>
+      </c>
+      <c r="B428">
+        <v>5620</v>
+      </c>
+      <c r="C428">
+        <v>43</v>
+      </c>
+      <c r="D428" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
+      <c r="A429" s="2">
+        <v>46175.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>5501</v>
+      </c>
+      <c r="C429">
+        <v>44</v>
+      </c>
+      <c r="D429" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
+      <c r="A430" s="2">
+        <v>46175.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>5444</v>
+      </c>
+      <c r="C430">
+        <v>45</v>
+      </c>
+      <c r="D430" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
+      <c r="A431" s="2">
+        <v>46175.46875</v>
+      </c>
+      <c r="B431">
+        <v>5373</v>
+      </c>
+      <c r="C431">
+        <v>46</v>
+      </c>
+      <c r="D431" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4">
+      <c r="A432" s="2">
+        <v>46175.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>5421</v>
+      </c>
+      <c r="C432">
+        <v>47</v>
+      </c>
+      <c r="D432" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4">
+      <c r="A433" s="2">
+        <v>46175.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>5452</v>
+      </c>
+      <c r="C433">
+        <v>48</v>
+      </c>
+      <c r="D433" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
+      <c r="A434" s="2">
+        <v>46175.5</v>
+      </c>
+      <c r="B434">
+        <v>5262</v>
+      </c>
+      <c r="C434">
+        <v>49</v>
+      </c>
+      <c r="D434" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
+      <c r="A435" s="2">
+        <v>46175.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>5264</v>
+      </c>
+      <c r="C435">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
+      <c r="A436" s="2">
+        <v>46175.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>5262</v>
+      </c>
+      <c r="C436">
+        <v>51</v>
+      </c>
+      <c r="D436" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4">
+      <c r="A437" s="2">
+        <v>46175.53125</v>
+      </c>
+      <c r="B437">
+        <v>5189</v>
+      </c>
+      <c r="C437">
+        <v>52</v>
+      </c>
+      <c r="D437" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
+      <c r="A438" s="2">
+        <v>46175.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>5256</v>
+      </c>
+      <c r="C438">
+        <v>53</v>
+      </c>
+      <c r="D438" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" s="2">
+        <v>46175.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>5414</v>
+      </c>
+      <c r="C439">
+        <v>54</v>
+      </c>
+      <c r="D439" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4">
+      <c r="A440" s="2">
+        <v>46175.5625</v>
+      </c>
+      <c r="B440">
+        <v>5479</v>
+      </c>
+      <c r="C440">
+        <v>55</v>
+      </c>
+      <c r="D440" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" s="2">
+        <v>46175.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>5326</v>
+      </c>
+      <c r="C441">
+        <v>56</v>
+      </c>
+      <c r="D441" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" s="2">
+        <v>46175.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>5137</v>
+      </c>
+      <c r="C442">
+        <v>57</v>
+      </c>
+      <c r="D442" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" s="2">
+        <v>46175.59375</v>
+      </c>
+      <c r="B443">
+        <v>5120</v>
+      </c>
+      <c r="C443">
+        <v>58</v>
+      </c>
+      <c r="D443" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" s="2">
+        <v>46175.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>5011</v>
+      </c>
+      <c r="C444">
+        <v>59</v>
+      </c>
+      <c r="D444" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" s="2">
+        <v>46175.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>5048</v>
+      </c>
+      <c r="C445">
+        <v>60</v>
+      </c>
+      <c r="D445" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" s="2">
+        <v>46175.625</v>
+      </c>
+      <c r="B446">
+        <v>4968</v>
+      </c>
+      <c r="C446">
+        <v>61</v>
+      </c>
+      <c r="D446" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" s="2">
+        <v>46175.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>5047</v>
+      </c>
+      <c r="C447">
+        <v>62</v>
+      </c>
+      <c r="D447" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" s="2">
+        <v>46175.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>5120</v>
+      </c>
+      <c r="C448">
+        <v>63</v>
+      </c>
+      <c r="D448" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" s="2">
+        <v>46175.65625</v>
+      </c>
+      <c r="B449">
+        <v>5046</v>
+      </c>
+      <c r="C449">
+        <v>64</v>
+      </c>
+      <c r="D449" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" s="2">
+        <v>46175.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>5233</v>
+      </c>
+      <c r="C450">
+        <v>65</v>
+      </c>
+      <c r="D450" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" s="2">
+        <v>46175.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>5318</v>
+      </c>
+      <c r="C451">
+        <v>66</v>
+      </c>
+      <c r="D451" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" s="2">
+        <v>46175.6875</v>
+      </c>
+      <c r="B452">
+        <v>5422</v>
+      </c>
+      <c r="C452">
+        <v>67</v>
+      </c>
+      <c r="D452" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" s="2">
+        <v>46175.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>5571</v>
+      </c>
+      <c r="C453">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" s="2">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>5540</v>
+      </c>
+      <c r="C454">
+        <v>69</v>
+      </c>
+      <c r="D454" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" s="2">
+        <v>46175.71875</v>
+      </c>
+      <c r="B455">
+        <v>5709</v>
+      </c>
+      <c r="C455">
+        <v>70</v>
+      </c>
+      <c r="D455" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" s="2">
+        <v>46175.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>5892</v>
+      </c>
+      <c r="C456">
+        <v>71</v>
+      </c>
+      <c r="D456" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" s="2">
+        <v>46175.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>6003</v>
+      </c>
+      <c r="C457">
+        <v>72</v>
+      </c>
+      <c r="D457" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" s="2">
+        <v>46175.75</v>
+      </c>
+      <c r="B458">
+        <v>6082</v>
+      </c>
+      <c r="C458">
+        <v>73</v>
+      </c>
+      <c r="D458" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" s="2">
+        <v>46175.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>6121</v>
+      </c>
+      <c r="C459">
+        <v>74</v>
+      </c>
+      <c r="D459" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" s="2">
+        <v>46175.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>6234</v>
+      </c>
+      <c r="C460">
+        <v>75</v>
+      </c>
+      <c r="D460" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" s="2">
+        <v>46175.78125</v>
+      </c>
+      <c r="B461">
+        <v>6320</v>
+      </c>
+      <c r="C461">
+        <v>76</v>
+      </c>
+      <c r="D461" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" s="2">
+        <v>46175.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>6394</v>
+      </c>
+      <c r="C462">
+        <v>77</v>
+      </c>
+      <c r="D462" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" s="2">
+        <v>46175.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>6462</v>
+      </c>
+      <c r="C463">
+        <v>78</v>
+      </c>
+      <c r="D463" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" s="2">
+        <v>46175.8125</v>
+      </c>
+      <c r="B464">
+        <v>6506</v>
+      </c>
+      <c r="C464">
+        <v>79</v>
+      </c>
+      <c r="D464" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" s="2">
+        <v>46175.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>6537</v>
+      </c>
+      <c r="C465">
+        <v>80</v>
+      </c>
+      <c r="D465" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" s="2">
+        <v>46175.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>6568</v>
+      </c>
+      <c r="C466">
+        <v>81</v>
+      </c>
+      <c r="D466" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" s="2">
+        <v>46175.84375</v>
+      </c>
+      <c r="B467">
+        <v>6627</v>
+      </c>
+      <c r="C467">
+        <v>82</v>
+      </c>
+      <c r="D467" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" s="2">
+        <v>46175.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>6625</v>
+      </c>
+      <c r="C468">
+        <v>83</v>
+      </c>
+      <c r="D468" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" s="2">
+        <v>46175.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>6587</v>
+      </c>
+      <c r="C469">
+        <v>84</v>
+      </c>
+      <c r="D469" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" s="2">
+        <v>46175.875</v>
+      </c>
+      <c r="B470">
+        <v>6446</v>
+      </c>
+      <c r="C470">
+        <v>85</v>
+      </c>
+      <c r="D470" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" s="2">
+        <v>46175.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>6296</v>
+      </c>
+      <c r="C471">
+        <v>86</v>
+      </c>
+      <c r="D471" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" s="2">
+        <v>46175.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>6174</v>
+      </c>
+      <c r="C472">
+        <v>87</v>
+      </c>
+      <c r="D472" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" s="2">
+        <v>46175.90625</v>
+      </c>
+      <c r="B473">
+        <v>6121</v>
+      </c>
+      <c r="C473">
+        <v>88</v>
+      </c>
+      <c r="D473" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" s="2">
+        <v>46175.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>5873</v>
+      </c>
+      <c r="C474">
+        <v>89</v>
+      </c>
+      <c r="D474" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" s="2">
+        <v>46175.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>5799</v>
+      </c>
+      <c r="C475">
+        <v>90</v>
+      </c>
+      <c r="D475" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" s="2">
+        <v>46175.9375</v>
+      </c>
+      <c r="B476">
+        <v>5640</v>
+      </c>
+      <c r="C476">
+        <v>91</v>
+      </c>
+      <c r="D476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" s="2">
+        <v>46175.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>5540</v>
+      </c>
+      <c r="C477">
+        <v>92</v>
+      </c>
+      <c r="D477" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" s="2">
+        <v>46175.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>5462</v>
+      </c>
+      <c r="C478">
+        <v>93</v>
+      </c>
+      <c r="D478" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" s="2">
+        <v>46175.96875</v>
+      </c>
+      <c r="B479">
+        <v>5416</v>
+      </c>
+      <c r="C479">
+        <v>94</v>
+      </c>
+      <c r="D479" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" s="2">
+        <v>46175.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>5285</v>
+      </c>
+      <c r="C480">
+        <v>95</v>
+      </c>
+      <c r="D480" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" s="2">
+        <v>46175.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>5194</v>
+      </c>
+      <c r="C481">
+        <v>96</v>
+      </c>
+      <c r="D481" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B482">
+        <v>5074</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
+      <c r="A483" s="2">
+        <v>46176.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>5052</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
+      <c r="A484" s="2">
+        <v>46176.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>4939</v>
+      </c>
+      <c r="C484">
+        <v>3</v>
+      </c>
+      <c r="D484" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
+      <c r="A485" s="2">
+        <v>46176.03125</v>
+      </c>
+      <c r="B485">
+        <v>4927</v>
+      </c>
+      <c r="C485">
+        <v>4</v>
+      </c>
+      <c r="D485" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4">
+      <c r="A486" s="2">
+        <v>46176.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>4896</v>
+      </c>
+      <c r="C486">
+        <v>5</v>
+      </c>
+      <c r="D486" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
+      <c r="A487" s="2">
+        <v>46176.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>4823</v>
+      </c>
+      <c r="C487">
+        <v>6</v>
+      </c>
+      <c r="D487" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4">
+      <c r="A488" s="2">
+        <v>46176.0625</v>
+      </c>
+      <c r="B488">
+        <v>4802</v>
+      </c>
+      <c r="C488">
+        <v>7</v>
+      </c>
+      <c r="D488" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
+      <c r="A489" s="2">
+        <v>46176.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>4833</v>
+      </c>
+      <c r="C489">
+        <v>8</v>
+      </c>
+      <c r="D489" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
+      <c r="A490" s="2">
+        <v>46176.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>4879</v>
+      </c>
+      <c r="C490">
+        <v>9</v>
+      </c>
+      <c r="D490" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" s="2">
+        <v>46176.09375</v>
+      </c>
+      <c r="B491">
+        <v>4900</v>
+      </c>
+      <c r="C491">
+        <v>10</v>
+      </c>
+      <c r="D491" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" s="2">
+        <v>46176.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>4884</v>
+      </c>
+      <c r="C492">
+        <v>11</v>
+      </c>
+      <c r="D492" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" s="2">
+        <v>46176.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>4904</v>
+      </c>
+      <c r="C493">
+        <v>12</v>
+      </c>
+      <c r="D493" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494" s="2">
+        <v>46176.125</v>
+      </c>
+      <c r="B494">
+        <v>4967</v>
+      </c>
+      <c r="C494">
+        <v>13</v>
+      </c>
+      <c r="D494" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495" s="2">
+        <v>46176.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>5065</v>
+      </c>
+      <c r="C495">
+        <v>14</v>
+      </c>
+      <c r="D495" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" s="2">
+        <v>46176.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>5077</v>
+      </c>
+      <c r="C496">
+        <v>15</v>
+      </c>
+      <c r="D496" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" s="2">
+        <v>46176.15625</v>
+      </c>
+      <c r="B497">
+        <v>5041</v>
+      </c>
+      <c r="C497">
+        <v>16</v>
+      </c>
+      <c r="D497" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" s="2">
+        <v>46176.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>5127</v>
+      </c>
+      <c r="C498">
+        <v>17</v>
+      </c>
+      <c r="D498" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" s="2">
+        <v>46176.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>5114</v>
+      </c>
+      <c r="C499">
+        <v>18</v>
+      </c>
+      <c r="D499" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" s="2">
+        <v>46176.1875</v>
+      </c>
+      <c r="B500">
+        <v>5167</v>
+      </c>
+      <c r="C500">
+        <v>19</v>
+      </c>
+      <c r="D500" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501" s="2">
+        <v>46176.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>5170</v>
+      </c>
+      <c r="C501">
+        <v>20</v>
+      </c>
+      <c r="D501" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502" s="2">
+        <v>46176.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>5067</v>
+      </c>
+      <c r="C502">
+        <v>21</v>
+      </c>
+      <c r="D502" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" s="2">
+        <v>46176.21875</v>
+      </c>
+      <c r="B503">
+        <v>5117</v>
+      </c>
+      <c r="C503">
+        <v>22</v>
+      </c>
+      <c r="D503" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" s="2">
+        <v>46176.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>5197</v>
+      </c>
+      <c r="C504">
+        <v>23</v>
+      </c>
+      <c r="D504" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" s="2">
+        <v>46176.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>5283</v>
+      </c>
+      <c r="C505">
+        <v>24</v>
+      </c>
+      <c r="D505" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" s="2">
+        <v>46176.25</v>
+      </c>
+      <c r="B506">
+        <v>5401</v>
+      </c>
+      <c r="C506">
+        <v>25</v>
+      </c>
+      <c r="D506" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" s="2">
+        <v>46176.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>5581</v>
+      </c>
+      <c r="C507">
+        <v>26</v>
+      </c>
+      <c r="D507" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" s="2">
+        <v>46176.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>5583</v>
+      </c>
+      <c r="C508">
+        <v>27</v>
+      </c>
+      <c r="D508" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" s="2">
+        <v>46176.28125</v>
+      </c>
+      <c r="B509">
+        <v>5587</v>
+      </c>
+      <c r="C509">
+        <v>28</v>
+      </c>
+      <c r="D509" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="2">
+        <v>46176.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>5743</v>
+      </c>
+      <c r="C510">
+        <v>29</v>
+      </c>
+      <c r="D510" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" s="2">
+        <v>46176.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>5690</v>
+      </c>
+      <c r="C511">
+        <v>30</v>
+      </c>
+      <c r="D511" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" s="2">
+        <v>46176.3125</v>
+      </c>
+      <c r="B512">
+        <v>5609</v>
+      </c>
+      <c r="C512">
+        <v>31</v>
+      </c>
+      <c r="D512" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" s="2">
+        <v>46176.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>5479</v>
+      </c>
+      <c r="C513">
+        <v>32</v>
+      </c>
+      <c r="D513" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" s="2">
+        <v>46176.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>5374</v>
+      </c>
+      <c r="C514">
+        <v>33</v>
+      </c>
+      <c r="D514" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" s="2">
+        <v>46176.34375</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+      <c r="C515">
+        <v>34</v>
+      </c>
+      <c r="D515" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" s="2">
+        <v>46176.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+      <c r="C516">
+        <v>35</v>
+      </c>
+      <c r="D516" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" s="2">
+        <v>46176.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+      <c r="C517">
+        <v>36</v>
+      </c>
+      <c r="D517" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" s="2">
+        <v>46176.375</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+      <c r="C518">
+        <v>37</v>
+      </c>
+      <c r="D518" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" s="2">
+        <v>46176.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+      <c r="C519">
+        <v>38</v>
+      </c>
+      <c r="D519" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" s="2">
+        <v>46176.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+      <c r="C520">
+        <v>39</v>
+      </c>
+      <c r="D520" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" s="2">
+        <v>46176.40625</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+      <c r="C521">
+        <v>40</v>
+      </c>
+      <c r="D521" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" s="2">
+        <v>46176.41666666666</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+      <c r="C522">
+        <v>41</v>
+      </c>
+      <c r="D522" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" s="2">
+        <v>46176.42708333334</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+      <c r="C523">
+        <v>42</v>
+      </c>
+      <c r="D523" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" s="2">
+        <v>46176.4375</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+      <c r="C524">
+        <v>43</v>
+      </c>
+      <c r="D524" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" s="2">
+        <v>46176.44791666666</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+      <c r="C525">
+        <v>44</v>
+      </c>
+      <c r="D525" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" s="2">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+      <c r="C526">
+        <v>45</v>
+      </c>
+      <c r="D526" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" s="2">
+        <v>46176.46875</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+      <c r="C527">
+        <v>46</v>
+      </c>
+      <c r="D527" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" s="2">
+        <v>46176.47916666666</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+      <c r="C528">
+        <v>47</v>
+      </c>
+      <c r="D528" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4">
+      <c r="A529" s="2">
+        <v>46176.48958333334</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+      <c r="C529">
+        <v>48</v>
+      </c>
+      <c r="D529" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
+      <c r="A530" s="2">
+        <v>46176.5</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+      <c r="C530">
+        <v>49</v>
+      </c>
+      <c r="D530" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
+      <c r="A531" s="2">
+        <v>46176.51041666666</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+      <c r="C531">
+        <v>50</v>
+      </c>
+      <c r="D531" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
+      <c r="A532" s="2">
+        <v>46176.52083333334</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+      <c r="C532">
+        <v>51</v>
+      </c>
+      <c r="D532" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
+      <c r="A533" s="2">
+        <v>46176.53125</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+      <c r="C533">
+        <v>52</v>
+      </c>
+      <c r="D533" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
+      <c r="A534" s="2">
+        <v>46176.54166666666</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+      <c r="C534">
+        <v>53</v>
+      </c>
+      <c r="D534" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
+      <c r="A535" s="2">
+        <v>46176.55208333334</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+      <c r="C535">
+        <v>54</v>
+      </c>
+      <c r="D535" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
+      <c r="A536" s="2">
+        <v>46176.5625</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+      <c r="C536">
+        <v>55</v>
+      </c>
+      <c r="D536" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
+      <c r="A537" s="2">
+        <v>46176.57291666666</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+      <c r="C537">
+        <v>56</v>
+      </c>
+      <c r="D537" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
+      <c r="A538" s="2">
+        <v>46176.58333333334</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+      <c r="C538">
+        <v>57</v>
+      </c>
+      <c r="D538" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
+      <c r="A539" s="2">
+        <v>46176.59375</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+      <c r="C539">
+        <v>58</v>
+      </c>
+      <c r="D539" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4">
+      <c r="A540" s="2">
+        <v>46176.60416666666</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+      <c r="C540">
+        <v>59</v>
+      </c>
+      <c r="D540" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
+      <c r="A541" s="2">
+        <v>46176.61458333334</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+      <c r="C541">
+        <v>60</v>
+      </c>
+      <c r="D541" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
+      <c r="A542" s="2">
+        <v>46176.625</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+      <c r="C542">
+        <v>61</v>
+      </c>
+      <c r="D542" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
+      <c r="A543" s="2">
+        <v>46176.63541666666</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+      <c r="C543">
+        <v>62</v>
+      </c>
+      <c r="D543" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
+      <c r="A544" s="2">
+        <v>46176.64583333334</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+      <c r="C544">
+        <v>63</v>
+      </c>
+      <c r="D544" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4">
+      <c r="A545" s="2">
+        <v>46176.65625</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+      <c r="C545">
+        <v>64</v>
+      </c>
+      <c r="D545" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
+      <c r="A546" s="2">
+        <v>46176.66666666666</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+      <c r="C546">
+        <v>65</v>
+      </c>
+      <c r="D546" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4">
+      <c r="A547" s="2">
+        <v>46176.67708333334</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+      <c r="C547">
+        <v>66</v>
+      </c>
+      <c r="D547" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4">
+      <c r="A548" s="2">
+        <v>46176.6875</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+      <c r="C548">
+        <v>67</v>
+      </c>
+      <c r="D548" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
+      <c r="A549" s="2">
+        <v>46176.69791666666</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+      <c r="C549">
+        <v>68</v>
+      </c>
+      <c r="D549" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
+      <c r="A550" s="2">
+        <v>46176.70833333334</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+      <c r="C550">
+        <v>69</v>
+      </c>
+      <c r="D550" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
+      <c r="A551" s="2">
+        <v>46176.71875</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+      <c r="C551">
+        <v>70</v>
+      </c>
+      <c r="D551" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
+      <c r="A552" s="2">
+        <v>46176.72916666666</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+      <c r="C552">
+        <v>71</v>
+      </c>
+      <c r="D552" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4">
+      <c r="A553" s="2">
+        <v>46176.73958333334</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+      <c r="C553">
+        <v>72</v>
+      </c>
+      <c r="D553" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4">
+      <c r="A554" s="2">
+        <v>46176.75</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+      <c r="C554">
+        <v>73</v>
+      </c>
+      <c r="D554" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
+      <c r="A555" s="2">
+        <v>46176.76041666666</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+      <c r="C555">
+        <v>74</v>
+      </c>
+      <c r="D555" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4">
+      <c r="A556" s="2">
+        <v>46176.77083333334</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+      <c r="C556">
+        <v>75</v>
+      </c>
+      <c r="D556" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4">
+      <c r="A557" s="2">
+        <v>46176.78125</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+      <c r="C557">
+        <v>76</v>
+      </c>
+      <c r="D557" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
+      <c r="A558" s="2">
+        <v>46176.79166666666</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+      <c r="C558">
+        <v>77</v>
+      </c>
+      <c r="D558" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
+      <c r="A559" s="2">
+        <v>46176.80208333334</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+      <c r="C559">
+        <v>78</v>
+      </c>
+      <c r="D559" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4">
+      <c r="A560" s="2">
+        <v>46176.8125</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+      <c r="C560">
+        <v>79</v>
+      </c>
+      <c r="D560" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4">
+      <c r="A561" s="2">
+        <v>46176.82291666666</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+      <c r="C561">
+        <v>80</v>
+      </c>
+      <c r="D561" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4">
+      <c r="A562" s="2">
+        <v>46176.83333333334</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+      <c r="C562">
+        <v>81</v>
+      </c>
+      <c r="D562" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
+      <c r="A563" s="2">
+        <v>46176.84375</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+      <c r="C563">
+        <v>82</v>
+      </c>
+      <c r="D563" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4">
+      <c r="A564" s="2">
+        <v>46176.85416666666</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+      <c r="C564">
+        <v>83</v>
+      </c>
+      <c r="D564" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4">
+      <c r="A565" s="2">
+        <v>46176.86458333334</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+      <c r="C565">
+        <v>84</v>
+      </c>
+      <c r="D565" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
+      <c r="A566" s="2">
+        <v>46176.875</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+      <c r="C566">
+        <v>85</v>
+      </c>
+      <c r="D566" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
+      <c r="A567" s="2">
+        <v>46176.88541666666</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+      <c r="C567">
+        <v>86</v>
+      </c>
+      <c r="D567" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" s="2">
+        <v>46176.89583333334</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+      <c r="C568">
+        <v>87</v>
+      </c>
+      <c r="D568" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" s="2">
+        <v>46176.90625</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+      <c r="C569">
+        <v>88</v>
+      </c>
+      <c r="D569" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" s="2">
+        <v>46176.91666666666</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+      <c r="C570">
+        <v>89</v>
+      </c>
+      <c r="D570" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" s="2">
+        <v>46176.92708333334</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+      <c r="C571">
+        <v>90</v>
+      </c>
+      <c r="D571" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" s="2">
+        <v>46176.9375</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+      <c r="C572">
+        <v>91</v>
+      </c>
+      <c r="D572" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" s="2">
+        <v>46176.94791666666</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+      <c r="C573">
+        <v>92</v>
+      </c>
+      <c r="D573" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4">
+      <c r="A574" s="2">
+        <v>46176.95833333334</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+      <c r="C574">
+        <v>93</v>
+      </c>
+      <c r="D574" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4">
+      <c r="A575" s="2">
+        <v>46176.96875</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+      <c r="C575">
+        <v>94</v>
+      </c>
+      <c r="D575" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4">
+      <c r="A576" s="2">
+        <v>46176.97916666666</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+      <c r="C576">
+        <v>95</v>
+      </c>
+      <c r="D576" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4">
+      <c r="A577" s="2">
+        <v>46176.98958333334</v>
+      </c>
+      <c r="B577">
+        <v>0</v>
+      </c>
+      <c r="C577">
+        <v>96</v>
+      </c>
+      <c r="D577" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -28,580 +28,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>03.06.202694</t>
-  </si>
-  <si>
-    <t>03.06.202695</t>
-  </si>
-  <si>
-    <t>03.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>11.06.202694</t>
+  </si>
+  <si>
+    <t>11.06.202695</t>
+  </si>
+  <si>
+    <t>11.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
   </si>
 </sst>
 </file>
@@ -982,10 +982,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
-        <v>5074</v>
+        <v>5347</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
-        <v>5052</v>
+        <v>5247</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
-        <v>4939</v>
+        <v>5231</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
-        <v>4927</v>
+        <v>5200</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
-        <v>4896</v>
+        <v>5133</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
-        <v>4823</v>
+        <v>5156</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
-        <v>4802</v>
+        <v>5086</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
-        <v>4833</v>
+        <v>5084</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
-        <v>4879</v>
+        <v>5169</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
-        <v>4900</v>
+        <v>5083</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
-        <v>4884</v>
+        <v>5129</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
-        <v>4904</v>
+        <v>5169</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>4967</v>
+        <v>5167</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>5065</v>
+        <v>5176</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>5077</v>
+        <v>5199</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>5041</v>
+        <v>5261</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>5127</v>
+        <v>5233</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>5114</v>
+        <v>5192</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1234,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
-        <v>5167</v>
+        <v>5165</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>5170</v>
+        <v>5270</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>5067</v>
+        <v>5245</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>5117</v>
+        <v>5311</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>5197</v>
+        <v>5321</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>5283</v>
+        <v>5438</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>5401</v>
+        <v>5613</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>5581</v>
+        <v>5703</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>5583</v>
+        <v>5792</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>5587</v>
+        <v>5732</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>5743</v>
+        <v>5720</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>5690</v>
+        <v>5722</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>5609</v>
+        <v>5734</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>5479</v>
+        <v>5698</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
-        <v>5374</v>
+        <v>5596</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>5260</v>
+        <v>5550</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>5247</v>
+        <v>5429</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>5078</v>
+        <v>5346</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>4823</v>
+        <v>5313</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>4700</v>
+        <v>5325</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
-        <v>4646</v>
+        <v>5301</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>4534</v>
+        <v>5263</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>4388</v>
+        <v>5092</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>4312</v>
+        <v>5112</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>4292</v>
+        <v>5053</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>4262</v>
+        <v>4946</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>4172</v>
+        <v>4922</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>4138</v>
+        <v>4953</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>4145</v>
+        <v>4889</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>4305</v>
+        <v>4895</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>4270</v>
+        <v>4978</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>4305</v>
+        <v>4994</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>4250</v>
+        <v>5044</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>4245</v>
+        <v>5019</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>4254</v>
+        <v>5161</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>4272</v>
+        <v>5237</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>4308</v>
+        <v>5316</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>4375</v>
+        <v>5356</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>4530</v>
+        <v>5336</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>4592</v>
+        <v>5334</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>4544</v>
+        <v>5397</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>4668</v>
+        <v>5451</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
-        <v>4858</v>
+        <v>5243</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>5007</v>
+        <v>5384</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>4993</v>
+        <v>5552</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>4998</v>
+        <v>5702</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>5006</v>
+        <v>5772</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>5089</v>
+        <v>5889</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>5287</v>
+        <v>5996</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>5397</v>
+        <v>6132</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>5457</v>
+        <v>6200</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>5604</v>
+        <v>6257</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>5796</v>
+        <v>6420</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>5919</v>
+        <v>6504</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>6083</v>
+        <v>6566</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>6153</v>
+        <v>6679</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>6234</v>
+        <v>6726</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>6413</v>
+        <v>6823</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>6364</v>
+        <v>6847</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>6490</v>
+        <v>6881</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>6516</v>
+        <v>6940</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>6592</v>
+        <v>6903</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>6613</v>
+        <v>6957</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>6731</v>
+        <v>6986</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>6797</v>
+        <v>6953</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>6720</v>
+        <v>6938</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>6599</v>
+        <v>6757</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>6444</v>
+        <v>6606</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>6302</v>
+        <v>6451</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>6148</v>
+        <v>6297</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>5905</v>
+        <v>6214</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>5750</v>
+        <v>6036</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>5691</v>
+        <v>5948</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
-        <v>5588</v>
+        <v>5845</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>5392</v>
+        <v>5677</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
-        <v>5276</v>
+        <v>5465</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
-        <v>5266</v>
+        <v>5401</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
-        <v>5221</v>
+        <v>5395</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
-        <v>5195</v>
+        <v>5392</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B99">
-        <v>5108</v>
+        <v>5346</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B100">
-        <v>5131</v>
+        <v>5260</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B101">
-        <v>5087</v>
+        <v>5202</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B102">
-        <v>5074</v>
+        <v>5203</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B103">
-        <v>5041</v>
+        <v>5220</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B104">
-        <v>4967</v>
+        <v>5253</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B105">
-        <v>4943</v>
+        <v>5196</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B106">
-        <v>4933</v>
+        <v>5221</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B107">
-        <v>4951</v>
+        <v>5193</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B108">
-        <v>4875</v>
+        <v>5178</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B109">
-        <v>4911</v>
+        <v>5238</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B110">
-        <v>4898</v>
+        <v>5256</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B111">
-        <v>4926</v>
+        <v>5275</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B112">
-        <v>4979</v>
+        <v>5289</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B113">
-        <v>4943</v>
+        <v>5272</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B114">
-        <v>5044</v>
+        <v>5280</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B115">
-        <v>5017</v>
+        <v>5228</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B116">
-        <v>5008</v>
+        <v>5240</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B117">
-        <v>5007</v>
+        <v>5393</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B118">
-        <v>5017</v>
+        <v>5382</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B119">
-        <v>5094</v>
+        <v>5467</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B120">
-        <v>5144</v>
+        <v>5496</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B121">
-        <v>5286</v>
+        <v>5656</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B122">
-        <v>5433</v>
+        <v>5926</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B123">
-        <v>5521</v>
+        <v>6056</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B124">
-        <v>5597</v>
+        <v>6167</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B125">
-        <v>5619</v>
+        <v>6207</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B126">
-        <v>5764</v>
+        <v>6252</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B127">
-        <v>5687</v>
+        <v>6358</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B128">
-        <v>5759</v>
+        <v>6398</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B129">
-        <v>5777</v>
+        <v>6425</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B130">
-        <v>5725</v>
+        <v>6415</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B131">
-        <v>5714</v>
+        <v>6491</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B132">
-        <v>5693</v>
+        <v>6433</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>6339</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>6327</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>6266</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>6181</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>6015</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>5842</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>5701</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>5696</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>5611</v>
       </c>
       <c r="C141">
         <v>44</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>5548</v>
       </c>
       <c r="C142">
         <v>45</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>5450</v>
       </c>
       <c r="C143">
         <v>46</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>5439</v>
       </c>
       <c r="C144">
         <v>47</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>5449</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>5515</v>
       </c>
       <c r="C146">
         <v>49</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>5559</v>
       </c>
       <c r="C147">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>5527</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>5453</v>
       </c>
       <c r="C149">
         <v>52</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -3516,7 +3516,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,580 +28,424 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>11.06.202694</t>
-  </si>
-  <si>
-    <t>11.06.202695</t>
-  </si>
-  <si>
-    <t>11.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
   </si>
 </sst>
 </file>
@@ -963,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -982,10 +826,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>5347</v>
+        <v>5444</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -996,10 +840,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>5247</v>
+        <v>5476</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1010,10 +854,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>5231</v>
+        <v>5490</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1024,10 +868,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>5200</v>
+        <v>5471</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1038,10 +882,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>5133</v>
+        <v>5391</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1052,10 +896,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>5156</v>
+        <v>5346</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1066,10 +910,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>5086</v>
+        <v>5340</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1080,10 +924,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>5084</v>
+        <v>5371</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1094,10 +938,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>5169</v>
+        <v>5206</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1108,10 +952,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>5083</v>
+        <v>5320</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1122,10 +966,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>5129</v>
+        <v>5308</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1136,10 +980,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>5169</v>
+        <v>5298</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1150,10 +994,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>5167</v>
+        <v>5335</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1164,10 +1008,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>5176</v>
+        <v>5338</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1178,10 +1022,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>5199</v>
+        <v>5371</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1192,10 +1036,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>5261</v>
+        <v>5384</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1206,10 +1050,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>5233</v>
+        <v>5387</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1220,10 +1064,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
-        <v>5192</v>
+        <v>5307</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1234,10 +1078,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
-        <v>5165</v>
+        <v>5261</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1248,10 +1092,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>5270</v>
+        <v>5362</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1262,10 +1106,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>5245</v>
+        <v>5374</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1276,10 +1120,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>5311</v>
+        <v>5485</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1290,10 +1134,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>5321</v>
+        <v>5530</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1304,10 +1148,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>5438</v>
+        <v>5599</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1318,10 +1162,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>5613</v>
+        <v>5806</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1332,10 +1176,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>5703</v>
+        <v>5813</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1346,10 +1190,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>5792</v>
+        <v>5830</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1360,10 +1204,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>5732</v>
+        <v>5818</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1374,10 +1218,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>5720</v>
+        <v>5845</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1388,10 +1232,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>5722</v>
+        <v>5812</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1402,10 +1246,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>5734</v>
+        <v>5766</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1416,10 +1260,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>5698</v>
+        <v>5707</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1430,10 +1274,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>5596</v>
+        <v>5580</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1444,10 +1288,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>5550</v>
+        <v>5485</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1458,10 +1302,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>5429</v>
+        <v>5409</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1472,10 +1316,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>5346</v>
+        <v>5304</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1486,10 +1330,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>5313</v>
+        <v>5193</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1500,10 +1344,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>5325</v>
+        <v>5128</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1514,10 +1358,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
-        <v>5301</v>
+        <v>4912</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1528,10 +1372,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>5263</v>
+        <v>4817</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1542,10 +1386,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>5092</v>
+        <v>4907</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1556,10 +1400,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>5112</v>
+        <v>4907</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1570,10 +1414,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>5053</v>
+        <v>4875</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1584,10 +1428,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>4946</v>
+        <v>4834</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1598,10 +1442,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>4922</v>
+        <v>4821</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1612,10 +1456,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>4953</v>
+        <v>4844</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1626,10 +1470,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>4889</v>
+        <v>4914</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1640,10 +1484,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>4895</v>
+        <v>4987</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1654,10 +1498,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>4978</v>
+        <v>5035</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1668,10 +1512,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>4994</v>
+        <v>5063</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1682,10 +1526,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>5044</v>
+        <v>5254</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1696,10 +1540,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>5019</v>
+        <v>5131</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1710,10 +1554,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>5161</v>
+        <v>5170</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1724,10 +1568,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>5237</v>
+        <v>5256</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1738,10 +1582,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>5316</v>
+        <v>5247</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1752,10 +1596,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
-        <v>5356</v>
+        <v>5319</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1766,10 +1610,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46184.58333333334</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>5336</v>
+        <v>5360</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1780,10 +1624,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46184.59375</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>5334</v>
+        <v>5461</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1794,10 +1638,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46184.60416666666</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>5397</v>
+        <v>5550</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1808,10 +1652,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46184.61458333334</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>5451</v>
+        <v>5594</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1822,10 +1666,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46184.625</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>5243</v>
+        <v>5645</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1836,10 +1680,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46184.63541666666</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
-        <v>5384</v>
+        <v>5742</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1850,10 +1694,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46184.64583333334</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
-        <v>5552</v>
+        <v>5690</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1864,10 +1708,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46184.65625</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>5702</v>
+        <v>5853</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1878,10 +1722,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46184.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
-        <v>5772</v>
+        <v>5783</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1892,10 +1736,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46184.67708333334</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
-        <v>5889</v>
+        <v>5864</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1906,10 +1750,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46184.6875</v>
+        <v>46212.6875</v>
       </c>
       <c r="B68">
-        <v>5996</v>
+        <v>5956</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1920,10 +1764,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46184.69791666666</v>
+        <v>46212.69791666666</v>
       </c>
       <c r="B69">
-        <v>6132</v>
+        <v>5996</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1934,10 +1778,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46184.70833333334</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="B70">
-        <v>6200</v>
+        <v>6131</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1948,10 +1792,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46184.71875</v>
+        <v>46212.71875</v>
       </c>
       <c r="B71">
-        <v>6257</v>
+        <v>6213</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1962,10 +1806,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46184.72916666666</v>
+        <v>46212.72916666666</v>
       </c>
       <c r="B72">
-        <v>6420</v>
+        <v>6241</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1976,10 +1820,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46184.73958333334</v>
+        <v>46212.73958333334</v>
       </c>
       <c r="B73">
-        <v>6504</v>
+        <v>6313</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1990,10 +1834,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46184.75</v>
+        <v>46212.75</v>
       </c>
       <c r="B74">
-        <v>6566</v>
+        <v>6314</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -2004,10 +1848,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46184.76041666666</v>
+        <v>46212.76041666666</v>
       </c>
       <c r="B75">
-        <v>6679</v>
+        <v>6399</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -2018,10 +1862,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46184.77083333334</v>
+        <v>46212.77083333334</v>
       </c>
       <c r="B76">
-        <v>6726</v>
+        <v>6477</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -2032,10 +1876,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46184.78125</v>
+        <v>46212.78125</v>
       </c>
       <c r="B77">
-        <v>6823</v>
+        <v>6576</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -2046,10 +1890,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46184.79166666666</v>
+        <v>46212.79166666666</v>
       </c>
       <c r="B78">
-        <v>6847</v>
+        <v>6653</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -2060,10 +1904,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46184.80208333334</v>
+        <v>46212.80208333334</v>
       </c>
       <c r="B79">
-        <v>6881</v>
+        <v>6662</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -2074,10 +1918,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46184.8125</v>
+        <v>46212.8125</v>
       </c>
       <c r="B80">
-        <v>6940</v>
+        <v>6722</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -2088,10 +1932,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46184.82291666666</v>
+        <v>46212.82291666666</v>
       </c>
       <c r="B81">
-        <v>6903</v>
+        <v>6742</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -2102,10 +1946,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46184.83333333334</v>
+        <v>46212.83333333334</v>
       </c>
       <c r="B82">
-        <v>6957</v>
+        <v>6824</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -2116,10 +1960,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46184.84375</v>
+        <v>46212.84375</v>
       </c>
       <c r="B83">
-        <v>6986</v>
+        <v>6881</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -2130,10 +1974,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46184.85416666666</v>
+        <v>46212.85416666666</v>
       </c>
       <c r="B84">
-        <v>6953</v>
+        <v>6910</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -2144,10 +1988,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46184.86458333334</v>
+        <v>46212.86458333334</v>
       </c>
       <c r="B85">
-        <v>6938</v>
+        <v>6844</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2158,10 +2002,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46184.875</v>
+        <v>46212.875</v>
       </c>
       <c r="B86">
-        <v>6757</v>
+        <v>6761</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2172,10 +2016,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46184.88541666666</v>
+        <v>46212.88541666666</v>
       </c>
       <c r="B87">
-        <v>6606</v>
+        <v>6699</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2186,10 +2030,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46184.89583333334</v>
+        <v>46212.89583333334</v>
       </c>
       <c r="B88">
-        <v>6451</v>
+        <v>6601</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2200,10 +2044,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46184.90625</v>
+        <v>46212.90625</v>
       </c>
       <c r="B89">
-        <v>6297</v>
+        <v>6366</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2214,10 +2058,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46184.91666666666</v>
+        <v>46212.91666666666</v>
       </c>
       <c r="B90">
-        <v>6214</v>
+        <v>6225</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2228,10 +2072,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46184.92708333334</v>
+        <v>46212.92708333334</v>
       </c>
       <c r="B91">
-        <v>6036</v>
+        <v>6162</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2242,10 +2086,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46184.9375</v>
+        <v>46212.9375</v>
       </c>
       <c r="B92">
-        <v>5948</v>
+        <v>5986</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2256,10 +2100,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46184.94791666666</v>
+        <v>46212.94791666666</v>
       </c>
       <c r="B93">
-        <v>5845</v>
+        <v>5867</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2270,10 +2114,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46184.95833333334</v>
+        <v>46212.95833333334</v>
       </c>
       <c r="B94">
-        <v>5677</v>
+        <v>5739</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2284,10 +2128,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46184.96875</v>
+        <v>46212.96875</v>
       </c>
       <c r="B95">
-        <v>5465</v>
+        <v>5630</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2298,10 +2142,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46184.97916666666</v>
+        <v>46212.97916666666</v>
       </c>
       <c r="B96">
-        <v>5401</v>
+        <v>5599</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2312,10 +2156,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46184.98958333334</v>
+        <v>46212.98958333334</v>
       </c>
       <c r="B97">
-        <v>5395</v>
+        <v>5619</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2326,10 +2170,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B98">
-        <v>5392</v>
+        <v>5509</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2340,10 +2184,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B99">
-        <v>5346</v>
+        <v>5396</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2354,10 +2198,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B100">
-        <v>5260</v>
+        <v>5402</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2368,10 +2212,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46185.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B101">
-        <v>5202</v>
+        <v>5325</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2382,10 +2226,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B102">
-        <v>5203</v>
+        <v>5426</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2396,10 +2240,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B103">
-        <v>5220</v>
+        <v>5441</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2410,10 +2254,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46185.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B104">
-        <v>5253</v>
+        <v>5421</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2424,10 +2268,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B105">
-        <v>5196</v>
+        <v>5389</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2438,10 +2282,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B106">
-        <v>5221</v>
+        <v>5242</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2452,10 +2296,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46185.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B107">
-        <v>5193</v>
+        <v>5426</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2466,10 +2310,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B108">
-        <v>5178</v>
+        <v>5181</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2480,10 +2324,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B109">
-        <v>5238</v>
+        <v>5373</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2494,10 +2338,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46185.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B110">
-        <v>5256</v>
+        <v>5420</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2508,10 +2352,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B111">
-        <v>5275</v>
+        <v>5394</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2522,10 +2366,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B112">
-        <v>5289</v>
+        <v>5379</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2536,10 +2380,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46185.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B113">
-        <v>5272</v>
+        <v>5231</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2550,10 +2394,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B114">
-        <v>5280</v>
+        <v>5300</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2564,10 +2408,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B115">
-        <v>5228</v>
+        <v>5287</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2578,10 +2422,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46185.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B116">
-        <v>5240</v>
+        <v>5202</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2592,10 +2436,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B117">
-        <v>5393</v>
+        <v>5225</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2606,10 +2450,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B118">
-        <v>5382</v>
+        <v>5311</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2620,10 +2464,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46185.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B119">
-        <v>5467</v>
+        <v>5394</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2634,10 +2478,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B120">
-        <v>5496</v>
+        <v>5403</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2648,10 +2492,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B121">
-        <v>5656</v>
+        <v>5514</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2662,10 +2506,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46185.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B122">
-        <v>5926</v>
+        <v>5707</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2676,10 +2520,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B123">
-        <v>6056</v>
+        <v>5692</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2690,10 +2534,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B124">
-        <v>6167</v>
+        <v>5711</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2704,10 +2548,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46185.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B125">
-        <v>6207</v>
+        <v>5778</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2718,10 +2562,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B126">
-        <v>6252</v>
+        <v>5791</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2732,10 +2576,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B127">
-        <v>6358</v>
+        <v>5789</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2746,10 +2590,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46185.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B128">
-        <v>6398</v>
+        <v>5752</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2760,10 +2604,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B129">
-        <v>6425</v>
+        <v>5657</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2774,10 +2618,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B130">
-        <v>6415</v>
+        <v>5505</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2788,10 +2632,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46185.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B131">
-        <v>6491</v>
+        <v>5400</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2802,10 +2646,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B132">
-        <v>6433</v>
+        <v>5297</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2816,10 +2660,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B133">
-        <v>6339</v>
+        <v>5240</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2830,10 +2674,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46185.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B134">
-        <v>6327</v>
+        <v>5099</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2844,10 +2688,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B135">
-        <v>6266</v>
+        <v>4940</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2858,10 +2702,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B136">
-        <v>6181</v>
+        <v>4858</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2872,10 +2716,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46185.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B137">
-        <v>6015</v>
+        <v>4851</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2886,10 +2730,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B138">
-        <v>5842</v>
+        <v>4875</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2900,10 +2744,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B139">
-        <v>5701</v>
+        <v>4818</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2914,10 +2758,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46185.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B140">
-        <v>5696</v>
+        <v>4758</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2928,744 +2772,16 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B141">
-        <v>5611</v>
+        <v>4654</v>
       </c>
       <c r="C141">
         <v>44</v>
       </c>
       <c r="D141" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="2">
-        <v>46185.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>5548</v>
-      </c>
-      <c r="C142">
-        <v>45</v>
-      </c>
-      <c r="D142" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="2">
-        <v>46185.46875</v>
-      </c>
-      <c r="B143">
-        <v>5450</v>
-      </c>
-      <c r="C143">
-        <v>46</v>
-      </c>
-      <c r="D143" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="2">
-        <v>46185.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>5439</v>
-      </c>
-      <c r="C144">
-        <v>47</v>
-      </c>
-      <c r="D144" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="2">
-        <v>46185.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>5449</v>
-      </c>
-      <c r="C145">
-        <v>48</v>
-      </c>
-      <c r="D145" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="2">
-        <v>46185.5</v>
-      </c>
-      <c r="B146">
-        <v>5515</v>
-      </c>
-      <c r="C146">
-        <v>49</v>
-      </c>
-      <c r="D146" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="2">
-        <v>46185.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>5559</v>
-      </c>
-      <c r="C147">
-        <v>50</v>
-      </c>
-      <c r="D147" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="2">
-        <v>46185.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>5527</v>
-      </c>
-      <c r="C148">
-        <v>51</v>
-      </c>
-      <c r="D148" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="2">
-        <v>46185.53125</v>
-      </c>
-      <c r="B149">
-        <v>5453</v>
-      </c>
-      <c r="C149">
-        <v>52</v>
-      </c>
-      <c r="D149" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="2">
-        <v>46185.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>53</v>
-      </c>
-      <c r="D150" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="2">
-        <v>46185.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>54</v>
-      </c>
-      <c r="D151" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="2">
-        <v>46185.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>55</v>
-      </c>
-      <c r="D152" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="2">
-        <v>46185.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>56</v>
-      </c>
-      <c r="D153" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="2">
-        <v>46185.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>57</v>
-      </c>
-      <c r="D154" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="2">
-        <v>46185.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>58</v>
-      </c>
-      <c r="D155" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" s="2">
-        <v>46185.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-      <c r="C156">
-        <v>59</v>
-      </c>
-      <c r="D156" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
-      <c r="A157" s="2">
-        <v>46185.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-      <c r="C157">
-        <v>60</v>
-      </c>
-      <c r="D157" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="2">
-        <v>46185.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-      <c r="C158">
-        <v>61</v>
-      </c>
-      <c r="D158" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" s="2">
-        <v>46185.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-      <c r="C159">
-        <v>62</v>
-      </c>
-      <c r="D159" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="2">
-        <v>46185.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-      <c r="C160">
-        <v>63</v>
-      </c>
-      <c r="D160" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="2">
-        <v>46185.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-      <c r="C161">
-        <v>64</v>
-      </c>
-      <c r="D161" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
-      <c r="A162" s="2">
-        <v>46185.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-      <c r="C162">
-        <v>65</v>
-      </c>
-      <c r="D162" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" s="2">
-        <v>46185.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="C163">
-        <v>66</v>
-      </c>
-      <c r="D163" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
-      <c r="A164" s="2">
-        <v>46185.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-      <c r="C164">
-        <v>67</v>
-      </c>
-      <c r="D164" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" s="2">
-        <v>46185.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-      <c r="C165">
-        <v>68</v>
-      </c>
-      <c r="D165" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" s="2">
-        <v>46185.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-      <c r="C166">
-        <v>69</v>
-      </c>
-      <c r="D166" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="2">
-        <v>46185.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-      <c r="C167">
-        <v>70</v>
-      </c>
-      <c r="D167" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="2">
-        <v>46185.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-      <c r="C168">
-        <v>71</v>
-      </c>
-      <c r="D168" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="2">
-        <v>46185.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-      <c r="C169">
-        <v>72</v>
-      </c>
-      <c r="D169" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
-      <c r="A170" s="2">
-        <v>46185.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-      <c r="C170">
-        <v>73</v>
-      </c>
-      <c r="D170" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
-      <c r="A171" s="2">
-        <v>46185.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-      <c r="C171">
-        <v>74</v>
-      </c>
-      <c r="D171" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
-      <c r="A172" s="2">
-        <v>46185.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-      <c r="C172">
-        <v>75</v>
-      </c>
-      <c r="D172" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
-      <c r="A173" s="2">
-        <v>46185.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-      <c r="C173">
-        <v>76</v>
-      </c>
-      <c r="D173" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
-      <c r="A174" s="2">
-        <v>46185.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-      <c r="C174">
-        <v>77</v>
-      </c>
-      <c r="D174" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="2">
-        <v>46185.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-      <c r="C175">
-        <v>78</v>
-      </c>
-      <c r="D175" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="2">
-        <v>46185.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-      <c r="C176">
-        <v>79</v>
-      </c>
-      <c r="D176" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
-      <c r="A177" s="2">
-        <v>46185.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-      <c r="C177">
-        <v>80</v>
-      </c>
-      <c r="D177" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4">
-      <c r="A178" s="2">
-        <v>46185.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-      <c r="C178">
-        <v>81</v>
-      </c>
-      <c r="D178" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
-      <c r="A179" s="2">
-        <v>46185.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-      <c r="C179">
-        <v>82</v>
-      </c>
-      <c r="D179" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
-      <c r="A180" s="2">
-        <v>46185.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-      <c r="C180">
-        <v>83</v>
-      </c>
-      <c r="D180" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
-      <c r="A181" s="2">
-        <v>46185.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-      <c r="C181">
-        <v>84</v>
-      </c>
-      <c r="D181" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
-      <c r="A182" s="2">
-        <v>46185.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-      <c r="C182">
-        <v>85</v>
-      </c>
-      <c r="D182" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
-      <c r="A183" s="2">
-        <v>46185.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-      <c r="C183">
-        <v>86</v>
-      </c>
-      <c r="D183" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
-      <c r="A184" s="2">
-        <v>46185.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-      <c r="C184">
-        <v>87</v>
-      </c>
-      <c r="D184" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
-      <c r="A185" s="2">
-        <v>46185.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-      <c r="C185">
-        <v>88</v>
-      </c>
-      <c r="D185" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
-      <c r="A186" s="2">
-        <v>46185.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-      <c r="C186">
-        <v>89</v>
-      </c>
-      <c r="D186" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
-      <c r="A187" s="2">
-        <v>46185.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-      <c r="C187">
-        <v>90</v>
-      </c>
-      <c r="D187" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
-      <c r="A188" s="2">
-        <v>46185.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-      <c r="C188">
-        <v>91</v>
-      </c>
-      <c r="D188" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
-      <c r="A189" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-      <c r="C189">
-        <v>92</v>
-      </c>
-      <c r="D189" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-      <c r="C190">
-        <v>93</v>
-      </c>
-      <c r="D190" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4">
-      <c r="A191" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-      <c r="C191">
-        <v>94</v>
-      </c>
-      <c r="D191" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
-      <c r="A192" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-      <c r="C192">
-        <v>95</v>
-      </c>
-      <c r="D192" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4">
-      <c r="A193" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>0</v>
-      </c>
-      <c r="C193">
-        <v>96</v>
-      </c>
-      <c r="D193" t="s">
-        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,294 +28,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.07.20261</t>
-  </si>
-  <si>
-    <t>09.07.20262</t>
-  </si>
-  <si>
-    <t>09.07.20263</t>
-  </si>
-  <si>
-    <t>09.07.20264</t>
-  </si>
-  <si>
-    <t>09.07.20265</t>
-  </si>
-  <si>
-    <t>09.07.20266</t>
-  </si>
-  <si>
-    <t>09.07.20267</t>
-  </si>
-  <si>
-    <t>09.07.20268</t>
-  </si>
-  <si>
-    <t>09.07.20269</t>
-  </si>
-  <si>
-    <t>09.07.202610</t>
-  </si>
-  <si>
-    <t>09.07.202611</t>
-  </si>
-  <si>
-    <t>09.07.202612</t>
-  </si>
-  <si>
-    <t>09.07.202613</t>
-  </si>
-  <si>
-    <t>09.07.202614</t>
-  </si>
-  <si>
-    <t>09.07.202615</t>
-  </si>
-  <si>
-    <t>09.07.202616</t>
-  </si>
-  <si>
-    <t>09.07.202617</t>
-  </si>
-  <si>
-    <t>09.07.202618</t>
-  </si>
-  <si>
-    <t>09.07.202619</t>
-  </si>
-  <si>
-    <t>09.07.202620</t>
-  </si>
-  <si>
-    <t>09.07.202621</t>
-  </si>
-  <si>
-    <t>09.07.202622</t>
-  </si>
-  <si>
-    <t>09.07.202623</t>
-  </si>
-  <si>
-    <t>09.07.202624</t>
-  </si>
-  <si>
-    <t>09.07.202625</t>
-  </si>
-  <si>
-    <t>09.07.202626</t>
-  </si>
-  <si>
-    <t>09.07.202627</t>
-  </si>
-  <si>
-    <t>09.07.202628</t>
-  </si>
-  <si>
-    <t>09.07.202629</t>
-  </si>
-  <si>
-    <t>09.07.202630</t>
-  </si>
-  <si>
-    <t>09.07.202631</t>
-  </si>
-  <si>
-    <t>09.07.202632</t>
-  </si>
-  <si>
-    <t>09.07.202633</t>
-  </si>
-  <si>
-    <t>09.07.202634</t>
-  </si>
-  <si>
-    <t>09.07.202635</t>
-  </si>
-  <si>
-    <t>09.07.202636</t>
-  </si>
-  <si>
-    <t>09.07.202637</t>
-  </si>
-  <si>
-    <t>09.07.202638</t>
-  </si>
-  <si>
-    <t>09.07.202639</t>
-  </si>
-  <si>
-    <t>09.07.202640</t>
-  </si>
-  <si>
-    <t>09.07.202641</t>
-  </si>
-  <si>
-    <t>09.07.202642</t>
-  </si>
-  <si>
-    <t>09.07.202643</t>
-  </si>
-  <si>
-    <t>09.07.202644</t>
-  </si>
-  <si>
-    <t>09.07.202645</t>
-  </si>
-  <si>
-    <t>09.07.202646</t>
-  </si>
-  <si>
-    <t>09.07.202647</t>
-  </si>
-  <si>
-    <t>09.07.202648</t>
-  </si>
-  <si>
-    <t>09.07.202649</t>
-  </si>
-  <si>
-    <t>09.07.202650</t>
-  </si>
-  <si>
-    <t>09.07.202651</t>
-  </si>
-  <si>
-    <t>09.07.202652</t>
-  </si>
-  <si>
-    <t>09.07.202653</t>
-  </si>
-  <si>
-    <t>09.07.202654</t>
-  </si>
-  <si>
-    <t>09.07.202655</t>
-  </si>
-  <si>
-    <t>09.07.202656</t>
-  </si>
-  <si>
-    <t>09.07.202657</t>
-  </si>
-  <si>
-    <t>09.07.202658</t>
-  </si>
-  <si>
-    <t>09.07.202659</t>
-  </si>
-  <si>
-    <t>09.07.202660</t>
-  </si>
-  <si>
-    <t>09.07.202661</t>
-  </si>
-  <si>
-    <t>09.07.202662</t>
-  </si>
-  <si>
-    <t>09.07.202663</t>
-  </si>
-  <si>
-    <t>09.07.202664</t>
-  </si>
-  <si>
-    <t>09.07.202665</t>
-  </si>
-  <si>
-    <t>09.07.202666</t>
-  </si>
-  <si>
-    <t>09.07.202667</t>
-  </si>
-  <si>
-    <t>09.07.202668</t>
-  </si>
-  <si>
-    <t>09.07.202669</t>
-  </si>
-  <si>
-    <t>09.07.202670</t>
-  </si>
-  <si>
-    <t>09.07.202671</t>
-  </si>
-  <si>
-    <t>09.07.202672</t>
-  </si>
-  <si>
-    <t>09.07.202673</t>
-  </si>
-  <si>
-    <t>09.07.202674</t>
-  </si>
-  <si>
-    <t>09.07.202675</t>
-  </si>
-  <si>
-    <t>09.07.202676</t>
-  </si>
-  <si>
-    <t>09.07.202677</t>
-  </si>
-  <si>
-    <t>09.07.202678</t>
-  </si>
-  <si>
-    <t>09.07.202679</t>
-  </si>
-  <si>
-    <t>09.07.202680</t>
-  </si>
-  <si>
-    <t>09.07.202681</t>
-  </si>
-  <si>
-    <t>09.07.202682</t>
-  </si>
-  <si>
-    <t>09.07.202683</t>
-  </si>
-  <si>
-    <t>09.07.202684</t>
-  </si>
-  <si>
-    <t>09.07.202685</t>
-  </si>
-  <si>
-    <t>09.07.202686</t>
-  </si>
-  <si>
-    <t>09.07.202687</t>
-  </si>
-  <si>
-    <t>09.07.202688</t>
-  </si>
-  <si>
-    <t>09.07.202689</t>
-  </si>
-  <si>
-    <t>09.07.202690</t>
-  </si>
-  <si>
-    <t>09.07.202691</t>
-  </si>
-  <si>
-    <t>09.07.202692</t>
-  </si>
-  <si>
-    <t>09.07.202693</t>
-  </si>
-  <si>
-    <t>09.07.202694</t>
-  </si>
-  <si>
-    <t>09.07.202695</t>
-  </si>
-  <si>
-    <t>09.07.202696</t>
-  </si>
-  <si>
     <t>10.07.20261</t>
   </si>
   <si>
@@ -446,6 +158,891 @@
   </si>
   <si>
     <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
+  </si>
+  <si>
+    <t>10.07.202693</t>
+  </si>
+  <si>
+    <t>10.07.202694</t>
+  </si>
+  <si>
+    <t>10.07.202695</t>
+  </si>
+  <si>
+    <t>10.07.202696</t>
+  </si>
+  <si>
+    <t>11.07.20261</t>
+  </si>
+  <si>
+    <t>11.07.20262</t>
+  </si>
+  <si>
+    <t>11.07.20263</t>
+  </si>
+  <si>
+    <t>11.07.20264</t>
+  </si>
+  <si>
+    <t>11.07.20265</t>
+  </si>
+  <si>
+    <t>11.07.20266</t>
+  </si>
+  <si>
+    <t>11.07.20267</t>
+  </si>
+  <si>
+    <t>11.07.20268</t>
+  </si>
+  <si>
+    <t>11.07.20269</t>
+  </si>
+  <si>
+    <t>11.07.202610</t>
+  </si>
+  <si>
+    <t>11.07.202611</t>
+  </si>
+  <si>
+    <t>11.07.202612</t>
+  </si>
+  <si>
+    <t>11.07.202613</t>
+  </si>
+  <si>
+    <t>11.07.202614</t>
+  </si>
+  <si>
+    <t>11.07.202615</t>
+  </si>
+  <si>
+    <t>11.07.202616</t>
+  </si>
+  <si>
+    <t>11.07.202617</t>
+  </si>
+  <si>
+    <t>11.07.202618</t>
+  </si>
+  <si>
+    <t>11.07.202619</t>
+  </si>
+  <si>
+    <t>11.07.202620</t>
+  </si>
+  <si>
+    <t>11.07.202621</t>
+  </si>
+  <si>
+    <t>11.07.202622</t>
+  </si>
+  <si>
+    <t>11.07.202623</t>
+  </si>
+  <si>
+    <t>11.07.202624</t>
+  </si>
+  <si>
+    <t>11.07.202625</t>
+  </si>
+  <si>
+    <t>11.07.202626</t>
+  </si>
+  <si>
+    <t>11.07.202627</t>
+  </si>
+  <si>
+    <t>11.07.202628</t>
+  </si>
+  <si>
+    <t>11.07.202629</t>
+  </si>
+  <si>
+    <t>11.07.202630</t>
+  </si>
+  <si>
+    <t>11.07.202631</t>
+  </si>
+  <si>
+    <t>11.07.202632</t>
+  </si>
+  <si>
+    <t>11.07.202633</t>
+  </si>
+  <si>
+    <t>11.07.202634</t>
+  </si>
+  <si>
+    <t>11.07.202635</t>
+  </si>
+  <si>
+    <t>11.07.202636</t>
+  </si>
+  <si>
+    <t>11.07.202637</t>
+  </si>
+  <si>
+    <t>11.07.202638</t>
+  </si>
+  <si>
+    <t>11.07.202639</t>
+  </si>
+  <si>
+    <t>11.07.202640</t>
+  </si>
+  <si>
+    <t>11.07.202641</t>
+  </si>
+  <si>
+    <t>11.07.202642</t>
+  </si>
+  <si>
+    <t>11.07.202643</t>
+  </si>
+  <si>
+    <t>11.07.202644</t>
+  </si>
+  <si>
+    <t>11.07.202645</t>
+  </si>
+  <si>
+    <t>11.07.202646</t>
+  </si>
+  <si>
+    <t>11.07.202647</t>
+  </si>
+  <si>
+    <t>11.07.202648</t>
+  </si>
+  <si>
+    <t>11.07.202649</t>
+  </si>
+  <si>
+    <t>11.07.202650</t>
+  </si>
+  <si>
+    <t>11.07.202651</t>
+  </si>
+  <si>
+    <t>11.07.202652</t>
+  </si>
+  <si>
+    <t>11.07.202653</t>
+  </si>
+  <si>
+    <t>11.07.202654</t>
+  </si>
+  <si>
+    <t>11.07.202655</t>
+  </si>
+  <si>
+    <t>11.07.202656</t>
+  </si>
+  <si>
+    <t>11.07.202657</t>
+  </si>
+  <si>
+    <t>11.07.202658</t>
+  </si>
+  <si>
+    <t>11.07.202659</t>
+  </si>
+  <si>
+    <t>11.07.202660</t>
+  </si>
+  <si>
+    <t>11.07.202661</t>
+  </si>
+  <si>
+    <t>11.07.202662</t>
+  </si>
+  <si>
+    <t>11.07.202663</t>
+  </si>
+  <si>
+    <t>11.07.202664</t>
+  </si>
+  <si>
+    <t>11.07.202665</t>
+  </si>
+  <si>
+    <t>11.07.202666</t>
+  </si>
+  <si>
+    <t>11.07.202667</t>
+  </si>
+  <si>
+    <t>11.07.202668</t>
+  </si>
+  <si>
+    <t>11.07.202669</t>
+  </si>
+  <si>
+    <t>11.07.202670</t>
+  </si>
+  <si>
+    <t>11.07.202671</t>
+  </si>
+  <si>
+    <t>11.07.202672</t>
+  </si>
+  <si>
+    <t>11.07.202673</t>
+  </si>
+  <si>
+    <t>11.07.202674</t>
+  </si>
+  <si>
+    <t>11.07.202675</t>
+  </si>
+  <si>
+    <t>11.07.202676</t>
+  </si>
+  <si>
+    <t>11.07.202677</t>
+  </si>
+  <si>
+    <t>11.07.202678</t>
+  </si>
+  <si>
+    <t>11.07.202679</t>
+  </si>
+  <si>
+    <t>11.07.202680</t>
+  </si>
+  <si>
+    <t>11.07.202681</t>
+  </si>
+  <si>
+    <t>11.07.202682</t>
+  </si>
+  <si>
+    <t>11.07.202683</t>
+  </si>
+  <si>
+    <t>11.07.202684</t>
+  </si>
+  <si>
+    <t>11.07.202685</t>
+  </si>
+  <si>
+    <t>11.07.202686</t>
+  </si>
+  <si>
+    <t>11.07.202687</t>
+  </si>
+  <si>
+    <t>11.07.202688</t>
+  </si>
+  <si>
+    <t>11.07.202689</t>
+  </si>
+  <si>
+    <t>11.07.202690</t>
+  </si>
+  <si>
+    <t>11.07.202691</t>
+  </si>
+  <si>
+    <t>11.07.202692</t>
+  </si>
+  <si>
+    <t>11.07.202693</t>
+  </si>
+  <si>
+    <t>11.07.202694</t>
+  </si>
+  <si>
+    <t>11.07.202695</t>
+  </si>
+  <si>
+    <t>11.07.202696</t>
+  </si>
+  <si>
+    <t>12.07.20261</t>
+  </si>
+  <si>
+    <t>12.07.20262</t>
+  </si>
+  <si>
+    <t>12.07.20263</t>
+  </si>
+  <si>
+    <t>12.07.20264</t>
+  </si>
+  <si>
+    <t>12.07.20265</t>
+  </si>
+  <si>
+    <t>12.07.20266</t>
+  </si>
+  <si>
+    <t>12.07.20267</t>
+  </si>
+  <si>
+    <t>12.07.20268</t>
+  </si>
+  <si>
+    <t>12.07.20269</t>
+  </si>
+  <si>
+    <t>12.07.202610</t>
+  </si>
+  <si>
+    <t>12.07.202611</t>
+  </si>
+  <si>
+    <t>12.07.202612</t>
+  </si>
+  <si>
+    <t>12.07.202613</t>
+  </si>
+  <si>
+    <t>12.07.202614</t>
+  </si>
+  <si>
+    <t>12.07.202615</t>
+  </si>
+  <si>
+    <t>12.07.202616</t>
+  </si>
+  <si>
+    <t>12.07.202617</t>
+  </si>
+  <si>
+    <t>12.07.202618</t>
+  </si>
+  <si>
+    <t>12.07.202619</t>
+  </si>
+  <si>
+    <t>12.07.202620</t>
+  </si>
+  <si>
+    <t>12.07.202621</t>
+  </si>
+  <si>
+    <t>12.07.202622</t>
+  </si>
+  <si>
+    <t>12.07.202623</t>
+  </si>
+  <si>
+    <t>12.07.202624</t>
+  </si>
+  <si>
+    <t>12.07.202625</t>
+  </si>
+  <si>
+    <t>12.07.202626</t>
+  </si>
+  <si>
+    <t>12.07.202627</t>
+  </si>
+  <si>
+    <t>12.07.202628</t>
+  </si>
+  <si>
+    <t>12.07.202629</t>
+  </si>
+  <si>
+    <t>12.07.202630</t>
+  </si>
+  <si>
+    <t>12.07.202631</t>
+  </si>
+  <si>
+    <t>12.07.202632</t>
+  </si>
+  <si>
+    <t>12.07.202633</t>
+  </si>
+  <si>
+    <t>12.07.202634</t>
+  </si>
+  <si>
+    <t>12.07.202635</t>
+  </si>
+  <si>
+    <t>12.07.202636</t>
+  </si>
+  <si>
+    <t>12.07.202637</t>
+  </si>
+  <si>
+    <t>12.07.202638</t>
+  </si>
+  <si>
+    <t>12.07.202639</t>
+  </si>
+  <si>
+    <t>12.07.202640</t>
+  </si>
+  <si>
+    <t>12.07.202641</t>
+  </si>
+  <si>
+    <t>12.07.202642</t>
+  </si>
+  <si>
+    <t>12.07.202643</t>
+  </si>
+  <si>
+    <t>12.07.202644</t>
+  </si>
+  <si>
+    <t>12.07.202645</t>
+  </si>
+  <si>
+    <t>12.07.202646</t>
+  </si>
+  <si>
+    <t>12.07.202647</t>
+  </si>
+  <si>
+    <t>12.07.202648</t>
+  </si>
+  <si>
+    <t>12.07.202649</t>
+  </si>
+  <si>
+    <t>12.07.202650</t>
+  </si>
+  <si>
+    <t>12.07.202651</t>
+  </si>
+  <si>
+    <t>12.07.202652</t>
+  </si>
+  <si>
+    <t>12.07.202653</t>
+  </si>
+  <si>
+    <t>12.07.202654</t>
+  </si>
+  <si>
+    <t>12.07.202655</t>
+  </si>
+  <si>
+    <t>12.07.202656</t>
+  </si>
+  <si>
+    <t>12.07.202657</t>
+  </si>
+  <si>
+    <t>12.07.202658</t>
+  </si>
+  <si>
+    <t>12.07.202659</t>
+  </si>
+  <si>
+    <t>12.07.202660</t>
+  </si>
+  <si>
+    <t>12.07.202661</t>
+  </si>
+  <si>
+    <t>12.07.202662</t>
+  </si>
+  <si>
+    <t>12.07.202663</t>
+  </si>
+  <si>
+    <t>12.07.202664</t>
+  </si>
+  <si>
+    <t>12.07.202665</t>
+  </si>
+  <si>
+    <t>12.07.202666</t>
+  </si>
+  <si>
+    <t>12.07.202667</t>
+  </si>
+  <si>
+    <t>12.07.202668</t>
+  </si>
+  <si>
+    <t>12.07.202669</t>
+  </si>
+  <si>
+    <t>12.07.202670</t>
+  </si>
+  <si>
+    <t>12.07.202671</t>
+  </si>
+  <si>
+    <t>12.07.202672</t>
+  </si>
+  <si>
+    <t>12.07.202673</t>
+  </si>
+  <si>
+    <t>12.07.202674</t>
+  </si>
+  <si>
+    <t>12.07.202675</t>
+  </si>
+  <si>
+    <t>12.07.202676</t>
+  </si>
+  <si>
+    <t>12.07.202677</t>
+  </si>
+  <si>
+    <t>12.07.202678</t>
+  </si>
+  <si>
+    <t>12.07.202679</t>
+  </si>
+  <si>
+    <t>12.07.202680</t>
+  </si>
+  <si>
+    <t>12.07.202681</t>
+  </si>
+  <si>
+    <t>12.07.202682</t>
+  </si>
+  <si>
+    <t>12.07.202683</t>
+  </si>
+  <si>
+    <t>12.07.202684</t>
+  </si>
+  <si>
+    <t>12.07.202685</t>
+  </si>
+  <si>
+    <t>12.07.202686</t>
+  </si>
+  <si>
+    <t>12.07.202687</t>
+  </si>
+  <si>
+    <t>12.07.202688</t>
+  </si>
+  <si>
+    <t>12.07.202689</t>
+  </si>
+  <si>
+    <t>12.07.202690</t>
+  </si>
+  <si>
+    <t>12.07.202691</t>
+  </si>
+  <si>
+    <t>12.07.202692</t>
+  </si>
+  <si>
+    <t>12.07.202693</t>
+  </si>
+  <si>
+    <t>12.07.202694</t>
+  </si>
+  <si>
+    <t>12.07.202695</t>
+  </si>
+  <si>
+    <t>12.07.202696</t>
+  </si>
+  <si>
+    <t>13.07.20261</t>
+  </si>
+  <si>
+    <t>13.07.20262</t>
+  </si>
+  <si>
+    <t>13.07.20263</t>
+  </si>
+  <si>
+    <t>13.07.20264</t>
+  </si>
+  <si>
+    <t>13.07.20265</t>
+  </si>
+  <si>
+    <t>13.07.20266</t>
+  </si>
+  <si>
+    <t>13.07.20267</t>
+  </si>
+  <si>
+    <t>13.07.20268</t>
+  </si>
+  <si>
+    <t>13.07.20269</t>
+  </si>
+  <si>
+    <t>13.07.202610</t>
+  </si>
+  <si>
+    <t>13.07.202611</t>
+  </si>
+  <si>
+    <t>13.07.202612</t>
+  </si>
+  <si>
+    <t>13.07.202613</t>
+  </si>
+  <si>
+    <t>13.07.202614</t>
+  </si>
+  <si>
+    <t>13.07.202615</t>
+  </si>
+  <si>
+    <t>13.07.202616</t>
+  </si>
+  <si>
+    <t>13.07.202617</t>
+  </si>
+  <si>
+    <t>13.07.202618</t>
+  </si>
+  <si>
+    <t>13.07.202619</t>
+  </si>
+  <si>
+    <t>13.07.202620</t>
+  </si>
+  <si>
+    <t>13.07.202621</t>
+  </si>
+  <si>
+    <t>13.07.202622</t>
+  </si>
+  <si>
+    <t>13.07.202623</t>
+  </si>
+  <si>
+    <t>13.07.202624</t>
+  </si>
+  <si>
+    <t>13.07.202625</t>
+  </si>
+  <si>
+    <t>13.07.202626</t>
+  </si>
+  <si>
+    <t>13.07.202627</t>
+  </si>
+  <si>
+    <t>13.07.202628</t>
+  </si>
+  <si>
+    <t>13.07.202629</t>
+  </si>
+  <si>
+    <t>13.07.202630</t>
+  </si>
+  <si>
+    <t>13.07.202631</t>
+  </si>
+  <si>
+    <t>13.07.202632</t>
+  </si>
+  <si>
+    <t>13.07.202633</t>
+  </si>
+  <si>
+    <t>13.07.202634</t>
+  </si>
+  <si>
+    <t>13.07.202635</t>
+  </si>
+  <si>
+    <t>13.07.202636</t>
+  </si>
+  <si>
+    <t>13.07.202637</t>
+  </si>
+  <si>
+    <t>13.07.202638</t>
+  </si>
+  <si>
+    <t>13.07.202639</t>
+  </si>
+  <si>
+    <t>13.07.202640</t>
+  </si>
+  <si>
+    <t>13.07.202641</t>
+  </si>
+  <si>
+    <t>13.07.202642</t>
+  </si>
+  <si>
+    <t>13.07.202643</t>
+  </si>
+  <si>
+    <t>13.07.202644</t>
+  </si>
+  <si>
+    <t>13.07.202645</t>
+  </si>
+  <si>
+    <t>13.07.202646</t>
+  </si>
+  <si>
+    <t>13.07.202647</t>
+  </si>
+  <si>
+    <t>13.07.202648</t>
+  </si>
+  <si>
+    <t>13.07.202649</t>
+  </si>
+  <si>
+    <t>13.07.202650</t>
+  </si>
+  <si>
+    <t>13.07.202651</t>
   </si>
 </sst>
 </file>
@@ -807,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -826,10 +1423,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>5444</v>
+        <v>5509</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -840,10 +1437,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46212.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
-        <v>5476</v>
+        <v>5396</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -854,10 +1451,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46212.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
-        <v>5490</v>
+        <v>5402</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -868,10 +1465,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46212.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
-        <v>5471</v>
+        <v>5325</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -882,10 +1479,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46212.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
-        <v>5391</v>
+        <v>5426</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -896,10 +1493,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46212.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
-        <v>5346</v>
+        <v>5441</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -910,10 +1507,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46212.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
-        <v>5340</v>
+        <v>5421</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -924,10 +1521,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46212.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
-        <v>5371</v>
+        <v>5389</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -938,10 +1535,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46212.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
-        <v>5206</v>
+        <v>5242</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -952,10 +1549,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46212.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
-        <v>5320</v>
+        <v>5426</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -966,10 +1563,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46212.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
-        <v>5308</v>
+        <v>5181</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -980,10 +1577,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46212.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
-        <v>5298</v>
+        <v>5373</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -994,10 +1591,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46212.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
-        <v>5335</v>
+        <v>5420</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -1008,10 +1605,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46212.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
-        <v>5338</v>
+        <v>5394</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1022,10 +1619,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46212.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
-        <v>5371</v>
+        <v>5379</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -1036,10 +1633,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46212.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
-        <v>5384</v>
+        <v>5231</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1050,10 +1647,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46212.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
-        <v>5387</v>
+        <v>5300</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -1064,10 +1661,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46212.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
-        <v>5307</v>
+        <v>5287</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -1078,10 +1675,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46212.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>5261</v>
+        <v>5202</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -1092,10 +1689,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46212.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>5362</v>
+        <v>5225</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1106,10 +1703,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46212.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>5374</v>
+        <v>5311</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1120,10 +1717,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46212.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>5485</v>
+        <v>5394</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1134,10 +1731,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46212.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>5530</v>
+        <v>5403</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -1148,10 +1745,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46212.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
-        <v>5599</v>
+        <v>5514</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1162,10 +1759,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46212.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>5806</v>
+        <v>5707</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -1176,10 +1773,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46212.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
-        <v>5813</v>
+        <v>5692</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1190,10 +1787,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46212.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
-        <v>5830</v>
+        <v>5711</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -1204,10 +1801,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46212.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>5818</v>
+        <v>5778</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -1218,10 +1815,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46212.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
-        <v>5845</v>
+        <v>5791</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -1232,10 +1829,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46212.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
-        <v>5812</v>
+        <v>5789</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1246,10 +1843,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46212.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>5766</v>
+        <v>5752</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -1260,10 +1857,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46212.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
-        <v>5707</v>
+        <v>5657</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -1274,10 +1871,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46212.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
-        <v>5580</v>
+        <v>5505</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -1288,10 +1885,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46212.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>5485</v>
+        <v>5400</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -1302,10 +1899,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46212.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>5409</v>
+        <v>5297</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -1316,10 +1913,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46212.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
-        <v>5304</v>
+        <v>5240</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -1330,10 +1927,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46212.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>5193</v>
+        <v>5099</v>
       </c>
       <c r="C38">
         <v>37</v>
@@ -1344,10 +1941,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46212.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
-        <v>5128</v>
+        <v>4940</v>
       </c>
       <c r="C39">
         <v>38</v>
@@ -1358,10 +1955,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46212.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
-        <v>4912</v>
+        <v>4858</v>
       </c>
       <c r="C40">
         <v>39</v>
@@ -1372,10 +1969,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46212.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>4817</v>
+        <v>4851</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -1386,10 +1983,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46212.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
-        <v>4907</v>
+        <v>4875</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -1400,10 +1997,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46212.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
-        <v>4907</v>
+        <v>4818</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -1414,10 +2011,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46212.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>4875</v>
+        <v>4758</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -1428,10 +2025,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46212.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>4834</v>
+        <v>4654</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -1442,10 +2039,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46212.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>4821</v>
+        <v>4632</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -1456,10 +2053,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46212.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>4844</v>
+        <v>4647</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -1470,10 +2067,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46212.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B48">
-        <v>4914</v>
+        <v>4698</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -1484,10 +2081,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46212.48958333334</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B49">
-        <v>4987</v>
+        <v>4753</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -1498,10 +2095,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46212.5</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>5035</v>
+        <v>4787</v>
       </c>
       <c r="C50">
         <v>49</v>
@@ -1512,10 +2109,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46212.51041666666</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B51">
-        <v>5063</v>
+        <v>4965</v>
       </c>
       <c r="C51">
         <v>50</v>
@@ -1526,10 +2123,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46212.52083333334</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B52">
-        <v>5254</v>
+        <v>5130</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -1540,10 +2137,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46212.53125</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>5131</v>
+        <v>5206</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -1554,10 +2151,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46212.54166666666</v>
+        <v>46213.54166666666</v>
       </c>
       <c r="B54">
-        <v>5170</v>
+        <v>5315</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -1568,10 +2165,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46212.55208333334</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="B55">
-        <v>5256</v>
+        <v>5412</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -1582,10 +2179,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46212.5625</v>
+        <v>46213.5625</v>
       </c>
       <c r="B56">
-        <v>5247</v>
+        <v>5464</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -1596,10 +2193,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46212.57291666666</v>
+        <v>46213.57291666666</v>
       </c>
       <c r="B57">
-        <v>5319</v>
+        <v>5433</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -1610,10 +2207,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46212.58333333334</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="B58">
-        <v>5360</v>
+        <v>5516</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -1624,10 +2221,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46212.59375</v>
+        <v>46213.59375</v>
       </c>
       <c r="B59">
-        <v>5461</v>
+        <v>5338</v>
       </c>
       <c r="C59">
         <v>58</v>
@@ -1638,10 +2235,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46212.60416666666</v>
+        <v>46213.60416666666</v>
       </c>
       <c r="B60">
-        <v>5550</v>
+        <v>5320</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -1652,10 +2249,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46212.61458333334</v>
+        <v>46213.61458333334</v>
       </c>
       <c r="B61">
-        <v>5594</v>
+        <v>5358</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -1666,10 +2263,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46212.625</v>
+        <v>46213.625</v>
       </c>
       <c r="B62">
-        <v>5645</v>
+        <v>5323</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -1680,10 +2277,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46212.63541666666</v>
+        <v>46213.63541666666</v>
       </c>
       <c r="B63">
-        <v>5742</v>
+        <v>5447</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -1694,10 +2291,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46212.64583333334</v>
+        <v>46213.64583333334</v>
       </c>
       <c r="B64">
-        <v>5690</v>
+        <v>5528</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -1708,10 +2305,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46212.65625</v>
+        <v>46213.65625</v>
       </c>
       <c r="B65">
-        <v>5853</v>
+        <v>5434</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -1722,10 +2319,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46212.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="B66">
-        <v>5783</v>
+        <v>5523</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -1736,10 +2333,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46212.67708333334</v>
+        <v>46213.67708333334</v>
       </c>
       <c r="B67">
-        <v>5864</v>
+        <v>5553</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -1750,10 +2347,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46212.6875</v>
+        <v>46213.6875</v>
       </c>
       <c r="B68">
-        <v>5956</v>
+        <v>5676</v>
       </c>
       <c r="C68">
         <v>67</v>
@@ -1764,10 +2361,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46212.69791666666</v>
+        <v>46213.69791666666</v>
       </c>
       <c r="B69">
-        <v>5996</v>
+        <v>5787</v>
       </c>
       <c r="C69">
         <v>68</v>
@@ -1778,10 +2375,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46212.70833333334</v>
+        <v>46213.70833333334</v>
       </c>
       <c r="B70">
-        <v>6131</v>
+        <v>5931</v>
       </c>
       <c r="C70">
         <v>69</v>
@@ -1792,10 +2389,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46212.71875</v>
+        <v>46213.71875</v>
       </c>
       <c r="B71">
-        <v>6213</v>
+        <v>6087</v>
       </c>
       <c r="C71">
         <v>70</v>
@@ -1806,10 +2403,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46212.72916666666</v>
+        <v>46213.72916666666</v>
       </c>
       <c r="B72">
-        <v>6241</v>
+        <v>6108</v>
       </c>
       <c r="C72">
         <v>71</v>
@@ -1820,10 +2417,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46212.73958333334</v>
+        <v>46213.73958333334</v>
       </c>
       <c r="B73">
-        <v>6313</v>
+        <v>6222</v>
       </c>
       <c r="C73">
         <v>72</v>
@@ -1834,10 +2431,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46212.75</v>
+        <v>46213.75</v>
       </c>
       <c r="B74">
-        <v>6314</v>
+        <v>6295</v>
       </c>
       <c r="C74">
         <v>73</v>
@@ -1848,10 +2445,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46212.76041666666</v>
+        <v>46213.76041666666</v>
       </c>
       <c r="B75">
-        <v>6399</v>
+        <v>6329</v>
       </c>
       <c r="C75">
         <v>74</v>
@@ -1862,10 +2459,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46212.77083333334</v>
+        <v>46213.77083333334</v>
       </c>
       <c r="B76">
-        <v>6477</v>
+        <v>6480</v>
       </c>
       <c r="C76">
         <v>75</v>
@@ -1876,10 +2473,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46212.78125</v>
+        <v>46213.78125</v>
       </c>
       <c r="B77">
-        <v>6576</v>
+        <v>6564</v>
       </c>
       <c r="C77">
         <v>76</v>
@@ -1890,10 +2487,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46212.79166666666</v>
+        <v>46213.79166666666</v>
       </c>
       <c r="B78">
-        <v>6653</v>
+        <v>6659</v>
       </c>
       <c r="C78">
         <v>77</v>
@@ -1904,10 +2501,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46212.80208333334</v>
+        <v>46213.80208333334</v>
       </c>
       <c r="B79">
-        <v>6662</v>
+        <v>6754</v>
       </c>
       <c r="C79">
         <v>78</v>
@@ -1918,10 +2515,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46212.8125</v>
+        <v>46213.8125</v>
       </c>
       <c r="B80">
-        <v>6722</v>
+        <v>6742</v>
       </c>
       <c r="C80">
         <v>79</v>
@@ -1932,10 +2529,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46212.82291666666</v>
+        <v>46213.82291666666</v>
       </c>
       <c r="B81">
-        <v>6742</v>
+        <v>6816</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1946,10 +2543,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46212.83333333334</v>
+        <v>46213.83333333334</v>
       </c>
       <c r="B82">
-        <v>6824</v>
+        <v>6785</v>
       </c>
       <c r="C82">
         <v>81</v>
@@ -1960,10 +2557,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46212.84375</v>
+        <v>46213.84375</v>
       </c>
       <c r="B83">
-        <v>6881</v>
+        <v>6859</v>
       </c>
       <c r="C83">
         <v>82</v>
@@ -1974,10 +2571,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46212.85416666666</v>
+        <v>46213.85416666666</v>
       </c>
       <c r="B84">
-        <v>6910</v>
+        <v>6905</v>
       </c>
       <c r="C84">
         <v>83</v>
@@ -1988,10 +2585,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46212.86458333334</v>
+        <v>46213.86458333334</v>
       </c>
       <c r="B85">
-        <v>6844</v>
+        <v>6833</v>
       </c>
       <c r="C85">
         <v>84</v>
@@ -2002,10 +2599,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46212.875</v>
+        <v>46213.875</v>
       </c>
       <c r="B86">
-        <v>6761</v>
+        <v>6806</v>
       </c>
       <c r="C86">
         <v>85</v>
@@ -2016,10 +2613,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46212.88541666666</v>
+        <v>46213.88541666666</v>
       </c>
       <c r="B87">
-        <v>6699</v>
+        <v>6637</v>
       </c>
       <c r="C87">
         <v>86</v>
@@ -2030,10 +2627,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46212.89583333334</v>
+        <v>46213.89583333334</v>
       </c>
       <c r="B88">
-        <v>6601</v>
+        <v>6518</v>
       </c>
       <c r="C88">
         <v>87</v>
@@ -2044,10 +2641,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46212.90625</v>
+        <v>46213.90625</v>
       </c>
       <c r="B89">
-        <v>6366</v>
+        <v>6356</v>
       </c>
       <c r="C89">
         <v>88</v>
@@ -2058,10 +2655,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46212.91666666666</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="B90">
-        <v>6225</v>
+        <v>6287</v>
       </c>
       <c r="C90">
         <v>89</v>
@@ -2072,10 +2669,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46212.92708333334</v>
+        <v>46213.92708333334</v>
       </c>
       <c r="B91">
-        <v>6162</v>
+        <v>6160</v>
       </c>
       <c r="C91">
         <v>90</v>
@@ -2086,10 +2683,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46212.9375</v>
+        <v>46213.9375</v>
       </c>
       <c r="B92">
-        <v>5986</v>
+        <v>6051</v>
       </c>
       <c r="C92">
         <v>91</v>
@@ -2100,10 +2697,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46212.94791666666</v>
+        <v>46213.94791666666</v>
       </c>
       <c r="B93">
-        <v>5867</v>
+        <v>5959</v>
       </c>
       <c r="C93">
         <v>92</v>
@@ -2114,10 +2711,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46212.95833333334</v>
+        <v>46213.95833333334</v>
       </c>
       <c r="B94">
-        <v>5739</v>
+        <v>5793</v>
       </c>
       <c r="C94">
         <v>93</v>
@@ -2128,10 +2725,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46212.96875</v>
+        <v>46213.96875</v>
       </c>
       <c r="B95">
-        <v>5630</v>
+        <v>5691</v>
       </c>
       <c r="C95">
         <v>94</v>
@@ -2142,10 +2739,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46212.97916666666</v>
+        <v>46213.97916666666</v>
       </c>
       <c r="B96">
-        <v>5599</v>
+        <v>5676</v>
       </c>
       <c r="C96">
         <v>95</v>
@@ -2156,10 +2753,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46212.98958333334</v>
+        <v>46213.98958333334</v>
       </c>
       <c r="B97">
-        <v>5619</v>
+        <v>5573</v>
       </c>
       <c r="C97">
         <v>96</v>
@@ -2170,10 +2767,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B98">
-        <v>5509</v>
+        <v>5515</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2184,10 +2781,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46213.01041666666</v>
+        <v>46214.01041666666</v>
       </c>
       <c r="B99">
-        <v>5396</v>
+        <v>5449</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -2198,10 +2795,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46213.02083333334</v>
+        <v>46214.02083333334</v>
       </c>
       <c r="B100">
-        <v>5402</v>
+        <v>5343</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -2212,10 +2809,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46213.03125</v>
+        <v>46214.03125</v>
       </c>
       <c r="B101">
-        <v>5325</v>
+        <v>5301</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2226,10 +2823,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46213.04166666666</v>
+        <v>46214.04166666666</v>
       </c>
       <c r="B102">
-        <v>5426</v>
+        <v>5320</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -2240,10 +2837,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46213.05208333334</v>
+        <v>46214.05208333334</v>
       </c>
       <c r="B103">
-        <v>5441</v>
+        <v>5342</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -2254,10 +2851,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46213.0625</v>
+        <v>46214.0625</v>
       </c>
       <c r="B104">
-        <v>5421</v>
+        <v>5301</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -2268,10 +2865,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46213.07291666666</v>
+        <v>46214.07291666666</v>
       </c>
       <c r="B105">
-        <v>5389</v>
+        <v>5228</v>
       </c>
       <c r="C105">
         <v>8</v>
@@ -2282,10 +2879,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46213.08333333334</v>
+        <v>46214.08333333334</v>
       </c>
       <c r="B106">
-        <v>5242</v>
+        <v>5133</v>
       </c>
       <c r="C106">
         <v>9</v>
@@ -2296,10 +2893,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46213.09375</v>
+        <v>46214.09375</v>
       </c>
       <c r="B107">
-        <v>5426</v>
+        <v>5153</v>
       </c>
       <c r="C107">
         <v>10</v>
@@ -2310,10 +2907,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46213.10416666666</v>
+        <v>46214.10416666666</v>
       </c>
       <c r="B108">
-        <v>5181</v>
+        <v>5171</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -2324,10 +2921,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46213.11458333334</v>
+        <v>46214.11458333334</v>
       </c>
       <c r="B109">
-        <v>5373</v>
+        <v>5123</v>
       </c>
       <c r="C109">
         <v>12</v>
@@ -2338,10 +2935,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46213.125</v>
+        <v>46214.125</v>
       </c>
       <c r="B110">
-        <v>5420</v>
+        <v>5180</v>
       </c>
       <c r="C110">
         <v>13</v>
@@ -2352,10 +2949,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46213.13541666666</v>
+        <v>46214.13541666666</v>
       </c>
       <c r="B111">
-        <v>5394</v>
+        <v>5091</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -2366,10 +2963,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46213.14583333334</v>
+        <v>46214.14583333334</v>
       </c>
       <c r="B112">
-        <v>5379</v>
+        <v>5127</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -2380,10 +2977,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46213.15625</v>
+        <v>46214.15625</v>
       </c>
       <c r="B113">
-        <v>5231</v>
+        <v>5127</v>
       </c>
       <c r="C113">
         <v>16</v>
@@ -2394,10 +2991,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46213.16666666666</v>
+        <v>46214.16666666666</v>
       </c>
       <c r="B114">
-        <v>5300</v>
+        <v>5168</v>
       </c>
       <c r="C114">
         <v>17</v>
@@ -2408,10 +3005,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46213.17708333334</v>
+        <v>46214.17708333334</v>
       </c>
       <c r="B115">
-        <v>5287</v>
+        <v>5082</v>
       </c>
       <c r="C115">
         <v>18</v>
@@ -2422,10 +3019,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46213.1875</v>
+        <v>46214.1875</v>
       </c>
       <c r="B116">
-        <v>5202</v>
+        <v>5040</v>
       </c>
       <c r="C116">
         <v>19</v>
@@ -2436,10 +3033,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46213.19791666666</v>
+        <v>46214.19791666666</v>
       </c>
       <c r="B117">
-        <v>5225</v>
+        <v>5087</v>
       </c>
       <c r="C117">
         <v>20</v>
@@ -2450,10 +3047,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46213.20833333334</v>
+        <v>46214.20833333334</v>
       </c>
       <c r="B118">
-        <v>5311</v>
+        <v>5024</v>
       </c>
       <c r="C118">
         <v>21</v>
@@ -2464,10 +3061,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46213.21875</v>
+        <v>46214.21875</v>
       </c>
       <c r="B119">
-        <v>5394</v>
+        <v>4973</v>
       </c>
       <c r="C119">
         <v>22</v>
@@ -2478,10 +3075,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46213.22916666666</v>
+        <v>46214.22916666666</v>
       </c>
       <c r="B120">
-        <v>5403</v>
+        <v>4957</v>
       </c>
       <c r="C120">
         <v>23</v>
@@ -2492,10 +3089,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46213.23958333334</v>
+        <v>46214.23958333334</v>
       </c>
       <c r="B121">
-        <v>5514</v>
+        <v>4867</v>
       </c>
       <c r="C121">
         <v>24</v>
@@ -2506,10 +3103,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46213.25</v>
+        <v>46214.25</v>
       </c>
       <c r="B122">
-        <v>5707</v>
+        <v>4908</v>
       </c>
       <c r="C122">
         <v>25</v>
@@ -2520,10 +3117,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46213.26041666666</v>
+        <v>46214.26041666666</v>
       </c>
       <c r="B123">
-        <v>5692</v>
+        <v>5033</v>
       </c>
       <c r="C123">
         <v>26</v>
@@ -2534,10 +3131,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46213.27083333334</v>
+        <v>46214.27083333334</v>
       </c>
       <c r="B124">
-        <v>5711</v>
+        <v>5001</v>
       </c>
       <c r="C124">
         <v>27</v>
@@ -2548,10 +3145,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46213.28125</v>
+        <v>46214.28125</v>
       </c>
       <c r="B125">
-        <v>5778</v>
+        <v>4955</v>
       </c>
       <c r="C125">
         <v>28</v>
@@ -2562,10 +3159,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46213.29166666666</v>
+        <v>46214.29166666666</v>
       </c>
       <c r="B126">
-        <v>5791</v>
+        <v>4896</v>
       </c>
       <c r="C126">
         <v>29</v>
@@ -2576,10 +3173,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46213.30208333334</v>
+        <v>46214.30208333334</v>
       </c>
       <c r="B127">
-        <v>5789</v>
+        <v>4829</v>
       </c>
       <c r="C127">
         <v>30</v>
@@ -2590,10 +3187,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46213.3125</v>
+        <v>46214.3125</v>
       </c>
       <c r="B128">
-        <v>5752</v>
+        <v>4744</v>
       </c>
       <c r="C128">
         <v>31</v>
@@ -2604,10 +3201,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46213.32291666666</v>
+        <v>46214.32291666666</v>
       </c>
       <c r="B129">
-        <v>5657</v>
+        <v>4726</v>
       </c>
       <c r="C129">
         <v>32</v>
@@ -2618,10 +3215,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46213.33333333334</v>
+        <v>46214.33333333334</v>
       </c>
       <c r="B130">
-        <v>5505</v>
+        <v>4605</v>
       </c>
       <c r="C130">
         <v>33</v>
@@ -2632,10 +3229,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46213.34375</v>
+        <v>46214.34375</v>
       </c>
       <c r="B131">
-        <v>5400</v>
+        <v>4508</v>
       </c>
       <c r="C131">
         <v>34</v>
@@ -2646,10 +3243,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46213.35416666666</v>
+        <v>46214.35416666666</v>
       </c>
       <c r="B132">
-        <v>5297</v>
+        <v>4407</v>
       </c>
       <c r="C132">
         <v>35</v>
@@ -2660,10 +3257,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46213.36458333334</v>
+        <v>46214.36458333334</v>
       </c>
       <c r="B133">
-        <v>5240</v>
+        <v>4395</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -2674,10 +3271,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46213.375</v>
+        <v>46214.375</v>
       </c>
       <c r="B134">
-        <v>5099</v>
+        <v>4292</v>
       </c>
       <c r="C134">
         <v>37</v>
@@ -2688,10 +3285,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46213.38541666666</v>
+        <v>46214.38541666666</v>
       </c>
       <c r="B135">
-        <v>4940</v>
+        <v>4172</v>
       </c>
       <c r="C135">
         <v>38</v>
@@ -2702,10 +3299,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46213.39583333334</v>
+        <v>46214.39583333334</v>
       </c>
       <c r="B136">
-        <v>4858</v>
+        <v>4048</v>
       </c>
       <c r="C136">
         <v>39</v>
@@ -2716,10 +3313,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46213.40625</v>
+        <v>46214.40625</v>
       </c>
       <c r="B137">
-        <v>4851</v>
+        <v>4021</v>
       </c>
       <c r="C137">
         <v>40</v>
@@ -2730,10 +3327,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46213.41666666666</v>
+        <v>46214.41666666666</v>
       </c>
       <c r="B138">
-        <v>4875</v>
+        <v>3863</v>
       </c>
       <c r="C138">
         <v>41</v>
@@ -2744,10 +3341,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46213.42708333334</v>
+        <v>46214.42708333334</v>
       </c>
       <c r="B139">
-        <v>4818</v>
+        <v>3845</v>
       </c>
       <c r="C139">
         <v>42</v>
@@ -2758,10 +3355,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46213.4375</v>
+        <v>46214.4375</v>
       </c>
       <c r="B140">
-        <v>4758</v>
+        <v>3851</v>
       </c>
       <c r="C140">
         <v>43</v>
@@ -2772,16 +3369,2802 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46213.44791666666</v>
+        <v>46214.44791666666</v>
       </c>
       <c r="B141">
-        <v>4654</v>
+        <v>3791</v>
       </c>
       <c r="C141">
         <v>44</v>
       </c>
       <c r="D141" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="2">
+        <v>46214.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>3924</v>
+      </c>
+      <c r="C142">
+        <v>45</v>
+      </c>
+      <c r="D142" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="2">
+        <v>46214.46875</v>
+      </c>
+      <c r="B143">
+        <v>3871</v>
+      </c>
+      <c r="C143">
+        <v>46</v>
+      </c>
+      <c r="D143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="2">
+        <v>46214.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>3928</v>
+      </c>
+      <c r="C144">
+        <v>47</v>
+      </c>
+      <c r="D144" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="2">
+        <v>46214.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>3967</v>
+      </c>
+      <c r="C145">
+        <v>48</v>
+      </c>
+      <c r="D145" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="2">
+        <v>46214.5</v>
+      </c>
+      <c r="B146">
+        <v>3895</v>
+      </c>
+      <c r="C146">
+        <v>49</v>
+      </c>
+      <c r="D146" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="2">
+        <v>46214.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>3952</v>
+      </c>
+      <c r="C147">
+        <v>50</v>
+      </c>
+      <c r="D147" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="2">
+        <v>46214.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>4003</v>
+      </c>
+      <c r="C148">
+        <v>51</v>
+      </c>
+      <c r="D148" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="2">
+        <v>46214.53125</v>
+      </c>
+      <c r="B149">
+        <v>4031</v>
+      </c>
+      <c r="C149">
+        <v>52</v>
+      </c>
+      <c r="D149" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="2">
+        <v>46214.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>4103</v>
+      </c>
+      <c r="C150">
+        <v>53</v>
+      </c>
+      <c r="D150" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="2">
+        <v>46214.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>4106</v>
+      </c>
+      <c r="C151">
+        <v>54</v>
+      </c>
+      <c r="D151" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
+        <v>46214.5625</v>
+      </c>
+      <c r="B152">
+        <v>4129</v>
+      </c>
+      <c r="C152">
+        <v>55</v>
+      </c>
+      <c r="D152" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
+        <v>46214.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>4090</v>
+      </c>
+      <c r="C153">
+        <v>56</v>
+      </c>
+      <c r="D153" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
+        <v>46214.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>4076</v>
+      </c>
+      <c r="C154">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
+        <v>46214.59375</v>
+      </c>
+      <c r="B155">
+        <v>4113</v>
+      </c>
+      <c r="C155">
+        <v>58</v>
+      </c>
+      <c r="D155" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="2">
+        <v>46214.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>4199</v>
+      </c>
+      <c r="C156">
+        <v>59</v>
+      </c>
+      <c r="D156" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="2">
+        <v>46214.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>4326</v>
+      </c>
+      <c r="C157">
+        <v>60</v>
+      </c>
+      <c r="D157" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="2">
+        <v>46214.625</v>
+      </c>
+      <c r="B158">
+        <v>4348</v>
+      </c>
+      <c r="C158">
+        <v>61</v>
+      </c>
+      <c r="D158" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="2">
+        <v>46214.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>4417</v>
+      </c>
+      <c r="C159">
+        <v>62</v>
+      </c>
+      <c r="D159" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="2">
+        <v>46214.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>4456</v>
+      </c>
+      <c r="C160">
+        <v>63</v>
+      </c>
+      <c r="D160" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="2">
+        <v>46214.65625</v>
+      </c>
+      <c r="B161">
+        <v>4546</v>
+      </c>
+      <c r="C161">
+        <v>64</v>
+      </c>
+      <c r="D161" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="2">
+        <v>46214.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>4587</v>
+      </c>
+      <c r="C162">
+        <v>65</v>
+      </c>
+      <c r="D162" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="2">
+        <v>46214.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>4688</v>
+      </c>
+      <c r="C163">
+        <v>66</v>
+      </c>
+      <c r="D163" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="2">
+        <v>46214.6875</v>
+      </c>
+      <c r="B164">
+        <v>4865</v>
+      </c>
+      <c r="C164">
+        <v>67</v>
+      </c>
+      <c r="D164" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="2">
+        <v>46214.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>4993</v>
+      </c>
+      <c r="C165">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="2">
+        <v>46214.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>5160</v>
+      </c>
+      <c r="C166">
+        <v>69</v>
+      </c>
+      <c r="D166" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="2">
+        <v>46214.71875</v>
+      </c>
+      <c r="B167">
+        <v>5320</v>
+      </c>
+      <c r="C167">
+        <v>70</v>
+      </c>
+      <c r="D167" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="2">
+        <v>46214.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>5497</v>
+      </c>
+      <c r="C168">
+        <v>71</v>
+      </c>
+      <c r="D168" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="2">
+        <v>46214.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>5654</v>
+      </c>
+      <c r="C169">
+        <v>72</v>
+      </c>
+      <c r="D169" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="2">
+        <v>46214.75</v>
+      </c>
+      <c r="B170">
+        <v>5795</v>
+      </c>
+      <c r="C170">
+        <v>73</v>
+      </c>
+      <c r="D170" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="2">
+        <v>46214.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>5829</v>
+      </c>
+      <c r="C171">
+        <v>74</v>
+      </c>
+      <c r="D171" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="2">
+        <v>46214.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>6003</v>
+      </c>
+      <c r="C172">
+        <v>75</v>
+      </c>
+      <c r="D172" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="2">
+        <v>46214.78125</v>
+      </c>
+      <c r="B173">
+        <v>6076</v>
+      </c>
+      <c r="C173">
+        <v>76</v>
+      </c>
+      <c r="D173" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="2">
+        <v>46214.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>6133</v>
+      </c>
+      <c r="C174">
+        <v>77</v>
+      </c>
+      <c r="D174" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="2">
+        <v>46214.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>6209</v>
+      </c>
+      <c r="C175">
+        <v>78</v>
+      </c>
+      <c r="D175" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="2">
+        <v>46214.8125</v>
+      </c>
+      <c r="B176">
+        <v>6241</v>
+      </c>
+      <c r="C176">
+        <v>79</v>
+      </c>
+      <c r="D176" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="2">
+        <v>46214.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>6307</v>
+      <